--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -51,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -510,8 +511,208 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:N5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -522,29 +522,33 @@
           <t>Run1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A1_SAA</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>97.72</v>
+        <v>91.09</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>97.78</v>
+        <v>92.8</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>99.44</v>
+        <v>99.19</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>97.75</v>
+        <v>91.94</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>85.08</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>11.754</v>
@@ -553,18 +557,18 @@
         <v>20.661</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>26.3246</v>
+        <v>26.3183</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -572,29 +576,33 @@
           <t>Run1</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A1_SAA</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>92.33</v>
+        <v>84.81</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>91.95</v>
+        <v>82.5</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>91.52</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>11.754</v>
@@ -603,18 +611,18 @@
         <v>20.661</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>26.3246</v>
+        <v>26.3183</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -622,29 +630,33 @@
           <t>Run1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A2_CASAA</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>80.77</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>84.27</v>
+        <v>92.75</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>91.91</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>82.48</v>
+        <v>91.86</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>70.19</v>
+        <v>84.94</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>77.23</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>11.754</v>
@@ -653,18 +665,18 @@
         <v>20.661</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>26.3246</v>
+        <v>26.2593</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -672,29 +684,33 @@
           <t>Run1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A2_CASAA</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>93.62</v>
+        <v>80.55</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>96.09</v>
+        <v>84.23</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>91.86</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>94.84</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>90.18000000000001</v>
+        <v>70</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>94.63</v>
+        <v>77.06</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>11.754</v>
@@ -703,16 +719,216 @@
         <v>20.661</v>
       </c>
       <c r="M5" s="2" t="n">
+        <v>26.2593</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>casaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>26.3246</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N5"/>
+  <autoFilter ref="A1:N9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -730,205 +730,421 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>Run2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A1_SAA_FROZEN</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>97.72</v>
+        <v>91.38</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>97.78</v>
+        <v>92.3</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>99.44</v>
+        <v>99.17</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>97.75</v>
+        <v>91.84</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>84.91</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>20.661</v>
+        <v>15.125</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>26.3246</v>
+        <v>26.1484</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>Run2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A1_SAA_FROZEN</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>92.33</v>
+        <v>86.03</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>91.95</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.55</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>91.52</v>
+        <v>76.83</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>20.661</v>
+        <v>15.125</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>26.3246</v>
+        <v>26.1484</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>Run2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>A3_ORACLE_FROZEN</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>80.77</v>
+        <v>91.13</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>84.27</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>91.91</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>82.48</v>
+        <v>91.88</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>70.19</v>
+        <v>84.98</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>77.23</v>
+        <v>91.45</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>20.661</v>
+        <v>15.125</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>26.3246</v>
+        <v>26.0894</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>Run2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>A3_ORACLE_FROZEN</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>93.62</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>96.09</v>
+        <v>85.05</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>92.36</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>94.84</v>
+        <v>83.52</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>90.18000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>94.63</v>
+        <v>78.55</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L9" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>26.0894</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>casaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L10" s="2" t="n">
         <v>20.661</v>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="M10" s="2" t="n">
         <v>26.3246</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N9"/>
+  <autoFilter ref="A1:N13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -946,93 +946,101 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>Run3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>A4_DETAIL_FROZEN</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>97.72</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>97.78</v>
+        <v>84.28</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>99.44</v>
+        <v>91.7</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>97.75</v>
+        <v>81.92</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>69.37</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>20.661</v>
+        <v>15.125</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>26.3246</v>
+        <v>26.0894</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>R4_0_A0_FULL12_FROZEN</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>82.42</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>92.33</v>
+        <v>83.87</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>92.12</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>91.95</v>
+        <v>83.14</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>71.14</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>91.52</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>20.661</v>
+        <v>15.125</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>26.3246</v>
@@ -1046,46 +1054,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>R4_1_VIT4_OLDHEAD</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>80.77</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>84.27</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>91.91</v>
+        <v>91.94</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>82.48</v>
+        <v>82.77</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>70.19</v>
+        <v>70.61</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>77.23</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>11.754</v>
+        <v>8.195</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>20.661</v>
+        <v>15.125</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>26.3246</v>
+        <v>24.1021</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1096,55 +1108,313 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>10.7311</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>83.81</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>10.9824</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Run1</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E18" s="2" t="n">
         <v>93.62</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F18" s="2" t="n">
         <v>96.09</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G18" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H18" s="2" t="n">
         <v>94.84</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="I18" s="2" t="n">
         <v>90.18000000000001</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J18" s="2" t="n">
         <v>94.63</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K18" s="2" t="n">
         <v>11.754</v>
       </c>
-      <c r="L13" s="2" t="n">
+      <c r="L18" s="2" t="n">
         <v>20.661</v>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="M18" s="2" t="n">
         <v>26.3246</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N13"/>
+  <autoFilter ref="A1:N18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1216,46 +1216,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>97.72</v>
+        <v>79.78</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>97.78</v>
+        <v>84.39</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>99.44</v>
+        <v>91.75</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>97.75</v>
+        <v>82.02</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>69.52</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>11.754</v>
+        <v>5.491</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>20.661</v>
+        <v>3.514</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>26.3246</v>
+        <v>11.5239</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1277,26 +1281,26 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>97.72</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>92.33</v>
+        <v>97.78</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.44</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>91.95</v>
+        <v>97.75</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>91.52</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>11.754</v>
@@ -1327,26 +1331,26 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>80.77</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>84.27</v>
+        <v>92.33</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>91.91</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>82.48</v>
+        <v>91.95</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>70.19</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>77.23</v>
+        <v>91.52</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>11.754</v>
@@ -1377,26 +1381,26 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>93.62</v>
+        <v>80.77</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>96.09</v>
+        <v>84.27</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>94.84</v>
+        <v>82.48</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>90.18000000000001</v>
+        <v>70.19</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>94.63</v>
+        <v>77.23</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>11.754</v>
@@ -1413,8 +1417,58 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N18"/>
+  <autoFilter ref="A1:N19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1000,125 +1000,125 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>82.42</v>
+        <v>93.13</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>83.87</v>
+        <v>95.16</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>92.12</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>83.14</v>
+        <v>94.13</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>71.14</v>
+        <v>88.91</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>15.125</v>
+        <v>0.62</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>86.37</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>89.25</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>91.94</v>
+        <v>98.78</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>82.77</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>70.61</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>87.14</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>8.195</v>
+        <v>2.596</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>15.125</v>
+        <v>0.62</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>24.1021</v>
+        <v>2.2136</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1127,336 +1127,352 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>79.94</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>91.89</v>
+        <v>91.81</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>82.3</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>69.92</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>76.84</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>5.492</v>
+        <v>2.596</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>3.515</v>
+        <v>0.62</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>10.7311</v>
+        <v>2.2136</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>80.87</v>
+        <v>90.16</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>83.81</v>
+        <v>93.97</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>91.81</v>
+        <v>99.38</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>92.02</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>69.95</v>
+        <v>85.23</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>5.533</v>
+        <v>2.596</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>3.556</v>
+        <v>0.62</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10.9824</v>
+        <v>2.2136</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>79.78</v>
+        <v>94.7</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>84.39</v>
+        <v>96.13</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>91.75</v>
+        <v>98.88</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>82.02</v>
+        <v>95.41</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>69.52</v>
+        <v>91.22</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>94.77</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>5.491</v>
+        <v>3.455</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>3.514</v>
+        <v>1.478</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>11.5239</v>
+        <v>3.5459</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>97.72</v>
+        <v>88.42</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>97.78</v>
+        <v>91.97</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>99.44</v>
+        <v>99.02</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>97.75</v>
+        <v>90.16</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>82.08</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>89.64</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>20.661</v>
+        <v>1.478</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>78.73</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>92.33</v>
+        <v>84.98</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>91.95</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.11</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>91.52</v>
+        <v>76.38</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>20.661</v>
+        <v>1.478</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>80.77</v>
+        <v>91.64</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>84.27</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>91.91</v>
+        <v>99.47</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>82.48</v>
+        <v>93.2</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>70.19</v>
+        <v>87.27</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>77.23</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>20.661</v>
+        <v>1.478</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>R4_0_A0_FULL12_FROZEN</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>93.62</v>
+        <v>82.42</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>96.09</v>
+        <v>83.87</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>92.12</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>94.84</v>
+        <v>83.14</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>90.18000000000001</v>
+        <v>71.14</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>94.63</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>20.661</v>
+        <v>15.125</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>26.3246</v>
@@ -1467,8 +1483,424 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>R4_1_VIT4_OLDHEAD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>8.195</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>24.1021</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>10.7311</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>83.81</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>10.9824</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>3.514</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>11.5239</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N19"/>
+  <autoFilter ref="A1:N27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,51 +524,51 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>91.09</v>
+        <v>94.08</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>92.8</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>99.19</v>
+        <v>98.69</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>91.94</v>
+        <v>94.67</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>85.08</v>
+        <v>89.87</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>93.92</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>11.754</v>
+        <v>2.378</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>20.661</v>
+        <v>2.378</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>26.3183</v>
+        <v>1.2051</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -578,51 +578,51 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>80.3</v>
+        <v>88.55</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>84.81</v>
+        <v>91.3</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>82.5</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>81.66</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>89.37</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>11.754</v>
+        <v>2.378</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>20.661</v>
+        <v>2.378</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>26.3183</v>
+        <v>1.2051</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -632,51 +632,51 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>82.09</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>92.75</v>
+        <v>82.84</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.77</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>91.86</v>
+        <v>82.47</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>84.94</v>
+        <v>70.16</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>77.09</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>11.754</v>
+        <v>2.378</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>20.661</v>
+        <v>2.378</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>26.2593</v>
+        <v>1.2051</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -686,763 +686,763 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>80.55</v>
+        <v>92.34</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>84.23</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>91.86</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>82.34999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>70</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>77.06</v>
+        <v>93.44</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>11.754</v>
+        <v>2.378</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>20.661</v>
+        <v>2.378</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>26.2593</v>
+        <v>1.2051</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>91.38</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>92.3</v>
+        <v>95.19</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>99.17</v>
+        <v>98.66</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>91.84</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>84.91</v>
+        <v>89.64</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>93.78</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>11.754</v>
+        <v>2.416</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>15.125</v>
+        <v>2.416</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>26.1484</v>
+        <v>1.2365</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>86.03</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>98.98</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>89.87</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>69.55</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>76.83</v>
+        <v>89.33</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>11.754</v>
+        <v>2.416</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>15.125</v>
+        <v>2.416</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>26.1484</v>
+        <v>1.2365</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>91.13</v>
+        <v>79.66</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>85.53</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>92.03</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>91.88</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>84.98</v>
+        <v>70.2</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>91.45</v>
+        <v>77.34</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>11.754</v>
+        <v>2.416</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>15.125</v>
+        <v>2.416</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>26.0894</v>
+        <v>1.2365</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>85.05</v>
+        <v>95.56</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>92.36</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>83.52</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>71.7</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>78.55</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>11.754</v>
+        <v>2.416</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>15.125</v>
+        <v>2.416</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>26.0894</v>
+        <v>1.2365</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>95.05</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>84.28</v>
+        <v>96.02</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>91.7</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>81.92</v>
+        <v>95.53</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>69.37</v>
+        <v>91.45</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>94.91</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>11.754</v>
+        <v>2.378</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>15.125</v>
+        <v>2.378</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>26.0894</v>
+        <v>1.2051</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>93.13</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>95.16</v>
+        <v>91.62</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>99.02</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>94.13</v>
+        <v>90.28</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>88.91</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>89.77</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2.596</v>
+        <v>2.378</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0.62</v>
+        <v>2.378</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2.2136</v>
+        <v>1.2051</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>86.37</v>
+        <v>79.3</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>89.25</v>
+        <v>85.94</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>98.78</v>
+        <v>92.06</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>70.19</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>87.14</v>
+        <v>77.36</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2.596</v>
+        <v>2.378</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0.62</v>
+        <v>2.378</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2.2136</v>
+        <v>1.2051</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>84.5</v>
+        <v>94.7</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>91.81</v>
+        <v>99.48</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>93.41</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>76.84</v>
+        <v>93.14</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>2.596</v>
+        <v>2.378</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0.62</v>
+        <v>2.378</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2.2136</v>
+        <v>1.2051</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>90.16</v>
+        <v>95.06</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>93.97</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>99.38</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>92.02</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>85.23</v>
+        <v>91.45</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>91.7</v>
+        <v>94.91</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>2.596</v>
+        <v>2.416</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0.62</v>
+        <v>2.416</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2.2136</v>
+        <v>1.2365</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>94.7</v>
+        <v>89.47</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>96.13</v>
+        <v>91.28</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>98.88</v>
+        <v>99.03</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>95.41</v>
+        <v>90.37</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>91.22</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>94.77</v>
+        <v>89.86</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>3.455</v>
+        <v>2.416</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1.478</v>
+        <v>2.416</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3.5459</v>
+        <v>1.2365</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>88.42</v>
+        <v>81.39</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>91.97</v>
+        <v>84.72</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>99.02</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>90.16</v>
+        <v>83.02</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>82.08</v>
+        <v>70.97</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>89.64</v>
+        <v>77.92</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>3.455</v>
+        <v>2.416</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1.478</v>
+        <v>2.416</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3.5459</v>
+        <v>1.2365</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>78.73</v>
+        <v>92</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>84.98</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>91.7</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>93.72</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>69.11</v>
+        <v>88.19</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>76.38</v>
+        <v>93.47</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>3.455</v>
+        <v>2.416</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1.478</v>
+        <v>2.416</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3.5459</v>
+        <v>1.2365</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>91.64</v>
+        <v>91.09</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>99.47</v>
+        <v>99.19</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>93.2</v>
+        <v>91.94</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>87.27</v>
+        <v>85.08</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>3.455</v>
+        <v>11.754</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1.478</v>
+        <v>20.661</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3.5459</v>
+        <v>26.3183</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1451,106 +1451,106 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>82.42</v>
+        <v>80.3</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>83.87</v>
+        <v>84.81</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>92.12</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>83.14</v>
+        <v>82.5</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>71.14</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>26.3246</v>
+        <v>26.3183</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>91.94</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>82.77</v>
+        <v>91.86</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>70.61</v>
+        <v>84.94</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>8.195</v>
+        <v>11.754</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>24.1021</v>
+        <v>26.2593</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1559,106 +1559,106 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>79.94</v>
+        <v>80.55</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>84.23</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>91.89</v>
+        <v>91.86</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>82.3</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>69.92</v>
+        <v>70</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>77.06</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>5.492</v>
+        <v>11.754</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>3.515</v>
+        <v>20.661</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>10.7311</v>
+        <v>26.2593</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>80.87</v>
+        <v>91.38</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>83.81</v>
+        <v>92.3</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>91.81</v>
+        <v>99.17</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>91.84</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>69.95</v>
+        <v>84.91</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>5.533</v>
+        <v>11.754</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>3.556</v>
+        <v>15.125</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>10.9824</v>
+        <v>26.1484</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1667,240 +1667,1104 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>79.78</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>84.39</v>
+        <v>86.03</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>91.75</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>82.02</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>69.52</v>
+        <v>69.55</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>76.83</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>5.491</v>
+        <v>11.754</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>3.514</v>
+        <v>15.125</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>11.5239</v>
+        <v>26.1484</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>Run2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>A3_ORACLE_FROZEN</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>97.72</v>
+        <v>91.13</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>97.78</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>99.44</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>97.75</v>
+        <v>91.88</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>84.98</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>91.45</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>20.661</v>
+        <v>15.125</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>26.3246</v>
+        <v>26.0894</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>Run2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>A3_ORACLE_FROZEN</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>92.33</v>
+        <v>85.05</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>92.36</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>91.95</v>
+        <v>83.52</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>91.52</v>
+        <v>78.55</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>20.661</v>
+        <v>15.125</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>26.3246</v>
+        <v>26.0894</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>Run3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>A4_DETAIL_FROZEN</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>80.77</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>84.27</v>
+        <v>84.28</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>91.91</v>
+        <v>91.7</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>82.48</v>
+        <v>81.92</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>70.19</v>
+        <v>69.37</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>77.23</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>20.661</v>
+        <v>15.125</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>26.3246</v>
+        <v>26.0894</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>93.13</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>95.16</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>98.56999999999999</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>94.13</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>88.91</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>93.31999999999999</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>2.596</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>2.2136</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>86.37</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>87.79000000000001</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>78.23999999999999</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>87.14</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>2.596</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>2.2136</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>79.93000000000001</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>69.70999999999999</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>2.596</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>2.2136</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>93.97</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>99.38</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>92.02</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>85.23</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>2.596</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>2.2136</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>96.13</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>95.41</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>94.77</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>91.97</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>78.73</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>84.98</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>69.11</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>76.38</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>87.27</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>R4_0_A0_FULL12_FROZEN</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>82.42</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>83.87</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>92.12</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>R4_1_VIT4_OLDHEAD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>8.195</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>24.1021</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>10.7311</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>83.81</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>10.9824</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>3.514</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>11.5239</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>Run1</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E43" s="2" t="n">
         <v>93.62</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="F43" s="2" t="n">
         <v>96.09</v>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="H43" s="2" t="n">
         <v>94.84</v>
       </c>
-      <c r="I27" s="2" t="n">
+      <c r="I43" s="2" t="n">
         <v>90.18000000000001</v>
       </c>
-      <c r="J27" s="2" t="n">
+      <c r="J43" s="2" t="n">
         <v>94.63</v>
       </c>
-      <c r="K27" s="2" t="n">
+      <c r="K43" s="2" t="n">
         <v>11.754</v>
       </c>
-      <c r="L27" s="2" t="n">
+      <c r="L43" s="2" t="n">
         <v>20.661</v>
       </c>
-      <c r="M27" s="2" t="n">
+      <c r="M43" s="2" t="n">
         <v>26.3246</v>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N27"/>
+  <autoFilter ref="A1:N43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1378,7 +1378,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1388,51 +1388,51 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>91.09</v>
+        <v>96.58</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>92.8</v>
+        <v>96.94</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>99.19</v>
+        <v>99.2</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>91.94</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>85.08</v>
+        <v>93.73</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>96.31</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>20.661</v>
+        <v>4.88</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>26.3183</v>
+        <v>2.6747</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1442,51 +1442,51 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>80.3</v>
+        <v>89.52</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>84.81</v>
+        <v>92.69</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>99.11</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>82.5</v>
+        <v>91.08</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>83.62</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>90.61</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>20.661</v>
+        <v>4.88</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>26.3183</v>
+        <v>2.6747</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1496,51 +1496,51 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>92.75</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.94</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>91.86</v>
+        <v>82.39</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>84.94</v>
+        <v>70.06</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>20.661</v>
+        <v>4.88</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>26.2593</v>
+        <v>2.6747</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1550,763 +1550,763 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>80.55</v>
+        <v>92.69</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>84.23</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>91.86</v>
+        <v>99.59</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>82.34999999999999</v>
+        <v>94.78</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>70</v>
+        <v>90.08</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>77.06</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>20.661</v>
+        <v>4.88</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>26.2593</v>
+        <v>2.6747</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>91.38</v>
+        <v>96.62</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>92.3</v>
+        <v>96.88</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>99.17</v>
+        <v>99.2</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>91.84</v>
+        <v>96.75</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>84.91</v>
+        <v>93.7</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>15.125</v>
+        <v>4.88</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>26.1484</v>
+        <v>2.6747</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>89.95</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>86.03</v>
+        <v>92.13</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.03</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>69.55</v>
+        <v>83.53</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>76.83</v>
+        <v>90.55</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>15.125</v>
+        <v>4.88</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>26.1484</v>
+        <v>2.6747</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>91.13</v>
+        <v>80.14</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>91.88</v>
+        <v>82.11</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>84.98</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>91.45</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>15.125</v>
+        <v>4.88</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>26.0894</v>
+        <v>2.6747</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>92.45</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>85.05</v>
+        <v>97.37</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>92.36</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>83.52</v>
+        <v>94.84</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>71.7</v>
+        <v>90.19</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>78.55</v>
+        <v>94.64</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>15.125</v>
+        <v>4.88</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>26.0894</v>
+        <v>2.6747</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>97.02</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>84.28</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>91.7</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>81.92</v>
+        <v>97.11</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>69.37</v>
+        <v>94.39</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>15.125</v>
+        <v>4.88</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>26.0894</v>
+        <v>2.6747</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>93.13</v>
+        <v>89.59</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>95.16</v>
+        <v>92.84</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>99.12</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>94.13</v>
+        <v>91.19</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>88.91</v>
+        <v>83.81</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>90.73</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>2.596</v>
+        <v>4.88</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0.62</v>
+        <v>4.88</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2.2136</v>
+        <v>2.6747</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>86.37</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>89.25</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>98.78</v>
+        <v>92.27</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>71.25</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>87.14</v>
+        <v>78.2</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>2.596</v>
+        <v>4.88</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0.62</v>
+        <v>4.88</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2.2136</v>
+        <v>2.6747</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>84.5</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>91.81</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>94.53</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>89.63</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>76.84</v>
+        <v>94.31</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2.596</v>
+        <v>4.88</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0.62</v>
+        <v>4.88</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2.2136</v>
+        <v>2.6747</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>90.16</v>
+        <v>97.03</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>93.97</v>
+        <v>97.33</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>99.38</v>
+        <v>99.3</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>92.02</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>85.23</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>91.7</v>
+        <v>96.78</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2.596</v>
+        <v>4.88</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0.62</v>
+        <v>4.88</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2.2136</v>
+        <v>2.6747</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>94.7</v>
+        <v>90.33</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>96.13</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>98.88</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>95.41</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>91.22</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>94.77</v>
+        <v>90.59</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>3.455</v>
+        <v>4.88</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1.478</v>
+        <v>4.88</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.6747</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>88.42</v>
+        <v>84.41</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>91.97</v>
+        <v>82.55</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>99.02</v>
+        <v>92.12</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>90.16</v>
+        <v>83.47</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>82.08</v>
+        <v>71.63</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>89.64</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>3.455</v>
+        <v>4.88</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1.478</v>
+        <v>4.88</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.6747</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>78.73</v>
+        <v>93.56</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>84.98</v>
+        <v>96.62</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>91.7</v>
+        <v>99.61</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>69.11</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>76.38</v>
+        <v>94.87</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>3.455</v>
+        <v>4.88</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1.478</v>
+        <v>4.88</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.6747</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>91.64</v>
+        <v>91.09</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>99.47</v>
+        <v>99.19</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>93.2</v>
+        <v>91.94</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>87.27</v>
+        <v>85.08</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>3.455</v>
+        <v>11.754</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1.478</v>
+        <v>20.661</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3.5459</v>
+        <v>26.3183</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2315,106 +2315,106 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>82.42</v>
+        <v>80.3</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>83.87</v>
+        <v>84.81</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>92.12</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>83.14</v>
+        <v>82.5</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>71.14</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>26.3246</v>
+        <v>26.3183</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>91.94</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>82.77</v>
+        <v>91.86</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>70.61</v>
+        <v>84.94</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>8.195</v>
+        <v>11.754</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>24.1021</v>
+        <v>26.2593</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2423,106 +2423,106 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>79.94</v>
+        <v>80.55</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>84.23</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>91.89</v>
+        <v>91.86</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>82.3</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>69.92</v>
+        <v>70</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>77.06</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>5.492</v>
+        <v>11.754</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>3.515</v>
+        <v>20.661</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>10.7311</v>
+        <v>26.2593</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>80.87</v>
+        <v>91.38</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>83.81</v>
+        <v>92.3</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>91.81</v>
+        <v>99.17</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>91.84</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>69.95</v>
+        <v>84.91</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>5.533</v>
+        <v>11.754</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>3.556</v>
+        <v>15.125</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>10.9824</v>
+        <v>26.1484</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2531,240 +2531,1104 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>79.78</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>84.39</v>
+        <v>86.03</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>91.75</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>82.02</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>69.52</v>
+        <v>69.55</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>76.83</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>5.491</v>
+        <v>11.754</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>3.514</v>
+        <v>15.125</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>11.5239</v>
+        <v>26.1484</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>Run2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>A3_ORACLE_FROZEN</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>97.72</v>
+        <v>91.13</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>97.78</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>99.44</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>97.75</v>
+        <v>91.88</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>84.98</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>91.45</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>20.661</v>
+        <v>15.125</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>26.3246</v>
+        <v>26.0894</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>Run2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>A3_ORACLE_FROZEN</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>92.33</v>
+        <v>85.05</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>92.36</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>91.95</v>
+        <v>83.52</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>91.52</v>
+        <v>78.55</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>20.661</v>
+        <v>15.125</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>26.3246</v>
+        <v>26.0894</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>Run3</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>A4_DETAIL_FROZEN</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
           <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>80.77</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>84.27</v>
+        <v>84.28</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>91.91</v>
+        <v>91.7</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>82.48</v>
+        <v>81.92</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>70.19</v>
+        <v>69.37</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>77.23</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>20.661</v>
+        <v>15.125</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>26.3246</v>
+        <v>26.0894</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>93.13</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>95.16</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>98.56999999999999</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>94.13</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>88.91</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>93.31999999999999</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>2.596</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>2.2136</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>86.37</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>87.79000000000001</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>78.23999999999999</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>87.14</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>2.596</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>2.2136</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>79.93000000000001</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>69.70999999999999</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>2.596</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>2.2136</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>93.97</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>99.38</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>92.02</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>85.23</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>2.596</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>2.2136</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>96.13</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>95.41</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>94.77</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>91.97</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>78.73</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>84.98</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>69.11</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>76.38</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>87.27</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>R4_0_A0_FULL12_FROZEN</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>82.42</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>83.87</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>92.12</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>R4_1_VIT4_OLDHEAD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>8.195</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>24.1021</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>10.7311</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>83.81</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>10.9824</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>3.514</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>11.5239</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="E59" s="2" t="n">
         <v>93.62</v>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="F59" s="2" t="n">
         <v>96.09</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G59" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="H43" s="2" t="n">
+      <c r="H59" s="2" t="n">
         <v>94.84</v>
       </c>
-      <c r="I43" s="2" t="n">
+      <c r="I59" s="2" t="n">
         <v>90.18000000000001</v>
       </c>
-      <c r="J43" s="2" t="n">
+      <c r="J59" s="2" t="n">
         <v>94.63</v>
       </c>
-      <c r="K43" s="2" t="n">
+      <c r="K59" s="2" t="n">
         <v>11.754</v>
       </c>
-      <c r="L43" s="2" t="n">
+      <c r="L59" s="2" t="n">
         <v>20.661</v>
       </c>
-      <c r="M43" s="2" t="n">
+      <c r="M59" s="2" t="n">
         <v>26.3246</v>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N43"/>
+  <autoFilter ref="A1:N59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2242,223 +2242,223 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>91.09</v>
+        <v>97.02</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>92.8</v>
+        <v>97.27</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>99.19</v>
+        <v>99.3</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>91.94</v>
+        <v>97.14</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>85.08</v>
+        <v>94.45</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>20.661</v>
+        <v>4.88</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>26.3183</v>
+        <v>2.6747</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>80.3</v>
+        <v>90.64</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>84.81</v>
+        <v>91.64</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>82.5</v>
+        <v>91.14</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>83.72</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>90.66</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>20.661</v>
+        <v>4.88</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>26.3183</v>
+        <v>2.6747</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>80.94</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>92.75</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>92.25</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>91.86</v>
+        <v>83.13</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>84.94</v>
+        <v>71.12</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>20.661</v>
+        <v>4.88</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>26.2593</v>
+        <v>2.6747</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>80.55</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>84.23</v>
+        <v>96.67</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>91.86</v>
+        <v>99.62</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>82.34999999999999</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>70</v>
+        <v>90.81</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>77.06</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>20.661</v>
+        <v>4.88</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>26.2593</v>
+        <v>2.6747</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2468,51 +2468,51 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>91.38</v>
+        <v>97.02</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>92.3</v>
+        <v>97.33</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>99.17</v>
+        <v>99.3</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>91.84</v>
+        <v>97.17</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>84.91</v>
+        <v>94.5</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>96.78</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>11.754</v>
+        <v>4.881</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>15.125</v>
+        <v>4.881</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>26.1484</v>
+        <v>2.6947</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2522,51 +2522,51 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>90.22</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>86.03</v>
+        <v>92.22</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>99.11</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>69.55</v>
+        <v>83.83</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>76.83</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>11.754</v>
+        <v>4.881</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>15.125</v>
+        <v>4.881</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>26.1484</v>
+        <v>2.6947</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2576,51 +2576,51 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>91.13</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>86.05</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>91.88</v>
+        <v>82.97</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>84.98</v>
+        <v>70.89</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>91.45</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>11.754</v>
+        <v>4.881</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>15.125</v>
+        <v>4.881</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>26.0894</v>
+        <v>2.6947</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2630,385 +2630,385 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>85.05</v>
+        <v>96</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>92.36</v>
+        <v>99.59</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>83.52</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>71.7</v>
+        <v>89.95</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>78.55</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>11.754</v>
+        <v>4.881</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>15.125</v>
+        <v>4.881</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>26.0894</v>
+        <v>2.6947</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>97.02</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>84.28</v>
+        <v>97.34</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>91.7</v>
+        <v>99.3</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>81.92</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>69.37</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>96.78</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>11.754</v>
+        <v>4.881</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>15.125</v>
+        <v>4.881</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>26.0894</v>
+        <v>2.6947</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>93.13</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>95.16</v>
+        <v>92.41</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>99.12</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>94.13</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>88.91</v>
+        <v>83.98</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>90.83</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2.596</v>
+        <v>4.881</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0.62</v>
+        <v>4.881</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2.2136</v>
+        <v>2.6947</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>86.37</v>
+        <v>80.69</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>89.25</v>
+        <v>85.12</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>98.78</v>
+        <v>92.12</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>70.72</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>87.14</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>2.596</v>
+        <v>4.881</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.62</v>
+        <v>4.881</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2.2136</v>
+        <v>2.6947</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>84.5</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>91.81</v>
+        <v>99.61</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>94.98</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>90.44</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>76.84</v>
+        <v>94.77</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2.596</v>
+        <v>4.881</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0.62</v>
+        <v>4.881</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2.2136</v>
+        <v>2.6947</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>90.16</v>
+        <v>91.09</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>93.97</v>
+        <v>92.8</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>99.38</v>
+        <v>99.19</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>92.02</v>
+        <v>91.94</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>85.23</v>
+        <v>85.08</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>91.7</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0.62</v>
+        <v>20.661</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.3183</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>94.7</v>
+        <v>80.3</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>96.13</v>
+        <v>84.81</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>98.88</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>95.41</v>
+        <v>82.5</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>91.22</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>94.77</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>3.455</v>
+        <v>11.754</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1.478</v>
+        <v>20.661</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3.5459</v>
+        <v>26.3183</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3017,52 +3017,52 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>88.42</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>91.97</v>
+        <v>92.75</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>99.02</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>90.16</v>
+        <v>91.86</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>82.08</v>
+        <v>84.94</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>89.64</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>3.455</v>
+        <v>11.754</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1.478</v>
+        <v>20.661</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3.5459</v>
+        <v>26.2593</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3071,106 +3071,106 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>78.73</v>
+        <v>80.55</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>84.98</v>
+        <v>84.23</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>91.7</v>
+        <v>91.86</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>69.11</v>
+        <v>70</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>76.38</v>
+        <v>77.06</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>3.455</v>
+        <v>11.754</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1.478</v>
+        <v>20.661</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3.5459</v>
+        <v>26.2593</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>91.64</v>
+        <v>91.38</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>99.47</v>
+        <v>99.17</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>93.2</v>
+        <v>91.84</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>87.27</v>
+        <v>84.91</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>3.455</v>
+        <v>11.754</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1.478</v>
+        <v>15.125</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3.5459</v>
+        <v>26.1484</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3179,22 +3179,22 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>82.42</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>83.87</v>
+        <v>86.03</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>92.12</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>83.14</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>71.14</v>
+        <v>69.55</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>76.83</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>11.754</v>
@@ -3203,82 +3203,82 @@
         <v>15.125</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>26.3246</v>
+        <v>26.1484</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>91.94</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>82.77</v>
+        <v>91.88</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>70.61</v>
+        <v>84.98</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>91.45</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>8.195</v>
+        <v>11.754</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>15.125</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>24.1021</v>
+        <v>26.0894</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3287,52 +3287,52 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>79.94</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>85.05</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>91.89</v>
+        <v>92.36</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>82.3</v>
+        <v>83.52</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>69.92</v>
+        <v>71.7</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>78.55</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>5.492</v>
+        <v>11.754</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>3.515</v>
+        <v>15.125</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>10.7311</v>
+        <v>26.0894</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>A4_DETAIL_FROZEN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3341,294 +3341,942 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>80.87</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>83.81</v>
+        <v>84.28</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>91.81</v>
+        <v>91.7</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>81.92</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>69.95</v>
+        <v>69.37</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>5.533</v>
+        <v>11.754</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>3.556</v>
+        <v>15.125</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>10.9824</v>
+        <v>26.0894</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>79.78</v>
+        <v>93.13</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>84.39</v>
+        <v>95.16</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>91.75</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>82.02</v>
+        <v>94.13</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>69.52</v>
+        <v>88.91</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>5.491</v>
+        <v>2.596</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>3.514</v>
+        <v>0.62</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>11.5239</v>
+        <v>2.2136</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>97.72</v>
+        <v>86.37</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>97.78</v>
+        <v>89.25</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>99.44</v>
+        <v>98.78</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>97.75</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>87.14</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>92.33</v>
+        <v>84.5</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.81</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>91.95</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>91.52</v>
+        <v>76.84</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>80.77</v>
+        <v>90.16</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>84.27</v>
+        <v>93.97</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>91.91</v>
+        <v>99.38</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>82.48</v>
+        <v>92.02</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>70.19</v>
+        <v>85.23</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>77.23</v>
+        <v>91.7</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>96.13</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>95.41</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>94.77</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>91.97</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>78.73</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>84.98</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>69.11</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>76.38</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>87.27</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>R4_0_A0_FULL12_FROZEN</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>82.42</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>83.87</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>92.12</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>R4_1_VIT4_OLDHEAD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>8.195</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>24.1021</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>10.7311</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>83.81</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>10.9824</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>3.514</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>11.5239</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
         <is>
           <t>Run1</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
-      <c r="E59" s="2" t="n">
+      <c r="E71" s="2" t="n">
         <v>93.62</v>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="F71" s="2" t="n">
         <v>96.09</v>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G71" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="H59" s="2" t="n">
+      <c r="H71" s="2" t="n">
         <v>94.84</v>
       </c>
-      <c r="I59" s="2" t="n">
+      <c r="I71" s="2" t="n">
         <v>90.18000000000001</v>
       </c>
-      <c r="J59" s="2" t="n">
+      <c r="J71" s="2" t="n">
         <v>94.63</v>
       </c>
-      <c r="K59" s="2" t="n">
+      <c r="K71" s="2" t="n">
         <v>11.754</v>
       </c>
-      <c r="L59" s="2" t="n">
+      <c r="L71" s="2" t="n">
         <v>20.661</v>
       </c>
-      <c r="M59" s="2" t="n">
+      <c r="M71" s="2" t="n">
         <v>26.3246</v>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N59"/>
+  <autoFilter ref="A1:N71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N71"/>
+  <dimension ref="A1:N79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2890,432 +2890,432 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>91.09</v>
+        <v>97.02</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>92.8</v>
+        <v>97.25</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>99.19</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>91.94</v>
+        <v>97.13</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>85.08</v>
+        <v>94.42</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>96.73</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>20.661</v>
+        <v>4.88</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>26.3183</v>
+        <v>2.6747</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>80.3</v>
+        <v>90.05</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>84.81</v>
+        <v>92.12</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>82.5</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>20.661</v>
+        <v>4.88</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>26.3183</v>
+        <v>2.6747</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>81.44</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>92.75</v>
+        <v>84.94</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>92.22</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>91.86</v>
+        <v>83.16</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>84.94</v>
+        <v>71.17</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>20.661</v>
+        <v>4.88</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>26.2593</v>
+        <v>2.6747</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>80.55</v>
+        <v>93.42</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>84.23</v>
+        <v>96.66</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>91.86</v>
+        <v>99.61</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>82.34999999999999</v>
+        <v>95.02</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>70</v>
+        <v>90.5</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>77.06</v>
+        <v>94.81</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>20.661</v>
+        <v>4.88</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>26.2593</v>
+        <v>2.6747</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>91.38</v>
+        <v>97.03</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>92.3</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>99.17</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>91.84</v>
+        <v>97.13</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>84.91</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>96.73</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>11.754</v>
+        <v>4.954</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>15.125</v>
+        <v>4.954</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>26.1484</v>
+        <v>2.9767</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>90.25</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>86.03</v>
+        <v>92.12</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>99.11</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>69.55</v>
+        <v>83.78</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>76.83</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>11.754</v>
+        <v>4.954</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>15.125</v>
+        <v>4.954</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>26.1484</v>
+        <v>2.9767</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>91.13</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>85.31</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>92.28</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>91.88</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>84.98</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>91.45</v>
+        <v>78.23</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>11.754</v>
+        <v>4.954</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>15.125</v>
+        <v>4.954</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>26.0894</v>
+        <v>2.9767</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>93.11</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>85.05</v>
+        <v>96.78</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>92.36</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>83.52</v>
+        <v>94.91</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>71.7</v>
+        <v>90.31</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>78.55</v>
+        <v>94.7</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>11.754</v>
+        <v>4.954</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>15.125</v>
+        <v>4.954</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>26.0894</v>
+        <v>2.9767</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -3327,120 +3327,120 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>91.09</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>84.28</v>
+        <v>92.8</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>91.7</v>
+        <v>99.19</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>81.92</v>
+        <v>91.94</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>69.37</v>
+        <v>85.08</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>26.0894</v>
+        <v>26.3183</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>93.13</v>
+        <v>80.3</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>95.16</v>
+        <v>84.81</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>94.13</v>
+        <v>82.5</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>88.91</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0.62</v>
+        <v>20.661</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.3183</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3449,52 +3449,52 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>86.37</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>89.25</v>
+        <v>92.75</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>98.78</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>91.86</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>84.94</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>87.14</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0.62</v>
+        <v>20.661</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.2593</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3503,160 +3503,160 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>80.55</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>84.5</v>
+        <v>84.23</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>91.81</v>
+        <v>91.86</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>70</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>76.84</v>
+        <v>77.06</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0.62</v>
+        <v>20.661</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.2593</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>90.16</v>
+        <v>91.38</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>93.97</v>
+        <v>92.3</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>99.38</v>
+        <v>99.17</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>92.02</v>
+        <v>91.84</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>85.23</v>
+        <v>84.91</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>91.7</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0.62</v>
+        <v>15.125</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.1484</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>94.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>96.13</v>
+        <v>86.03</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>98.88</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>95.41</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>91.22</v>
+        <v>69.55</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>94.77</v>
+        <v>76.83</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>3.455</v>
+        <v>11.754</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>1.478</v>
+        <v>15.125</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3.5459</v>
+        <v>26.1484</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3665,52 +3665,52 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>88.42</v>
+        <v>91.13</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>91.97</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>99.02</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>90.16</v>
+        <v>91.88</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>82.08</v>
+        <v>84.98</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>89.64</v>
+        <v>91.45</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>3.455</v>
+        <v>11.754</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1.478</v>
+        <v>15.125</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3.5459</v>
+        <v>26.0894</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3719,214 +3719,214 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>78.73</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>84.98</v>
+        <v>85.05</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>91.7</v>
+        <v>92.36</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>83.52</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>69.11</v>
+        <v>71.7</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>76.38</v>
+        <v>78.55</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>3.455</v>
+        <v>11.754</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>1.478</v>
+        <v>15.125</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3.5459</v>
+        <v>26.0894</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>A4_DETAIL_FROZEN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>91.64</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>84.28</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>99.47</v>
+        <v>91.7</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>93.2</v>
+        <v>81.92</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>87.27</v>
+        <v>69.37</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>3.455</v>
+        <v>11.754</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1.478</v>
+        <v>15.125</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3.5459</v>
+        <v>26.0894</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>82.42</v>
+        <v>93.13</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>83.87</v>
+        <v>95.16</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>92.12</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>83.14</v>
+        <v>94.13</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>71.14</v>
+        <v>88.91</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>15.125</v>
+        <v>0.62</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>86.37</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>89.25</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>91.94</v>
+        <v>98.78</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>82.77</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>70.61</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>87.14</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>8.195</v>
+        <v>2.596</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>15.125</v>
+        <v>0.62</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>24.1021</v>
+        <v>2.2136</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3935,336 +3935,352 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>79.94</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>91.89</v>
+        <v>91.81</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>82.3</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>69.92</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>76.84</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>5.492</v>
+        <v>2.596</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>3.515</v>
+        <v>0.62</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>10.7311</v>
+        <v>2.2136</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>80.87</v>
+        <v>90.16</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>83.81</v>
+        <v>93.97</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>91.81</v>
+        <v>99.38</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>92.02</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>69.95</v>
+        <v>85.23</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>5.533</v>
+        <v>2.596</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>3.556</v>
+        <v>0.62</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>10.9824</v>
+        <v>2.2136</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>79.78</v>
+        <v>94.7</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>84.39</v>
+        <v>96.13</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>91.75</v>
+        <v>98.88</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>82.02</v>
+        <v>95.41</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>69.52</v>
+        <v>91.22</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>94.77</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>5.491</v>
+        <v>3.455</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>3.514</v>
+        <v>1.478</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>11.5239</v>
+        <v>3.5459</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>97.72</v>
+        <v>88.42</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>97.78</v>
+        <v>91.97</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>99.44</v>
+        <v>99.02</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>97.75</v>
+        <v>90.16</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>82.08</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>89.64</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>20.661</v>
+        <v>1.478</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>78.73</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>92.33</v>
+        <v>84.98</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>91.95</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.11</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>91.52</v>
+        <v>76.38</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>20.661</v>
+        <v>1.478</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>80.77</v>
+        <v>91.64</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>84.27</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>91.91</v>
+        <v>99.47</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>82.48</v>
+        <v>93.2</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>70.19</v>
+        <v>87.27</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>77.23</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>20.661</v>
+        <v>1.478</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>R4_0_A0_FULL12_FROZEN</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>93.62</v>
+        <v>82.42</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>96.09</v>
+        <v>83.87</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>92.12</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>94.84</v>
+        <v>83.14</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>90.18000000000001</v>
+        <v>71.14</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>94.63</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>20.661</v>
+        <v>15.125</v>
       </c>
       <c r="M71" s="2" t="n">
         <v>26.3246</v>
@@ -4275,8 +4291,424 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>R4_1_VIT4_OLDHEAD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>8.195</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>24.1021</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>10.7311</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>83.81</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>10.9824</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>3.514</v>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>11.5239</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N71"/>
+  <autoFilter ref="A1:N79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N79"/>
+  <dimension ref="A1:N91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3322,773 +3322,773 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>91.09</v>
+        <v>96.97</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>92.8</v>
+        <v>97.08</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>99.19</v>
+        <v>99.27</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>91.94</v>
+        <v>97.02</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>85.08</v>
+        <v>94.22</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>11.754</v>
+        <v>4.89</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>20.661</v>
+        <v>4.89</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>26.3183</v>
+        <v>2.717</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>80.3</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>84.81</v>
+        <v>92.33</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>99.12</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>82.5</v>
+        <v>91.23</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>83.87</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>11.754</v>
+        <v>4.89</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>20.661</v>
+        <v>4.89</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>26.3183</v>
+        <v>2.717</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>92.75</v>
+        <v>84.53</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>91.86</v>
+        <v>83.19</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>84.94</v>
+        <v>71.22</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>78.11</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>11.754</v>
+        <v>4.89</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>20.661</v>
+        <v>4.89</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>26.2593</v>
+        <v>2.717</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>80.55</v>
+        <v>94.02</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>84.23</v>
+        <v>96.37</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>91.86</v>
+        <v>99.62</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>82.34999999999999</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>70</v>
+        <v>90.8</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>77.06</v>
+        <v>94.98</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>11.754</v>
+        <v>4.89</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>20.661</v>
+        <v>4.89</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>26.2593</v>
+        <v>2.717</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>91.38</v>
+        <v>96.94</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>92.3</v>
+        <v>97.17</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>99.17</v>
+        <v>99.27</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>91.84</v>
+        <v>97.05</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>84.91</v>
+        <v>94.27</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>96.64</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>15.125</v>
+        <v>4.88</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>26.1484</v>
+        <v>2.6747</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>90.09</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>86.03</v>
+        <v>92.62</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>99.13</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.34</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>69.55</v>
+        <v>84.06</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>76.83</v>
+        <v>90.88</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>15.125</v>
+        <v>4.88</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>26.1484</v>
+        <v>2.6747</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>91.13</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>92.34</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>91.88</v>
+        <v>83.31</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>84.98</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>91.45</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>15.125</v>
+        <v>4.88</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>26.0894</v>
+        <v>2.6747</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>85.05</v>
+        <v>96.38</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>92.36</v>
+        <v>99.61</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>83.52</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>71.7</v>
+        <v>90.61</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>78.55</v>
+        <v>94.87</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>15.125</v>
+        <v>4.88</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>26.0894</v>
+        <v>2.6747</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>97</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>84.28</v>
+        <v>97.33</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>91.7</v>
+        <v>99.3</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>81.92</v>
+        <v>97.17</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>69.37</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>96.77</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>15.125</v>
+        <v>4.88</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>26.0894</v>
+        <v>2.6747</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>93.13</v>
+        <v>89.63</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>95.16</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>99.11</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>94.13</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>88.91</v>
+        <v>83.73</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>2.596</v>
+        <v>4.88</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0.62</v>
+        <v>4.88</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2.2136</v>
+        <v>2.6747</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>86.37</v>
+        <v>80.41</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>89.25</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>98.78</v>
+        <v>92.05</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>70.47</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>87.14</v>
+        <v>77.53</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2.596</v>
+        <v>4.88</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0.62</v>
+        <v>4.88</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2.2136</v>
+        <v>2.6747</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>93.44</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>84.5</v>
+        <v>96.28</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>91.81</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>94.84</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>90.19</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>76.84</v>
+        <v>94.63</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2.596</v>
+        <v>4.88</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0.62</v>
+        <v>4.88</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2.2136</v>
+        <v>2.6747</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>90.16</v>
+        <v>91.09</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>93.97</v>
+        <v>92.8</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>99.38</v>
+        <v>99.19</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>92.02</v>
+        <v>91.94</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>85.23</v>
+        <v>85.08</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>91.7</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0.62</v>
+        <v>20.661</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.3183</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>94.7</v>
+        <v>80.3</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>96.13</v>
+        <v>84.81</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>98.88</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>95.41</v>
+        <v>82.5</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>91.22</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>94.77</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>3.455</v>
+        <v>11.754</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>1.478</v>
+        <v>20.661</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3.5459</v>
+        <v>26.3183</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4097,52 +4097,52 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>88.42</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>91.97</v>
+        <v>92.75</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>99.02</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>90.16</v>
+        <v>91.86</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>82.08</v>
+        <v>84.94</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>89.64</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>3.455</v>
+        <v>11.754</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1.478</v>
+        <v>20.661</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3.5459</v>
+        <v>26.2593</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4151,106 +4151,106 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>78.73</v>
+        <v>80.55</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>84.98</v>
+        <v>84.23</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>91.7</v>
+        <v>91.86</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>69.11</v>
+        <v>70</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>76.38</v>
+        <v>77.06</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>3.455</v>
+        <v>11.754</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1.478</v>
+        <v>20.661</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3.5459</v>
+        <v>26.2593</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>91.64</v>
+        <v>91.38</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>99.47</v>
+        <v>99.17</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>93.2</v>
+        <v>91.84</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>87.27</v>
+        <v>84.91</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>3.455</v>
+        <v>11.754</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1.478</v>
+        <v>15.125</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3.5459</v>
+        <v>26.1484</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4259,22 +4259,22 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>82.42</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>83.87</v>
+        <v>86.03</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>92.12</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>83.14</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>71.14</v>
+        <v>69.55</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>76.83</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>11.754</v>
@@ -4283,82 +4283,82 @@
         <v>15.125</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>26.3246</v>
+        <v>26.1484</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>91.94</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>82.77</v>
+        <v>91.88</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>70.61</v>
+        <v>84.98</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>91.45</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>8.195</v>
+        <v>11.754</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>15.125</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>24.1021</v>
+        <v>26.0894</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4367,52 +4367,52 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>79.94</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>85.05</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>91.89</v>
+        <v>92.36</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>82.3</v>
+        <v>83.52</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>69.92</v>
+        <v>71.7</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>78.55</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>5.492</v>
+        <v>11.754</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>3.515</v>
+        <v>15.125</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>10.7311</v>
+        <v>26.0894</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>A4_DETAIL_FROZEN</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4421,294 +4421,942 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>80.87</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>83.81</v>
+        <v>84.28</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>91.81</v>
+        <v>91.7</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>81.92</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>69.95</v>
+        <v>69.37</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>5.533</v>
+        <v>11.754</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>3.556</v>
+        <v>15.125</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>10.9824</v>
+        <v>26.0894</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>79.78</v>
+        <v>93.13</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>84.39</v>
+        <v>95.16</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>91.75</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>82.02</v>
+        <v>94.13</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>69.52</v>
+        <v>88.91</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>5.491</v>
+        <v>2.596</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>3.514</v>
+        <v>0.62</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>11.5239</v>
+        <v>2.2136</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>97.72</v>
+        <v>86.37</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>97.78</v>
+        <v>89.25</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>99.44</v>
+        <v>98.78</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>97.75</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>87.14</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>92.33</v>
+        <v>84.5</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.81</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>91.95</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>91.52</v>
+        <v>76.84</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>80.77</v>
+        <v>90.16</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>84.27</v>
+        <v>93.97</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>91.91</v>
+        <v>99.38</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>82.48</v>
+        <v>92.02</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>70.19</v>
+        <v>85.23</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>77.23</v>
+        <v>91.7</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>96.13</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>95.41</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>94.77</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>91.97</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>78.73</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>84.98</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>69.11</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>76.38</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>87.27</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>R4_0_A0_FULL12_FROZEN</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>82.42</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>83.87</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>92.12</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>R4_1_VIT4_OLDHEAD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>8.195</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>24.1021</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>10.7311</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>83.81</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>10.9824</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>3.514</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>11.5239</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
         <is>
           <t>Run1</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr">
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
-      <c r="E79" s="2" t="n">
+      <c r="E91" s="2" t="n">
         <v>93.62</v>
       </c>
-      <c r="F79" s="2" t="n">
+      <c r="F91" s="2" t="n">
         <v>96.09</v>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="G91" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="H79" s="2" t="n">
+      <c r="H91" s="2" t="n">
         <v>94.84</v>
       </c>
-      <c r="I79" s="2" t="n">
+      <c r="I91" s="2" t="n">
         <v>90.18000000000001</v>
       </c>
-      <c r="J79" s="2" t="n">
+      <c r="J91" s="2" t="n">
         <v>94.63</v>
       </c>
-      <c r="K79" s="2" t="n">
+      <c r="K91" s="2" t="n">
         <v>11.754</v>
       </c>
-      <c r="L79" s="2" t="n">
+      <c r="L91" s="2" t="n">
         <v>20.661</v>
       </c>
-      <c r="M79" s="2" t="n">
+      <c r="M91" s="2" t="n">
         <v>26.3246</v>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N79"/>
+  <autoFilter ref="A1:N91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N91"/>
+  <dimension ref="A1:N99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1381,51 +1381,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>Exploration/Exp1/STG_INJ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>96.58</v>
+        <v>90.38</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>96.94</v>
+        <v>91.91</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>99.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>96.76000000000001</v>
+        <v>91.14</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>93.73</v>
+        <v>83.72</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>96.31</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>90.66</v>
+      </c>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -1435,51 +1425,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>Exploration/Exp1/STG_INJ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>89.52</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>92.69</v>
+        <v>82.19</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>99.11</v>
+        <v>91.41</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>91.08</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>83.62</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>90.61</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>76.08</v>
+      </c>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -1489,51 +1469,43 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>Exploration/Exp1/STG_SUP</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>90.63</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>85.01000000000001</v>
+        <v>91.56</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>91.94</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>82.39</v>
+        <v>91.09</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>70.06</v>
+        <v>83.64</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>77.18000000000001</v>
+        <v>90.62</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>31.978582</v>
+      </c>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -1543,51 +1515,43 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>Exploration/Exp1/STG_SUP</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>92.69</v>
+        <v>81.28</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>96.95999999999999</v>
+        <v>82.75</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>99.59</v>
+        <v>91.59</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>94.78</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>90.08</v>
+        <v>69.5</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>94.56999999999999</v>
+        <v>76.52</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>31.978582</v>
+      </c>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -1597,51 +1561,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>Exploration/Exp1/STG_V2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>96.62</v>
+        <v>90.52</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>96.88</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>99.2</v>
+        <v>99.11</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>96.75</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>93.7</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>96.29000000000001</v>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>90.70999999999999</v>
+      </c>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -1651,51 +1605,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>Exploration/Exp1/STG_V2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>89.95</v>
+        <v>79.34</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>92.13</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>91.63</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>91.03</v>
+        <v>81.72</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>83.53</v>
+        <v>69.09</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>90.55</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>76.3</v>
+      </c>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -1712,31 +1656,31 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>80.14</v>
+        <v>96.58</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>84.18000000000001</v>
+        <v>96.94</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>91.76000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>82.11</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>69.65000000000001</v>
+        <v>93.73</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>76.76000000000001</v>
+        <v>96.31</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>4.88</v>
@@ -1766,31 +1710,31 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>92.45</v>
+        <v>89.52</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>97.37</v>
+        <v>92.69</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.11</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>94.84</v>
+        <v>91.08</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>90.19</v>
+        <v>83.62</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>94.64</v>
+        <v>90.61</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>4.88</v>
@@ -1820,31 +1764,31 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>97.02</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>97.20999999999999</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>99.29000000000001</v>
+        <v>91.94</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>97.11</v>
+        <v>82.39</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>94.39</v>
+        <v>70.06</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>96.70999999999999</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>4.88</v>
@@ -1874,31 +1818,31 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>89.59</v>
+        <v>92.69</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>92.84</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>99.12</v>
+        <v>99.59</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>91.19</v>
+        <v>94.78</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>83.81</v>
+        <v>90.08</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>90.73</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>4.88</v>
@@ -1928,31 +1872,31 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>81.23999999999999</v>
+        <v>96.62</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>85.29000000000001</v>
+        <v>96.88</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>92.27</v>
+        <v>99.2</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>83.20999999999999</v>
+        <v>96.75</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>71.25</v>
+        <v>93.7</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>78.2</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>4.88</v>
@@ -1982,31 +1926,31 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>93.09999999999999</v>
+        <v>89.95</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>96.01000000000001</v>
+        <v>92.13</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>99.56999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>94.53</v>
+        <v>91.03</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>89.63</v>
+        <v>83.53</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>94.31</v>
+        <v>90.55</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>4.88</v>
@@ -2036,31 +1980,31 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>97.03</v>
+        <v>80.14</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>97.33</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>99.3</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>97.18000000000001</v>
+        <v>82.11</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>94.51000000000001</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>96.78</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>4.88</v>
@@ -2090,31 +2034,31 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>90.33</v>
+        <v>92.45</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>91.81999999999999</v>
+        <v>97.37</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>91.06999999999999</v>
+        <v>94.84</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>90.19</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>90.59</v>
+        <v>94.64</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>4.88</v>
@@ -2144,31 +2088,31 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>84.41</v>
+        <v>97.02</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>82.55</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>92.12</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>83.47</v>
+        <v>97.11</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>71.63</v>
+        <v>94.39</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>78.29000000000001</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>4.88</v>
@@ -2198,31 +2142,31 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>93.56</v>
+        <v>89.59</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>96.62</v>
+        <v>92.84</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>99.61</v>
+        <v>99.12</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>91.19</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>83.81</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>94.87</v>
+        <v>90.73</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>4.88</v>
@@ -2247,36 +2191,36 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>97.02</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>97.27</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>99.3</v>
+        <v>92.27</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>97.14</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>94.45</v>
+        <v>71.25</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>96.73999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>4.88</v>
@@ -2301,36 +2245,36 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>90.64</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>91.64</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>91.14</v>
+        <v>94.53</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>83.72</v>
+        <v>89.63</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>90.66</v>
+        <v>94.31</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>4.88</v>
@@ -2355,36 +2299,36 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>80.94</v>
+        <v>97.03</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>85.43000000000001</v>
+        <v>97.33</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>92.25</v>
+        <v>99.3</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>83.13</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>71.12</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>96.78</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>4.88</v>
@@ -2409,36 +2353,36 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>93.73999999999999</v>
+        <v>90.33</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>96.67</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>99.62</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>95.18000000000001</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>90.81</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>94.98999999999999</v>
+        <v>90.59</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>4.88</v>
@@ -2463,45 +2407,45 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>97.02</v>
+        <v>84.41</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>97.33</v>
+        <v>82.55</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>99.3</v>
+        <v>92.12</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>97.17</v>
+        <v>83.47</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>94.5</v>
+        <v>71.63</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>96.78</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -2517,45 +2461,45 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>90.22</v>
+        <v>93.56</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>92.22</v>
+        <v>96.62</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>99.11</v>
+        <v>99.61</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>83.83</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>90.73999999999999</v>
+        <v>94.87</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -2576,40 +2520,40 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>80.09999999999999</v>
+        <v>97.02</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>86.05</v>
+        <v>97.27</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>92.23999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>82.97</v>
+        <v>97.14</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>70.89</v>
+        <v>94.45</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>77.95999999999999</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -2630,40 +2574,40 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>93.45999999999999</v>
+        <v>90.64</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>96</v>
+        <v>91.64</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>99.59</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>94.70999999999999</v>
+        <v>91.14</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>89.95</v>
+        <v>83.72</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>94.48999999999999</v>
+        <v>90.66</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -2684,40 +2628,40 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>97.02</v>
+        <v>80.94</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>97.34</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>99.3</v>
+        <v>92.25</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>97.18000000000001</v>
+        <v>83.13</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>94.51000000000001</v>
+        <v>71.12</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>96.78</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -2738,40 +2682,40 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>90.20999999999999</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>92.41</v>
+        <v>96.67</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>99.12</v>
+        <v>99.62</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>91.29000000000001</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>83.98</v>
+        <v>90.81</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>90.83</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -2792,31 +2736,31 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>80.69</v>
+        <v>97.02</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>85.12</v>
+        <v>97.33</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>92.12</v>
+        <v>99.3</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>82.84999999999999</v>
+        <v>97.17</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>70.72</v>
+        <v>94.5</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>77.73999999999999</v>
+        <v>96.78</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>4.881</v>
@@ -2846,31 +2790,31 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>93.8</v>
+        <v>90.22</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>96.18000000000001</v>
+        <v>92.22</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>99.61</v>
+        <v>99.11</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>94.98</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>90.44</v>
+        <v>83.83</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>94.77</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>4.881</v>
@@ -2895,45 +2839,45 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>97.02</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>97.25</v>
+        <v>86.05</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>99.29000000000001</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>97.13</v>
+        <v>82.97</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>94.42</v>
+        <v>70.89</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>96.73</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>4.88</v>
+        <v>4.881</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>4.88</v>
+        <v>4.881</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.6947</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -2949,45 +2893,45 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>90.05</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>92.12</v>
+        <v>96</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.59</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>91.06999999999999</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>89.95</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>4.88</v>
+        <v>4.881</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>4.88</v>
+        <v>4.881</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.6947</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -3003,45 +2947,45 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>81.44</v>
+        <v>97.02</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>84.94</v>
+        <v>97.34</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>92.22</v>
+        <v>99.3</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>83.16</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>71.17</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>96.78</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>4.88</v>
+        <v>4.881</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>4.88</v>
+        <v>4.881</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.6947</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -3057,45 +3001,45 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>93.42</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>96.66</v>
+        <v>92.41</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>99.61</v>
+        <v>99.12</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>95.02</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>90.5</v>
+        <v>83.98</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>94.81</v>
+        <v>90.83</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>4.88</v>
+        <v>4.881</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>4.88</v>
+        <v>4.881</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.6947</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -3111,45 +3055,45 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>97.03</v>
+        <v>80.69</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>97.23999999999999</v>
+        <v>85.12</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>99.29000000000001</v>
+        <v>92.12</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>97.13</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>94.43000000000001</v>
+        <v>70.72</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>96.73</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6947</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -3165,45 +3109,45 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>90.25</v>
+        <v>93.8</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>92.12</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>99.11</v>
+        <v>99.61</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>94.98</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>83.78</v>
+        <v>90.44</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>90.70999999999999</v>
+        <v>94.77</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6947</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -3224,40 +3168,40 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>81.26000000000001</v>
+        <v>97.02</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>85.31</v>
+        <v>97.25</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>92.28</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>83.23999999999999</v>
+        <v>97.13</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>71.29000000000001</v>
+        <v>94.42</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>78.23</v>
+        <v>96.73</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>4.954</v>
+        <v>4.88</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>4.954</v>
+        <v>4.88</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6747</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -3278,40 +3222,40 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>93.11</v>
+        <v>90.05</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>96.78</v>
+        <v>92.12</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>94.91</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>90.31</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>94.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>4.954</v>
+        <v>4.88</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>4.954</v>
+        <v>4.88</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6747</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -3327,45 +3271,45 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>96.97</v>
+        <v>81.44</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>97.08</v>
+        <v>84.94</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>99.27</v>
+        <v>92.22</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>97.02</v>
+        <v>83.16</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>94.22</v>
+        <v>71.17</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>96.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>4.89</v>
+        <v>4.88</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>4.89</v>
+        <v>4.88</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2.717</v>
+        <v>2.6747</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -3381,45 +3325,45 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>90.15000000000001</v>
+        <v>93.42</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>92.33</v>
+        <v>96.66</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>99.12</v>
+        <v>99.61</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>91.23</v>
+        <v>95.02</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>83.87</v>
+        <v>90.5</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>90.76000000000001</v>
+        <v>94.81</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>4.89</v>
+        <v>4.88</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>4.89</v>
+        <v>4.88</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2.717</v>
+        <v>2.6747</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -3435,45 +3379,45 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>81.90000000000001</v>
+        <v>97.03</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>84.53</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>92.2</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>83.19</v>
+        <v>97.13</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>71.22</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>78.11</v>
+        <v>96.73</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>4.89</v>
+        <v>4.954</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>4.89</v>
+        <v>4.954</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2.717</v>
+        <v>2.9767</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -3489,45 +3433,45 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>94.02</v>
+        <v>90.25</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>96.37</v>
+        <v>92.12</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>99.62</v>
+        <v>99.11</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>95.18000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>90.8</v>
+        <v>83.78</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>94.98</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>4.89</v>
+        <v>4.954</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>4.89</v>
+        <v>4.954</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2.717</v>
+        <v>2.9767</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -3543,45 +3487,45 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>96.94</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>97.17</v>
+        <v>85.31</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>99.27</v>
+        <v>92.28</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>97.05</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>94.27</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>96.64</v>
+        <v>78.23</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.9767</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -3597,45 +3541,45 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>90.09</v>
+        <v>93.11</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>92.62</v>
+        <v>96.78</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>99.13</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>91.34</v>
+        <v>94.91</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>84.06</v>
+        <v>90.31</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>90.88</v>
+        <v>94.7</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.9767</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -3656,40 +3600,40 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>81.09999999999999</v>
+        <v>96.97</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>85.65000000000001</v>
+        <v>97.08</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>92.34</v>
+        <v>99.27</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>83.31</v>
+        <v>97.02</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>94.22</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>78.34999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.717</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -3710,40 +3654,40 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>93.8</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>96.38</v>
+        <v>92.33</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>99.61</v>
+        <v>99.12</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>91.23</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>90.61</v>
+        <v>83.87</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>94.87</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.717</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -3764,40 +3708,40 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>97</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>97.33</v>
+        <v>84.53</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>99.3</v>
+        <v>92.2</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>97.17</v>
+        <v>83.19</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>94.48999999999999</v>
+        <v>71.22</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>96.77</v>
+        <v>78.11</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.717</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -3818,40 +3762,40 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>89.63</v>
+        <v>94.02</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>92.70999999999999</v>
+        <v>96.37</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>99.11</v>
+        <v>99.62</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>91.15000000000001</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>83.73</v>
+        <v>90.8</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>90.68000000000001</v>
+        <v>94.98</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.717</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -3872,31 +3816,31 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>80.41</v>
+        <v>96.94</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>85.06999999999999</v>
+        <v>97.17</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>92.05</v>
+        <v>99.27</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>82.68000000000001</v>
+        <v>97.05</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>70.47</v>
+        <v>94.27</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>77.53</v>
+        <v>96.64</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>4.88</v>
@@ -3926,31 +3870,31 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>93.44</v>
+        <v>90.09</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>96.28</v>
+        <v>92.62</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.13</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>94.84</v>
+        <v>91.34</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>90.19</v>
+        <v>84.06</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>94.63</v>
+        <v>90.88</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>4.88</v>
@@ -3970,341 +3914,341 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>91.09</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>92.8</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>99.19</v>
+        <v>92.34</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>91.94</v>
+        <v>83.31</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>85.08</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>20.661</v>
+        <v>4.88</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>26.3183</v>
+        <v>2.6747</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>80.3</v>
+        <v>93.8</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>84.81</v>
+        <v>96.38</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>99.61</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>82.5</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>90.61</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>94.87</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>20.661</v>
+        <v>4.88</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>26.3183</v>
+        <v>2.6747</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>97</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>92.75</v>
+        <v>97.33</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>91.86</v>
+        <v>97.17</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>84.94</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>96.77</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>20.661</v>
+        <v>4.88</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>26.2593</v>
+        <v>2.6747</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>80.55</v>
+        <v>89.63</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>84.23</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>91.86</v>
+        <v>99.11</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>82.34999999999999</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>70</v>
+        <v>83.73</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>77.06</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>20.661</v>
+        <v>4.88</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>26.2593</v>
+        <v>2.6747</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>91.38</v>
+        <v>80.41</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>92.3</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>99.17</v>
+        <v>92.05</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>91.84</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>84.91</v>
+        <v>70.47</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>77.53</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>15.125</v>
+        <v>4.88</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>26.1484</v>
+        <v>2.6747</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>93.44</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>86.03</v>
+        <v>96.28</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>94.84</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>69.55</v>
+        <v>90.19</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>76.83</v>
+        <v>94.63</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>11.754</v>
+        <v>4.88</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>15.125</v>
+        <v>4.88</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>26.1484</v>
+        <v>2.6747</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run8</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>CTRL_R8</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4313,52 +4257,52 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>91.13</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.11</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>91.88</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>84.98</v>
+        <v>83.84</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>91.45</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>11.754</v>
+        <v>31.026</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>15.125</v>
+        <v>31.026</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>26.0894</v>
+        <v>13.6715</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_vmamba_str</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run8</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>CTRL_R8</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4367,35 +4311,35 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>79.66</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>85.05</v>
+        <v>84.22</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>92.36</v>
+        <v>91.69</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>83.52</v>
+        <v>81.88</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>71.7</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>78.55</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>11.754</v>
+        <v>31.026</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>15.125</v>
+        <v>31.026</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>26.0894</v>
+        <v>13.6715</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_vmamba_str</t>
         </is>
       </c>
     </row>
@@ -4407,120 +4351,120 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>91.09</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>84.28</v>
+        <v>92.8</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>91.7</v>
+        <v>99.19</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>81.92</v>
+        <v>91.94</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>69.37</v>
+        <v>85.08</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>26.0894</v>
+        <v>26.3183</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>93.13</v>
+        <v>80.3</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>95.16</v>
+        <v>84.81</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>94.13</v>
+        <v>82.5</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>88.91</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0.62</v>
+        <v>20.661</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.3183</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4529,52 +4473,52 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>86.37</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>89.25</v>
+        <v>92.75</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>98.78</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>91.86</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>84.94</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>87.14</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0.62</v>
+        <v>20.661</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.2593</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4583,160 +4527,160 @@
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>80.55</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>84.5</v>
+        <v>84.23</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>91.81</v>
+        <v>91.86</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>70</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>76.84</v>
+        <v>77.06</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0.62</v>
+        <v>20.661</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.2593</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>90.16</v>
+        <v>91.38</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>93.97</v>
+        <v>92.3</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>99.38</v>
+        <v>99.17</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>92.02</v>
+        <v>91.84</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>85.23</v>
+        <v>84.91</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>91.7</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0.62</v>
+        <v>15.125</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.1484</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>94.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>96.13</v>
+        <v>86.03</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>98.88</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>95.41</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>91.22</v>
+        <v>69.55</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>94.77</v>
+        <v>76.83</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>3.455</v>
+        <v>11.754</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1.478</v>
+        <v>15.125</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>3.5459</v>
+        <v>26.1484</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4745,52 +4689,52 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>88.42</v>
+        <v>91.13</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>91.97</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>99.02</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>90.16</v>
+        <v>91.88</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>82.08</v>
+        <v>84.98</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>89.64</v>
+        <v>91.45</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>3.455</v>
+        <v>11.754</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1.478</v>
+        <v>15.125</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3.5459</v>
+        <v>26.0894</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4799,214 +4743,214 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>78.73</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>84.98</v>
+        <v>85.05</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>91.7</v>
+        <v>92.36</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>83.52</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>69.11</v>
+        <v>71.7</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>76.38</v>
+        <v>78.55</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>3.455</v>
+        <v>11.754</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1.478</v>
+        <v>15.125</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3.5459</v>
+        <v>26.0894</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>A4_DETAIL_FROZEN</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>91.64</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>84.28</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>99.47</v>
+        <v>91.7</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>93.2</v>
+        <v>81.92</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>87.27</v>
+        <v>69.37</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>3.455</v>
+        <v>11.754</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1.478</v>
+        <v>15.125</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3.5459</v>
+        <v>26.0894</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>82.42</v>
+        <v>93.13</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>83.87</v>
+        <v>95.16</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>92.12</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>83.14</v>
+        <v>94.13</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>71.14</v>
+        <v>88.91</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>15.125</v>
+        <v>0.62</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>86.37</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>89.25</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>91.94</v>
+        <v>98.78</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>82.77</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>70.61</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>87.14</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>8.195</v>
+        <v>2.596</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>15.125</v>
+        <v>0.62</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>24.1021</v>
+        <v>2.2136</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5015,336 +4959,352 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>79.94</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>91.89</v>
+        <v>91.81</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>82.3</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>69.92</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>76.84</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>5.492</v>
+        <v>2.596</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>3.515</v>
+        <v>0.62</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>10.7311</v>
+        <v>2.2136</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>80.87</v>
+        <v>90.16</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>83.81</v>
+        <v>93.97</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>91.81</v>
+        <v>99.38</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>92.02</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>69.95</v>
+        <v>85.23</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>5.533</v>
+        <v>2.596</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>3.556</v>
+        <v>0.62</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>10.9824</v>
+        <v>2.2136</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>79.78</v>
+        <v>94.7</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>84.39</v>
+        <v>96.13</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>91.75</v>
+        <v>98.88</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>82.02</v>
+        <v>95.41</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>69.52</v>
+        <v>91.22</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>94.77</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>5.491</v>
+        <v>3.455</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>3.514</v>
+        <v>1.478</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>11.5239</v>
+        <v>3.5459</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>97.72</v>
+        <v>88.42</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>97.78</v>
+        <v>91.97</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>99.44</v>
+        <v>99.02</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>97.75</v>
+        <v>90.16</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>82.08</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>89.64</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>20.661</v>
+        <v>1.478</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>78.73</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>92.33</v>
+        <v>84.98</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>91.95</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.11</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>91.52</v>
+        <v>76.38</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>20.661</v>
+        <v>1.478</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>80.77</v>
+        <v>91.64</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>84.27</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>91.91</v>
+        <v>99.47</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>82.48</v>
+        <v>93.2</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>70.19</v>
+        <v>87.27</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>77.23</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>20.661</v>
+        <v>1.478</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>R4_0_A0_FULL12_FROZEN</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>93.62</v>
+        <v>82.42</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>96.09</v>
+        <v>83.87</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>92.12</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>94.84</v>
+        <v>83.14</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>90.18000000000001</v>
+        <v>71.14</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>94.63</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>20.661</v>
+        <v>15.125</v>
       </c>
       <c r="M91" s="2" t="n">
         <v>26.3246</v>
@@ -5355,8 +5315,424 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>R4_1_VIT4_OLDHEAD</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>8.195</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>24.1021</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>10.7311</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>83.81</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>10.9824</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>3.514</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>11.5239</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N91"/>
+  <autoFilter ref="A1:N99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -1381,7 +1381,6 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>Exploration/Exp1/STG_INJ</t>
@@ -1425,7 +1424,6 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>Exploration/Exp1/STG_INJ</t>
@@ -1469,7 +1467,6 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>Exploration/Exp1/STG_SUP</t>
@@ -1515,7 +1512,6 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>Exploration/Exp1/STG_SUP</t>
@@ -1561,7 +1557,6 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>Exploration/Exp1/STG_V2</t>
@@ -1605,7 +1600,6 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>Exploration/Exp1/STG_V2</t>
@@ -5542,7 +5536,6 @@
           <t>Run1</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>CDD-CD-256</t>
@@ -5592,7 +5585,6 @@
           <t>Run1</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>LEVIR-CD-256</t>
@@ -5642,7 +5634,6 @@
           <t>Run1</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>SYSU-CD-256</t>
@@ -5692,7 +5683,6 @@
           <t>Run1</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>

--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N99"/>
+  <dimension ref="A1:N102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1381,6 +1381,7 @@
           <t>CASA-TViM</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>Exploration/Exp1/STG_INJ</t>
@@ -1424,6 +1425,7 @@
           <t>CASA-TViM</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>Exploration/Exp1/STG_INJ</t>
@@ -1467,6 +1469,7 @@
           <t>CASA-TViM</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>Exploration/Exp1/STG_SUP</t>
@@ -1512,6 +1515,7 @@
           <t>CASA-TViM</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>Exploration/Exp1/STG_SUP</t>
@@ -1557,6 +1561,7 @@
           <t>CASA-TViM</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>Exploration/Exp1/STG_V2</t>
@@ -1600,6 +1605,7 @@
           <t>CASA-TViM</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>Exploration/Exp1/STG_V2</t>
@@ -4340,162 +4346,162 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run9</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>S0_CTRL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>91.09</v>
+        <v>97.77</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>92.8</v>
+        <v>97.77</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>99.19</v>
+        <v>99.45</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>91.94</v>
+        <v>97.77</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>85.08</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>11.754</v>
+        <v>31.977</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>20.661</v>
+        <v>31.977</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>26.3183</v>
+        <v>14.6841</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run9</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>S0_CTRL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>80.3</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>84.81</v>
+        <v>92.53</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>99.11</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>82.5</v>
+        <v>91.14</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>83.72</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>90.67</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>11.754</v>
+        <v>31.977</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>20.661</v>
+        <v>31.977</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>26.3183</v>
+        <v>14.6841</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run9</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>S1_HSAM</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>97.66</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>92.75</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.42</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>91.86</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>84.94</v>
+        <v>95.42</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>11.754</v>
+        <v>31.977</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>20.661</v>
+        <v>31.977</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>26.2593</v>
+        <v>14.769</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
@@ -4512,31 +4518,31 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>80.55</v>
+        <v>91.09</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>84.23</v>
+        <v>92.8</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>91.86</v>
+        <v>99.19</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>82.34999999999999</v>
+        <v>91.94</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>70</v>
+        <v>85.08</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>77.06</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>11.754</v>
@@ -4545,11 +4551,11 @@
         <v>20.661</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>26.2593</v>
+        <v>26.3183</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -4561,45 +4567,45 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>91.38</v>
+        <v>80.3</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>92.3</v>
+        <v>84.81</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>99.17</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>91.84</v>
+        <v>82.5</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>84.91</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>26.1484</v>
+        <v>26.3183</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
@@ -4615,49 +4621,49 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>86.03</v>
+        <v>92.75</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.86</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>69.55</v>
+        <v>84.94</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>76.83</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>26.1484</v>
+        <v>26.2593</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -4669,45 +4675,45 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>91.13</v>
+        <v>80.55</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>84.23</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.86</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>91.88</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>84.98</v>
+        <v>70</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>91.45</v>
+        <v>77.06</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>26.0894</v>
+        <v>26.2593</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -4728,31 +4734,31 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.38</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>85.05</v>
+        <v>92.3</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>92.36</v>
+        <v>99.17</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>83.52</v>
+        <v>91.84</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>71.7</v>
+        <v>84.91</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>78.55</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>11.754</v>
@@ -4761,11 +4767,11 @@
         <v>15.125</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>26.0894</v>
+        <v>26.1484</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -4777,12 +4783,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4791,22 +4797,22 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>84.28</v>
+        <v>86.03</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>91.7</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>81.92</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>69.37</v>
+        <v>69.55</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>76.83</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>11.754</v>
@@ -4815,136 +4821,136 @@
         <v>15.125</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>26.0894</v>
+        <v>26.1484</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>93.13</v>
+        <v>91.13</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>95.16</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>94.13</v>
+        <v>91.88</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>88.91</v>
+        <v>84.98</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>91.45</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0.62</v>
+        <v>15.125</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.0894</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>86.37</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>89.25</v>
+        <v>85.05</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>98.78</v>
+        <v>92.36</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>83.52</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>87.14</v>
+        <v>78.55</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0.62</v>
+        <v>15.125</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.0894</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A4_DETAIL_FROZEN</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4953,35 +4959,35 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>84.5</v>
+        <v>84.28</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>91.81</v>
+        <v>91.7</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>81.92</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>69.37</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>76.84</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0.62</v>
+        <v>15.125</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.0894</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -5003,26 +5009,26 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>90.16</v>
+        <v>93.13</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>93.97</v>
+        <v>95.16</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>99.38</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>92.02</v>
+        <v>94.13</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>85.23</v>
+        <v>88.91</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>91.7</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>2.596</v>
@@ -5052,40 +5058,40 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>94.7</v>
+        <v>86.37</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>96.13</v>
+        <v>89.25</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>98.88</v>
+        <v>98.78</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>95.41</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>91.22</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>94.77</v>
+        <v>87.14</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -5106,40 +5112,40 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>88.42</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>91.97</v>
+        <v>84.5</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>99.02</v>
+        <v>91.81</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>90.16</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>82.08</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>89.64</v>
+        <v>76.84</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -5160,40 +5166,40 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>78.73</v>
+        <v>90.16</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>84.98</v>
+        <v>93.97</v>
       </c>
       <c r="G89" s="2" t="n">
+        <v>99.38</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>92.02</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>85.23</v>
+      </c>
+      <c r="J89" s="2" t="n">
         <v>91.7</v>
       </c>
-      <c r="H89" s="2" t="n">
-        <v>81.73999999999999</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>69.11</v>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>76.38</v>
-      </c>
       <c r="K89" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -5219,26 +5225,26 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>91.64</v>
+        <v>94.7</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>96.13</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>99.47</v>
+        <v>98.88</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>93.2</v>
+        <v>95.41</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>87.27</v>
+        <v>91.22</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>94.77</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>3.455</v>
@@ -5258,71 +5264,71 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>82.42</v>
+        <v>88.42</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>83.87</v>
+        <v>91.97</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>92.12</v>
+        <v>99.02</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>83.14</v>
+        <v>90.16</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>71.14</v>
+        <v>82.08</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>89.64</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>15.125</v>
+        <v>1.478</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5331,89 +5337,89 @@
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>78.73</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>84.98</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>91.94</v>
+        <v>91.7</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>82.77</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>70.61</v>
+        <v>69.11</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>76.38</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>8.195</v>
+        <v>3.455</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>15.125</v>
+        <v>1.478</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>24.1021</v>
+        <v>3.5459</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>79.94</v>
+        <v>91.64</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>91.89</v>
+        <v>99.47</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>82.3</v>
+        <v>93.2</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>69.92</v>
+        <v>87.27</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>5.492</v>
+        <v>3.455</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>3.515</v>
+        <v>1.478</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>10.7311</v>
+        <v>3.5459</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5436,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>R4_0_A0_FULL12_FROZEN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5439,31 +5445,31 @@
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>80.87</v>
+        <v>82.42</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>83.81</v>
+        <v>83.87</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>91.81</v>
+        <v>92.12</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>83.14</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>69.95</v>
+        <v>71.14</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>5.533</v>
+        <v>11.754</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>3.556</v>
+        <v>15.125</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>10.9824</v>
+        <v>26.3246</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
@@ -5484,7 +5490,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>R4_1_VIT4_OLDHEAD</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5493,31 +5499,31 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>79.78</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>84.39</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>91.75</v>
+        <v>91.94</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>82.02</v>
+        <v>82.77</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>69.52</v>
+        <v>70.61</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>5.491</v>
+        <v>8.195</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>3.514</v>
+        <v>15.125</v>
       </c>
       <c r="M95" s="2" t="n">
-        <v>11.5239</v>
+        <v>24.1021</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -5528,45 +5534,50 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>97.72</v>
+        <v>79.94</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>97.78</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>99.44</v>
+        <v>91.89</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>97.75</v>
+        <v>82.3</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>69.92</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>11.754</v>
+        <v>5.492</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>20.661</v>
+        <v>3.515</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>26.3246</v>
+        <v>10.7311</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -5577,45 +5588,50 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>80.87</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>92.33</v>
+        <v>83.81</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.81</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>91.95</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.95</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>91.52</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>11.754</v>
+        <v>5.533</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>20.661</v>
+        <v>3.556</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>26.3246</v>
+        <v>10.9824</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -5626,12 +5642,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5640,31 +5661,31 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>80.77</v>
+        <v>79.78</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>84.27</v>
+        <v>84.39</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>91.91</v>
+        <v>91.75</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>82.48</v>
+        <v>82.02</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>70.19</v>
+        <v>69.52</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>77.23</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>11.754</v>
+        <v>5.491</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>20.661</v>
+        <v>3.514</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>26.3246</v>
+        <v>11.5239</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -5683,28 +5704,29 @@
           <t>Run1</t>
         </is>
       </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>93.62</v>
+        <v>97.72</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>96.09</v>
+        <v>97.78</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.44</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>94.84</v>
+        <v>97.75</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>90.18000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>94.63</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>11.754</v>
@@ -5721,8 +5743,158 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N99"/>
+  <autoFilter ref="A1:N102"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N102"/>
+  <dimension ref="A1:N103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4508,7 +4508,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4518,44 +4518,42 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>91.09</v>
+        <v>80.27</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>92.8</v>
+        <v>85.19</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>99.19</v>
+        <v>92.06</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>91.94</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>85.08</v>
+        <v>70.44</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>11.754</v>
+        <v>3.016737</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M77" s="2" t="n">
-        <v>26.3183</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M77" s="2" t="n"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
@@ -4577,26 +4575,26 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>80.3</v>
+        <v>91.09</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>84.81</v>
+        <v>92.8</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>99.19</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>82.5</v>
+        <v>91.94</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>85.08</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>11.754</v>
@@ -4626,31 +4624,31 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>92.75</v>
+        <v>84.81</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>91.86</v>
+        <v>82.5</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>84.94</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>11.754</v>
@@ -4659,11 +4657,11 @@
         <v>20.661</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>26.2593</v>
+        <v>26.3183</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -4685,26 +4683,26 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>80.55</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>84.23</v>
+        <v>92.75</v>
       </c>
       <c r="G80" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H80" s="2" t="n">
         <v>91.86</v>
       </c>
-      <c r="H80" s="2" t="n">
-        <v>82.34999999999999</v>
-      </c>
       <c r="I80" s="2" t="n">
-        <v>70</v>
+        <v>84.94</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>77.06</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>11.754</v>
@@ -4729,49 +4727,49 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>91.38</v>
+        <v>80.55</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>92.3</v>
+        <v>84.23</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>99.17</v>
+        <v>91.86</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>91.84</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>84.91</v>
+        <v>70</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>77.06</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>26.1484</v>
+        <v>26.2593</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -4793,26 +4791,26 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>91.38</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>86.03</v>
+        <v>92.3</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>99.17</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.84</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>69.55</v>
+        <v>84.91</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>76.83</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>11.754</v>
@@ -4842,31 +4840,31 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>91.13</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>86.03</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>91.88</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>84.98</v>
+        <v>69.55</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>91.45</v>
+        <v>76.83</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>11.754</v>
@@ -4875,11 +4873,11 @@
         <v>15.125</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>26.0894</v>
+        <v>26.1484</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -4901,26 +4899,26 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>85.05</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>92.36</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>83.52</v>
+        <v>91.88</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>71.7</v>
+        <v>84.98</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>78.55</v>
+        <v>91.45</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>11.754</v>
@@ -4945,12 +4943,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4959,22 +4957,22 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>84.28</v>
+        <v>85.05</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>91.7</v>
+        <v>92.36</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>81.92</v>
+        <v>83.52</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>69.37</v>
+        <v>71.7</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>78.55</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>11.754</v>
@@ -4994,54 +4992,54 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A4_DETAIL_FROZEN</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>93.13</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>95.16</v>
+        <v>84.28</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>94.13</v>
+        <v>81.92</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>88.91</v>
+        <v>69.37</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0.62</v>
+        <v>15.125</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.0894</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -5063,26 +5061,26 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>86.37</v>
+        <v>93.13</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>89.25</v>
+        <v>95.16</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>98.78</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>94.13</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>88.91</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>87.14</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>2.596</v>
@@ -5117,26 +5115,26 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>86.37</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>84.5</v>
+        <v>89.25</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>91.81</v>
+        <v>98.78</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>76.84</v>
+        <v>87.14</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>2.596</v>
@@ -5171,26 +5169,26 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>90.16</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>93.97</v>
+        <v>84.5</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>99.38</v>
+        <v>91.81</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>92.02</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>85.23</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>91.7</v>
+        <v>76.84</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>2.596</v>
@@ -5220,40 +5218,40 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>94.7</v>
+        <v>90.16</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>96.13</v>
+        <v>93.97</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>98.88</v>
+        <v>99.38</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>95.41</v>
+        <v>92.02</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>91.22</v>
+        <v>85.23</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>94.77</v>
+        <v>91.7</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -5279,26 +5277,26 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>88.42</v>
+        <v>94.7</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>91.97</v>
+        <v>96.13</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>99.02</v>
+        <v>98.88</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>90.16</v>
+        <v>95.41</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>82.08</v>
+        <v>91.22</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>89.64</v>
+        <v>94.77</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>3.455</v>
@@ -5333,26 +5331,26 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>78.73</v>
+        <v>88.42</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>84.98</v>
+        <v>91.97</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>91.7</v>
+        <v>99.02</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>90.16</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>69.11</v>
+        <v>82.08</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>76.38</v>
+        <v>89.64</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>3.455</v>
@@ -5387,26 +5385,26 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>91.64</v>
+        <v>78.73</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>84.98</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>99.47</v>
+        <v>91.7</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>93.2</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>87.27</v>
+        <v>69.11</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>76.38</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>3.455</v>
@@ -5426,54 +5424,54 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>82.42</v>
+        <v>91.64</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>83.87</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>92.12</v>
+        <v>99.47</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>83.14</v>
+        <v>93.2</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>71.14</v>
+        <v>87.27</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>15.125</v>
+        <v>1.478</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5488,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>R4_0_A0_FULL12_FROZEN</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5499,31 +5497,31 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>82.42</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>83.87</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>91.94</v>
+        <v>92.12</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>82.77</v>
+        <v>83.14</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>70.61</v>
+        <v>71.14</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>8.195</v>
+        <v>11.754</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>15.125</v>
       </c>
       <c r="M95" s="2" t="n">
-        <v>24.1021</v>
+        <v>26.3246</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -5544,7 +5542,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>R4_1_VIT4_OLDHEAD</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5553,31 +5551,31 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>79.94</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>91.89</v>
+        <v>91.94</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>82.3</v>
+        <v>82.77</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>69.92</v>
+        <v>70.61</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>5.492</v>
+        <v>8.195</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>3.515</v>
+        <v>15.125</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>10.7311</v>
+        <v>24.1021</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -5598,7 +5596,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5607,31 +5605,31 @@
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>80.87</v>
+        <v>79.94</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>83.81</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>91.81</v>
+        <v>91.89</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>69.95</v>
+        <v>69.92</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>5.533</v>
+        <v>5.492</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>3.556</v>
+        <v>3.515</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>10.9824</v>
+        <v>10.7311</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -5652,7 +5650,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5661,31 +5659,31 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>79.78</v>
+        <v>80.87</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>84.39</v>
+        <v>83.81</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>91.75</v>
+        <v>91.81</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>82.02</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>69.52</v>
+        <v>69.95</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>5.491</v>
+        <v>5.533</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>3.514</v>
+        <v>3.556</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>11.5239</v>
+        <v>10.9824</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -5696,46 +5694,50 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>97.72</v>
+        <v>79.78</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>97.78</v>
+        <v>84.39</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>99.44</v>
+        <v>91.75</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>97.75</v>
+        <v>82.02</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>69.52</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>11.754</v>
+        <v>5.491</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>20.661</v>
+        <v>3.514</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>26.3246</v>
+        <v>11.5239</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -5757,26 +5759,26 @@
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>97.72</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>92.33</v>
+        <v>97.78</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.44</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>91.95</v>
+        <v>97.75</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>91.52</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>11.754</v>
@@ -5807,26 +5809,26 @@
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>80.77</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>84.27</v>
+        <v>92.33</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>91.91</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>82.48</v>
+        <v>91.95</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>70.19</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>77.23</v>
+        <v>91.52</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>11.754</v>
@@ -5857,26 +5859,26 @@
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>93.62</v>
+        <v>80.77</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>96.09</v>
+        <v>84.27</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>94.84</v>
+        <v>82.48</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>90.18000000000001</v>
+        <v>70.19</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>94.63</v>
+        <v>77.23</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>11.754</v>
@@ -5893,8 +5895,58 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N102"/>
+  <autoFilter ref="A1:N103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N103"/>
+  <dimension ref="A1:N104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4560,54 +4560,52 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>91.09</v>
+        <v>78.67</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>92.8</v>
+        <v>85.08</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>99.19</v>
+        <v>91.72</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>91.94</v>
+        <v>81.75</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>85.08</v>
+        <v>69.13</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M78" s="2" t="n">
-        <v>26.3183</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M78" s="2" t="n"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
@@ -4629,26 +4627,26 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>80.3</v>
+        <v>91.09</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>84.81</v>
+        <v>92.8</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>99.19</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>82.5</v>
+        <v>91.94</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>85.08</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>11.754</v>
@@ -4678,31 +4676,31 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>92.75</v>
+        <v>84.81</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>91.86</v>
+        <v>82.5</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>84.94</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>11.754</v>
@@ -4711,11 +4709,11 @@
         <v>20.661</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>26.2593</v>
+        <v>26.3183</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -4737,26 +4735,26 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>80.55</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>84.23</v>
+        <v>92.75</v>
       </c>
       <c r="G81" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H81" s="2" t="n">
         <v>91.86</v>
       </c>
-      <c r="H81" s="2" t="n">
-        <v>82.34999999999999</v>
-      </c>
       <c r="I81" s="2" t="n">
-        <v>70</v>
+        <v>84.94</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>77.06</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>11.754</v>
@@ -4781,49 +4779,49 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>91.38</v>
+        <v>80.55</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>92.3</v>
+        <v>84.23</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>99.17</v>
+        <v>91.86</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>91.84</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>84.91</v>
+        <v>70</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>77.06</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>26.1484</v>
+        <v>26.2593</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -4845,26 +4843,26 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>91.38</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>86.03</v>
+        <v>92.3</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>99.17</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.84</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>69.55</v>
+        <v>84.91</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>76.83</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>11.754</v>
@@ -4894,31 +4892,31 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>91.13</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>86.03</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>91.88</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>84.98</v>
+        <v>69.55</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>91.45</v>
+        <v>76.83</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>11.754</v>
@@ -4927,11 +4925,11 @@
         <v>15.125</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>26.0894</v>
+        <v>26.1484</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -4953,26 +4951,26 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>85.05</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>92.36</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>83.52</v>
+        <v>91.88</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>71.7</v>
+        <v>84.98</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>78.55</v>
+        <v>91.45</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>11.754</v>
@@ -4997,12 +4995,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5011,22 +5009,22 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>84.28</v>
+        <v>85.05</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>91.7</v>
+        <v>92.36</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>81.92</v>
+        <v>83.52</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>69.37</v>
+        <v>71.7</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>78.55</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>11.754</v>
@@ -5046,54 +5044,54 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A4_DETAIL_FROZEN</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>93.13</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>95.16</v>
+        <v>84.28</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>94.13</v>
+        <v>81.92</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>88.91</v>
+        <v>69.37</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>0.62</v>
+        <v>15.125</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.0894</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -5115,26 +5113,26 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>86.37</v>
+        <v>93.13</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>89.25</v>
+        <v>95.16</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>98.78</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>94.13</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>88.91</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>87.14</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>2.596</v>
@@ -5169,26 +5167,26 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>86.37</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>84.5</v>
+        <v>89.25</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>91.81</v>
+        <v>98.78</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>76.84</v>
+        <v>87.14</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>2.596</v>
@@ -5223,26 +5221,26 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>90.16</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>93.97</v>
+        <v>84.5</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>99.38</v>
+        <v>91.81</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>92.02</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>85.23</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>91.7</v>
+        <v>76.84</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>2.596</v>
@@ -5272,40 +5270,40 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>94.7</v>
+        <v>90.16</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>96.13</v>
+        <v>93.97</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>98.88</v>
+        <v>99.38</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>95.41</v>
+        <v>92.02</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>91.22</v>
+        <v>85.23</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>94.77</v>
+        <v>91.7</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -5331,26 +5329,26 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>88.42</v>
+        <v>94.7</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>91.97</v>
+        <v>96.13</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>99.02</v>
+        <v>98.88</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>90.16</v>
+        <v>95.41</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>82.08</v>
+        <v>91.22</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>89.64</v>
+        <v>94.77</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>3.455</v>
@@ -5385,26 +5383,26 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>78.73</v>
+        <v>88.42</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>84.98</v>
+        <v>91.97</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>91.7</v>
+        <v>99.02</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>90.16</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>69.11</v>
+        <v>82.08</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>76.38</v>
+        <v>89.64</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>3.455</v>
@@ -5439,26 +5437,26 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>91.64</v>
+        <v>78.73</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>84.98</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>99.47</v>
+        <v>91.7</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>93.2</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>87.27</v>
+        <v>69.11</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>76.38</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>3.455</v>
@@ -5478,54 +5476,54 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>82.42</v>
+        <v>91.64</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>83.87</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>92.12</v>
+        <v>99.47</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>83.14</v>
+        <v>93.2</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>71.14</v>
+        <v>87.27</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>15.125</v>
+        <v>1.478</v>
       </c>
       <c r="M95" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5540,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>R4_0_A0_FULL12_FROZEN</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5551,31 +5549,31 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>82.42</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>83.87</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>91.94</v>
+        <v>92.12</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>82.77</v>
+        <v>83.14</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>70.61</v>
+        <v>71.14</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>8.195</v>
+        <v>11.754</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>15.125</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>24.1021</v>
+        <v>26.3246</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -5596,7 +5594,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>R4_1_VIT4_OLDHEAD</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5605,31 +5603,31 @@
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>79.94</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>91.89</v>
+        <v>91.94</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>82.3</v>
+        <v>82.77</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>69.92</v>
+        <v>70.61</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>5.492</v>
+        <v>8.195</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>3.515</v>
+        <v>15.125</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>10.7311</v>
+        <v>24.1021</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -5650,7 +5648,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5659,31 +5657,31 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>80.87</v>
+        <v>79.94</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>83.81</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>91.81</v>
+        <v>91.89</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>69.95</v>
+        <v>69.92</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>5.533</v>
+        <v>5.492</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>3.556</v>
+        <v>3.515</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>10.9824</v>
+        <v>10.7311</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -5704,7 +5702,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5713,31 +5711,31 @@
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>79.78</v>
+        <v>80.87</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>84.39</v>
+        <v>83.81</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>91.75</v>
+        <v>91.81</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>82.02</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>69.52</v>
+        <v>69.95</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>5.491</v>
+        <v>5.533</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>3.514</v>
+        <v>3.556</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>11.5239</v>
+        <v>10.9824</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -5748,46 +5746,50 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>97.72</v>
+        <v>79.78</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>97.78</v>
+        <v>84.39</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>99.44</v>
+        <v>91.75</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>97.75</v>
+        <v>82.02</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>69.52</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>11.754</v>
+        <v>5.491</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>20.661</v>
+        <v>3.514</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>26.3246</v>
+        <v>11.5239</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -5809,26 +5811,26 @@
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>97.72</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>92.33</v>
+        <v>97.78</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.44</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>91.95</v>
+        <v>97.75</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>91.52</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>11.754</v>
@@ -5859,26 +5861,26 @@
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>80.77</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>84.27</v>
+        <v>92.33</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>91.91</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>82.48</v>
+        <v>91.95</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>70.19</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>77.23</v>
+        <v>91.52</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>11.754</v>
@@ -5909,26 +5911,26 @@
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>93.62</v>
+        <v>80.77</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>96.09</v>
+        <v>84.27</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>94.84</v>
+        <v>82.48</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>90.18000000000001</v>
+        <v>70.19</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>94.63</v>
+        <v>77.23</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>11.754</v>
@@ -5945,8 +5947,58 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N103"/>
+  <autoFilter ref="A1:N104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N104"/>
+  <dimension ref="A1:N105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4612,54 +4612,52 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>91.09</v>
+        <v>82.83</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>92.8</v>
+        <v>82.86</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>99.19</v>
+        <v>91.91</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>91.94</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>85.08</v>
+        <v>70.72</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M79" s="2" t="n">
-        <v>26.3183</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M79" s="2" t="n"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
@@ -4681,26 +4679,26 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>80.3</v>
+        <v>91.09</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>84.81</v>
+        <v>92.8</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>99.19</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>82.5</v>
+        <v>91.94</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>85.08</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>11.754</v>
@@ -4730,31 +4728,31 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>92.75</v>
+        <v>84.81</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>91.86</v>
+        <v>82.5</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>84.94</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>11.754</v>
@@ -4763,11 +4761,11 @@
         <v>20.661</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>26.2593</v>
+        <v>26.3183</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -4789,26 +4787,26 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>80.55</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>84.23</v>
+        <v>92.75</v>
       </c>
       <c r="G82" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H82" s="2" t="n">
         <v>91.86</v>
       </c>
-      <c r="H82" s="2" t="n">
-        <v>82.34999999999999</v>
-      </c>
       <c r="I82" s="2" t="n">
-        <v>70</v>
+        <v>84.94</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>77.06</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>11.754</v>
@@ -4833,49 +4831,49 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>91.38</v>
+        <v>80.55</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>92.3</v>
+        <v>84.23</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>99.17</v>
+        <v>91.86</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>91.84</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>84.91</v>
+        <v>70</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>77.06</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>26.1484</v>
+        <v>26.2593</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -4897,26 +4895,26 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>91.38</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>86.03</v>
+        <v>92.3</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>99.17</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.84</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>69.55</v>
+        <v>84.91</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>76.83</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>11.754</v>
@@ -4946,31 +4944,31 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>91.13</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>86.03</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>91.88</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>84.98</v>
+        <v>69.55</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>91.45</v>
+        <v>76.83</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>11.754</v>
@@ -4979,11 +4977,11 @@
         <v>15.125</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>26.0894</v>
+        <v>26.1484</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -5005,26 +5003,26 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>85.05</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>92.36</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>83.52</v>
+        <v>91.88</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>71.7</v>
+        <v>84.98</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>78.55</v>
+        <v>91.45</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>11.754</v>
@@ -5049,12 +5047,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5063,22 +5061,22 @@
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>84.28</v>
+        <v>85.05</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>91.7</v>
+        <v>92.36</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>81.92</v>
+        <v>83.52</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>69.37</v>
+        <v>71.7</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>78.55</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>11.754</v>
@@ -5098,54 +5096,54 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A4_DETAIL_FROZEN</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>93.13</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>95.16</v>
+        <v>84.28</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>94.13</v>
+        <v>81.92</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>88.91</v>
+        <v>69.37</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0.62</v>
+        <v>15.125</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.0894</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -5167,26 +5165,26 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>86.37</v>
+        <v>93.13</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>89.25</v>
+        <v>95.16</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>98.78</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>94.13</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>88.91</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>87.14</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>2.596</v>
@@ -5221,26 +5219,26 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>86.37</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>84.5</v>
+        <v>89.25</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>91.81</v>
+        <v>98.78</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>76.84</v>
+        <v>87.14</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>2.596</v>
@@ -5275,26 +5273,26 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>90.16</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>93.97</v>
+        <v>84.5</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>99.38</v>
+        <v>91.81</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>92.02</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>85.23</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>91.7</v>
+        <v>76.84</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>2.596</v>
@@ -5324,40 +5322,40 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>94.7</v>
+        <v>90.16</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>96.13</v>
+        <v>93.97</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>98.88</v>
+        <v>99.38</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>95.41</v>
+        <v>92.02</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>91.22</v>
+        <v>85.23</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>94.77</v>
+        <v>91.7</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -5383,26 +5381,26 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>88.42</v>
+        <v>94.7</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>91.97</v>
+        <v>96.13</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>99.02</v>
+        <v>98.88</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>90.16</v>
+        <v>95.41</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>82.08</v>
+        <v>91.22</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>89.64</v>
+        <v>94.77</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>3.455</v>
@@ -5437,26 +5435,26 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>78.73</v>
+        <v>88.42</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>84.98</v>
+        <v>91.97</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>91.7</v>
+        <v>99.02</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>90.16</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>69.11</v>
+        <v>82.08</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>76.38</v>
+        <v>89.64</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>3.455</v>
@@ -5491,26 +5489,26 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>91.64</v>
+        <v>78.73</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>84.98</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>99.47</v>
+        <v>91.7</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>93.2</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>87.27</v>
+        <v>69.11</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>76.38</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>3.455</v>
@@ -5530,54 +5528,54 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>82.42</v>
+        <v>91.64</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>83.87</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>92.12</v>
+        <v>99.47</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>83.14</v>
+        <v>93.2</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>71.14</v>
+        <v>87.27</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>15.125</v>
+        <v>1.478</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5592,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>R4_0_A0_FULL12_FROZEN</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5603,31 +5601,31 @@
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>82.42</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>83.87</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>91.94</v>
+        <v>92.12</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>82.77</v>
+        <v>83.14</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>70.61</v>
+        <v>71.14</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>8.195</v>
+        <v>11.754</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>15.125</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>24.1021</v>
+        <v>26.3246</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -5648,7 +5646,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>R4_1_VIT4_OLDHEAD</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5657,31 +5655,31 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>79.94</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>91.89</v>
+        <v>91.94</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>82.3</v>
+        <v>82.77</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>69.92</v>
+        <v>70.61</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>5.492</v>
+        <v>8.195</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>3.515</v>
+        <v>15.125</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>10.7311</v>
+        <v>24.1021</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -5702,7 +5700,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5711,31 +5709,31 @@
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>80.87</v>
+        <v>79.94</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>83.81</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>91.81</v>
+        <v>91.89</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>69.95</v>
+        <v>69.92</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>5.533</v>
+        <v>5.492</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>3.556</v>
+        <v>3.515</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>10.9824</v>
+        <v>10.7311</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -5756,7 +5754,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5765,31 +5763,31 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>79.78</v>
+        <v>80.87</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>84.39</v>
+        <v>83.81</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>91.75</v>
+        <v>91.81</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>82.02</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>69.52</v>
+        <v>69.95</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>5.491</v>
+        <v>5.533</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>3.514</v>
+        <v>3.556</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>11.5239</v>
+        <v>10.9824</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -5800,46 +5798,50 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>97.72</v>
+        <v>79.78</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>97.78</v>
+        <v>84.39</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>99.44</v>
+        <v>91.75</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>97.75</v>
+        <v>82.02</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>69.52</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>11.754</v>
+        <v>5.491</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>20.661</v>
+        <v>3.514</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>26.3246</v>
+        <v>11.5239</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -5861,26 +5863,26 @@
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>97.72</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>92.33</v>
+        <v>97.78</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.44</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>91.95</v>
+        <v>97.75</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>91.52</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>11.754</v>
@@ -5911,26 +5913,26 @@
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>80.77</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>84.27</v>
+        <v>92.33</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>91.91</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>82.48</v>
+        <v>91.95</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>70.19</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>77.23</v>
+        <v>91.52</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>11.754</v>
@@ -5961,26 +5963,26 @@
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>93.62</v>
+        <v>80.77</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>96.09</v>
+        <v>84.27</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>94.84</v>
+        <v>82.48</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>90.18000000000001</v>
+        <v>70.19</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>94.63</v>
+        <v>77.23</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>11.754</v>
@@ -5997,8 +5999,58 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N104"/>
+  <autoFilter ref="A1:N105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$106</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N105"/>
+  <dimension ref="A1:N106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4579,33 +4579,33 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>78.67</v>
+        <v>80.39</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>85.08</v>
+        <v>82.89</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>91.72</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>81.75</v>
+        <v>81.62</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>69.13</v>
+        <v>68.95</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>76.40000000000001</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>3.049509</v>
+        <v>3.016737</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>3.133176</v>
+        <v>3.100404</v>
       </c>
       <c r="M78" s="2" t="n"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_hyperbolic</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4631,22 +4631,22 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>82.83</v>
+        <v>78.67</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>82.86</v>
+        <v>85.08</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>91.91</v>
+        <v>91.72</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>82.84999999999999</v>
+        <v>81.75</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>70.72</v>
+        <v>69.13</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>77.56</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>3.049509</v>
@@ -4657,61 +4657,59 @@
       <c r="M79" s="2" t="n"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>91.09</v>
+        <v>82.83</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>92.8</v>
+        <v>82.86</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>99.19</v>
+        <v>91.91</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>91.94</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>85.08</v>
+        <v>70.72</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>26.3183</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M80" s="2" t="n"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
@@ -4733,26 +4731,26 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>80.3</v>
+        <v>91.09</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>84.81</v>
+        <v>92.8</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>99.19</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>82.5</v>
+        <v>91.94</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>85.08</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>11.754</v>
@@ -4782,31 +4780,31 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>92.75</v>
+        <v>84.81</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>91.86</v>
+        <v>82.5</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>84.94</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>11.754</v>
@@ -4815,11 +4813,11 @@
         <v>20.661</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>26.2593</v>
+        <v>26.3183</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -4841,26 +4839,26 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>80.55</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>84.23</v>
+        <v>92.75</v>
       </c>
       <c r="G83" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H83" s="2" t="n">
         <v>91.86</v>
       </c>
-      <c r="H83" s="2" t="n">
-        <v>82.34999999999999</v>
-      </c>
       <c r="I83" s="2" t="n">
-        <v>70</v>
+        <v>84.94</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>77.06</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>11.754</v>
@@ -4885,49 +4883,49 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>91.38</v>
+        <v>80.55</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>92.3</v>
+        <v>84.23</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>99.17</v>
+        <v>91.86</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>91.84</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>84.91</v>
+        <v>70</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>77.06</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>26.1484</v>
+        <v>26.2593</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -4949,26 +4947,26 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>91.38</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>86.03</v>
+        <v>92.3</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>99.17</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.84</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>69.55</v>
+        <v>84.91</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>76.83</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>11.754</v>
@@ -4998,31 +4996,31 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>91.13</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>86.03</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>91.88</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>84.98</v>
+        <v>69.55</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>91.45</v>
+        <v>76.83</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>11.754</v>
@@ -5031,11 +5029,11 @@
         <v>15.125</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>26.0894</v>
+        <v>26.1484</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -5057,26 +5055,26 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>85.05</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>92.36</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>83.52</v>
+        <v>91.88</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>71.7</v>
+        <v>84.98</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>78.55</v>
+        <v>91.45</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>11.754</v>
@@ -5101,12 +5099,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5115,22 +5113,22 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>84.28</v>
+        <v>85.05</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>91.7</v>
+        <v>92.36</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>81.92</v>
+        <v>83.52</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>69.37</v>
+        <v>71.7</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>78.55</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>11.754</v>
@@ -5150,54 +5148,54 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A4_DETAIL_FROZEN</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>93.13</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>95.16</v>
+        <v>84.28</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>94.13</v>
+        <v>81.92</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>88.91</v>
+        <v>69.37</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0.62</v>
+        <v>15.125</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.0894</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -5219,26 +5217,26 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>86.37</v>
+        <v>93.13</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>89.25</v>
+        <v>95.16</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>98.78</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>94.13</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>88.91</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>87.14</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>2.596</v>
@@ -5273,26 +5271,26 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>86.37</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>84.5</v>
+        <v>89.25</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>91.81</v>
+        <v>98.78</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>76.84</v>
+        <v>87.14</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>2.596</v>
@@ -5327,26 +5325,26 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>90.16</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>93.97</v>
+        <v>84.5</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>99.38</v>
+        <v>91.81</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>92.02</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>85.23</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>91.7</v>
+        <v>76.84</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>2.596</v>
@@ -5376,40 +5374,40 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>94.7</v>
+        <v>90.16</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>96.13</v>
+        <v>93.97</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>98.88</v>
+        <v>99.38</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>95.41</v>
+        <v>92.02</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>91.22</v>
+        <v>85.23</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>94.77</v>
+        <v>91.7</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -5435,26 +5433,26 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>88.42</v>
+        <v>94.7</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>91.97</v>
+        <v>96.13</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>99.02</v>
+        <v>98.88</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>90.16</v>
+        <v>95.41</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>82.08</v>
+        <v>91.22</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>89.64</v>
+        <v>94.77</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>3.455</v>
@@ -5489,26 +5487,26 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>78.73</v>
+        <v>88.42</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>84.98</v>
+        <v>91.97</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>91.7</v>
+        <v>99.02</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>90.16</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>69.11</v>
+        <v>82.08</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>76.38</v>
+        <v>89.64</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>3.455</v>
@@ -5543,26 +5541,26 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>91.64</v>
+        <v>78.73</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>84.98</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>99.47</v>
+        <v>91.7</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>93.2</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>87.27</v>
+        <v>69.11</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>76.38</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>3.455</v>
@@ -5582,54 +5580,54 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>82.42</v>
+        <v>91.64</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>83.87</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>92.12</v>
+        <v>99.47</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>83.14</v>
+        <v>93.2</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>71.14</v>
+        <v>87.27</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>15.125</v>
+        <v>1.478</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5644,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>R4_0_A0_FULL12_FROZEN</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5655,31 +5653,31 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>82.42</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>83.87</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>91.94</v>
+        <v>92.12</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>82.77</v>
+        <v>83.14</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>70.61</v>
+        <v>71.14</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>8.195</v>
+        <v>11.754</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>15.125</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>24.1021</v>
+        <v>26.3246</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -5700,7 +5698,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>R4_1_VIT4_OLDHEAD</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5709,31 +5707,31 @@
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>79.94</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>91.89</v>
+        <v>91.94</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>82.3</v>
+        <v>82.77</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>69.92</v>
+        <v>70.61</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>5.492</v>
+        <v>8.195</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>3.515</v>
+        <v>15.125</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>10.7311</v>
+        <v>24.1021</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -5754,7 +5752,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5763,31 +5761,31 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>80.87</v>
+        <v>79.94</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>83.81</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>91.81</v>
+        <v>91.89</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>69.95</v>
+        <v>69.92</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>5.533</v>
+        <v>5.492</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>3.556</v>
+        <v>3.515</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>10.9824</v>
+        <v>10.7311</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -5808,7 +5806,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5817,31 +5815,31 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>79.78</v>
+        <v>80.87</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>84.39</v>
+        <v>83.81</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>91.75</v>
+        <v>91.81</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>82.02</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>69.52</v>
+        <v>69.95</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>5.491</v>
+        <v>5.533</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>3.514</v>
+        <v>3.556</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>11.5239</v>
+        <v>10.9824</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -5852,46 +5850,50 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>97.72</v>
+        <v>79.78</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>97.78</v>
+        <v>84.39</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>99.44</v>
+        <v>91.75</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>97.75</v>
+        <v>82.02</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>69.52</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>11.754</v>
+        <v>5.491</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>20.661</v>
+        <v>3.514</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>26.3246</v>
+        <v>11.5239</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -5913,26 +5915,26 @@
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>97.72</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>92.33</v>
+        <v>97.78</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.44</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>91.95</v>
+        <v>97.75</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>91.52</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>11.754</v>
@@ -5963,26 +5965,26 @@
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>80.77</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>84.27</v>
+        <v>92.33</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>91.91</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>82.48</v>
+        <v>91.95</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>70.19</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>77.23</v>
+        <v>91.52</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>11.754</v>
@@ -6013,26 +6015,26 @@
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>93.62</v>
+        <v>80.77</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>96.09</v>
+        <v>84.27</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>94.84</v>
+        <v>82.48</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>90.18000000000001</v>
+        <v>70.19</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>94.63</v>
+        <v>77.23</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>11.754</v>
@@ -6049,8 +6051,58 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N105"/>
+  <autoFilter ref="A1:N106"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$108</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N106"/>
+  <dimension ref="A1:N108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4627,26 +4627,26 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>78.67</v>
+        <v>90.55</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>85.08</v>
+        <v>92.03</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>91.72</v>
+        <v>99.12</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>81.75</v>
+        <v>91.28</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>69.13</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>76.40000000000001</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>3.049509</v>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4683,22 +4683,22 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>82.83</v>
+        <v>78.67</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>82.86</v>
+        <v>85.08</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>91.91</v>
+        <v>91.72</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>82.84999999999999</v>
+        <v>81.75</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>70.72</v>
+        <v>69.13</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>77.56</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>3.049509</v>
@@ -4709,24 +4709,24 @@
       <c r="M80" s="2" t="n"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4735,52 +4735,50 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>91.09</v>
+        <v>89.72</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>92.8</v>
+        <v>93.12</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>99.19</v>
+        <v>99.14</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>91.94</v>
+        <v>91.39</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>85.08</v>
+        <v>84.14</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M81" s="2" t="n">
-        <v>26.3183</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M81" s="2" t="n"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4789,35 +4787,33 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>80.3</v>
+        <v>82.83</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>84.81</v>
+        <v>82.86</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>82.5</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>70.72</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M82" s="2" t="n">
-        <v>26.3183</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M82" s="2" t="n"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4830,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4843,22 +4839,22 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>91.09</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>92.75</v>
+        <v>92.8</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.19</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>91.86</v>
+        <v>91.94</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>84.94</v>
+        <v>85.08</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>11.754</v>
@@ -4867,11 +4863,11 @@
         <v>20.661</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>26.2593</v>
+        <v>26.3183</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4884,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4897,22 +4893,22 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>80.55</v>
+        <v>80.3</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>84.23</v>
+        <v>84.81</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>91.86</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>82.34999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>70</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>77.06</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>11.754</v>
@@ -4921,11 +4917,11 @@
         <v>20.661</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>26.2593</v>
+        <v>26.3183</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4933,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4951,35 +4947,35 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>91.38</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>92.3</v>
+        <v>92.75</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>99.17</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>91.84</v>
+        <v>91.86</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>84.91</v>
+        <v>84.94</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>26.1484</v>
+        <v>26.2593</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -4991,12 +4987,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5005,35 +5001,35 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>80.55</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>86.03</v>
+        <v>84.23</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>91.86</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>69.55</v>
+        <v>70</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>76.83</v>
+        <v>77.06</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>26.1484</v>
+        <v>26.2593</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5046,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5059,22 +5055,22 @@
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>91.13</v>
+        <v>91.38</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.17</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>91.88</v>
+        <v>91.84</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>84.98</v>
+        <v>84.91</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>91.45</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>11.754</v>
@@ -5083,11 +5079,11 @@
         <v>15.125</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>26.0894</v>
+        <v>26.1484</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5100,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5113,22 +5109,22 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>86.03</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="H88" s="2" t="n">
         <v>82.04000000000001</v>
       </c>
-      <c r="F88" s="2" t="n">
-        <v>85.05</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>92.36</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>83.52</v>
-      </c>
       <c r="I88" s="2" t="n">
-        <v>71.7</v>
+        <v>69.55</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>78.55</v>
+        <v>76.83</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>11.754</v>
@@ -5137,11 +5133,11 @@
         <v>15.125</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>26.0894</v>
+        <v>26.1484</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -5153,36 +5149,36 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>84.28</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>91.7</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>81.92</v>
+        <v>91.88</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>69.37</v>
+        <v>84.98</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>91.45</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>11.754</v>
@@ -5202,108 +5198,108 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>93.13</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>95.16</v>
+        <v>85.05</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>92.36</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>94.13</v>
+        <v>83.52</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>88.91</v>
+        <v>71.7</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>78.55</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0.62</v>
+        <v>15.125</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.0894</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A4_DETAIL_FROZEN</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>86.37</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>89.25</v>
+        <v>84.28</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>98.78</v>
+        <v>91.7</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>81.92</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>69.37</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>87.14</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0.62</v>
+        <v>15.125</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.0894</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -5325,26 +5321,26 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>93.13</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>84.5</v>
+        <v>95.16</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>91.81</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>94.13</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>88.91</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>76.84</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>2.596</v>
@@ -5379,26 +5375,26 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>90.16</v>
+        <v>86.37</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>93.97</v>
+        <v>89.25</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>99.38</v>
+        <v>98.78</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>92.02</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>85.23</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>91.7</v>
+        <v>87.14</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>2.596</v>
@@ -5428,40 +5424,40 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>94.7</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>96.13</v>
+        <v>84.5</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>98.88</v>
+        <v>91.81</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>95.41</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>91.22</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>94.77</v>
+        <v>76.84</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
@@ -5482,40 +5478,40 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>88.42</v>
+        <v>90.16</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>91.97</v>
+        <v>93.97</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>99.02</v>
+        <v>99.38</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>90.16</v>
+        <v>92.02</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>82.08</v>
+        <v>85.23</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>89.64</v>
+        <v>91.7</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M95" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -5541,26 +5537,26 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>78.73</v>
+        <v>94.7</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>84.98</v>
+        <v>96.13</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>91.7</v>
+        <v>98.88</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>95.41</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>69.11</v>
+        <v>91.22</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>76.38</v>
+        <v>94.77</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>3.455</v>
@@ -5595,26 +5591,26 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>91.64</v>
+        <v>88.42</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>91.97</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>99.47</v>
+        <v>99.02</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>93.2</v>
+        <v>90.16</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>87.27</v>
+        <v>82.08</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>89.64</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>3.455</v>
@@ -5634,17 +5630,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5653,89 +5649,89 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>82.42</v>
+        <v>78.73</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>83.87</v>
+        <v>84.98</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>92.12</v>
+        <v>91.7</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>83.14</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>71.14</v>
+        <v>69.11</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>76.38</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>15.125</v>
+        <v>1.478</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>91.64</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>91.94</v>
+        <v>99.47</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>82.77</v>
+        <v>93.2</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>70.61</v>
+        <v>87.27</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>8.195</v>
+        <v>3.455</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>15.125</v>
+        <v>1.478</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>24.1021</v>
+        <v>3.5459</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5748,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>R4_0_A0_FULL12_FROZEN</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5761,31 +5757,31 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>79.94</v>
+        <v>82.42</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>83.87</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>91.89</v>
+        <v>92.12</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>82.3</v>
+        <v>83.14</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>69.92</v>
+        <v>71.14</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>5.492</v>
+        <v>11.754</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>3.515</v>
+        <v>15.125</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>10.7311</v>
+        <v>26.3246</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -5806,7 +5802,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>R4_1_VIT4_OLDHEAD</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5815,31 +5811,31 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>80.87</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>83.81</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>91.81</v>
+        <v>91.94</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>82.77</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>69.95</v>
+        <v>70.61</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>5.533</v>
+        <v>8.195</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>3.556</v>
+        <v>15.125</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>10.9824</v>
+        <v>24.1021</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -5860,7 +5856,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5869,31 +5865,31 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>79.78</v>
+        <v>79.94</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>84.39</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>91.75</v>
+        <v>91.89</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>82.02</v>
+        <v>82.3</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>69.52</v>
+        <v>69.92</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>5.491</v>
+        <v>5.492</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>3.514</v>
+        <v>3.515</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>11.5239</v>
+        <v>10.7311</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -5904,46 +5900,50 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>97.72</v>
+        <v>80.87</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>97.78</v>
+        <v>83.81</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>99.44</v>
+        <v>91.81</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>97.75</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>69.95</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>11.754</v>
+        <v>5.533</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>20.661</v>
+        <v>3.556</v>
       </c>
       <c r="M103" s="2" t="n">
-        <v>26.3246</v>
+        <v>10.9824</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
@@ -5954,46 +5954,50 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>79.78</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>92.33</v>
+        <v>84.39</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.75</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>91.95</v>
+        <v>82.02</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.52</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>91.52</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>11.754</v>
+        <v>5.491</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>20.661</v>
+        <v>3.514</v>
       </c>
       <c r="M104" s="2" t="n">
-        <v>26.3246</v>
+        <v>11.5239</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -6015,26 +6019,26 @@
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>80.77</v>
+        <v>97.72</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>84.27</v>
+        <v>97.78</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>91.91</v>
+        <v>99.44</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>82.48</v>
+        <v>97.75</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>70.19</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>77.23</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>11.754</v>
@@ -6065,26 +6069,26 @@
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>93.62</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>96.09</v>
+        <v>92.33</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>94.84</v>
+        <v>91.95</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>90.18000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>94.63</v>
+        <v>91.52</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>11.754</v>
@@ -6101,8 +6105,108 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N106"/>
+  <autoFilter ref="A1:N108"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$109</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N108"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4575,26 +4575,26 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>80.39</v>
+        <v>91.2</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>82.89</v>
+        <v>91.72</v>
       </c>
       <c r="G78" s="2" t="n">
+        <v>99.13</v>
+      </c>
+      <c r="H78" s="2" t="n">
         <v>91.45999999999999</v>
       </c>
-      <c r="H78" s="2" t="n">
-        <v>81.62</v>
-      </c>
       <c r="I78" s="2" t="n">
-        <v>68.95</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>76.06999999999999</v>
+        <v>91</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>3.016737</v>
@@ -4622,42 +4622,42 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>90.55</v>
+        <v>80.39</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>92.03</v>
+        <v>82.89</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>99.12</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>91.28</v>
+        <v>81.62</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>83.95999999999999</v>
+        <v>68.95</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>90.81999999999999</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>3.049509</v>
+        <v>3.016737</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>3.133176</v>
+        <v>3.100404</v>
       </c>
       <c r="M79" s="2" t="n"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_hyperbolic</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
@@ -4679,26 +4679,26 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>78.67</v>
+        <v>90.55</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>85.08</v>
+        <v>92.03</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>91.72</v>
+        <v>99.12</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>81.75</v>
+        <v>91.28</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>69.13</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>76.40000000000001</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>3.049509</v>
@@ -4726,31 +4726,31 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>89.72</v>
+        <v>78.67</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>93.12</v>
+        <v>85.08</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>99.14</v>
+        <v>91.72</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>91.39</v>
+        <v>81.75</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>84.14</v>
+        <v>69.13</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>90.93000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>3.049509</v>
@@ -4761,7 +4761,7 @@
       <c r="M81" s="2" t="n"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
@@ -4783,26 +4783,26 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>82.83</v>
+        <v>89.72</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>82.86</v>
+        <v>93.12</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>91.91</v>
+        <v>99.14</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>82.84999999999999</v>
+        <v>91.39</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>70.72</v>
+        <v>84.14</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>77.56</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>3.049509</v>
@@ -4820,54 +4820,52 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>91.09</v>
+        <v>82.83</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>92.8</v>
+        <v>82.86</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>99.19</v>
+        <v>91.91</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>91.94</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>85.08</v>
+        <v>70.72</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>26.3183</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M83" s="2" t="n"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
@@ -4889,26 +4887,26 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>80.3</v>
+        <v>91.09</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>84.81</v>
+        <v>92.8</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>99.19</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>82.5</v>
+        <v>91.94</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>85.08</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>11.754</v>
@@ -4938,31 +4936,31 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>92.75</v>
+        <v>84.81</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>91.86</v>
+        <v>82.5</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>84.94</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>11.754</v>
@@ -4971,11 +4969,11 @@
         <v>20.661</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>26.2593</v>
+        <v>26.3183</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -4997,26 +4995,26 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>80.55</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>84.23</v>
+        <v>92.75</v>
       </c>
       <c r="G86" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H86" s="2" t="n">
         <v>91.86</v>
       </c>
-      <c r="H86" s="2" t="n">
-        <v>82.34999999999999</v>
-      </c>
       <c r="I86" s="2" t="n">
-        <v>70</v>
+        <v>84.94</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>77.06</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>11.754</v>
@@ -5041,49 +5039,49 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>91.38</v>
+        <v>80.55</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>92.3</v>
+        <v>84.23</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>99.17</v>
+        <v>91.86</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>91.84</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>84.91</v>
+        <v>70</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>77.06</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>26.1484</v>
+        <v>26.2593</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -5105,26 +5103,26 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>91.38</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>86.03</v>
+        <v>92.3</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>99.17</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.84</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>69.55</v>
+        <v>84.91</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>76.83</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>11.754</v>
@@ -5154,31 +5152,31 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>91.13</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>86.03</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>91.88</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>84.98</v>
+        <v>69.55</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>91.45</v>
+        <v>76.83</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>11.754</v>
@@ -5187,11 +5185,11 @@
         <v>15.125</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>26.0894</v>
+        <v>26.1484</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -5213,26 +5211,26 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>85.05</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>92.36</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>83.52</v>
+        <v>91.88</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>71.7</v>
+        <v>84.98</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>78.55</v>
+        <v>91.45</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>11.754</v>
@@ -5257,12 +5255,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5271,22 +5269,22 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>84.28</v>
+        <v>85.05</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>91.7</v>
+        <v>92.36</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>81.92</v>
+        <v>83.52</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>69.37</v>
+        <v>71.7</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>78.55</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>11.754</v>
@@ -5306,54 +5304,54 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A4_DETAIL_FROZEN</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>93.13</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>95.16</v>
+        <v>84.28</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>94.13</v>
+        <v>81.92</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>88.91</v>
+        <v>69.37</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0.62</v>
+        <v>15.125</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.0894</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -5375,26 +5373,26 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>86.37</v>
+        <v>93.13</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>89.25</v>
+        <v>95.16</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>98.78</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>94.13</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>88.91</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>87.14</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>2.596</v>
@@ -5429,26 +5427,26 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>86.37</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>84.5</v>
+        <v>89.25</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>91.81</v>
+        <v>98.78</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>76.84</v>
+        <v>87.14</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>2.596</v>
@@ -5483,26 +5481,26 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>90.16</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>93.97</v>
+        <v>84.5</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>99.38</v>
+        <v>91.81</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>92.02</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>85.23</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>91.7</v>
+        <v>76.84</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>2.596</v>
@@ -5532,40 +5530,40 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>94.7</v>
+        <v>90.16</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>96.13</v>
+        <v>93.97</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>98.88</v>
+        <v>99.38</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>95.41</v>
+        <v>92.02</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>91.22</v>
+        <v>85.23</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>94.77</v>
+        <v>91.7</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -5591,26 +5589,26 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>88.42</v>
+        <v>94.7</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>91.97</v>
+        <v>96.13</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>99.02</v>
+        <v>98.88</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>90.16</v>
+        <v>95.41</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>82.08</v>
+        <v>91.22</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>89.64</v>
+        <v>94.77</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>3.455</v>
@@ -5645,26 +5643,26 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>78.73</v>
+        <v>88.42</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>84.98</v>
+        <v>91.97</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>91.7</v>
+        <v>99.02</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>90.16</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>69.11</v>
+        <v>82.08</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>76.38</v>
+        <v>89.64</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>3.455</v>
@@ -5699,26 +5697,26 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>91.64</v>
+        <v>78.73</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>84.98</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>99.47</v>
+        <v>91.7</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>93.2</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>87.27</v>
+        <v>69.11</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>76.38</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>3.455</v>
@@ -5738,54 +5736,54 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>82.42</v>
+        <v>91.64</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>83.87</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>92.12</v>
+        <v>99.47</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>83.14</v>
+        <v>93.2</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>71.14</v>
+        <v>87.27</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>15.125</v>
+        <v>1.478</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5800,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>R4_0_A0_FULL12_FROZEN</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5811,31 +5809,31 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>82.42</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>83.87</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>91.94</v>
+        <v>92.12</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>82.77</v>
+        <v>83.14</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>70.61</v>
+        <v>71.14</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>8.195</v>
+        <v>11.754</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>15.125</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>24.1021</v>
+        <v>26.3246</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -5856,7 +5854,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>R4_1_VIT4_OLDHEAD</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5865,31 +5863,31 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>79.94</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>91.89</v>
+        <v>91.94</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>82.3</v>
+        <v>82.77</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>69.92</v>
+        <v>70.61</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>5.492</v>
+        <v>8.195</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>3.515</v>
+        <v>15.125</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>10.7311</v>
+        <v>24.1021</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -5910,7 +5908,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5919,31 +5917,31 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>80.87</v>
+        <v>79.94</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>83.81</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>91.81</v>
+        <v>91.89</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>69.95</v>
+        <v>69.92</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>5.533</v>
+        <v>5.492</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>3.556</v>
+        <v>3.515</v>
       </c>
       <c r="M103" s="2" t="n">
-        <v>10.9824</v>
+        <v>10.7311</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
@@ -5964,7 +5962,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5973,31 +5971,31 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>79.78</v>
+        <v>80.87</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>84.39</v>
+        <v>83.81</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>91.75</v>
+        <v>91.81</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>82.02</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>69.52</v>
+        <v>69.95</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>5.491</v>
+        <v>5.533</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>3.514</v>
+        <v>3.556</v>
       </c>
       <c r="M104" s="2" t="n">
-        <v>11.5239</v>
+        <v>10.9824</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -6008,46 +6006,50 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>97.72</v>
+        <v>79.78</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>97.78</v>
+        <v>84.39</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>99.44</v>
+        <v>91.75</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>97.75</v>
+        <v>82.02</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>69.52</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>11.754</v>
+        <v>5.491</v>
       </c>
       <c r="L105" s="2" t="n">
-        <v>20.661</v>
+        <v>3.514</v>
       </c>
       <c r="M105" s="2" t="n">
-        <v>26.3246</v>
+        <v>11.5239</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
@@ -6069,26 +6071,26 @@
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>97.72</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>92.33</v>
+        <v>97.78</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.44</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>91.95</v>
+        <v>97.75</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>91.52</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>11.754</v>
@@ -6119,26 +6121,26 @@
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>80.77</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>84.27</v>
+        <v>92.33</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>91.91</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>82.48</v>
+        <v>91.95</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>70.19</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>77.23</v>
+        <v>91.52</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>11.754</v>
@@ -6169,26 +6171,26 @@
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>93.62</v>
+        <v>80.77</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>96.09</v>
+        <v>84.27</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>94.84</v>
+        <v>82.48</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>90.18000000000001</v>
+        <v>70.19</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>94.63</v>
+        <v>77.23</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>11.754</v>
@@ -6205,8 +6207,58 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N108"/>
+  <autoFilter ref="A1:N109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$112</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:N112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4674,42 +4674,42 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>90.55</v>
+        <v>92.61</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>92.03</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>99.12</v>
+        <v>99.52</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>91.28</v>
+        <v>93.92</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>83.95999999999999</v>
+        <v>88.53</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>90.81999999999999</v>
+        <v>93.67</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>3.049509</v>
+        <v>3.016737</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>3.133176</v>
+        <v>3.100404</v>
       </c>
       <c r="M80" s="2" t="n"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_hyperbolic</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
@@ -4731,26 +4731,26 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>78.67</v>
+        <v>90.55</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>85.08</v>
+        <v>92.03</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>91.72</v>
+        <v>99.12</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>81.75</v>
+        <v>91.28</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>69.13</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>76.40000000000001</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>3.049509</v>
@@ -4778,31 +4778,31 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>89.72</v>
+        <v>78.67</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>93.12</v>
+        <v>85.08</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>99.14</v>
+        <v>91.72</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>91.39</v>
+        <v>81.75</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>84.14</v>
+        <v>69.13</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>90.93000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>3.049509</v>
@@ -4813,7 +4813,7 @@
       <c r="M82" s="2" t="n"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
@@ -4830,31 +4830,31 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>82.83</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>82.86</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>91.91</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>82.84999999999999</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>70.72</v>
+        <v>88.8</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>77.56</v>
+        <v>93.83</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>3.049509</v>
@@ -4865,24 +4865,24 @@
       <c r="M83" s="2" t="n"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4891,52 +4891,50 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>91.09</v>
+        <v>89.72</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>92.8</v>
+        <v>93.12</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>99.19</v>
+        <v>99.14</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>91.94</v>
+        <v>91.39</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>85.08</v>
+        <v>84.14</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M84" s="2" t="n">
-        <v>26.3183</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M84" s="2" t="n"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4945,89 +4943,85 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>80.3</v>
+        <v>82.83</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>84.81</v>
+        <v>82.86</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>82.5</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>70.72</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M85" s="2" t="n">
-        <v>26.3183</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M85" s="2" t="n"/>
       <c r="N85" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>92.75</v>
+        <v>96.08</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>91.86</v>
+        <v>94.53</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>84.94</v>
+        <v>89.63</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M86" s="2" t="n">
-        <v>26.2593</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M86" s="2" t="n"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
@@ -5044,31 +5038,31 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>80.55</v>
+        <v>91.09</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>84.23</v>
+        <v>92.8</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>91.86</v>
+        <v>99.19</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>82.34999999999999</v>
+        <v>91.94</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>70</v>
+        <v>85.08</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>77.06</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>11.754</v>
@@ -5077,11 +5071,11 @@
         <v>20.661</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>26.2593</v>
+        <v>26.3183</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -5093,45 +5087,45 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>91.38</v>
+        <v>80.3</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>92.3</v>
+        <v>84.81</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>99.17</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>91.84</v>
+        <v>82.5</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>84.91</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>26.1484</v>
+        <v>26.3183</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -5147,49 +5141,49 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>86.03</v>
+        <v>92.75</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.86</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>69.55</v>
+        <v>84.94</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>76.83</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>26.1484</v>
+        <v>26.2593</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -5201,45 +5195,45 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>91.13</v>
+        <v>80.55</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>84.23</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.86</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>91.88</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>84.98</v>
+        <v>70</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>91.45</v>
+        <v>77.06</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>26.0894</v>
+        <v>26.2593</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -5260,31 +5254,31 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>91.38</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>85.05</v>
+        <v>92.3</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>92.36</v>
+        <v>99.17</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>83.52</v>
+        <v>91.84</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>71.7</v>
+        <v>84.91</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>78.55</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>11.754</v>
@@ -5293,11 +5287,11 @@
         <v>15.125</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>26.0894</v>
+        <v>26.1484</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5303,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5323,22 +5317,22 @@
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>84.28</v>
+        <v>86.03</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>91.7</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>81.92</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>69.37</v>
+        <v>69.55</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>76.83</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>11.754</v>
@@ -5347,136 +5341,136 @@
         <v>15.125</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>26.0894</v>
+        <v>26.1484</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>93.13</v>
+        <v>91.13</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>95.16</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>94.13</v>
+        <v>91.88</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>88.91</v>
+        <v>84.98</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>91.45</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0.62</v>
+        <v>15.125</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.0894</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>86.37</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>89.25</v>
+        <v>85.05</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>98.78</v>
+        <v>92.36</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>83.52</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>87.14</v>
+        <v>78.55</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0.62</v>
+        <v>15.125</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.0894</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>A4_DETAIL_FROZEN</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5485,35 +5479,35 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>84.5</v>
+        <v>84.28</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>91.81</v>
+        <v>91.7</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>81.92</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>69.37</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>76.84</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>2.596</v>
+        <v>11.754</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0.62</v>
+        <v>15.125</v>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2.2136</v>
+        <v>26.0894</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -5535,26 +5529,26 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>90.16</v>
+        <v>93.13</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>93.97</v>
+        <v>95.16</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>99.38</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>92.02</v>
+        <v>94.13</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>85.23</v>
+        <v>88.91</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>91.7</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>2.596</v>
@@ -5584,40 +5578,40 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>94.7</v>
+        <v>86.37</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>96.13</v>
+        <v>89.25</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>98.88</v>
+        <v>98.78</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>95.41</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>91.22</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>94.77</v>
+        <v>87.14</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -5638,40 +5632,40 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>88.42</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>91.97</v>
+        <v>84.5</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>99.02</v>
+        <v>91.81</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>90.16</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>82.08</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>89.64</v>
+        <v>76.84</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -5692,40 +5686,40 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>78.73</v>
+        <v>90.16</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>84.98</v>
+        <v>93.97</v>
       </c>
       <c r="G99" s="2" t="n">
+        <v>99.38</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>92.02</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>85.23</v>
+      </c>
+      <c r="J99" s="2" t="n">
         <v>91.7</v>
       </c>
-      <c r="H99" s="2" t="n">
-        <v>81.73999999999999</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>69.11</v>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>76.38</v>
-      </c>
       <c r="K99" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -5751,26 +5745,26 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>91.64</v>
+        <v>94.7</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>96.13</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>99.47</v>
+        <v>98.88</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>93.2</v>
+        <v>95.41</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>87.27</v>
+        <v>91.22</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>94.77</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>3.455</v>
@@ -5790,71 +5784,71 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>82.42</v>
+        <v>88.42</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>83.87</v>
+        <v>91.97</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>92.12</v>
+        <v>99.02</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>83.14</v>
+        <v>90.16</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>71.14</v>
+        <v>82.08</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>89.64</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>15.125</v>
+        <v>1.478</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5863,89 +5857,89 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>78.73</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>84.98</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>91.94</v>
+        <v>91.7</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>82.77</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>70.61</v>
+        <v>69.11</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>76.38</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>8.195</v>
+        <v>3.455</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>15.125</v>
+        <v>1.478</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>24.1021</v>
+        <v>3.5459</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>79.94</v>
+        <v>91.64</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>91.89</v>
+        <v>99.47</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>82.3</v>
+        <v>93.2</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>69.92</v>
+        <v>87.27</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>5.492</v>
+        <v>3.455</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>3.515</v>
+        <v>1.478</v>
       </c>
       <c r="M103" s="2" t="n">
-        <v>10.7311</v>
+        <v>3.5459</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5956,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>R4_0_A0_FULL12_FROZEN</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5971,31 +5965,31 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>80.87</v>
+        <v>82.42</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>83.81</v>
+        <v>83.87</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>91.81</v>
+        <v>92.12</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>83.14</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>69.95</v>
+        <v>71.14</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>5.533</v>
+        <v>11.754</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>3.556</v>
+        <v>15.125</v>
       </c>
       <c r="M104" s="2" t="n">
-        <v>10.9824</v>
+        <v>26.3246</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -6016,7 +6010,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>R4_1_VIT4_OLDHEAD</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6025,31 +6019,31 @@
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>79.78</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>84.39</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>91.75</v>
+        <v>91.94</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>82.02</v>
+        <v>82.77</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>69.52</v>
+        <v>70.61</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>5.491</v>
+        <v>8.195</v>
       </c>
       <c r="L105" s="2" t="n">
-        <v>3.514</v>
+        <v>15.125</v>
       </c>
       <c r="M105" s="2" t="n">
-        <v>11.5239</v>
+        <v>24.1021</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
@@ -6060,46 +6054,50 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>97.72</v>
+        <v>79.94</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>97.78</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>99.44</v>
+        <v>91.89</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>97.75</v>
+        <v>82.3</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>69.92</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>11.754</v>
+        <v>5.492</v>
       </c>
       <c r="L106" s="2" t="n">
-        <v>20.661</v>
+        <v>3.515</v>
       </c>
       <c r="M106" s="2" t="n">
-        <v>26.3246</v>
+        <v>10.7311</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
@@ -6110,46 +6108,50 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>80.87</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>92.33</v>
+        <v>83.81</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.81</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>91.95</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.95</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>91.52</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>11.754</v>
+        <v>5.533</v>
       </c>
       <c r="L107" s="2" t="n">
-        <v>20.661</v>
+        <v>3.556</v>
       </c>
       <c r="M107" s="2" t="n">
-        <v>26.3246</v>
+        <v>10.9824</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
@@ -6160,46 +6162,50 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
           <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>80.77</v>
+        <v>79.78</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>84.27</v>
+        <v>84.39</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>91.91</v>
+        <v>91.75</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>82.48</v>
+        <v>82.02</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>70.19</v>
+        <v>69.52</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>77.23</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>11.754</v>
+        <v>5.491</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>20.661</v>
+        <v>3.514</v>
       </c>
       <c r="M108" s="2" t="n">
-        <v>26.3246</v>
+        <v>11.5239</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -6221,26 +6227,26 @@
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>93.62</v>
+        <v>97.72</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>96.09</v>
+        <v>97.78</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.44</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>94.84</v>
+        <v>97.75</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>90.18000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>94.63</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>11.754</v>
@@ -6257,8 +6263,158 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N109"/>
+  <autoFilter ref="A1:N112"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$116</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N112"/>
+  <dimension ref="A1:N116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5514,216 +5514,208 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>93.13</v>
+        <v>90.41</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>95.16</v>
+        <v>91.83</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>94.13</v>
+        <v>91.11</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>88.91</v>
+        <v>83.67</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>90.64</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M96" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M96" s="2" t="n"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>86.37</v>
+        <v>79.81</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>89.25</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>98.78</v>
+        <v>91.61</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>81.78</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>87.14</v>
+        <v>76.34</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M97" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M97" s="2" t="n"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>90.61</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>84.5</v>
+        <v>92.37</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>91.81</v>
+        <v>99.14</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>91.48</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>76.84</v>
+        <v>91.03</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2.596</v>
+        <v>3.050665</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M98" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M98" s="2" t="n"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>90.16</v>
+        <v>90.58</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>93.97</v>
+        <v>91.77</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>99.38</v>
+        <v>99.11</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>92.02</v>
+        <v>91.17</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>85.23</v>
+        <v>83.77</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>91.7</v>
+        <v>90.7</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>2.596</v>
+        <v>3.059369</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M99" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.143036</v>
+      </c>
+      <c r="M99" s="2" t="n"/>
       <c r="N99" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5732,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5749,31 +5741,31 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>94.7</v>
+        <v>93.13</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>96.13</v>
+        <v>95.16</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>98.88</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>95.41</v>
+        <v>94.13</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>91.22</v>
+        <v>88.91</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>94.77</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -5794,7 +5786,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5803,31 +5795,31 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>88.42</v>
+        <v>86.37</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>91.97</v>
+        <v>89.25</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>99.02</v>
+        <v>98.78</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>90.16</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>82.08</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>89.64</v>
+        <v>87.14</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -5848,7 +5840,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5857,31 +5849,31 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>78.73</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>84.98</v>
+        <v>84.5</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>91.7</v>
+        <v>91.81</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>69.11</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>76.38</v>
+        <v>76.84</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -5902,7 +5894,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5911,31 +5903,31 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>91.64</v>
+        <v>90.16</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>93.97</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>99.47</v>
+        <v>99.38</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>93.2</v>
+        <v>92.02</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>87.27</v>
+        <v>85.23</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M103" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
@@ -5946,125 +5938,125 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>82.42</v>
+        <v>94.7</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>83.87</v>
+        <v>96.13</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>92.12</v>
+        <v>98.88</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>83.14</v>
+        <v>95.41</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>71.14</v>
+        <v>91.22</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>94.77</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>15.125</v>
+        <v>1.478</v>
       </c>
       <c r="M104" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>88.42</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>91.97</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>91.94</v>
+        <v>99.02</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>82.77</v>
+        <v>90.16</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>70.61</v>
+        <v>82.08</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>89.64</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>8.195</v>
+        <v>3.455</v>
       </c>
       <c r="L105" s="2" t="n">
-        <v>15.125</v>
+        <v>1.478</v>
       </c>
       <c r="M105" s="2" t="n">
-        <v>24.1021</v>
+        <v>3.5459</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6073,89 +6065,89 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>79.94</v>
+        <v>78.73</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>84.98</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>91.89</v>
+        <v>91.7</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>82.3</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>69.92</v>
+        <v>69.11</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>76.38</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>5.492</v>
+        <v>3.455</v>
       </c>
       <c r="L106" s="2" t="n">
-        <v>3.515</v>
+        <v>1.478</v>
       </c>
       <c r="M106" s="2" t="n">
-        <v>10.7311</v>
+        <v>3.5459</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>80.87</v>
+        <v>91.64</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>83.81</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>91.81</v>
+        <v>99.47</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>69.95</v>
+        <v>87.27</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>5.533</v>
+        <v>3.455</v>
       </c>
       <c r="L107" s="2" t="n">
-        <v>3.556</v>
+        <v>1.478</v>
       </c>
       <c r="M107" s="2" t="n">
-        <v>10.9824</v>
+        <v>3.5459</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6164,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>R4_0_A0_FULL12_FROZEN</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6181,31 +6173,31 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>79.78</v>
+        <v>82.42</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>84.39</v>
+        <v>83.87</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>91.75</v>
+        <v>92.12</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>82.02</v>
+        <v>83.14</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>69.52</v>
+        <v>71.14</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>5.491</v>
+        <v>11.754</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>3.514</v>
+        <v>15.125</v>
       </c>
       <c r="M108" s="2" t="n">
-        <v>11.5239</v>
+        <v>26.3246</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -6216,46 +6208,50 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>R4_1_VIT4_OLDHEAD</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>97.72</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>97.78</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>99.44</v>
+        <v>91.94</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>97.75</v>
+        <v>82.77</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>70.61</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>11.754</v>
+        <v>8.195</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>20.661</v>
+        <v>15.125</v>
       </c>
       <c r="M109" s="2" t="n">
-        <v>26.3246</v>
+        <v>24.1021</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
@@ -6266,46 +6262,50 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>79.94</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>92.33</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.89</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>91.95</v>
+        <v>82.3</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.92</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>91.52</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>11.754</v>
+        <v>5.492</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>20.661</v>
+        <v>3.515</v>
       </c>
       <c r="M110" s="2" t="n">
-        <v>26.3246</v>
+        <v>10.7311</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -6316,46 +6316,50 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
       <c r="D111" t="inlineStr">
         <is>
           <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>80.77</v>
+        <v>80.87</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>84.27</v>
+        <v>83.81</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>91.91</v>
+        <v>91.81</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>82.48</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>70.19</v>
+        <v>69.95</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>77.23</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>11.754</v>
+        <v>5.533</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>20.661</v>
+        <v>3.556</v>
       </c>
       <c r="M111" s="2" t="n">
-        <v>26.3246</v>
+        <v>10.9824</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
@@ -6366,55 +6370,259 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>3.514</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>11.5239</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
         <is>
           <t>Run1</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr">
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
-      <c r="E112" s="2" t="n">
+      <c r="E116" s="2" t="n">
         <v>93.62</v>
       </c>
-      <c r="F112" s="2" t="n">
+      <c r="F116" s="2" t="n">
         <v>96.09</v>
       </c>
-      <c r="G112" s="2" t="n">
+      <c r="G116" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="H112" s="2" t="n">
+      <c r="H116" s="2" t="n">
         <v>94.84</v>
       </c>
-      <c r="I112" s="2" t="n">
+      <c r="I116" s="2" t="n">
         <v>90.18000000000001</v>
       </c>
-      <c r="J112" s="2" t="n">
+      <c r="J116" s="2" t="n">
         <v>94.63</v>
       </c>
-      <c r="K112" s="2" t="n">
+      <c r="K116" s="2" t="n">
         <v>11.754</v>
       </c>
-      <c r="L112" s="2" t="n">
+      <c r="L116" s="2" t="n">
         <v>20.661</v>
       </c>
-      <c r="M112" s="2" t="n">
+      <c r="M116" s="2" t="n">
         <v>26.3246</v>
       </c>
-      <c r="N112" t="inlineStr">
+      <c r="N116" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N112"/>
+  <autoFilter ref="A1:N116"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$117</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N116"/>
+  <dimension ref="A1:N117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5680,96 +5680,94 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>90.58</v>
+        <v>77.55</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>91.77</v>
+        <v>85.81</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>99.11</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>91.17</v>
+        <v>81.47</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>83.77</v>
+        <v>68.73</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>90.7</v>
+        <v>76.12</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>3.059369</v>
+        <v>3.050665</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>3.143036</v>
+        <v>3.134332</v>
       </c>
       <c r="M99" s="2" t="n"/>
       <c r="N99" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>93.13</v>
+        <v>90.58</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>95.16</v>
+        <v>91.77</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>99.11</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>94.13</v>
+        <v>91.17</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>88.91</v>
+        <v>83.77</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>2.596</v>
+        <v>3.059369</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M100" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.143036</v>
+      </c>
+      <c r="M100" s="2" t="n"/>
       <c r="N100" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
@@ -5791,26 +5789,26 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>86.37</v>
+        <v>93.13</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>89.25</v>
+        <v>95.16</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>98.78</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>94.13</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>88.91</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>87.14</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>2.596</v>
@@ -5845,26 +5843,26 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>86.37</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>84.5</v>
+        <v>89.25</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>91.81</v>
+        <v>98.78</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>76.84</v>
+        <v>87.14</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>2.596</v>
@@ -5899,26 +5897,26 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>90.16</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>93.97</v>
+        <v>84.5</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>99.38</v>
+        <v>91.81</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>92.02</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>85.23</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>91.7</v>
+        <v>76.84</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>2.596</v>
@@ -5948,40 +5946,40 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>94.7</v>
+        <v>90.16</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>96.13</v>
+        <v>93.97</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>98.88</v>
+        <v>99.38</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>95.41</v>
+        <v>92.02</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>91.22</v>
+        <v>85.23</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>94.77</v>
+        <v>91.7</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -6007,26 +6005,26 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>88.42</v>
+        <v>94.7</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>91.97</v>
+        <v>96.13</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>99.02</v>
+        <v>98.88</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>90.16</v>
+        <v>95.41</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>82.08</v>
+        <v>91.22</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>89.64</v>
+        <v>94.77</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>3.455</v>
@@ -6061,26 +6059,26 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>78.73</v>
+        <v>88.42</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>84.98</v>
+        <v>91.97</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>91.7</v>
+        <v>99.02</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>90.16</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>69.11</v>
+        <v>82.08</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>76.38</v>
+        <v>89.64</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>3.455</v>
@@ -6115,26 +6113,26 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>91.64</v>
+        <v>78.73</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>84.98</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>99.47</v>
+        <v>91.7</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>93.2</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>87.27</v>
+        <v>69.11</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>76.38</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>3.455</v>
@@ -6154,54 +6152,54 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>82.42</v>
+        <v>91.64</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>83.87</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>92.12</v>
+        <v>99.47</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>83.14</v>
+        <v>93.2</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>71.14</v>
+        <v>87.27</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>15.125</v>
+        <v>1.478</v>
       </c>
       <c r="M108" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6216,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>R4_0_A0_FULL12_FROZEN</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6227,31 +6225,31 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>82.42</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>83.87</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>91.94</v>
+        <v>92.12</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>82.77</v>
+        <v>83.14</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>70.61</v>
+        <v>71.14</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>8.195</v>
+        <v>11.754</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>15.125</v>
       </c>
       <c r="M109" s="2" t="n">
-        <v>24.1021</v>
+        <v>26.3246</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
@@ -6272,7 +6270,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>R4_1_VIT4_OLDHEAD</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6281,31 +6279,31 @@
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>79.94</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>91.89</v>
+        <v>91.94</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>82.3</v>
+        <v>82.77</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>69.92</v>
+        <v>70.61</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>5.492</v>
+        <v>8.195</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>3.515</v>
+        <v>15.125</v>
       </c>
       <c r="M110" s="2" t="n">
-        <v>10.7311</v>
+        <v>24.1021</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -6326,7 +6324,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6335,31 +6333,31 @@
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>80.87</v>
+        <v>79.94</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>83.81</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>91.81</v>
+        <v>91.89</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>69.95</v>
+        <v>69.92</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>5.533</v>
+        <v>5.492</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>3.556</v>
+        <v>3.515</v>
       </c>
       <c r="M111" s="2" t="n">
-        <v>10.9824</v>
+        <v>10.7311</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
@@ -6380,7 +6378,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6389,31 +6387,31 @@
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>79.78</v>
+        <v>80.87</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>84.39</v>
+        <v>83.81</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>91.75</v>
+        <v>91.81</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>82.02</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>69.52</v>
+        <v>69.95</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>5.491</v>
+        <v>5.533</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>3.514</v>
+        <v>3.556</v>
       </c>
       <c r="M112" s="2" t="n">
-        <v>11.5239</v>
+        <v>10.9824</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
@@ -6424,46 +6422,50 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>97.72</v>
+        <v>79.78</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>97.78</v>
+        <v>84.39</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>99.44</v>
+        <v>91.75</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>97.75</v>
+        <v>82.02</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>69.52</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>11.754</v>
+        <v>5.491</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>20.661</v>
+        <v>3.514</v>
       </c>
       <c r="M113" s="2" t="n">
-        <v>26.3246</v>
+        <v>11.5239</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
@@ -6485,26 +6487,26 @@
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>97.72</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>92.33</v>
+        <v>97.78</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.44</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>91.95</v>
+        <v>97.75</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>91.52</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>11.754</v>
@@ -6535,26 +6537,26 @@
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>80.77</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>84.27</v>
+        <v>92.33</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>91.91</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>82.48</v>
+        <v>91.95</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>70.19</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>77.23</v>
+        <v>91.52</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>11.754</v>
@@ -6585,26 +6587,26 @@
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>93.62</v>
+        <v>80.77</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>96.09</v>
+        <v>84.27</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>94.84</v>
+        <v>82.48</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>90.18000000000001</v>
+        <v>70.19</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>94.63</v>
+        <v>77.23</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>11.754</v>
@@ -6621,8 +6623,58 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N116"/>
+  <autoFilter ref="A1:N117"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N117"/>
+  <dimension ref="A1:N124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5529,26 +5529,26 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>90.41</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>91.83</v>
+        <v>97.47</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.37</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>91.11</v>
+        <v>97.45</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>83.67</v>
+        <v>95.02</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>90.64</v>
+        <v>97.09</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>3.016737</v>
@@ -5581,26 +5581,26 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>79.81</v>
+        <v>90.41</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>83.84999999999999</v>
+        <v>91.83</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>91.61</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>81.78</v>
+        <v>91.11</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>69.18000000000001</v>
+        <v>83.67</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>76.34</v>
+        <v>90.64</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>3.016737</v>
@@ -5628,42 +5628,42 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>90.61</v>
+        <v>79.81</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>92.37</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>99.14</v>
+        <v>91.61</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>91.48</v>
+        <v>81.78</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>84.3</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>91.03</v>
+        <v>76.34</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.016737</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.100404</v>
       </c>
       <c r="M98" s="2" t="n"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
@@ -5680,42 +5680,42 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>77.55</v>
+        <v>93.2</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>85.81</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>91.68000000000001</v>
+        <v>99.52</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>81.47</v>
+        <v>93.95</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>68.73</v>
+        <v>88.59</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>76.12</v>
+        <v>93.7</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.016737</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.100404</v>
       </c>
       <c r="M99" s="2" t="n"/>
       <c r="N99" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
@@ -5732,420 +5732,406 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>90.58</v>
+        <v>97.48</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>91.77</v>
+        <v>97.45</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>99.11</v>
+        <v>99.37</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>91.17</v>
+        <v>97.47</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>83.77</v>
+        <v>95.06</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>90.7</v>
+        <v>97.11</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>3.059369</v>
+        <v>3.050665</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>3.143036</v>
+        <v>3.134332</v>
       </c>
       <c r="M100" s="2" t="n"/>
       <c r="N100" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>93.13</v>
+        <v>90.61</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>95.16</v>
+        <v>92.37</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>99.14</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>94.13</v>
+        <v>91.48</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>88.91</v>
+        <v>84.3</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>91.03</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>2.596</v>
+        <v>3.050665</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M101" s="2" t="n"/>
       <c r="N101" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>86.37</v>
+        <v>77.55</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>89.25</v>
+        <v>85.81</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>98.78</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>81.47</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>68.73</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>87.14</v>
+        <v>76.12</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>2.596</v>
+        <v>3.050665</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M102" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M102" s="2" t="n"/>
       <c r="N102" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>84.5</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>91.81</v>
+        <v>99.56</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>89.25</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>76.84</v>
+        <v>94.09</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>2.596</v>
+        <v>3.050665</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M103" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M103" s="2" t="n"/>
       <c r="N103" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>90.16</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>93.97</v>
+        <v>97.45</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>99.38</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>92.02</v>
+        <v>97.48</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>85.23</v>
+        <v>95.09</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>91.7</v>
+        <v>97.13</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>2.596</v>
+        <v>3.059369</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M104" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.143036</v>
+      </c>
+      <c r="M104" s="2" t="n"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>94.7</v>
+        <v>90.58</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>96.13</v>
+        <v>91.77</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>98.88</v>
+        <v>99.11</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>95.41</v>
+        <v>91.17</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>91.22</v>
+        <v>83.77</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>94.77</v>
+        <v>90.7</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>3.455</v>
+        <v>3.059369</v>
       </c>
       <c r="L105" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M105" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.143036</v>
+      </c>
+      <c r="M105" s="2" t="n"/>
       <c r="N105" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>88.42</v>
+        <v>76.7</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>91.97</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>99.02</v>
+        <v>91.52</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>90.16</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>82.08</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>89.64</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>3.455</v>
+        <v>3.059369</v>
       </c>
       <c r="L106" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M106" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.143036</v>
+      </c>
+      <c r="M106" s="2" t="n"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>78.73</v>
+        <v>92.61</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>84.98</v>
+        <v>95.31</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>91.7</v>
+        <v>99.53</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>93.94</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>69.11</v>
+        <v>88.58</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>76.38</v>
+        <v>93.69</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>3.455</v>
+        <v>3.059369</v>
       </c>
       <c r="L107" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M107" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.143036</v>
+      </c>
+      <c r="M107" s="2" t="n"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
@@ -6162,40 +6148,40 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>91.64</v>
+        <v>93.13</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>95.16</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>99.47</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>93.2</v>
+        <v>94.13</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>87.27</v>
+        <v>88.91</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -6206,71 +6192,71 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>82.42</v>
+        <v>86.37</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>83.87</v>
+        <v>89.25</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>92.12</v>
+        <v>98.78</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>83.14</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>71.14</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>87.14</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>15.125</v>
+        <v>0.62</v>
       </c>
       <c r="M109" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6279,340 +6265,352 @@
         </is>
       </c>
       <c r="E110" s="2" t="n">
+        <v>79.93000000000001</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H110" s="2" t="n">
         <v>82.15000000000001</v>
       </c>
-      <c r="F110" s="2" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="G110" s="2" t="n">
-        <v>91.94</v>
-      </c>
-      <c r="H110" s="2" t="n">
-        <v>82.77</v>
-      </c>
       <c r="I110" s="2" t="n">
-        <v>70.61</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>76.84</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>8.195</v>
+        <v>2.596</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>15.125</v>
+        <v>0.62</v>
       </c>
       <c r="M110" s="2" t="n">
-        <v>24.1021</v>
+        <v>2.2136</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>79.94</v>
+        <v>90.16</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>93.97</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>91.89</v>
+        <v>99.38</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>82.3</v>
+        <v>92.02</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>69.92</v>
+        <v>85.23</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>5.492</v>
+        <v>2.596</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>3.515</v>
+        <v>0.62</v>
       </c>
       <c r="M111" s="2" t="n">
-        <v>10.7311</v>
+        <v>2.2136</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>80.87</v>
+        <v>94.7</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>83.81</v>
+        <v>96.13</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>91.81</v>
+        <v>98.88</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>95.41</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>69.95</v>
+        <v>91.22</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>94.77</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>5.533</v>
+        <v>3.455</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>3.556</v>
+        <v>1.478</v>
       </c>
       <c r="M112" s="2" t="n">
-        <v>10.9824</v>
+        <v>3.5459</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>79.78</v>
+        <v>88.42</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>84.39</v>
+        <v>91.97</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>91.75</v>
+        <v>99.02</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>82.02</v>
+        <v>90.16</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>69.52</v>
+        <v>82.08</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>89.64</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>5.491</v>
+        <v>3.455</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>3.514</v>
+        <v>1.478</v>
       </c>
       <c r="M113" s="2" t="n">
-        <v>11.5239</v>
+        <v>3.5459</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>97.72</v>
+        <v>78.73</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>97.78</v>
+        <v>84.98</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>99.44</v>
+        <v>91.7</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>97.75</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>69.11</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>76.38</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L114" s="2" t="n">
-        <v>20.661</v>
+        <v>1.478</v>
       </c>
       <c r="M114" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>91.64</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>92.33</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.47</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>91.95</v>
+        <v>93.2</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>87.27</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>91.52</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L115" s="2" t="n">
-        <v>20.661</v>
+        <v>1.478</v>
       </c>
       <c r="M115" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>R4_0_A0_FULL12_FROZEN</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
           <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>80.77</v>
+        <v>82.42</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>84.27</v>
+        <v>83.87</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>91.91</v>
+        <v>92.12</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>82.48</v>
+        <v>83.14</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>70.19</v>
+        <v>71.14</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>77.23</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>20.661</v>
+        <v>15.125</v>
       </c>
       <c r="M116" s="2" t="n">
         <v>26.3246</v>
@@ -6626,55 +6624,421 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>R4_1_VIT4_OLDHEAD</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>8.195</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>24.1021</v>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>10.7311</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>83.81</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>10.9824</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>3.514</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>11.5239</v>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
         <is>
           <t>Run1</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr">
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
-      <c r="E117" s="2" t="n">
+      <c r="E124" s="2" t="n">
         <v>93.62</v>
       </c>
-      <c r="F117" s="2" t="n">
+      <c r="F124" s="2" t="n">
         <v>96.09</v>
       </c>
-      <c r="G117" s="2" t="n">
+      <c r="G124" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="H117" s="2" t="n">
+      <c r="H124" s="2" t="n">
         <v>94.84</v>
       </c>
-      <c r="I117" s="2" t="n">
+      <c r="I124" s="2" t="n">
         <v>90.18000000000001</v>
       </c>
-      <c r="J117" s="2" t="n">
+      <c r="J124" s="2" t="n">
         <v>94.63</v>
       </c>
-      <c r="K117" s="2" t="n">
+      <c r="K124" s="2" t="n">
         <v>11.754</v>
       </c>
-      <c r="L117" s="2" t="n">
+      <c r="L124" s="2" t="n">
         <v>20.661</v>
       </c>
-      <c r="M117" s="2" t="n">
+      <c r="M124" s="2" t="n">
         <v>26.3246</v>
       </c>
-      <c r="N117" t="inlineStr">
+      <c r="N124" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N117"/>
+  <autoFilter ref="A1:N124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$136</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N124"/>
+  <dimension ref="A1:N136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6138,17 +6138,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6157,52 +6157,50 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>93.13</v>
+        <v>97.41</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>95.16</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>99.36</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>94.13</v>
+        <v>97.42</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>88.91</v>
+        <v>94.98</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M108" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M108" s="2" t="n"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6211,52 +6209,50 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>86.37</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>89.25</v>
+        <v>92.58</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>98.78</v>
+        <v>99.14</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>91.42</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>84.19</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>87.14</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M109" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M109" s="2" t="n"/>
       <c r="N109" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6265,52 +6261,50 @@
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>80.38</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>84.5</v>
+        <v>85.22</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>91.81</v>
+        <v>92.09</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>70.55</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>76.84</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M110" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M110" s="2" t="n"/>
       <c r="N110" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6319,52 +6313,50 @@
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>90.16</v>
+        <v>92.87</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>93.97</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>99.38</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>92.02</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>85.23</v>
+        <v>89.44</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>91.7</v>
+        <v>94.2</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M111" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M111" s="2" t="n"/>
       <c r="N111" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6373,52 +6365,50 @@
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>94.7</v>
+        <v>97.52</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>96.13</v>
+        <v>97.42</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>98.88</v>
+        <v>99.38</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>95.41</v>
+        <v>97.47</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>91.22</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>94.77</v>
+        <v>97.11</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>3.455</v>
+        <v>3.060525</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M112" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.144192</v>
+      </c>
+      <c r="M112" s="2" t="n"/>
       <c r="N112" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6427,52 +6417,50 @@
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>88.42</v>
+        <v>90.48</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>91.97</v>
+        <v>92.91</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>99.02</v>
+        <v>99.16</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>90.16</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>82.08</v>
+        <v>84.64</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>89.64</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>3.455</v>
+        <v>3.060525</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M113" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.144192</v>
+      </c>
+      <c r="M113" s="2" t="n"/>
       <c r="N113" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6481,52 +6469,50 @@
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>78.73</v>
+        <v>83.2</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>84.98</v>
+        <v>80.95</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>91.7</v>
+        <v>91.42</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>82.06</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>69.11</v>
+        <v>69.58</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>76.38</v>
+        <v>76.42</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>3.455</v>
+        <v>3.060525</v>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M114" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.144192</v>
+      </c>
+      <c r="M114" s="2" t="n"/>
       <c r="N114" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6535,160 +6521,154 @@
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>91.64</v>
+        <v>92.36</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>95.44</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>99.47</v>
+        <v>99.52</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>93.2</v>
+        <v>93.88</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>87.27</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>93.63</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>3.455</v>
+        <v>3.060525</v>
       </c>
       <c r="L115" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.144192</v>
+      </c>
+      <c r="M115" s="2" t="n"/>
       <c r="N115" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>82.42</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>83.87</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>92.12</v>
+        <v>99.38</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>83.14</v>
+        <v>97.47</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>71.14</v>
+        <v>95.06</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>97.11</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>11.754</v>
+        <v>3.077293</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>26.3246</v>
-      </c>
+        <v>3.16096</v>
+      </c>
+      <c r="M116" s="2" t="n"/>
       <c r="N116" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>90.45</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>91.94</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>82.77</v>
+        <v>91.55</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>70.61</v>
+        <v>84.42</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>91.11</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>8.195</v>
+        <v>3.077293</v>
       </c>
       <c r="L117" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M117" s="2" t="n">
-        <v>24.1021</v>
-      </c>
+        <v>3.16096</v>
+      </c>
+      <c r="M117" s="2" t="n"/>
       <c r="N117" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6697,348 +6677,992 @@
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>79.94</v>
+        <v>78.5</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>91.89</v>
+        <v>91.97</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>82.3</v>
+        <v>82.17</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>69.92</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>77</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>5.492</v>
+        <v>3.077293</v>
       </c>
       <c r="L118" s="2" t="n">
-        <v>3.515</v>
-      </c>
-      <c r="M118" s="2" t="n">
-        <v>10.7311</v>
-      </c>
+        <v>3.16096</v>
+      </c>
+      <c r="M118" s="2" t="n"/>
       <c r="N118" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>80.87</v>
+        <v>91.88</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>83.81</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>91.81</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>93.41</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>69.95</v>
+        <v>87.63</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>93.14</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>5.533</v>
+        <v>3.077293</v>
       </c>
       <c r="L119" s="2" t="n">
-        <v>3.556</v>
-      </c>
-      <c r="M119" s="2" t="n">
-        <v>10.9824</v>
-      </c>
+        <v>3.16096</v>
+      </c>
+      <c r="M119" s="2" t="n"/>
       <c r="N119" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>79.78</v>
+        <v>93.13</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>84.39</v>
+        <v>95.16</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>91.75</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>82.02</v>
+        <v>94.13</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>69.52</v>
+        <v>88.91</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>5.491</v>
+        <v>2.596</v>
       </c>
       <c r="L120" s="2" t="n">
-        <v>3.514</v>
+        <v>0.62</v>
       </c>
       <c r="M120" s="2" t="n">
-        <v>11.5239</v>
+        <v>2.2136</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>97.72</v>
+        <v>86.37</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>97.78</v>
+        <v>89.25</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>99.44</v>
+        <v>98.78</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>97.75</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>87.14</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L121" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M121" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>92.33</v>
+        <v>84.5</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.81</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>91.95</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>91.52</v>
+        <v>76.84</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L122" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M122" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>80.77</v>
+        <v>90.16</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>84.27</v>
+        <v>93.97</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>91.91</v>
+        <v>99.38</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>82.48</v>
+        <v>92.02</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>70.19</v>
+        <v>85.23</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>77.23</v>
+        <v>91.7</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L123" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M123" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>96.13</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>95.41</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>94.77</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>91.97</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>78.73</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>84.98</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>69.11</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>76.38</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>87.27</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>R4_0_A0_FULL12_FROZEN</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>82.42</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>83.87</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>92.12</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>R4_1_VIT4_OLDHEAD</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>8.195</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>24.1021</v>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>10.7311</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>83.81</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>10.9824</v>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>3.514</v>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>11.5239</v>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
         <is>
           <t>Run1</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr">
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J133" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
-      <c r="E124" s="2" t="n">
+      <c r="E136" s="2" t="n">
         <v>93.62</v>
       </c>
-      <c r="F124" s="2" t="n">
+      <c r="F136" s="2" t="n">
         <v>96.09</v>
       </c>
-      <c r="G124" s="2" t="n">
+      <c r="G136" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="H124" s="2" t="n">
+      <c r="H136" s="2" t="n">
         <v>94.84</v>
       </c>
-      <c r="I124" s="2" t="n">
+      <c r="I136" s="2" t="n">
         <v>90.18000000000001</v>
       </c>
-      <c r="J124" s="2" t="n">
+      <c r="J136" s="2" t="n">
         <v>94.63</v>
       </c>
-      <c r="K124" s="2" t="n">
+      <c r="K136" s="2" t="n">
         <v>11.754</v>
       </c>
-      <c r="L124" s="2" t="n">
+      <c r="L136" s="2" t="n">
         <v>20.661</v>
       </c>
-      <c r="M124" s="2" t="n">
+      <c r="M136" s="2" t="n">
         <v>26.3246</v>
       </c>
-      <c r="N124" t="inlineStr">
+      <c r="N136" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N124"/>
+  <autoFilter ref="A1:N136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$148</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N136"/>
+  <dimension ref="A1:N148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6762,17 +6762,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6781,52 +6781,50 @@
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>93.13</v>
+        <v>97.5</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>95.16</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>99.36</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>94.13</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>88.91</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L120" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M120" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M120" s="2" t="n"/>
       <c r="N120" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6835,52 +6833,50 @@
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>86.37</v>
+        <v>90.69</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>89.25</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>98.78</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>91.55</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>84.42</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>87.14</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L121" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M121" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M121" s="2" t="n"/>
       <c r="N121" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6889,52 +6885,50 @@
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>82.58</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>84.5</v>
+        <v>82.25</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>91.81</v>
+        <v>91.69</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>82.42</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>70.09</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>76.84</v>
+        <v>76.98</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M122" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M122" s="2" t="n"/>
       <c r="N122" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6943,52 +6937,50 @@
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>90.16</v>
+        <v>92.31</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>93.97</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>99.38</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>92.02</v>
+        <v>93.44</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>85.23</v>
+        <v>87.69</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>91.7</v>
+        <v>93.17</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L123" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M123" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M123" s="2" t="n"/>
       <c r="N123" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6997,52 +6989,50 @@
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>94.7</v>
+        <v>97.53</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>96.13</v>
+        <v>97.38</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>98.88</v>
+        <v>99.37</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>95.41</v>
+        <v>97.45</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>91.22</v>
+        <v>95.03</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>94.77</v>
+        <v>97.09</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L124" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M124" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M124" s="2" t="n"/>
       <c r="N124" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7051,52 +7041,50 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>88.42</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>91.97</v>
+        <v>91.77</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>99.02</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>90.16</v>
+        <v>91.05</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>82.08</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>89.64</v>
+        <v>90.58</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L125" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M125" s="2" t="n"/>
       <c r="N125" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7105,52 +7093,50 @@
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>78.73</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>84.98</v>
+        <v>85.91</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>91.7</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>80.83</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>69.11</v>
+        <v>67.83</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>76.38</v>
+        <v>75.37</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L126" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M126" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M126" s="2" t="n"/>
       <c r="N126" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -7159,160 +7145,154 @@
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>91.64</v>
+        <v>93.55</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>95.95</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>99.47</v>
+        <v>99.59</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>93.2</v>
+        <v>94.73</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>87.27</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L127" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M127" s="2" t="n"/>
       <c r="N127" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>82.42</v>
+        <v>97.45</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>83.87</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>92.12</v>
+        <v>99.38</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>83.14</v>
+        <v>97.47</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>71.14</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>97.12</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>11.754</v>
+        <v>3.067561</v>
       </c>
       <c r="L128" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M128" s="2" t="n">
-        <v>26.3246</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M128" s="2" t="n"/>
       <c r="N128" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>90.67</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>92.58</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>91.94</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>82.77</v>
+        <v>91.62</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>70.61</v>
+        <v>84.53</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>91.17</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>8.195</v>
+        <v>3.067561</v>
       </c>
       <c r="L129" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M129" s="2" t="n">
-        <v>24.1021</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M129" s="2" t="n"/>
       <c r="N129" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -7321,348 +7301,992 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>79.94</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>87.42</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>91.89</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>82.3</v>
+        <v>82.39</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>69.92</v>
+        <v>70.05</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>77.36</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>5.492</v>
+        <v>3.067561</v>
       </c>
       <c r="L130" s="2" t="n">
-        <v>3.515</v>
-      </c>
-      <c r="M130" s="2" t="n">
-        <v>10.7311</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M130" s="2" t="n"/>
       <c r="N130" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>80.87</v>
+        <v>92.61</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>83.81</v>
+        <v>95.77</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>91.81</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>94.16</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>69.95</v>
+        <v>88.97</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>5.533</v>
+        <v>3.067561</v>
       </c>
       <c r="L131" s="2" t="n">
-        <v>3.556</v>
-      </c>
-      <c r="M131" s="2" t="n">
-        <v>10.9824</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M131" s="2" t="n"/>
       <c r="N131" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>79.78</v>
+        <v>93.13</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>84.39</v>
+        <v>95.16</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>91.75</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>82.02</v>
+        <v>94.13</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>69.52</v>
+        <v>88.91</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>5.491</v>
+        <v>2.596</v>
       </c>
       <c r="L132" s="2" t="n">
-        <v>3.514</v>
+        <v>0.62</v>
       </c>
       <c r="M132" s="2" t="n">
-        <v>11.5239</v>
+        <v>2.2136</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>97.72</v>
+        <v>86.37</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>97.78</v>
+        <v>89.25</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>99.44</v>
+        <v>98.78</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>97.75</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>87.14</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L133" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M133" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>92.33</v>
+        <v>84.5</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.81</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>91.95</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>91.52</v>
+        <v>76.84</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L134" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M134" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>80.77</v>
+        <v>90.16</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>84.27</v>
+        <v>93.97</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>91.91</v>
+        <v>99.38</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>82.48</v>
+        <v>92.02</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>70.19</v>
+        <v>85.23</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>77.23</v>
+        <v>91.7</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L135" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M135" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>96.13</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>95.41</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>94.77</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>91.97</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>78.73</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>84.98</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>69.11</v>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>76.38</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>87.27</v>
+      </c>
+      <c r="J139" s="2" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>R4_0_A0_FULL12_FROZEN</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>82.42</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>83.87</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>92.12</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>R4_1_VIT4_OLDHEAD</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="J141" s="2" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>8.195</v>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>24.1021</v>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>10.7311</v>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>83.81</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="J143" s="2" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>10.9824</v>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>3.514</v>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>11.5239</v>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
         <is>
           <t>Run1</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr">
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G145" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
-      <c r="E136" s="2" t="n">
+      <c r="E148" s="2" t="n">
         <v>93.62</v>
       </c>
-      <c r="F136" s="2" t="n">
+      <c r="F148" s="2" t="n">
         <v>96.09</v>
       </c>
-      <c r="G136" s="2" t="n">
+      <c r="G148" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="H136" s="2" t="n">
+      <c r="H148" s="2" t="n">
         <v>94.84</v>
       </c>
-      <c r="I136" s="2" t="n">
+      <c r="I148" s="2" t="n">
         <v>90.18000000000001</v>
       </c>
-      <c r="J136" s="2" t="n">
+      <c r="J148" s="2" t="n">
         <v>94.63</v>
       </c>
-      <c r="K136" s="2" t="n">
+      <c r="K148" s="2" t="n">
         <v>11.754</v>
       </c>
-      <c r="L136" s="2" t="n">
+      <c r="L148" s="2" t="n">
         <v>20.661</v>
       </c>
-      <c r="M136" s="2" t="n">
+      <c r="M148" s="2" t="n">
         <v>26.3246</v>
       </c>
-      <c r="N136" t="inlineStr">
+      <c r="N148" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N136"/>
+  <autoFilter ref="A1:N148"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$160</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N148"/>
+  <dimension ref="A1:N160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7386,17 +7386,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7405,52 +7405,50 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>93.13</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>95.16</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>99.37</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>94.13</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>88.91</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L132" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M132" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M132" s="2" t="n"/>
       <c r="N132" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -7459,52 +7457,50 @@
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>86.37</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>89.25</v>
+        <v>92.27</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>98.78</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>87.14</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L133" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M133" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M133" s="2" t="n"/>
       <c r="N133" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7513,52 +7509,50 @@
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>79.92</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>84.5</v>
+        <v>84.81</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>91.81</v>
+        <v>91.89</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>69.91</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>76.84</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L134" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M134" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M134" s="2" t="n"/>
       <c r="N134" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7567,52 +7561,50 @@
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>90.16</v>
+        <v>92.78</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>93.97</v>
+        <v>95.23</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>99.38</v>
+        <v>99.53</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>92.02</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>85.23</v>
+        <v>88.66</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>91.7</v>
+        <v>93.75</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L135" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M135" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M135" s="2" t="n"/>
       <c r="N135" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7621,52 +7613,50 @@
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>94.7</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>96.13</v>
+        <v>97.45</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>98.88</v>
+        <v>99.37</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>95.41</v>
+        <v>97.47</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>91.22</v>
+        <v>95.06</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>94.77</v>
+        <v>97.11</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L136" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M136" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M136" s="2" t="n"/>
       <c r="N136" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7675,52 +7665,50 @@
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>88.42</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>91.97</v>
+        <v>93.42</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>99.02</v>
+        <v>99.16</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>90.16</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>82.08</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>89.64</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L137" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M137" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M137" s="2" t="n"/>
       <c r="N137" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7729,52 +7717,50 @@
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>78.73</v>
+        <v>77.78</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>84.98</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>91.7</v>
+        <v>91.28</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>69.11</v>
+        <v>67.77</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>76.38</v>
+        <v>75.16</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L138" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M138" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M138" s="2" t="n"/>
       <c r="N138" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7783,160 +7769,154 @@
         </is>
       </c>
       <c r="E139" s="2" t="n">
-        <v>91.64</v>
+        <v>93.05</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>96.14</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>99.47</v>
+        <v>99.58</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>93.2</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>87.27</v>
+        <v>89.7</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L139" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M139" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M139" s="2" t="n"/>
       <c r="N139" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>82.42</v>
+        <v>97.41</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>83.87</v>
+        <v>97.53</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>92.12</v>
+        <v>99.38</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>83.14</v>
+        <v>97.47</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>71.14</v>
+        <v>95.06</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>97.11</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>11.754</v>
+        <v>3.067561</v>
       </c>
       <c r="L140" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M140" s="2" t="n">
-        <v>26.3246</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M140" s="2" t="n"/>
       <c r="N140" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>91.98</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>91.94</v>
+        <v>99.12</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>82.77</v>
+        <v>91.33</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>70.61</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>90.87</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>8.195</v>
+        <v>3.067561</v>
       </c>
       <c r="L141" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M141" s="2" t="n">
-        <v>24.1021</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M141" s="2" t="n"/>
       <c r="N141" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7945,348 +7925,992 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>79.94</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>85.53</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>91.89</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>82.3</v>
+        <v>81.14</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>69.92</v>
+        <v>68.27</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>5.492</v>
+        <v>3.067561</v>
       </c>
       <c r="L142" s="2" t="n">
-        <v>3.515</v>
-      </c>
-      <c r="M142" s="2" t="n">
-        <v>10.7311</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M142" s="2" t="n"/>
       <c r="N142" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E143" s="2" t="n">
-        <v>80.87</v>
+        <v>92.63</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>83.81</v>
+        <v>96.55</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>91.81</v>
+        <v>99.58</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>94.55</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>69.95</v>
+        <v>89.67</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>94.33</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>5.533</v>
+        <v>3.067561</v>
       </c>
       <c r="L143" s="2" t="n">
-        <v>3.556</v>
-      </c>
-      <c r="M143" s="2" t="n">
-        <v>10.9824</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M143" s="2" t="n"/>
       <c r="N143" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>79.78</v>
+        <v>93.13</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>84.39</v>
+        <v>95.16</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>91.75</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>82.02</v>
+        <v>94.13</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>69.52</v>
+        <v>88.91</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>5.491</v>
+        <v>2.596</v>
       </c>
       <c r="L144" s="2" t="n">
-        <v>3.514</v>
+        <v>0.62</v>
       </c>
       <c r="M144" s="2" t="n">
-        <v>11.5239</v>
+        <v>2.2136</v>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>97.72</v>
+        <v>86.37</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>97.78</v>
+        <v>89.25</v>
       </c>
       <c r="G145" s="2" t="n">
-        <v>99.44</v>
+        <v>98.78</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>97.75</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>87.14</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L145" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M145" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E146" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>92.33</v>
+        <v>84.5</v>
       </c>
       <c r="G146" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.81</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>91.95</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>91.52</v>
+        <v>76.84</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L146" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M146" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>80.77</v>
+        <v>90.16</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>84.27</v>
+        <v>93.97</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>91.91</v>
+        <v>99.38</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>82.48</v>
+        <v>92.02</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>70.19</v>
+        <v>85.23</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>77.23</v>
+        <v>91.7</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L147" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M147" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>96.13</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>95.41</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>94.77</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>91.97</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>78.73</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>84.98</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>69.11</v>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>76.38</v>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="G151" s="2" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>87.27</v>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>R4_0_A0_FULL12_FROZEN</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>82.42</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>83.87</v>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>92.12</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>R4_1_VIT4_OLDHEAD</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G153" s="2" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>8.195</v>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>24.1021</v>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>10.7311</v>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>83.81</v>
+      </c>
+      <c r="G155" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>10.9824</v>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="G156" s="2" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>3.514</v>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>11.5239</v>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
         <is>
           <t>Run1</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr">
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G157" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G158" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G159" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
-      <c r="E148" s="2" t="n">
+      <c r="E160" s="2" t="n">
         <v>93.62</v>
       </c>
-      <c r="F148" s="2" t="n">
+      <c r="F160" s="2" t="n">
         <v>96.09</v>
       </c>
-      <c r="G148" s="2" t="n">
+      <c r="G160" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="H148" s="2" t="n">
+      <c r="H160" s="2" t="n">
         <v>94.84</v>
       </c>
-      <c r="I148" s="2" t="n">
+      <c r="I160" s="2" t="n">
         <v>90.18000000000001</v>
       </c>
-      <c r="J148" s="2" t="n">
+      <c r="J160" s="2" t="n">
         <v>94.63</v>
       </c>
-      <c r="K148" s="2" t="n">
+      <c r="K160" s="2" t="n">
         <v>11.754</v>
       </c>
-      <c r="L148" s="2" t="n">
+      <c r="L160" s="2" t="n">
         <v>20.661</v>
       </c>
-      <c r="M148" s="2" t="n">
+      <c r="M160" s="2" t="n">
         <v>26.3246</v>
       </c>
-      <c r="N148" t="inlineStr">
+      <c r="N160" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N148"/>
+  <autoFilter ref="A1:N160"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$172</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N160"/>
+  <dimension ref="A1:N172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -533,42 +533,40 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>94.08</v>
+        <v>96.73</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>95.26000000000001</v>
+        <v>96.87</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>98.69</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>94.67</v>
+        <v>96.8</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>89.87</v>
+        <v>93.8</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>93.92</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2.378</v>
+        <v>1.93581</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.047125</v>
+      </c>
+      <c r="M2" s="2" t="n"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -578,7 +576,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -587,42 +585,40 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>88.55</v>
+        <v>90.42</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>91.3</v>
+        <v>91.48999999999999</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>98.98999999999999</v>
+        <v>99.08</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>89.90000000000001</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>81.66</v>
+        <v>83.41</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>89.37</v>
+        <v>90.47</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2.378</v>
+        <v>1.93581</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.047125</v>
+      </c>
+      <c r="M3" s="2" t="n"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -632,7 +628,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -641,42 +637,40 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>82.09</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>82.84</v>
+        <v>85.69</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>91.77</v>
+        <v>91.58</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>82.47</v>
+        <v>81.22</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>70.16</v>
+        <v>68.37</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>77.09</v>
+        <v>75.81</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2.378</v>
+        <v>1.93581</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.047125</v>
+      </c>
+      <c r="M4" s="2" t="n"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -686,7 +680,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -695,42 +689,40 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>92.34</v>
+        <v>92.83</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>95.36</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>93.7</v>
+        <v>94.08</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>88.15000000000001</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>93.44</v>
+        <v>93.84</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2.378</v>
+        <v>1.93581</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.047125</v>
+      </c>
+      <c r="M5" s="2" t="n"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -740,7 +732,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -749,42 +741,40 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>93.90000000000001</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>95.19</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>98.66</v>
+        <v>99.2</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>94.54000000000001</v>
+        <v>96.75</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>89.64</v>
+        <v>93.7</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>93.78</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2.416</v>
+        <v>1.952266</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.063581</v>
+      </c>
+      <c r="M6" s="2" t="n"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -794,7 +784,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -803,42 +793,40 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>88.81999999999999</v>
+        <v>89.59</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>90.93000000000001</v>
+        <v>92.42</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>98.98</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>89.87</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>81.59999999999999</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>89.33</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2.416</v>
+        <v>1.952266</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.063581</v>
+      </c>
+      <c r="M7" s="2" t="n"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -848,7 +836,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -857,42 +845,40 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>79.66</v>
+        <v>77.34</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>85.53</v>
+        <v>86.3</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>92.03</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>82.48999999999999</v>
+        <v>81.58</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>70.2</v>
+        <v>68.88</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>77.34</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2.416</v>
+        <v>1.952266</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.063581</v>
+      </c>
+      <c r="M8" s="2" t="n"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -902,7 +888,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -911,42 +897,40 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>91.81999999999999</v>
+        <v>92.63</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>95.56</v>
+        <v>95.34</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>99.53</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>93.65000000000001</v>
+        <v>93.97</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>88.06999999999999</v>
+        <v>88.62</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>93.40000000000001</v>
+        <v>93.72</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2.416</v>
+        <v>1.952266</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.063581</v>
+      </c>
+      <c r="M9" s="2" t="n"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -956,7 +940,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -965,42 +949,40 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>95.05</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>96.02</v>
+        <v>96.83</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>95.53</v>
+        <v>96.75</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>91.45</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>94.91</v>
+        <v>96.3</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2.378</v>
+        <v>1.952266</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.063581</v>
+      </c>
+      <c r="M10" s="2" t="n"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1010,7 +992,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1019,42 +1001,40 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>88.98999999999999</v>
+        <v>89.95</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>91.62</v>
+        <v>92.37</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>99.02</v>
+        <v>99.11</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>90.28</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>82.29000000000001</v>
+        <v>83.73</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>89.77</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2.378</v>
+        <v>1.952266</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.063581</v>
+      </c>
+      <c r="M11" s="2" t="n"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1064,7 +1044,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1073,42 +1053,40 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>79.3</v>
+        <v>79.52</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>85.94</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>92.06</v>
+        <v>91.73</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>82.48999999999999</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>70.19</v>
+        <v>69.39</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>77.36</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2.378</v>
+        <v>1.952266</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.063581</v>
+      </c>
+      <c r="M12" s="2" t="n"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1118,7 +1096,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1127,35 +1105,33 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>92.15000000000001</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>94.7</v>
+        <v>95.33</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>99.48</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>93.41</v>
+        <v>93.78</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>87.63</v>
+        <v>88.3</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>93.14</v>
+        <v>93.53</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>2.378</v>
+        <v>1.952266</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.063581</v>
+      </c>
+      <c r="M13" s="2" t="n"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1148,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1181,31 +1157,31 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>95.06</v>
+        <v>94.08</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>96.01000000000001</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>98.69</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>95.54000000000001</v>
+        <v>94.67</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>91.45</v>
+        <v>89.87</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>94.91</v>
+        <v>93.92</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1226,7 +1202,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1235,31 +1211,31 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>89.47</v>
+        <v>88.55</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>91.28</v>
+        <v>91.3</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>99.03</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>90.37</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>82.43000000000001</v>
+        <v>81.66</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>89.86</v>
+        <v>89.37</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1280,7 +1256,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1289,31 +1265,31 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>81.39</v>
+        <v>82.09</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>84.72</v>
+        <v>82.84</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>92.15000000000001</v>
+        <v>91.77</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>83.02</v>
+        <v>82.47</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>70.97</v>
+        <v>70.16</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>77.92</v>
+        <v>77.09</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1334,7 +1310,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1343,31 +1319,31 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>92</v>
+        <v>92.34</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>99.51000000000001</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>93.72</v>
+        <v>93.7</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>88.19</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>93.47</v>
+        <v>93.44</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1378,275 +1354,331 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_INJ</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>90.38</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>91.91</v>
+        <v>95.19</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>98.66</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>91.14</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>83.72</v>
+        <v>89.64</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>90.66</v>
-      </c>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
+        <v>93.78</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_INJ</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>81.18000000000001</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>82.19</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>91.41</v>
+        <v>98.98</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>81.68000000000001</v>
+        <v>89.87</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>69.04000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>76.08</v>
-      </c>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
+        <v>89.33</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_SUP</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>90.63</v>
+        <v>79.66</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>91.56</v>
+        <v>85.53</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>92.03</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>91.09</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>83.64</v>
+        <v>70.2</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>90.62</v>
+        <v>77.34</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>31.978582</v>
-      </c>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
+        <v>2.416</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_SUP</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>81.28</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>82.75</v>
+        <v>95.56</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>91.59</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>82.01000000000001</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>69.5</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>76.52</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>31.978582</v>
-      </c>
-      <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="n"/>
+        <v>2.416</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_V2</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>90.52</v>
+        <v>95.05</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>91.84999999999999</v>
+        <v>96.02</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>99.11</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>95.53</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>83.79000000000001</v>
+        <v>91.45</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>90.70999999999999</v>
-      </c>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
+        <v>94.91</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>1.2051</v>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_V2</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>79.34</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>84.23999999999999</v>
+        <v>91.62</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>91.63</v>
+        <v>99.02</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>81.72</v>
+        <v>90.28</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>69.09</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="n"/>
+        <v>89.77</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>1.2051</v>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1656,51 +1688,51 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>96.58</v>
+        <v>79.3</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>96.94</v>
+        <v>85.94</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>99.2</v>
+        <v>92.06</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>96.76000000000001</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>93.73</v>
+        <v>70.19</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>96.31</v>
+        <v>77.36</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>4.88</v>
+        <v>2.378</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>4.88</v>
+        <v>2.378</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2051</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1710,51 +1742,51 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>89.52</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>92.69</v>
+        <v>94.7</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>99.11</v>
+        <v>99.48</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>91.08</v>
+        <v>93.41</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>83.62</v>
+        <v>87.63</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>90.61</v>
+        <v>93.14</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>4.88</v>
+        <v>2.378</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>4.88</v>
+        <v>2.378</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2051</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1764,51 +1796,51 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>95.06</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>85.01000000000001</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>91.94</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>82.39</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>70.06</v>
+        <v>91.45</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>77.18000000000001</v>
+        <v>94.91</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2365</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1818,51 +1850,51 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>92.69</v>
+        <v>89.47</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>96.95999999999999</v>
+        <v>91.28</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>99.59</v>
+        <v>99.03</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>94.78</v>
+        <v>90.37</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>90.08</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>94.56999999999999</v>
+        <v>89.86</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2365</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1872,51 +1904,51 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>96.62</v>
+        <v>81.39</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>96.88</v>
+        <v>84.72</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>99.2</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>96.75</v>
+        <v>83.02</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>93.7</v>
+        <v>70.97</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>96.29000000000001</v>
+        <v>77.92</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2365</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1926,44 +1958,44 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>89.95</v>
+        <v>92</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>92.13</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>91.03</v>
+        <v>93.72</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>83.53</v>
+        <v>88.19</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>90.55</v>
+        <v>93.47</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2365</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
@@ -1973,51 +2005,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>Exploration/Exp1/STG_INJ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>80.14</v>
+        <v>90.38</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>84.18000000000001</v>
+        <v>91.91</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>91.76000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>82.11</v>
+        <v>91.14</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>69.65000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>76.76000000000001</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>90.66</v>
+      </c>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -2027,51 +2049,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>Exploration/Exp1/STG_INJ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>92.45</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>97.37</v>
+        <v>82.19</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>91.41</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>94.84</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>90.19</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>94.64</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>76.08</v>
+      </c>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -2081,51 +2093,43 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>Exploration/Exp1/STG_SUP</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>97.02</v>
+        <v>90.63</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>97.20999999999999</v>
+        <v>91.56</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>99.29000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>97.11</v>
+        <v>91.09</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>94.39</v>
+        <v>83.64</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>96.70999999999999</v>
+        <v>90.62</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>31.978582</v>
+      </c>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -2135,51 +2139,43 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>Exploration/Exp1/STG_SUP</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>89.59</v>
+        <v>81.28</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>92.84</v>
+        <v>82.75</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>99.12</v>
+        <v>91.59</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>91.19</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>83.81</v>
+        <v>69.5</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>90.73</v>
+        <v>76.52</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M33" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>31.978582</v>
+      </c>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -2189,51 +2185,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>Exploration/Exp1/STG_V2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>81.23999999999999</v>
+        <v>90.52</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>85.29000000000001</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>92.27</v>
+        <v>99.11</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>83.20999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>71.25</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M34" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>90.70999999999999</v>
+      </c>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -2243,51 +2229,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>Exploration/Exp1/STG_V2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>93.09999999999999</v>
+        <v>79.34</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>96.01000000000001</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>99.56999999999999</v>
+        <v>91.63</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>94.53</v>
+        <v>81.72</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>89.63</v>
+        <v>69.09</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>94.31</v>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M35" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>76.3</v>
+      </c>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2280,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2313,22 +2289,22 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>97.03</v>
+        <v>96.58</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>97.33</v>
+        <v>96.94</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>97.18000000000001</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>94.51000000000001</v>
+        <v>93.73</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>96.78</v>
+        <v>96.31</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>4.88</v>
@@ -2358,7 +2334,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2367,22 +2343,22 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>90.33</v>
+        <v>89.52</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>91.81999999999999</v>
+        <v>92.69</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.11</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>91.06999999999999</v>
+        <v>91.08</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>83.62</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>90.59</v>
+        <v>90.61</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>4.88</v>
@@ -2412,7 +2388,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2421,22 +2397,22 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>84.41</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>82.55</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>92.12</v>
+        <v>91.94</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>83.47</v>
+        <v>82.39</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>71.63</v>
+        <v>70.06</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>78.29000000000001</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>4.88</v>
@@ -2466,7 +2442,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2475,22 +2451,22 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>93.56</v>
+        <v>92.69</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>96.62</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>99.61</v>
+        <v>99.59</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>94.78</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>90.08</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>94.87</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>4.88</v>
@@ -2515,12 +2491,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2529,22 +2505,22 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>97.02</v>
+        <v>96.62</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>97.27</v>
+        <v>96.88</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>97.14</v>
+        <v>96.75</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>94.45</v>
+        <v>93.7</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>96.73999999999999</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>4.88</v>
@@ -2569,12 +2545,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2583,22 +2559,22 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>90.64</v>
+        <v>89.95</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>91.64</v>
+        <v>92.13</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>99.09999999999999</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>91.14</v>
+        <v>91.03</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>83.72</v>
+        <v>83.53</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>90.66</v>
+        <v>90.55</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>4.88</v>
@@ -2623,12 +2599,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2637,22 +2613,22 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>80.94</v>
+        <v>80.14</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>85.43000000000001</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>92.25</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>83.13</v>
+        <v>82.11</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>71.12</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>4.88</v>
@@ -2677,12 +2653,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2691,22 +2667,22 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>93.73999999999999</v>
+        <v>92.45</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>96.67</v>
+        <v>97.37</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>99.62</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>95.18000000000001</v>
+        <v>94.84</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>90.81</v>
+        <v>90.19</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>94.98999999999999</v>
+        <v>94.64</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>4.88</v>
@@ -2731,12 +2707,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2748,28 +2724,28 @@
         <v>97.02</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>97.33</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>99.3</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>97.17</v>
+        <v>97.11</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>94.5</v>
+        <v>94.39</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>96.78</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -2785,12 +2761,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2799,31 +2775,31 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>90.22</v>
+        <v>89.59</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>92.22</v>
+        <v>92.84</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>99.11</v>
+        <v>99.12</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>91.19</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>83.83</v>
+        <v>83.81</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>90.73999999999999</v>
+        <v>90.73</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -2839,12 +2815,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2853,31 +2829,31 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>80.09999999999999</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>86.05</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>92.23999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>82.97</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>70.89</v>
+        <v>71.25</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>77.95999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -2893,12 +2869,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2907,31 +2883,31 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>93.45999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>96</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>99.59</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>94.70999999999999</v>
+        <v>94.53</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>89.95</v>
+        <v>89.63</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>94.48999999999999</v>
+        <v>94.31</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -2947,12 +2923,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2961,10 +2937,10 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>97.02</v>
+        <v>97.03</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>97.34</v>
+        <v>97.33</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>99.3</v>
@@ -2979,13 +2955,13 @@
         <v>96.78</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -3001,12 +2977,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3015,31 +2991,31 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>90.20999999999999</v>
+        <v>90.33</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>92.41</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>99.12</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>91.29000000000001</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>83.98</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>90.83</v>
+        <v>90.59</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -3055,12 +3031,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3069,31 +3045,31 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>80.69</v>
+        <v>84.41</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>85.12</v>
+        <v>82.55</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>92.12</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>82.84999999999999</v>
+        <v>83.47</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>70.72</v>
+        <v>71.63</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>77.73999999999999</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -3109,12 +3085,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3123,31 +3099,31 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>93.8</v>
+        <v>93.56</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>96.18000000000001</v>
+        <v>96.62</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>99.61</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>94.98</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>90.44</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>94.77</v>
+        <v>94.87</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -3163,12 +3139,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3180,19 +3156,19 @@
         <v>97.02</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>97.25</v>
+        <v>97.27</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>99.29000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>97.13</v>
+        <v>97.14</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>94.42</v>
+        <v>94.45</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>96.73</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>4.88</v>
@@ -3217,12 +3193,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3231,22 +3207,22 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>90.05</v>
+        <v>90.64</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>92.12</v>
+        <v>91.64</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>99.09999999999999</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>91.06999999999999</v>
+        <v>91.14</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>83.72</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>90.66</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>4.88</v>
@@ -3271,12 +3247,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3285,19 +3261,19 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>81.44</v>
+        <v>80.94</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>84.94</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>92.22</v>
+        <v>92.25</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>83.16</v>
+        <v>83.13</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>71.17</v>
+        <v>71.12</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>78.09999999999999</v>
@@ -3325,12 +3301,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3339,22 +3315,22 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>93.42</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>96.66</v>
+        <v>96.67</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>99.61</v>
+        <v>99.62</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>95.02</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>90.5</v>
+        <v>90.81</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>94.81</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>4.88</v>
@@ -3379,12 +3355,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3393,31 +3369,31 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>97.03</v>
+        <v>97.02</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>97.23999999999999</v>
+        <v>97.33</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>99.29000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>97.13</v>
+        <v>97.17</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>94.43000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>96.73</v>
+        <v>96.78</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6947</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -3433,12 +3409,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3447,31 +3423,31 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>90.25</v>
+        <v>90.22</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>92.12</v>
+        <v>92.22</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>99.11</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>83.78</v>
+        <v>83.83</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>90.70999999999999</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6947</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -3487,12 +3463,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3501,31 +3477,31 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>81.26000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>85.31</v>
+        <v>86.05</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>92.28</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>83.23999999999999</v>
+        <v>82.97</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>71.29000000000001</v>
+        <v>70.89</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>78.23</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6947</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -3541,12 +3517,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3555,31 +3531,31 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>93.11</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>96.78</v>
+        <v>96</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.59</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>94.91</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>90.31</v>
+        <v>89.95</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>94.7</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6947</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -3595,12 +3571,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3609,31 +3585,31 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>96.97</v>
+        <v>97.02</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>97.08</v>
+        <v>97.34</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>99.27</v>
+        <v>99.3</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>97.02</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>94.22</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>96.59999999999999</v>
+        <v>96.78</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2.717</v>
+        <v>2.6947</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -3649,12 +3625,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3663,31 +3639,31 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>90.15000000000001</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>92.33</v>
+        <v>92.41</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>99.12</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>91.23</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>83.87</v>
+        <v>83.98</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>90.76000000000001</v>
+        <v>90.83</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2.717</v>
+        <v>2.6947</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -3703,12 +3679,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3717,31 +3693,31 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>81.90000000000001</v>
+        <v>80.69</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>84.53</v>
+        <v>85.12</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>92.2</v>
+        <v>92.12</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>83.19</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>71.22</v>
+        <v>70.72</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>78.11</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2.717</v>
+        <v>2.6947</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -3757,12 +3733,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3771,31 +3747,31 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>94.02</v>
+        <v>93.8</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>96.37</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>99.62</v>
+        <v>99.61</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>95.18000000000001</v>
+        <v>94.98</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>90.8</v>
+        <v>90.44</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>94.98</v>
+        <v>94.77</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2.717</v>
+        <v>2.6947</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -3811,12 +3787,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3825,22 +3801,22 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>96.94</v>
+        <v>97.02</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>97.17</v>
+        <v>97.25</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>99.27</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>97.05</v>
+        <v>97.13</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>94.27</v>
+        <v>94.42</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>96.64</v>
+        <v>96.73</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>4.88</v>
@@ -3865,12 +3841,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3879,22 +3855,22 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>90.09</v>
+        <v>90.05</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>92.62</v>
+        <v>92.12</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>99.13</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>91.34</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>84.06</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>90.88</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>4.88</v>
@@ -3919,12 +3895,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3933,22 +3909,22 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>81.09999999999999</v>
+        <v>81.44</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>85.65000000000001</v>
+        <v>84.94</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>92.34</v>
+        <v>92.22</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>83.31</v>
+        <v>83.16</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>71.17</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>78.34999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>4.88</v>
@@ -3973,12 +3949,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3987,22 +3963,22 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>93.8</v>
+        <v>93.42</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>96.38</v>
+        <v>96.66</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>99.61</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>95.02</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>90.61</v>
+        <v>90.5</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>94.87</v>
+        <v>94.81</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>4.88</v>
@@ -4027,12 +4003,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4041,31 +4017,31 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>97</v>
+        <v>97.03</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>97.33</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>99.3</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>97.17</v>
+        <v>97.13</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>94.48999999999999</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>96.77</v>
+        <v>96.73</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.9767</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
@@ -4081,12 +4057,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4095,31 +4071,31 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>89.63</v>
+        <v>90.25</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>92.70999999999999</v>
+        <v>92.12</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>99.11</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>91.15000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>83.73</v>
+        <v>83.78</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>90.68000000000001</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.9767</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
@@ -4135,12 +4111,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4149,31 +4125,31 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>80.41</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>85.06999999999999</v>
+        <v>85.31</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>92.05</v>
+        <v>92.28</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>82.68000000000001</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>70.47</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>77.53</v>
+        <v>78.23</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.9767</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
@@ -4189,12 +4165,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4203,31 +4179,31 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>93.44</v>
+        <v>93.11</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>96.28</v>
+        <v>96.78</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>94.84</v>
+        <v>94.91</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>90.19</v>
+        <v>90.31</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>94.63</v>
+        <v>94.7</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.9767</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -4243,49 +4219,49 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Run8</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CTRL_R8</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>90.43000000000001</v>
+        <v>96.97</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>92.01000000000001</v>
+        <v>97.08</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>99.11</v>
+        <v>99.27</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>97.02</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>83.84</v>
+        <v>94.22</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>90.73999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>31.026</v>
+        <v>4.89</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>31.026</v>
+        <v>4.89</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>13.6715</v>
+        <v>2.717</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>casa_vmamba_str</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -4297,49 +4273,49 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Run8</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CTRL_R8</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>79.66</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>84.22</v>
+        <v>92.33</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>91.69</v>
+        <v>99.12</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>81.88</v>
+        <v>91.23</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>69.31999999999999</v>
+        <v>83.87</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>76.48999999999999</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>31.026</v>
+        <v>4.89</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>31.026</v>
+        <v>4.89</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>13.6715</v>
+        <v>2.717</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>casa_vmamba_str</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -4351,49 +4327,49 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Run9</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>S0_CTRL</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>97.77</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>97.77</v>
+        <v>84.53</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>99.45</v>
+        <v>92.2</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>97.77</v>
+        <v>83.19</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>95.65000000000001</v>
+        <v>71.22</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>97.45999999999999</v>
+        <v>78.11</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>31.977</v>
+        <v>4.89</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>31.977</v>
+        <v>4.89</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>14.6841</v>
+        <v>2.717</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -4405,49 +4381,49 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Run9</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>S0_CTRL</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>89.79000000000001</v>
+        <v>94.02</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>92.53</v>
+        <v>96.37</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>99.11</v>
+        <v>99.62</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>91.14</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>83.72</v>
+        <v>90.8</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>90.67</v>
+        <v>94.98</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>31.977</v>
+        <v>4.89</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>31.977</v>
+        <v>4.89</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>14.6841</v>
+        <v>2.717</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -4459,12 +4435,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Run9</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>S1_HSAM</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4473,260 +4449,268 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>97.66</v>
+        <v>96.94</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>97.65000000000001</v>
+        <v>97.17</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>99.42</v>
+        <v>99.27</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>97.65000000000001</v>
+        <v>97.05</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>95.42</v>
+        <v>94.27</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>97.31999999999999</v>
+        <v>96.64</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>31.977</v>
+        <v>4.88</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>31.977</v>
+        <v>4.88</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>14.769</v>
+        <v>2.6747</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>80.27</v>
+        <v>90.09</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>85.19</v>
+        <v>92.62</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>92.06</v>
+        <v>99.13</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>82.65000000000001</v>
+        <v>91.34</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>70.44</v>
+        <v>84.06</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>90.88</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>3.016737</v>
+        <v>4.88</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M77" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_none</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>91.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>91.72</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>99.13</v>
+        <v>92.34</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>91.45999999999999</v>
+        <v>83.31</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>84.26000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>91</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>3.016737</v>
+        <v>4.88</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M78" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_none</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>80.39</v>
+        <v>93.8</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>82.89</v>
+        <v>96.38</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>91.45999999999999</v>
+        <v>99.61</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>81.62</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>68.95</v>
+        <v>90.61</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>76.06999999999999</v>
+        <v>94.87</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>3.016737</v>
+        <v>4.88</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M79" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_none</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>92.61</v>
+        <v>97</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>95.26000000000001</v>
+        <v>97.33</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>99.52</v>
+        <v>99.3</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>93.92</v>
+        <v>97.17</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>88.53</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>93.67</v>
+        <v>96.77</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>3.016737</v>
+        <v>4.88</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M80" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_none</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4735,50 +4719,52 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>90.55</v>
+        <v>89.63</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>92.03</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>99.12</v>
+        <v>99.11</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>91.28</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>83.95999999999999</v>
+        <v>83.73</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>90.81999999999999</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>3.049509</v>
+        <v>4.88</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M81" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_hyperbolic</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4787,50 +4773,52 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>78.67</v>
+        <v>80.41</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>85.08</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>91.72</v>
+        <v>92.05</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>81.75</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>69.13</v>
+        <v>70.47</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>76.40000000000001</v>
+        <v>77.53</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>3.049509</v>
+        <v>4.88</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M82" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_hyperbolic</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4839,50 +4827,52 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>92.84999999999999</v>
+        <v>93.44</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>95.31999999999999</v>
+        <v>96.28</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>99.54000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>94.06999999999999</v>
+        <v>94.84</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>88.8</v>
+        <v>90.19</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>93.83</v>
+        <v>94.63</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>3.049509</v>
+        <v>4.88</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M83" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_hyperbolic</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run8</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>CTRL_R8</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4891,50 +4881,52 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>89.72</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>93.12</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>99.14</v>
+        <v>99.11</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>91.39</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>84.14</v>
+        <v>83.84</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>90.93000000000001</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>3.049509</v>
+        <v>31.026</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M84" s="2" t="n"/>
+        <v>31.026</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>13.6715</v>
+      </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>casa_vmamba_str</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run8</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>CTRL_R8</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4943,102 +4935,106 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>82.83</v>
+        <v>79.66</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>82.86</v>
+        <v>84.22</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>91.91</v>
+        <v>91.69</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>82.84999999999999</v>
+        <v>81.88</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>70.72</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>77.56</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>3.049509</v>
+        <v>31.026</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M85" s="2" t="n"/>
+        <v>31.026</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>13.6715</v>
+      </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>casa_vmamba_str</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run9</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>S0_CTRL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>93.04000000000001</v>
+        <v>97.77</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>96.08</v>
+        <v>97.77</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>99.56999999999999</v>
+        <v>99.45</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>94.53</v>
+        <v>97.77</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>89.63</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>94.31</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>3.049509</v>
+        <v>31.977</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M86" s="2" t="n"/>
+        <v>31.977</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>14.6841</v>
+      </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run9</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>S0_CTRL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5047,96 +5043,96 @@
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>91.09</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>92.8</v>
+        <v>92.53</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>99.19</v>
+        <v>99.11</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>91.94</v>
+        <v>91.14</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>85.08</v>
+        <v>83.72</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>90.67</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>11.754</v>
+        <v>31.977</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>20.661</v>
+        <v>31.977</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>26.3183</v>
+        <v>14.6841</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run9</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>S1_HSAM</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>80.3</v>
+        <v>97.66</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>84.81</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>99.42</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>82.5</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>95.42</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>11.754</v>
+        <v>31.977</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>20.661</v>
+        <v>31.977</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>26.3183</v>
+        <v>14.769</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5146,105 +5142,101 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>80.27</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>92.75</v>
+        <v>85.19</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>92.06</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>91.86</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>84.94</v>
+        <v>70.44</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>11.754</v>
+        <v>3.016737</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M89" s="2" t="n">
-        <v>26.2593</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M89" s="2" t="n"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>80.55</v>
+        <v>91.2</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>84.23</v>
+        <v>91.72</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>91.86</v>
+        <v>99.13</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>82.34999999999999</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>70</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>77.06</v>
+        <v>91</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>11.754</v>
+        <v>3.016737</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M90" s="2" t="n">
-        <v>26.2593</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M90" s="2" t="n"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5254,51 +5246,49 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>91.38</v>
+        <v>80.39</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>92.3</v>
+        <v>82.89</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>99.17</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>91.84</v>
+        <v>81.62</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>84.91</v>
+        <v>68.95</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>11.754</v>
+        <v>3.016737</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M91" s="2" t="n">
-        <v>26.1484</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M91" s="2" t="n"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5308,51 +5298,49 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>92.61</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>86.03</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>99.52</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>93.92</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>69.55</v>
+        <v>88.53</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>76.83</v>
+        <v>93.67</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>11.754</v>
+        <v>3.016737</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M92" s="2" t="n">
-        <v>26.1484</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M92" s="2" t="n"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5362,7 +5350,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5371,42 +5359,40 @@
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>91.13</v>
+        <v>90.55</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>92.03</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.12</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>91.88</v>
+        <v>91.28</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>84.98</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>91.45</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M93" s="2" t="n">
-        <v>26.0894</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M93" s="2" t="n"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5416,7 +5402,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5425,366 +5411,366 @@
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>78.67</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>85.05</v>
+        <v>85.08</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>92.36</v>
+        <v>91.72</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>83.52</v>
+        <v>81.75</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>71.7</v>
+        <v>69.13</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>78.55</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M94" s="2" t="n">
-        <v>26.0894</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M94" s="2" t="n"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>84.28</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>91.7</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>81.92</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>69.37</v>
+        <v>88.8</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>93.83</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M95" s="2" t="n">
-        <v>26.0894</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M95" s="2" t="n"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>89.72</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>97.47</v>
+        <v>93.12</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>99.37</v>
+        <v>99.14</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>97.45</v>
+        <v>91.39</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>95.02</v>
+        <v>84.14</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>97.09</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>3.016737</v>
+        <v>3.049509</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>3.100404</v>
+        <v>3.133176</v>
       </c>
       <c r="M96" s="2" t="n"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>90.41</v>
+        <v>82.83</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>91.83</v>
+        <v>82.86</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>91.11</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>83.67</v>
+        <v>70.72</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>90.64</v>
+        <v>77.56</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>3.016737</v>
+        <v>3.049509</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>3.100404</v>
+        <v>3.133176</v>
       </c>
       <c r="M97" s="2" t="n"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>79.81</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>83.84999999999999</v>
+        <v>96.08</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>91.61</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>81.78</v>
+        <v>94.53</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>69.18000000000001</v>
+        <v>89.63</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>76.34</v>
+        <v>94.31</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>3.016737</v>
+        <v>3.049509</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>3.100404</v>
+        <v>3.133176</v>
       </c>
       <c r="M98" s="2" t="n"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>93.2</v>
+        <v>91.09</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>94.70999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>99.52</v>
+        <v>99.19</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>93.95</v>
+        <v>91.94</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>88.59</v>
+        <v>85.08</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>93.7</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>3.016737</v>
+        <v>11.754</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M99" s="2" t="n"/>
+        <v>20.661</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>26.3183</v>
+      </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>97.48</v>
+        <v>80.3</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>97.45</v>
+        <v>84.81</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>99.37</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>97.47</v>
+        <v>82.5</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>95.06</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>97.11</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>3.050665</v>
+        <v>11.754</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>3.134332</v>
-      </c>
-      <c r="M100" s="2" t="n"/>
+        <v>20.661</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>26.3183</v>
+      </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5793,50 +5779,52 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>90.61</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>92.37</v>
+        <v>92.75</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>99.14</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>91.48</v>
+        <v>91.86</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>84.3</v>
+        <v>84.94</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>91.03</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>3.050665</v>
+        <v>11.754</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>3.134332</v>
-      </c>
-      <c r="M101" s="2" t="n"/>
+        <v>20.661</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>26.2593</v>
+      </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5845,154 +5833,160 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>77.55</v>
+        <v>80.55</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>85.81</v>
+        <v>84.23</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>91.68000000000001</v>
+        <v>91.86</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>81.47</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>68.73</v>
+        <v>70</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>76.12</v>
+        <v>77.06</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>3.050665</v>
+        <v>11.754</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>3.134332</v>
-      </c>
-      <c r="M102" s="2" t="n"/>
+        <v>20.661</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>26.2593</v>
+      </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>92.5</v>
+        <v>91.38</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>96.20999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>99.56</v>
+        <v>99.17</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>94.31999999999999</v>
+        <v>91.84</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>89.25</v>
+        <v>84.91</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>94.09</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>3.050665</v>
+        <v>11.754</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>3.134332</v>
-      </c>
-      <c r="M103" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>26.1484</v>
+      </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>97.51000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>97.45</v>
+        <v>86.03</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>99.38</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>97.48</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>95.09</v>
+        <v>69.55</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>97.13</v>
+        <v>76.83</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>3.059369</v>
+        <v>11.754</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>3.143036</v>
-      </c>
-      <c r="M104" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>26.1484</v>
+      </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6001,50 +5995,52 @@
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>90.58</v>
+        <v>91.13</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>91.77</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>99.11</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>91.17</v>
+        <v>91.88</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>83.77</v>
+        <v>84.98</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>90.7</v>
+        <v>91.45</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>3.059369</v>
+        <v>11.754</v>
       </c>
       <c r="L105" s="2" t="n">
-        <v>3.143036</v>
-      </c>
-      <c r="M105" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>26.0894</v>
+      </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6053,40 +6049,42 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>76.7</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>85.81999999999999</v>
+        <v>85.05</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>91.52</v>
+        <v>92.36</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>81.01000000000001</v>
+        <v>83.52</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>68.06999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>75.56999999999999</v>
+        <v>78.55</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>3.059369</v>
+        <v>11.754</v>
       </c>
       <c r="L106" s="2" t="n">
-        <v>3.143036</v>
-      </c>
-      <c r="M106" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>26.0894</v>
+      </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6096,42 +6094,44 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>A4_DETAIL_FROZEN</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>92.61</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>95.31</v>
+        <v>84.28</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>99.53</v>
+        <v>91.7</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>93.94</v>
+        <v>81.92</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>88.58</v>
+        <v>69.37</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>93.69</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>3.059369</v>
+        <v>11.754</v>
       </c>
       <c r="L107" s="2" t="n">
-        <v>3.143036</v>
-      </c>
-      <c r="M107" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>26.0894</v>
+      </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6157,22 +6157,22 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>97.41</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>97.47</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>99.36</v>
+        <v>99.37</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>97.42</v>
+        <v>97.45</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>94.98</v>
+        <v>95.02</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>97.06</v>
+        <v>97.09</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>3.016737</v>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6209,22 +6209,22 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>90.29000000000001</v>
+        <v>90.41</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>92.58</v>
+        <v>91.83</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>99.14</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>91.42</v>
+        <v>91.11</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>84.19</v>
+        <v>83.67</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>90.95999999999999</v>
+        <v>90.64</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>3.016737</v>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6261,22 +6261,22 @@
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>80.38</v>
+        <v>79.81</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>85.22</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>92.09</v>
+        <v>91.61</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>82.73</v>
+        <v>81.78</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>70.55</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>77.59999999999999</v>
+        <v>76.34</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>3.016737</v>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6313,22 +6313,22 @@
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>92.87</v>
+        <v>93.2</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>96.04000000000001</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>99.56999999999999</v>
+        <v>99.52</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>94.43000000000001</v>
+        <v>93.95</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>89.44</v>
+        <v>88.59</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>94.2</v>
+        <v>93.7</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>3.016737</v>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6365,28 +6365,28 @@
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>97.52</v>
+        <v>97.48</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>97.42</v>
+        <v>97.45</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>99.38</v>
+        <v>99.37</v>
       </c>
       <c r="H112" s="2" t="n">
         <v>97.47</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>95.06</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>97.11</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>3.060525</v>
+        <v>3.050665</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>3.144192</v>
+        <v>3.134332</v>
       </c>
       <c r="M112" s="2" t="n"/>
       <c r="N112" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6417,28 +6417,28 @@
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>90.48</v>
+        <v>90.61</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>92.91</v>
+        <v>92.37</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>99.16</v>
+        <v>99.14</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>91.68000000000001</v>
+        <v>91.48</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>84.64</v>
+        <v>84.3</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>91.23999999999999</v>
+        <v>91.03</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>3.060525</v>
+        <v>3.050665</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>3.144192</v>
+        <v>3.134332</v>
       </c>
       <c r="M113" s="2" t="n"/>
       <c r="N113" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6469,28 +6469,28 @@
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>83.2</v>
+        <v>77.55</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>80.95</v>
+        <v>85.81</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>91.42</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>82.06</v>
+        <v>81.47</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>69.58</v>
+        <v>68.73</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>76.42</v>
+        <v>76.12</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>3.060525</v>
+        <v>3.050665</v>
       </c>
       <c r="L114" s="2" t="n">
-        <v>3.144192</v>
+        <v>3.134332</v>
       </c>
       <c r="M114" s="2" t="n"/>
       <c r="N114" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6521,28 +6521,28 @@
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>92.36</v>
+        <v>92.5</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>95.44</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>99.52</v>
+        <v>99.56</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>93.88</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>88.45999999999999</v>
+        <v>89.25</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>93.63</v>
+        <v>94.09</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>3.060525</v>
+        <v>3.050665</v>
       </c>
       <c r="L115" s="2" t="n">
-        <v>3.144192</v>
+        <v>3.134332</v>
       </c>
       <c r="M115" s="2" t="n"/>
       <c r="N115" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6573,28 +6573,28 @@
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>97.51000000000001</v>
+        <v>97.45</v>
       </c>
       <c r="G116" s="2" t="n">
         <v>99.38</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>97.47</v>
+        <v>97.48</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>95.06</v>
+        <v>95.09</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>97.11</v>
+        <v>97.13</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>3.077293</v>
+        <v>3.059369</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>3.16096</v>
+        <v>3.143036</v>
       </c>
       <c r="M116" s="2" t="n"/>
       <c r="N116" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6625,28 +6625,28 @@
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>90.45</v>
+        <v>90.58</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>92.68000000000001</v>
+        <v>91.77</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>99.15000000000001</v>
+        <v>99.11</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>91.55</v>
+        <v>91.17</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>84.42</v>
+        <v>83.77</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>91.11</v>
+        <v>90.7</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>3.077293</v>
+        <v>3.059369</v>
       </c>
       <c r="L117" s="2" t="n">
-        <v>3.16096</v>
+        <v>3.143036</v>
       </c>
       <c r="M117" s="2" t="n"/>
       <c r="N117" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6677,28 +6677,28 @@
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>78.5</v>
+        <v>76.7</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>86.2</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>91.97</v>
+        <v>91.52</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>82.17</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>69.73999999999999</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>77</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>3.077293</v>
+        <v>3.059369</v>
       </c>
       <c r="L118" s="2" t="n">
-        <v>3.16096</v>
+        <v>3.143036</v>
       </c>
       <c r="M118" s="2" t="n"/>
       <c r="N118" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6729,28 +6729,28 @@
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>91.88</v>
+        <v>92.61</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>94.98999999999999</v>
+        <v>95.31</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>99.48999999999999</v>
+        <v>99.53</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>93.41</v>
+        <v>93.94</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>87.63</v>
+        <v>88.58</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>93.14</v>
+        <v>93.69</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>3.077293</v>
+        <v>3.059369</v>
       </c>
       <c r="L119" s="2" t="n">
-        <v>3.16096</v>
+        <v>3.143036</v>
       </c>
       <c r="M119" s="2" t="n"/>
       <c r="N119" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6781,22 +6781,22 @@
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>97.5</v>
+        <v>97.41</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>97.34999999999999</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="G120" s="2" t="n">
         <v>99.36</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>97.42</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>94.98999999999999</v>
+        <v>94.98</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>97.06999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>3.016737</v>
@@ -6819,7 +6819,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6833,22 +6833,22 @@
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>90.69</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>92.43000000000001</v>
+        <v>92.58</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>99.15000000000001</v>
+        <v>99.14</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>91.55</v>
+        <v>91.42</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>84.42</v>
+        <v>84.19</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>3.016737</v>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6885,22 +6885,22 @@
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>82.58</v>
+        <v>80.38</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>82.25</v>
+        <v>85.22</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>91.69</v>
+        <v>92.09</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>82.42</v>
+        <v>82.73</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>70.09</v>
+        <v>70.55</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>76.98</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>3.016737</v>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6937,22 +6937,22 @@
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>92.31</v>
+        <v>92.87</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>94.59999999999999</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>99.48999999999999</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>93.44</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>87.69</v>
+        <v>89.44</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>93.17</v>
+        <v>94.2</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>3.016737</v>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6989,28 +6989,28 @@
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>97.53</v>
+        <v>97.52</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>97.38</v>
+        <v>97.42</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>99.37</v>
+        <v>99.38</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>97.45</v>
+        <v>97.47</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>95.03</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>97.09</v>
+        <v>97.11</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.060525</v>
       </c>
       <c r="L124" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.144192</v>
       </c>
       <c r="M124" s="2" t="n"/>
       <c r="N124" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7041,28 +7041,28 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>90.34999999999999</v>
+        <v>90.48</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>91.77</v>
+        <v>92.91</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.16</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>91.05</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>83.56999999999999</v>
+        <v>84.64</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>90.58</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.060525</v>
       </c>
       <c r="L125" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.144192</v>
       </c>
       <c r="M125" s="2" t="n"/>
       <c r="N125" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7093,28 +7093,28 @@
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>76.31999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>85.91</v>
+        <v>80.95</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>91.45999999999999</v>
+        <v>91.42</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>80.83</v>
+        <v>82.06</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>67.83</v>
+        <v>69.58</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>75.37</v>
+        <v>76.42</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.060525</v>
       </c>
       <c r="L126" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.144192</v>
       </c>
       <c r="M126" s="2" t="n"/>
       <c r="N126" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7145,28 +7145,28 @@
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>93.55</v>
+        <v>92.36</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>95.95</v>
+        <v>95.44</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>99.59</v>
+        <v>99.52</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>94.73</v>
+        <v>93.88</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>89.98999999999999</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>94.52</v>
+        <v>93.63</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.060525</v>
       </c>
       <c r="L127" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.144192</v>
       </c>
       <c r="M127" s="2" t="n"/>
       <c r="N127" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>97.45</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>97.48999999999999</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="G128" s="2" t="n">
         <v>99.38</v>
@@ -7209,16 +7209,16 @@
         <v>97.47</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>95.06</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>97.12</v>
+        <v>97.11</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.077293</v>
       </c>
       <c r="L128" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.16096</v>
       </c>
       <c r="M128" s="2" t="n"/>
       <c r="N128" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7249,28 +7249,28 @@
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>90.67</v>
+        <v>90.45</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>92.58</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="G129" s="2" t="n">
         <v>99.15000000000001</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>91.62</v>
+        <v>91.55</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>84.53</v>
+        <v>84.42</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>91.17</v>
+        <v>91.11</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.077293</v>
       </c>
       <c r="L129" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.16096</v>
       </c>
       <c r="M129" s="2" t="n"/>
       <c r="N129" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7301,28 +7301,28 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>77.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>87.42</v>
+        <v>86.2</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>92.15000000000001</v>
+        <v>91.97</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>82.39</v>
+        <v>82.17</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>70.05</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>77.36</v>
+        <v>77</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.077293</v>
       </c>
       <c r="L130" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.16096</v>
       </c>
       <c r="M130" s="2" t="n"/>
       <c r="N130" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7353,28 +7353,28 @@
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>92.61</v>
+        <v>91.88</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>95.77</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>99.54000000000001</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>94.16</v>
+        <v>93.41</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>88.97</v>
+        <v>87.63</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>93.93000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.077293</v>
       </c>
       <c r="L131" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.16096</v>
       </c>
       <c r="M131" s="2" t="n"/>
       <c r="N131" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7405,13 +7405,13 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>97.31999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>97.54000000000001</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>99.37</v>
+        <v>99.36</v>
       </c>
       <c r="H132" s="2" t="n">
         <v>97.43000000000001</v>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>89.79000000000001</v>
+        <v>90.69</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>92.27</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>91.01000000000001</v>
+        <v>91.55</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>83.51000000000001</v>
+        <v>84.42</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>90.54000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>3.016737</v>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7509,22 +7509,22 @@
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>79.92</v>
+        <v>82.58</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>84.81</v>
+        <v>82.25</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>91.89</v>
+        <v>91.69</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>82.29000000000001</v>
+        <v>82.42</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>69.91</v>
+        <v>70.09</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>76.98</v>
       </c>
       <c r="K134" s="2" t="n">
         <v>3.016737</v>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7561,22 +7561,22 @@
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>92.78</v>
+        <v>92.31</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>95.23</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>99.53</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>93.98999999999999</v>
+        <v>93.44</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>88.66</v>
+        <v>87.69</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>93.75</v>
+        <v>93.17</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>3.016737</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7613,22 +7613,22 @@
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>97.48999999999999</v>
+        <v>97.53</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>97.45</v>
+        <v>97.38</v>
       </c>
       <c r="G136" s="2" t="n">
         <v>99.37</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>97.47</v>
+        <v>97.45</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>95.06</v>
+        <v>95.03</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>97.11</v>
+        <v>97.09</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>3.050665</v>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7665,22 +7665,22 @@
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>89.73999999999999</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>93.42</v>
+        <v>91.77</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>99.16</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>91.54000000000001</v>
+        <v>91.05</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>84.40000000000001</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>90.58</v>
       </c>
       <c r="K137" s="2" t="n">
         <v>3.050665</v>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7717,22 +7717,22 @@
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>77.78</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>84.04000000000001</v>
+        <v>85.91</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>91.28</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>80.79000000000001</v>
+        <v>80.83</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>67.77</v>
+        <v>67.83</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>75.16</v>
+        <v>75.37</v>
       </c>
       <c r="K138" s="2" t="n">
         <v>3.050665</v>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7769,22 +7769,22 @@
         </is>
       </c>
       <c r="E139" s="2" t="n">
-        <v>93.05</v>
+        <v>93.55</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>96.14</v>
+        <v>95.95</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>99.58</v>
+        <v>99.59</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>94.56999999999999</v>
+        <v>94.73</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>89.7</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>94.34999999999999</v>
+        <v>94.52</v>
       </c>
       <c r="K139" s="2" t="n">
         <v>3.050665</v>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>97.41</v>
+        <v>97.45</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>97.53</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="G140" s="2" t="n">
         <v>99.38</v>
@@ -7833,10 +7833,10 @@
         <v>97.47</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>95.06</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>97.11</v>
+        <v>97.12</v>
       </c>
       <c r="K140" s="2" t="n">
         <v>3.067561</v>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7873,22 +7873,22 @@
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>90.68000000000001</v>
+        <v>90.67</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>91.98</v>
+        <v>92.58</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>99.12</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>91.33</v>
+        <v>91.62</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>84.04000000000001</v>
+        <v>84.53</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>90.87</v>
+        <v>91.17</v>
       </c>
       <c r="K141" s="2" t="n">
         <v>3.067561</v>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7925,22 +7925,22 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>77.18000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>85.53</v>
+        <v>87.42</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>91.54000000000001</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>81.14</v>
+        <v>82.39</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>68.27</v>
+        <v>70.05</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>75.70999999999999</v>
+        <v>77.36</v>
       </c>
       <c r="K142" s="2" t="n">
         <v>3.067561</v>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -7977,22 +7977,22 @@
         </is>
       </c>
       <c r="E143" s="2" t="n">
-        <v>92.63</v>
+        <v>92.61</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>96.55</v>
+        <v>95.77</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>99.58</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>94.55</v>
+        <v>94.16</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>89.67</v>
+        <v>88.97</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>94.33</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="K143" s="2" t="n">
         <v>3.067561</v>
@@ -8010,17 +8010,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8029,52 +8029,50 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>93.13</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>95.16</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>99.37</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>94.13</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>88.91</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L144" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M144" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M144" s="2" t="n"/>
       <c r="N144" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -8083,52 +8081,50 @@
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>86.37</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>89.25</v>
+        <v>92.27</v>
       </c>
       <c r="G145" s="2" t="n">
-        <v>98.78</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>87.14</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L145" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M145" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M145" s="2" t="n"/>
       <c r="N145" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -8137,52 +8133,50 @@
         </is>
       </c>
       <c r="E146" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>79.92</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>84.5</v>
+        <v>84.81</v>
       </c>
       <c r="G146" s="2" t="n">
-        <v>91.81</v>
+        <v>91.89</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>69.91</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>76.84</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L146" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M146" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M146" s="2" t="n"/>
       <c r="N146" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -8191,52 +8185,50 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>90.16</v>
+        <v>92.78</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>93.97</v>
+        <v>95.23</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>99.38</v>
+        <v>99.53</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>92.02</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>85.23</v>
+        <v>88.66</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>91.7</v>
+        <v>93.75</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L147" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M147" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M147" s="2" t="n"/>
       <c r="N147" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -8245,52 +8237,50 @@
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>94.7</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>96.13</v>
+        <v>97.45</v>
       </c>
       <c r="G148" s="2" t="n">
-        <v>98.88</v>
+        <v>99.37</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>95.41</v>
+        <v>97.47</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>91.22</v>
+        <v>95.06</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>94.77</v>
+        <v>97.11</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L148" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M148" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M148" s="2" t="n"/>
       <c r="N148" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -8299,52 +8289,50 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>88.42</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>91.97</v>
+        <v>93.42</v>
       </c>
       <c r="G149" s="2" t="n">
-        <v>99.02</v>
+        <v>99.16</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>90.16</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>82.08</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>89.64</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L149" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M149" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M149" s="2" t="n"/>
       <c r="N149" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -8353,52 +8341,50 @@
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>78.73</v>
+        <v>77.78</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>84.98</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="G150" s="2" t="n">
-        <v>91.7</v>
+        <v>91.28</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>69.11</v>
+        <v>67.77</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>76.38</v>
+        <v>75.16</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L150" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M150" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M150" s="2" t="n"/>
       <c r="N150" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -8407,160 +8393,154 @@
         </is>
       </c>
       <c r="E151" s="2" t="n">
-        <v>91.64</v>
+        <v>93.05</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>96.14</v>
       </c>
       <c r="G151" s="2" t="n">
-        <v>99.47</v>
+        <v>99.58</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>93.2</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>87.27</v>
+        <v>89.7</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L151" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M151" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M151" s="2" t="n"/>
       <c r="N151" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E152" s="2" t="n">
-        <v>82.42</v>
+        <v>97.41</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>83.87</v>
+        <v>97.53</v>
       </c>
       <c r="G152" s="2" t="n">
-        <v>92.12</v>
+        <v>99.38</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>83.14</v>
+        <v>97.47</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>71.14</v>
+        <v>95.06</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>97.11</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>11.754</v>
+        <v>3.067561</v>
       </c>
       <c r="L152" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M152" s="2" t="n">
-        <v>26.3246</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M152" s="2" t="n"/>
       <c r="N152" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E153" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>91.98</v>
       </c>
       <c r="G153" s="2" t="n">
-        <v>91.94</v>
+        <v>99.12</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>82.77</v>
+        <v>91.33</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>70.61</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>90.87</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>8.195</v>
+        <v>3.067561</v>
       </c>
       <c r="L153" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M153" s="2" t="n">
-        <v>24.1021</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M153" s="2" t="n"/>
       <c r="N153" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -8569,348 +8549,992 @@
         </is>
       </c>
       <c r="E154" s="2" t="n">
-        <v>79.94</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>85.53</v>
       </c>
       <c r="G154" s="2" t="n">
-        <v>91.89</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>82.3</v>
+        <v>81.14</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>69.92</v>
+        <v>68.27</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>5.492</v>
+        <v>3.067561</v>
       </c>
       <c r="L154" s="2" t="n">
-        <v>3.515</v>
-      </c>
-      <c r="M154" s="2" t="n">
-        <v>10.7311</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M154" s="2" t="n"/>
       <c r="N154" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>80.87</v>
+        <v>92.63</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>83.81</v>
+        <v>96.55</v>
       </c>
       <c r="G155" s="2" t="n">
-        <v>91.81</v>
+        <v>99.58</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>94.55</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>69.95</v>
+        <v>89.67</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>94.33</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>5.533</v>
+        <v>3.067561</v>
       </c>
       <c r="L155" s="2" t="n">
-        <v>3.556</v>
-      </c>
-      <c r="M155" s="2" t="n">
-        <v>10.9824</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M155" s="2" t="n"/>
       <c r="N155" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E156" s="2" t="n">
-        <v>79.78</v>
+        <v>93.13</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>84.39</v>
+        <v>95.16</v>
       </c>
       <c r="G156" s="2" t="n">
-        <v>91.75</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>82.02</v>
+        <v>94.13</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>69.52</v>
+        <v>88.91</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>5.491</v>
+        <v>2.596</v>
       </c>
       <c r="L156" s="2" t="n">
-        <v>3.514</v>
+        <v>0.62</v>
       </c>
       <c r="M156" s="2" t="n">
-        <v>11.5239</v>
+        <v>2.2136</v>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E157" s="2" t="n">
-        <v>97.72</v>
+        <v>86.37</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>97.78</v>
+        <v>89.25</v>
       </c>
       <c r="G157" s="2" t="n">
-        <v>99.44</v>
+        <v>98.78</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>97.75</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>87.14</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L157" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M157" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E158" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F158" s="2" t="n">
-        <v>92.33</v>
+        <v>84.5</v>
       </c>
       <c r="G158" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.81</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>91.95</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>91.52</v>
+        <v>76.84</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L158" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M158" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>80.77</v>
+        <v>90.16</v>
       </c>
       <c r="F159" s="2" t="n">
-        <v>84.27</v>
+        <v>93.97</v>
       </c>
       <c r="G159" s="2" t="n">
-        <v>91.91</v>
+        <v>99.38</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>82.48</v>
+        <v>92.02</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>70.19</v>
+        <v>85.23</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>77.23</v>
+        <v>91.7</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L159" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M159" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>96.13</v>
+      </c>
+      <c r="G160" s="2" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>95.41</v>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>94.77</v>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>91.97</v>
+      </c>
+      <c r="G161" s="2" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M161" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>78.73</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>84.98</v>
+      </c>
+      <c r="G162" s="2" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>69.11</v>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>76.38</v>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="G163" s="2" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>87.27</v>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>R4_0_A0_FULL12_FROZEN</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>82.42</v>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>83.87</v>
+      </c>
+      <c r="G164" s="2" t="n">
+        <v>92.12</v>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>R4_1_VIT4_OLDHEAD</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G165" s="2" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>8.195</v>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>24.1021</v>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="G166" s="2" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>10.7311</v>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>83.81</v>
+      </c>
+      <c r="G167" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H167" s="2" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="K167" s="2" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="M167" s="2" t="n">
+        <v>10.9824</v>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="G168" s="2" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="K168" s="2" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>3.514</v>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>11.5239</v>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
         <is>
           <t>Run1</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr">
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G169" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K169" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M169" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G170" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G171" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K171" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M171" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
-      <c r="E160" s="2" t="n">
+      <c r="E172" s="2" t="n">
         <v>93.62</v>
       </c>
-      <c r="F160" s="2" t="n">
+      <c r="F172" s="2" t="n">
         <v>96.09</v>
       </c>
-      <c r="G160" s="2" t="n">
+      <c r="G172" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="H160" s="2" t="n">
+      <c r="H172" s="2" t="n">
         <v>94.84</v>
       </c>
-      <c r="I160" s="2" t="n">
+      <c r="I172" s="2" t="n">
         <v>90.18000000000001</v>
       </c>
-      <c r="J160" s="2" t="n">
+      <c r="J172" s="2" t="n">
         <v>94.63</v>
       </c>
-      <c r="K160" s="2" t="n">
+      <c r="K172" s="2" t="n">
         <v>11.754</v>
       </c>
-      <c r="L160" s="2" t="n">
+      <c r="L172" s="2" t="n">
         <v>20.661</v>
       </c>
-      <c r="M160" s="2" t="n">
+      <c r="M172" s="2" t="n">
         <v>26.3246</v>
       </c>
-      <c r="N160" t="inlineStr">
+      <c r="N172" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N160"/>
+  <autoFilter ref="A1:N172"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$174</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N172"/>
+  <dimension ref="A1:N174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1138,71 +1138,69 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2_val</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>94.08</v>
+        <v>89.58</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>95.26000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>98.69</v>
+        <v>99.08</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>94.67</v>
+        <v>90.83</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>89.87</v>
+        <v>83.19</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>93.92</v>
+        <v>90.34</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>2.378</v>
+        <v>1.93581</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.047125</v>
+      </c>
+      <c r="M14" s="2" t="n"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2_val</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1211,35 +1209,33 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>88.55</v>
+        <v>89.88</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>91.3</v>
+        <v>91.91</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>98.98999999999999</v>
+        <v>99.08</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>89.90000000000001</v>
+        <v>90.88</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>81.66</v>
+        <v>83.29000000000001</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>89.37</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2.378</v>
+        <v>1.952266</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.063581</v>
+      </c>
+      <c r="M15" s="2" t="n"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
@@ -1261,26 +1257,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>82.09</v>
+        <v>94.08</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>82.84</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>91.77</v>
+        <v>98.69</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>82.47</v>
+        <v>94.67</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>70.16</v>
+        <v>89.87</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>77.09</v>
+        <v>93.92</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>2.378</v>
@@ -1315,26 +1311,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>92.34</v>
+        <v>88.55</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>93.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>88.15000000000001</v>
+        <v>81.66</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>93.44</v>
+        <v>89.37</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>2.378</v>
@@ -1364,40 +1360,40 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>93.90000000000001</v>
+        <v>82.09</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>95.19</v>
+        <v>82.84</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>98.66</v>
+        <v>91.77</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>94.54000000000001</v>
+        <v>82.47</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>89.64</v>
+        <v>70.16</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>93.78</v>
+        <v>77.09</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1418,40 +1414,40 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>88.81999999999999</v>
+        <v>92.34</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>90.93000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>98.98</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>89.87</v>
+        <v>93.7</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>81.59999999999999</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>89.33</v>
+        <v>93.44</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1477,26 +1473,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>79.66</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>85.53</v>
+        <v>95.19</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>92.03</v>
+        <v>98.66</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>82.48999999999999</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>70.2</v>
+        <v>89.64</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>77.34</v>
+        <v>93.78</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>2.416</v>
@@ -1531,26 +1527,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>91.81999999999999</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>95.56</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>98.98</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>93.65000000000001</v>
+        <v>89.87</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>88.06999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>93.40000000000001</v>
+        <v>89.33</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>2.416</v>
@@ -1580,40 +1576,40 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>95.05</v>
+        <v>79.66</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>96.02</v>
+        <v>85.53</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>92.03</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>95.53</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>91.45</v>
+        <v>70.2</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>94.91</v>
+        <v>77.34</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>2.378</v>
+        <v>2.416</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2.378</v>
+        <v>2.416</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1.2051</v>
+        <v>1.2365</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1634,40 +1630,40 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>88.98999999999999</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>91.62</v>
+        <v>95.56</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>99.02</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>90.28</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>82.29000000000001</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>89.77</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>2.378</v>
+        <v>2.416</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>2.378</v>
+        <v>2.416</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1.2051</v>
+        <v>1.2365</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1693,26 +1689,26 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>79.3</v>
+        <v>95.05</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>85.94</v>
+        <v>96.02</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>92.06</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>82.48999999999999</v>
+        <v>95.53</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>70.19</v>
+        <v>91.45</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>77.36</v>
+        <v>94.91</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>2.378</v>
@@ -1747,26 +1743,26 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>92.15000000000001</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>94.7</v>
+        <v>91.62</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>99.48</v>
+        <v>99.02</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>93.41</v>
+        <v>90.28</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>87.63</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>93.14</v>
+        <v>89.77</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>2.378</v>
@@ -1796,40 +1792,40 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>95.06</v>
+        <v>79.3</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>96.01000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>92.06</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>95.54000000000001</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>91.45</v>
+        <v>70.19</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>94.91</v>
+        <v>77.36</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1850,40 +1846,40 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>89.47</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>91.28</v>
+        <v>94.7</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>99.03</v>
+        <v>99.48</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>90.37</v>
+        <v>93.41</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>82.43000000000001</v>
+        <v>87.63</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>89.86</v>
+        <v>93.14</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -1909,26 +1905,26 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>81.39</v>
+        <v>95.06</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>84.72</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>92.15000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>83.02</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>70.97</v>
+        <v>91.45</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>77.92</v>
+        <v>94.91</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>2.416</v>
@@ -1963,26 +1959,26 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>92</v>
+        <v>89.47</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>91.28</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>99.03</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>93.72</v>
+        <v>90.37</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>88.19</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>93.47</v>
+        <v>89.86</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>2.416</v>
@@ -2002,88 +1998,108 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_INJ</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>90.38</v>
+        <v>81.39</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>91.91</v>
+        <v>84.72</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>91.14</v>
+        <v>83.02</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>83.72</v>
+        <v>70.97</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>90.66</v>
-      </c>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="n"/>
+        <v>77.92</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_INJ</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>81.18000000000001</v>
+        <v>92</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>82.19</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>91.41</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>81.68000000000001</v>
+        <v>93.72</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>69.04000000000001</v>
+        <v>88.19</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>76.08</v>
-      </c>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n"/>
+        <v>93.47</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2112,7 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_SUP</t>
+          <t>Exploration/Exp1/STG_INJ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2105,26 +2121,24 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>90.63</v>
+        <v>90.38</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>91.56</v>
+        <v>91.91</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>99.09999999999999</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>91.09</v>
+        <v>91.14</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>83.64</v>
+        <v>83.72</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>90.62</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>31.978582</v>
-      </c>
+        <v>90.66</v>
+      </c>
+      <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
       <c r="M32" s="2" t="n"/>
       <c r="N32" t="inlineStr">
@@ -2142,7 +2156,7 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_SUP</t>
+          <t>Exploration/Exp1/STG_INJ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2151,26 +2165,24 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>81.28</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>82.75</v>
+        <v>82.19</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>91.59</v>
+        <v>91.41</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>82.01000000000001</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>69.5</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>76.52</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>31.978582</v>
-      </c>
+        <v>76.08</v>
+      </c>
+      <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="n"/>
       <c r="N33" t="inlineStr">
@@ -2188,7 +2200,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_V2</t>
+          <t>Exploration/Exp1/STG_SUP</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2197,24 +2209,26 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>90.52</v>
+        <v>90.63</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>91.84999999999999</v>
+        <v>91.56</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>99.11</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>91.09</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>83.79000000000001</v>
+        <v>83.64</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>90.70999999999999</v>
-      </c>
-      <c r="K34" s="2" t="n"/>
+        <v>90.62</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>31.978582</v>
+      </c>
       <c r="L34" s="2" t="n"/>
       <c r="M34" s="2" t="n"/>
       <c r="N34" t="inlineStr">
@@ -2232,7 +2246,7 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_V2</t>
+          <t>Exploration/Exp1/STG_SUP</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2241,24 +2255,26 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>79.34</v>
+        <v>81.28</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>84.23999999999999</v>
+        <v>82.75</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>91.63</v>
+        <v>91.59</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>81.72</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>69.09</v>
+        <v>69.5</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="K35" s="2" t="n"/>
+        <v>76.52</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>31.978582</v>
+      </c>
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n"/>
       <c r="N35" t="inlineStr">
@@ -2273,51 +2289,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>Exploration/Exp1/STG_V2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>96.58</v>
+        <v>90.52</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>96.94</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>99.2</v>
+        <v>99.11</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>96.76000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>93.73</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>96.31</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M36" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>90.70999999999999</v>
+      </c>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -2327,51 +2333,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>Exploration/Exp1/STG_V2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>89.52</v>
+        <v>79.34</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>92.69</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>99.11</v>
+        <v>91.63</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>91.08</v>
+        <v>81.72</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>83.62</v>
+        <v>69.09</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>90.61</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M37" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>76.3</v>
+      </c>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -2393,26 +2389,26 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>96.58</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>85.01000000000001</v>
+        <v>96.94</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>91.94</v>
+        <v>99.2</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>82.39</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>70.06</v>
+        <v>93.73</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>77.18000000000001</v>
+        <v>96.31</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>4.88</v>
@@ -2447,26 +2443,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
+        <v>89.52</v>
+      </c>
+      <c r="F39" s="2" t="n">
         <v>92.69</v>
       </c>
-      <c r="F39" s="2" t="n">
-        <v>96.95999999999999</v>
-      </c>
       <c r="G39" s="2" t="n">
-        <v>99.59</v>
+        <v>99.11</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>94.78</v>
+        <v>91.08</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>90.08</v>
+        <v>83.62</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>94.56999999999999</v>
+        <v>90.61</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>4.88</v>
@@ -2496,31 +2492,31 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>96.62</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>96.88</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>99.2</v>
+        <v>91.94</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>96.75</v>
+        <v>82.39</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>93.7</v>
+        <v>70.06</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>96.29000000000001</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>4.88</v>
@@ -2550,31 +2546,31 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>89.95</v>
+        <v>92.69</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>92.13</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.59</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>91.03</v>
+        <v>94.78</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>83.53</v>
+        <v>90.08</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>90.55</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>4.88</v>
@@ -2609,26 +2605,26 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>80.14</v>
+        <v>96.62</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>84.18000000000001</v>
+        <v>96.88</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>91.76000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>82.11</v>
+        <v>96.75</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>69.65000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>76.76000000000001</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>4.88</v>
@@ -2663,26 +2659,26 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>92.45</v>
+        <v>89.95</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>97.37</v>
+        <v>92.13</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>94.84</v>
+        <v>91.03</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>90.19</v>
+        <v>83.53</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>94.64</v>
+        <v>90.55</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>4.88</v>
@@ -2712,31 +2708,31 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>97.02</v>
+        <v>80.14</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>97.20999999999999</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>99.29000000000001</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>97.11</v>
+        <v>82.11</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>94.39</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>96.70999999999999</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>4.88</v>
@@ -2766,31 +2762,31 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>89.59</v>
+        <v>92.45</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>92.84</v>
+        <v>97.37</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>99.12</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>91.19</v>
+        <v>94.84</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>83.81</v>
+        <v>90.19</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>90.73</v>
+        <v>94.64</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>4.88</v>
@@ -2825,26 +2821,26 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>81.23999999999999</v>
+        <v>97.02</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>85.29000000000001</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>92.27</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>83.20999999999999</v>
+        <v>97.11</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>71.25</v>
+        <v>94.39</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>78.2</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>4.88</v>
@@ -2879,26 +2875,26 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>93.09999999999999</v>
+        <v>89.59</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>96.01000000000001</v>
+        <v>92.84</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>99.56999999999999</v>
+        <v>99.12</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>94.53</v>
+        <v>91.19</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>89.63</v>
+        <v>83.81</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>94.31</v>
+        <v>90.73</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>4.88</v>
@@ -2928,31 +2924,31 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>97.03</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>97.33</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>99.3</v>
+        <v>92.27</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>97.18000000000001</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>94.51000000000001</v>
+        <v>71.25</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>96.78</v>
+        <v>78.2</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>4.88</v>
@@ -2982,31 +2978,31 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>90.33</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>91.81999999999999</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>91.06999999999999</v>
+        <v>94.53</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>89.63</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>90.59</v>
+        <v>94.31</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>4.88</v>
@@ -3041,26 +3037,26 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>84.41</v>
+        <v>97.03</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>82.55</v>
+        <v>97.33</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>92.12</v>
+        <v>99.3</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>83.47</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>71.63</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>78.29000000000001</v>
+        <v>96.78</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>4.88</v>
@@ -3095,26 +3091,26 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>93.56</v>
+        <v>90.33</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>96.62</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>99.61</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>94.87</v>
+        <v>90.59</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>4.88</v>
@@ -3139,36 +3135,36 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>97.02</v>
+        <v>84.41</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>97.27</v>
+        <v>82.55</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>99.3</v>
+        <v>92.12</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>97.14</v>
+        <v>83.47</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>94.45</v>
+        <v>71.63</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>96.73999999999999</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>4.88</v>
@@ -3193,36 +3189,36 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>90.64</v>
+        <v>93.56</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>91.64</v>
+        <v>96.62</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.61</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>91.14</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>83.72</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>90.66</v>
+        <v>94.87</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>4.88</v>
@@ -3257,26 +3253,26 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>80.94</v>
+        <v>97.02</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>85.43000000000001</v>
+        <v>97.27</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>92.25</v>
+        <v>99.3</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>83.13</v>
+        <v>97.14</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>71.12</v>
+        <v>94.45</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>4.88</v>
@@ -3311,26 +3307,26 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>93.73999999999999</v>
+        <v>90.64</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>96.67</v>
+        <v>91.64</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>99.62</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>95.18000000000001</v>
+        <v>91.14</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>90.81</v>
+        <v>83.72</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>94.98999999999999</v>
+        <v>90.66</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>4.88</v>
@@ -3360,40 +3356,40 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>97.02</v>
+        <v>80.94</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>97.33</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>99.3</v>
+        <v>92.25</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>97.17</v>
+        <v>83.13</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>94.5</v>
+        <v>71.12</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>96.78</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -3414,40 +3410,40 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>90.22</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>92.22</v>
+        <v>96.67</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>99.11</v>
+        <v>99.62</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>83.83</v>
+        <v>90.81</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>90.73999999999999</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -3473,26 +3469,26 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>80.09999999999999</v>
+        <v>97.02</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>86.05</v>
+        <v>97.33</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>92.23999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>82.97</v>
+        <v>97.17</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>70.89</v>
+        <v>94.5</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>77.95999999999999</v>
+        <v>96.78</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>4.881</v>
@@ -3527,26 +3523,26 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>93.45999999999999</v>
+        <v>90.22</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>96</v>
+        <v>92.22</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>99.59</v>
+        <v>99.11</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>94.70999999999999</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>89.95</v>
+        <v>83.83</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>94.48999999999999</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>4.881</v>
@@ -3576,31 +3572,31 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>97.02</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>97.34</v>
+        <v>86.05</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>99.3</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>97.18000000000001</v>
+        <v>82.97</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>94.51000000000001</v>
+        <v>70.89</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>96.78</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>4.881</v>
@@ -3630,31 +3626,31 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>90.20999999999999</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>92.41</v>
+        <v>96</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>99.12</v>
+        <v>99.59</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>91.29000000000001</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>83.98</v>
+        <v>89.95</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>90.83</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>4.881</v>
@@ -3689,26 +3685,26 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>80.69</v>
+        <v>97.02</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>85.12</v>
+        <v>97.34</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>92.12</v>
+        <v>99.3</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>82.84999999999999</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>70.72</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>77.73999999999999</v>
+        <v>96.78</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>4.881</v>
@@ -3743,26 +3739,26 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>93.8</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>96.18000000000001</v>
+        <v>92.41</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>99.61</v>
+        <v>99.12</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>94.98</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>90.44</v>
+        <v>83.98</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>94.77</v>
+        <v>90.83</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>4.881</v>
@@ -3787,45 +3783,45 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>97.02</v>
+        <v>80.69</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>97.25</v>
+        <v>85.12</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>99.29000000000001</v>
+        <v>92.12</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>97.13</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>94.42</v>
+        <v>70.72</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>96.73</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>4.88</v>
+        <v>4.881</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>4.88</v>
+        <v>4.881</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.6947</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -3841,45 +3837,45 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>90.05</v>
+        <v>93.8</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>92.12</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.61</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>91.06999999999999</v>
+        <v>94.98</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>90.44</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>94.77</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>4.88</v>
+        <v>4.881</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>4.88</v>
+        <v>4.881</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.6947</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -3905,26 +3901,26 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>81.44</v>
+        <v>97.02</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>84.94</v>
+        <v>97.25</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>92.22</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>83.16</v>
+        <v>97.13</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>71.17</v>
+        <v>94.42</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>96.73</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>4.88</v>
@@ -3959,26 +3955,26 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>93.42</v>
+        <v>90.05</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>96.66</v>
+        <v>92.12</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>99.61</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>95.02</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>90.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>94.81</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>4.88</v>
@@ -4008,40 +4004,40 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>97.03</v>
+        <v>81.44</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>97.23999999999999</v>
+        <v>84.94</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>99.29000000000001</v>
+        <v>92.22</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>97.13</v>
+        <v>83.16</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>94.43000000000001</v>
+        <v>71.17</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>96.73</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>4.954</v>
+        <v>4.88</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>4.954</v>
+        <v>4.88</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6747</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
@@ -4062,40 +4058,40 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>90.25</v>
+        <v>93.42</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>92.12</v>
+        <v>96.66</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>99.11</v>
+        <v>99.61</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>95.02</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>83.78</v>
+        <v>90.5</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>90.70999999999999</v>
+        <v>94.81</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>4.954</v>
+        <v>4.88</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>4.954</v>
+        <v>4.88</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6747</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
@@ -4121,26 +4117,26 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>81.26000000000001</v>
+        <v>97.03</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>85.31</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>92.28</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>83.23999999999999</v>
+        <v>97.13</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>71.29000000000001</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>78.23</v>
+        <v>96.73</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>4.954</v>
@@ -4175,26 +4171,26 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>93.11</v>
+        <v>90.25</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>96.78</v>
+        <v>92.12</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.11</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>94.91</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>90.31</v>
+        <v>83.78</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>94.7</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>4.954</v>
@@ -4219,45 +4215,45 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>96.97</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>97.08</v>
+        <v>85.31</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>99.27</v>
+        <v>92.28</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>97.02</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>94.22</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>96.59999999999999</v>
+        <v>78.23</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>4.89</v>
+        <v>4.954</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>4.89</v>
+        <v>4.954</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2.717</v>
+        <v>2.9767</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -4273,45 +4269,45 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>90.15000000000001</v>
+        <v>93.11</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>92.33</v>
+        <v>96.78</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>99.12</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>91.23</v>
+        <v>94.91</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>83.87</v>
+        <v>90.31</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>90.76000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>4.89</v>
+        <v>4.954</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>4.89</v>
+        <v>4.954</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2.717</v>
+        <v>2.9767</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
@@ -4337,26 +4333,26 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>81.90000000000001</v>
+        <v>96.97</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>84.53</v>
+        <v>97.08</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>92.2</v>
+        <v>99.27</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>83.19</v>
+        <v>97.02</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>71.22</v>
+        <v>94.22</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>78.11</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>4.89</v>
@@ -4391,26 +4387,26 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>94.02</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>96.37</v>
+        <v>92.33</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>99.62</v>
+        <v>99.12</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>95.18000000000001</v>
+        <v>91.23</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>90.8</v>
+        <v>83.87</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>94.98</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>4.89</v>
@@ -4440,40 +4436,40 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>96.94</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>97.17</v>
+        <v>84.53</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>99.27</v>
+        <v>92.2</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>97.05</v>
+        <v>83.19</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>94.27</v>
+        <v>71.22</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>96.64</v>
+        <v>78.11</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.717</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -4494,40 +4490,40 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>90.09</v>
+        <v>94.02</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>92.62</v>
+        <v>96.37</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>99.13</v>
+        <v>99.62</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>91.34</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>84.06</v>
+        <v>90.8</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>90.88</v>
+        <v>94.98</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.717</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
@@ -4553,26 +4549,26 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>81.09999999999999</v>
+        <v>96.94</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>85.65000000000001</v>
+        <v>97.17</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>92.34</v>
+        <v>99.27</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>83.31</v>
+        <v>97.05</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>94.27</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>78.34999999999999</v>
+        <v>96.64</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>4.88</v>
@@ -4607,26 +4603,26 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>93.8</v>
+        <v>90.09</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>96.38</v>
+        <v>92.62</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>99.61</v>
+        <v>99.13</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>91.34</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>90.61</v>
+        <v>84.06</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>94.87</v>
+        <v>90.88</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>4.88</v>
@@ -4656,31 +4652,31 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>97</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>97.33</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>99.3</v>
+        <v>92.34</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>97.17</v>
+        <v>83.31</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>94.48999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>96.77</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>4.88</v>
@@ -4710,31 +4706,31 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>89.63</v>
+        <v>93.8</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>92.70999999999999</v>
+        <v>96.38</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>99.11</v>
+        <v>99.61</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>91.15000000000001</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>83.73</v>
+        <v>90.61</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>90.68000000000001</v>
+        <v>94.87</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>4.88</v>
@@ -4769,26 +4765,26 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>80.41</v>
+        <v>97</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>85.06999999999999</v>
+        <v>97.33</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>92.05</v>
+        <v>99.3</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>82.68000000000001</v>
+        <v>97.17</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>70.47</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>77.53</v>
+        <v>96.77</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>4.88</v>
@@ -4823,26 +4819,26 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>93.44</v>
+        <v>89.63</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>96.28</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.11</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>94.84</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>90.19</v>
+        <v>83.73</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>94.63</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>4.88</v>
@@ -4867,49 +4863,49 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Run8</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CTRL_R8</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>90.43000000000001</v>
+        <v>80.41</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>92.01000000000001</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>99.11</v>
+        <v>92.05</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>83.84</v>
+        <v>70.47</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>90.73999999999999</v>
+        <v>77.53</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>31.026</v>
+        <v>4.88</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>31.026</v>
+        <v>4.88</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>13.6715</v>
+        <v>2.6747</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>casa_vmamba_str</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -4921,49 +4917,49 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Run8</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CTRL_R8</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>79.66</v>
+        <v>93.44</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>84.22</v>
+        <v>96.28</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>91.69</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>81.88</v>
+        <v>94.84</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>69.31999999999999</v>
+        <v>90.19</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>76.48999999999999</v>
+        <v>94.63</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>31.026</v>
+        <v>4.88</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>31.026</v>
+        <v>4.88</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>13.6715</v>
+        <v>2.6747</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>casa_vmamba_str</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -4975,49 +4971,49 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Run9</t>
+          <t>Run8</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>S0_CTRL</t>
+          <t>CTRL_R8</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>97.77</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>97.77</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>99.45</v>
+        <v>99.11</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>97.77</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>95.65000000000001</v>
+        <v>83.84</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>97.45999999999999</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>31.977</v>
+        <v>31.026</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>31.977</v>
+        <v>31.026</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>14.6841</v>
+        <v>13.6715</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_vmamba_str</t>
         </is>
       </c>
     </row>
@@ -5029,49 +5025,49 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Run9</t>
+          <t>Run8</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>S0_CTRL</t>
+          <t>CTRL_R8</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>89.79000000000001</v>
+        <v>79.66</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>92.53</v>
+        <v>84.22</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>99.11</v>
+        <v>91.69</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>91.14</v>
+        <v>81.88</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>83.72</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>90.67</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>31.977</v>
+        <v>31.026</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>31.977</v>
+        <v>31.026</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>14.6841</v>
+        <v>13.6715</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_vmamba_str</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5084,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>S1_HSAM</t>
+          <t>S0_CTRL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5097,22 +5093,22 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>97.66</v>
+        <v>97.77</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>97.65000000000001</v>
+        <v>97.77</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>99.42</v>
+        <v>99.45</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>97.65000000000001</v>
+        <v>97.77</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>95.42</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>97.31999999999999</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>31.977</v>
@@ -5121,7 +5117,7 @@
         <v>31.977</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>14.769</v>
+        <v>14.6841</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -5132,104 +5128,108 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run9</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>S0_CTRL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>80.27</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>85.19</v>
+        <v>92.53</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>92.06</v>
+        <v>99.11</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>82.65000000000001</v>
+        <v>91.14</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>70.44</v>
+        <v>83.72</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>90.67</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>3.016737</v>
+        <v>31.977</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M89" s="2" t="n"/>
+        <v>31.977</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>14.6841</v>
+      </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_none</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run9</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>S1_HSAM</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>91.2</v>
+        <v>97.66</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>91.72</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>99.13</v>
+        <v>99.42</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>91.45999999999999</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>84.26000000000001</v>
+        <v>95.42</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>91</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>3.016737</v>
+        <v>31.977</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M90" s="2" t="n"/>
+        <v>31.977</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>14.769</v>
+      </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_none</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5255,22 +5255,22 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>80.39</v>
+        <v>80.27</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>82.89</v>
+        <v>85.19</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>91.45999999999999</v>
+        <v>92.06</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>81.62</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>68.95</v>
+        <v>70.44</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>76.06999999999999</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>3.016737</v>
@@ -5303,26 +5303,26 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>92.61</v>
+        <v>91.2</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>95.26000000000001</v>
+        <v>91.72</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>99.52</v>
+        <v>99.13</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>93.92</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>88.53</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>93.67</v>
+        <v>91</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>3.016737</v>
@@ -5350,42 +5350,42 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>90.55</v>
+        <v>80.39</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>92.03</v>
+        <v>82.89</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>99.12</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>91.28</v>
+        <v>81.62</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>83.95999999999999</v>
+        <v>68.95</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>90.81999999999999</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>3.049509</v>
+        <v>3.016737</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>3.133176</v>
+        <v>3.100404</v>
       </c>
       <c r="M93" s="2" t="n"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_hyperbolic</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
@@ -5402,42 +5402,42 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>78.67</v>
+        <v>92.61</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>85.08</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>91.72</v>
+        <v>99.52</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>81.75</v>
+        <v>93.92</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>69.13</v>
+        <v>88.53</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>76.40000000000001</v>
+        <v>93.67</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>3.049509</v>
+        <v>3.016737</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>3.133176</v>
+        <v>3.100404</v>
       </c>
       <c r="M94" s="2" t="n"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_hyperbolic</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
@@ -5459,26 +5459,26 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>92.84999999999999</v>
+        <v>90.55</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>95.31999999999999</v>
+        <v>92.03</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>99.54000000000001</v>
+        <v>99.12</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>94.06999999999999</v>
+        <v>91.28</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>88.8</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>93.83</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>3.049509</v>
@@ -5506,31 +5506,31 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>89.72</v>
+        <v>78.67</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>93.12</v>
+        <v>85.08</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>99.14</v>
+        <v>91.72</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>91.39</v>
+        <v>81.75</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>84.14</v>
+        <v>69.13</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>90.93000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>3.049509</v>
@@ -5541,7 +5541,7 @@
       <c r="M96" s="2" t="n"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
@@ -5558,31 +5558,31 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>82.83</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>82.86</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>91.91</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>82.84999999999999</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>70.72</v>
+        <v>88.8</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>77.56</v>
+        <v>93.83</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>3.049509</v>
@@ -5593,7 +5593,7 @@
       <c r="M97" s="2" t="n"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
@@ -5615,26 +5615,26 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>93.04000000000001</v>
+        <v>89.72</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>96.08</v>
+        <v>93.12</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>99.56999999999999</v>
+        <v>99.14</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>94.53</v>
+        <v>91.39</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>89.63</v>
+        <v>84.14</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>94.31</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>3.049509</v>
@@ -5652,108 +5652,104 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>91.09</v>
+        <v>82.83</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>92.8</v>
+        <v>82.86</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>99.19</v>
+        <v>91.91</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>91.94</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>85.08</v>
+        <v>70.72</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M99" s="2" t="n">
-        <v>26.3183</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M99" s="2" t="n"/>
       <c r="N99" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>80.3</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>84.81</v>
+        <v>96.08</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>82.5</v>
+        <v>94.53</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>89.63</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M100" s="2" t="n">
-        <v>26.3183</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M100" s="2" t="n"/>
       <c r="N100" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5766,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5779,22 +5775,22 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>91.09</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>92.75</v>
+        <v>92.8</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.19</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>91.86</v>
+        <v>91.94</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>84.94</v>
+        <v>85.08</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>11.754</v>
@@ -5803,11 +5799,11 @@
         <v>20.661</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>26.2593</v>
+        <v>26.3183</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5820,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5833,22 +5829,22 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>80.55</v>
+        <v>80.3</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>84.23</v>
+        <v>84.81</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>91.86</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>82.34999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>70</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>77.06</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>11.754</v>
@@ -5857,11 +5853,11 @@
         <v>20.661</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>26.2593</v>
+        <v>26.3183</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -5873,12 +5869,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5887,35 +5883,35 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>91.38</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>92.3</v>
+        <v>92.75</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>99.17</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>91.84</v>
+        <v>91.86</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>84.91</v>
+        <v>84.94</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M103" s="2" t="n">
-        <v>26.1484</v>
+        <v>26.2593</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5923,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5941,35 +5937,35 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>80.55</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>86.03</v>
+        <v>84.23</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>91.86</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>69.55</v>
+        <v>70</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>76.83</v>
+        <v>77.06</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>11.754</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>15.125</v>
+        <v>20.661</v>
       </c>
       <c r="M104" s="2" t="n">
-        <v>26.1484</v>
+        <v>26.2593</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5982,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5995,22 +5991,22 @@
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>91.13</v>
+        <v>91.38</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.17</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>91.88</v>
+        <v>91.84</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>84.98</v>
+        <v>84.91</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>91.45</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>11.754</v>
@@ -6019,11 +6015,11 @@
         <v>15.125</v>
       </c>
       <c r="M105" s="2" t="n">
-        <v>26.0894</v>
+        <v>26.1484</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6036,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6049,22 +6045,22 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>86.03</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="H106" s="2" t="n">
         <v>82.04000000000001</v>
       </c>
-      <c r="F106" s="2" t="n">
-        <v>85.05</v>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>92.36</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>83.52</v>
-      </c>
       <c r="I106" s="2" t="n">
-        <v>71.7</v>
+        <v>69.55</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>78.55</v>
+        <v>76.83</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>11.754</v>
@@ -6073,11 +6069,11 @@
         <v>15.125</v>
       </c>
       <c r="M106" s="2" t="n">
-        <v>26.0894</v>
+        <v>26.1484</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
@@ -6089,36 +6085,36 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>84.28</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>91.7</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>81.92</v>
+        <v>91.88</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>69.37</v>
+        <v>84.98</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>91.45</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>11.754</v>
@@ -6138,59 +6134,61 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>97.47</v>
+        <v>85.05</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>99.37</v>
+        <v>92.36</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>97.45</v>
+        <v>83.52</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>95.02</v>
+        <v>71.7</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>97.09</v>
+        <v>78.55</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>3.016737</v>
+        <v>11.754</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M108" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>26.0894</v>
+      </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6200,42 +6198,44 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>A4_DETAIL_FROZEN</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>90.41</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>91.83</v>
+        <v>84.28</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>91.11</v>
+        <v>81.92</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>83.67</v>
+        <v>69.37</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>90.64</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>3.016737</v>
+        <v>11.754</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M109" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>26.0894</v>
+      </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -6257,26 +6257,26 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>79.81</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>83.84999999999999</v>
+        <v>97.47</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>91.61</v>
+        <v>99.37</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>81.78</v>
+        <v>97.45</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>69.18000000000001</v>
+        <v>95.02</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>76.34</v>
+        <v>97.09</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>3.016737</v>
@@ -6309,26 +6309,26 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>93.2</v>
+        <v>90.41</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>94.70999999999999</v>
+        <v>91.83</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>99.52</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>93.95</v>
+        <v>91.11</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>88.59</v>
+        <v>83.67</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>93.7</v>
+        <v>90.64</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>3.016737</v>
@@ -6356,42 +6356,42 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>97.48</v>
+        <v>79.81</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>97.45</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>99.37</v>
+        <v>91.61</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>97.47</v>
+        <v>81.78</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>95.06</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>97.11</v>
+        <v>76.34</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.016737</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.100404</v>
       </c>
       <c r="M112" s="2" t="n"/>
       <c r="N112" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
@@ -6408,42 +6408,42 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>90.61</v>
+        <v>93.2</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>92.37</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>99.14</v>
+        <v>99.52</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>91.48</v>
+        <v>93.95</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>84.3</v>
+        <v>88.59</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>91.03</v>
+        <v>93.7</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.016737</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.100404</v>
       </c>
       <c r="M113" s="2" t="n"/>
       <c r="N113" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
@@ -6465,26 +6465,26 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>77.55</v>
+        <v>97.48</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>85.81</v>
+        <v>97.45</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>91.68000000000001</v>
+        <v>99.37</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>81.47</v>
+        <v>97.47</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>68.73</v>
+        <v>95.06</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>76.12</v>
+        <v>97.11</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>3.050665</v>
@@ -6517,26 +6517,26 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>92.5</v>
+        <v>90.61</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>96.20999999999999</v>
+        <v>92.37</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>99.56</v>
+        <v>99.14</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>94.31999999999999</v>
+        <v>91.48</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>89.25</v>
+        <v>84.3</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>94.09</v>
+        <v>91.03</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>3.050665</v>
@@ -6564,42 +6564,42 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>97.51000000000001</v>
+        <v>77.55</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>97.45</v>
+        <v>85.81</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>99.38</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>97.48</v>
+        <v>81.47</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>95.09</v>
+        <v>68.73</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>97.13</v>
+        <v>76.12</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>3.059369</v>
+        <v>3.050665</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>3.143036</v>
+        <v>3.134332</v>
       </c>
       <c r="M116" s="2" t="n"/>
       <c r="N116" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
@@ -6616,42 +6616,42 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>90.58</v>
+        <v>92.5</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>91.77</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>99.11</v>
+        <v>99.56</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>91.17</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>83.77</v>
+        <v>89.25</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>90.7</v>
+        <v>94.09</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>3.059369</v>
+        <v>3.050665</v>
       </c>
       <c r="L117" s="2" t="n">
-        <v>3.143036</v>
+        <v>3.134332</v>
       </c>
       <c r="M117" s="2" t="n"/>
       <c r="N117" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
@@ -6673,26 +6673,26 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>76.7</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>85.81999999999999</v>
+        <v>97.45</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>91.52</v>
+        <v>99.38</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>81.01000000000001</v>
+        <v>97.48</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>68.06999999999999</v>
+        <v>95.09</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>75.56999999999999</v>
+        <v>97.13</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>3.059369</v>
@@ -6725,26 +6725,26 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>92.61</v>
+        <v>90.58</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>95.31</v>
+        <v>91.77</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>99.53</v>
+        <v>99.11</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>93.94</v>
+        <v>91.17</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>88.58</v>
+        <v>83.77</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>93.69</v>
+        <v>90.7</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>3.059369</v>
@@ -6767,47 +6767,47 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>97.41</v>
+        <v>76.7</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>99.36</v>
+        <v>91.52</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>97.42</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>94.98</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>97.06</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>3.016737</v>
+        <v>3.059369</v>
       </c>
       <c r="L120" s="2" t="n">
-        <v>3.100404</v>
+        <v>3.143036</v>
       </c>
       <c r="M120" s="2" t="n"/>
       <c r="N120" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
@@ -6819,47 +6819,47 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>90.29000000000001</v>
+        <v>92.61</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>92.58</v>
+        <v>95.31</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>99.14</v>
+        <v>99.53</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>91.42</v>
+        <v>93.94</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>84.19</v>
+        <v>88.58</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>90.95999999999999</v>
+        <v>93.69</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>3.016737</v>
+        <v>3.059369</v>
       </c>
       <c r="L121" s="2" t="n">
-        <v>3.100404</v>
+        <v>3.143036</v>
       </c>
       <c r="M121" s="2" t="n"/>
       <c r="N121" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
@@ -6881,26 +6881,26 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>80.38</v>
+        <v>97.41</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>85.22</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>92.09</v>
+        <v>99.36</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>82.73</v>
+        <v>97.42</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>70.55</v>
+        <v>94.98</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>77.59999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>3.016737</v>
@@ -6933,26 +6933,26 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>92.87</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>96.04000000000001</v>
+        <v>92.58</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>99.56999999999999</v>
+        <v>99.14</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>94.43000000000001</v>
+        <v>91.42</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>89.44</v>
+        <v>84.19</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>94.2</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>3.016737</v>
@@ -6980,42 +6980,42 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>97.52</v>
+        <v>80.38</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>97.42</v>
+        <v>85.22</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>99.38</v>
+        <v>92.09</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>97.47</v>
+        <v>82.73</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>70.55</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>97.11</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>3.060525</v>
+        <v>3.016737</v>
       </c>
       <c r="L124" s="2" t="n">
-        <v>3.144192</v>
+        <v>3.100404</v>
       </c>
       <c r="M124" s="2" t="n"/>
       <c r="N124" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
@@ -7032,42 +7032,42 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>90.48</v>
+        <v>92.87</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>92.91</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>99.16</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>91.68000000000001</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>84.64</v>
+        <v>89.44</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>91.23999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>3.060525</v>
+        <v>3.016737</v>
       </c>
       <c r="L125" s="2" t="n">
-        <v>3.144192</v>
+        <v>3.100404</v>
       </c>
       <c r="M125" s="2" t="n"/>
       <c r="N125" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
@@ -7089,26 +7089,26 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>83.2</v>
+        <v>97.52</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>80.95</v>
+        <v>97.42</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>91.42</v>
+        <v>99.38</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>82.06</v>
+        <v>97.47</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>69.58</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>76.42</v>
+        <v>97.11</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>3.060525</v>
@@ -7141,26 +7141,26 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>92.36</v>
+        <v>90.48</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>95.44</v>
+        <v>92.91</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>99.52</v>
+        <v>99.16</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>93.88</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>88.45999999999999</v>
+        <v>84.64</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>93.63</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>3.060525</v>
@@ -7188,42 +7188,42 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>97.51000000000001</v>
+        <v>80.95</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>99.38</v>
+        <v>91.42</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>97.47</v>
+        <v>82.06</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>95.06</v>
+        <v>69.58</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>97.11</v>
+        <v>76.42</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>3.077293</v>
+        <v>3.060525</v>
       </c>
       <c r="L128" s="2" t="n">
-        <v>3.16096</v>
+        <v>3.144192</v>
       </c>
       <c r="M128" s="2" t="n"/>
       <c r="N128" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
@@ -7240,42 +7240,42 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>90.45</v>
+        <v>92.36</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>92.68000000000001</v>
+        <v>95.44</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>99.15000000000001</v>
+        <v>99.52</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>91.55</v>
+        <v>93.88</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>84.42</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>91.11</v>
+        <v>93.63</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>3.077293</v>
+        <v>3.060525</v>
       </c>
       <c r="L129" s="2" t="n">
-        <v>3.16096</v>
+        <v>3.144192</v>
       </c>
       <c r="M129" s="2" t="n"/>
       <c r="N129" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
@@ -7297,26 +7297,26 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>78.5</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>86.2</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>91.97</v>
+        <v>99.38</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>82.17</v>
+        <v>97.47</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>69.73999999999999</v>
+        <v>95.06</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>77</v>
+        <v>97.11</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>3.077293</v>
@@ -7349,26 +7349,26 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>91.88</v>
+        <v>90.45</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>94.98999999999999</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>99.48999999999999</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>93.41</v>
+        <v>91.55</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>87.63</v>
+        <v>84.42</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>93.14</v>
+        <v>91.11</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>3.077293</v>
@@ -7391,47 +7391,47 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>97.5</v>
+        <v>78.5</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>97.34999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>99.36</v>
+        <v>91.97</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>82.17</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>94.98999999999999</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>97.06999999999999</v>
+        <v>77</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>3.016737</v>
+        <v>3.077293</v>
       </c>
       <c r="L132" s="2" t="n">
-        <v>3.100404</v>
+        <v>3.16096</v>
       </c>
       <c r="M132" s="2" t="n"/>
       <c r="N132" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
@@ -7443,47 +7443,47 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>90.69</v>
+        <v>91.88</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>92.43000000000001</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>99.15000000000001</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>91.55</v>
+        <v>93.41</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>84.42</v>
+        <v>87.63</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>93.14</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>3.016737</v>
+        <v>3.077293</v>
       </c>
       <c r="L133" s="2" t="n">
-        <v>3.100404</v>
+        <v>3.16096</v>
       </c>
       <c r="M133" s="2" t="n"/>
       <c r="N133" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
@@ -7505,26 +7505,26 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>82.58</v>
+        <v>97.5</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>82.25</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>91.69</v>
+        <v>99.36</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>82.42</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>70.09</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>76.98</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="K134" s="2" t="n">
         <v>3.016737</v>
@@ -7557,26 +7557,26 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>92.31</v>
+        <v>90.69</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>94.59999999999999</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>99.48999999999999</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>93.44</v>
+        <v>91.55</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>87.69</v>
+        <v>84.42</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>93.17</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>3.016737</v>
@@ -7604,42 +7604,42 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>97.53</v>
+        <v>82.58</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>97.38</v>
+        <v>82.25</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>99.37</v>
+        <v>91.69</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>97.45</v>
+        <v>82.42</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>95.03</v>
+        <v>70.09</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>97.09</v>
+        <v>76.98</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.016737</v>
       </c>
       <c r="L136" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.100404</v>
       </c>
       <c r="M136" s="2" t="n"/>
       <c r="N136" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
@@ -7656,42 +7656,42 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>90.34999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>91.77</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>91.05</v>
+        <v>93.44</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>83.56999999999999</v>
+        <v>87.69</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>90.58</v>
+        <v>93.17</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.016737</v>
       </c>
       <c r="L137" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.100404</v>
       </c>
       <c r="M137" s="2" t="n"/>
       <c r="N137" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
@@ -7713,26 +7713,26 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>76.31999999999999</v>
+        <v>97.53</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>85.91</v>
+        <v>97.38</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>91.45999999999999</v>
+        <v>99.37</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>80.83</v>
+        <v>97.45</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>67.83</v>
+        <v>95.03</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>75.37</v>
+        <v>97.09</v>
       </c>
       <c r="K138" s="2" t="n">
         <v>3.050665</v>
@@ -7765,26 +7765,26 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E139" s="2" t="n">
-        <v>93.55</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>95.95</v>
+        <v>91.77</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>99.59</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>94.73</v>
+        <v>91.05</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>89.98999999999999</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>94.52</v>
+        <v>90.58</v>
       </c>
       <c r="K139" s="2" t="n">
         <v>3.050665</v>
@@ -7812,42 +7812,42 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>97.45</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>97.48999999999999</v>
+        <v>85.91</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>99.38</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>97.47</v>
+        <v>80.83</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>67.83</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>97.12</v>
+        <v>75.37</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.050665</v>
       </c>
       <c r="L140" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.134332</v>
       </c>
       <c r="M140" s="2" t="n"/>
       <c r="N140" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
@@ -7864,42 +7864,42 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>90.67</v>
+        <v>93.55</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>92.58</v>
+        <v>95.95</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>99.15000000000001</v>
+        <v>99.59</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>91.62</v>
+        <v>94.73</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>84.53</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>91.17</v>
+        <v>94.52</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.050665</v>
       </c>
       <c r="L141" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.134332</v>
       </c>
       <c r="M141" s="2" t="n"/>
       <c r="N141" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
@@ -7921,26 +7921,26 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>77.90000000000001</v>
+        <v>97.45</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>87.42</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>92.15000000000001</v>
+        <v>99.38</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>82.39</v>
+        <v>97.47</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>70.05</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>77.36</v>
+        <v>97.12</v>
       </c>
       <c r="K142" s="2" t="n">
         <v>3.067561</v>
@@ -7973,26 +7973,26 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E143" s="2" t="n">
-        <v>92.61</v>
+        <v>90.67</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>95.77</v>
+        <v>92.58</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>99.54000000000001</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>94.16</v>
+        <v>91.62</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>88.97</v>
+        <v>84.53</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>93.93000000000001</v>
+        <v>91.17</v>
       </c>
       <c r="K143" s="2" t="n">
         <v>3.067561</v>
@@ -8015,47 +8015,47 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>97.31999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>97.54000000000001</v>
+        <v>87.42</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>99.37</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>82.39</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>94.98999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>97.06999999999999</v>
+        <v>77.36</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>3.016737</v>
+        <v>3.067561</v>
       </c>
       <c r="L144" s="2" t="n">
-        <v>3.100404</v>
+        <v>3.151228</v>
       </c>
       <c r="M144" s="2" t="n"/>
       <c r="N144" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
@@ -8067,47 +8067,47 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>89.79000000000001</v>
+        <v>92.61</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>92.27</v>
+        <v>95.77</v>
       </c>
       <c r="G145" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>91.01000000000001</v>
+        <v>94.16</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>83.51000000000001</v>
+        <v>88.97</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>90.54000000000001</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>3.016737</v>
+        <v>3.067561</v>
       </c>
       <c r="L145" s="2" t="n">
-        <v>3.100404</v>
+        <v>3.151228</v>
       </c>
       <c r="M145" s="2" t="n"/>
       <c r="N145" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
@@ -8129,26 +8129,26 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E146" s="2" t="n">
-        <v>79.92</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>84.81</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="G146" s="2" t="n">
-        <v>91.89</v>
+        <v>99.37</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>82.29000000000001</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>69.91</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="K146" s="2" t="n">
         <v>3.016737</v>
@@ -8181,26 +8181,26 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>92.78</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>95.23</v>
+        <v>92.27</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>99.53</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>93.98999999999999</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>88.66</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>93.75</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="K147" s="2" t="n">
         <v>3.016737</v>
@@ -8228,42 +8228,42 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>97.48999999999999</v>
+        <v>79.92</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>97.45</v>
+        <v>84.81</v>
       </c>
       <c r="G148" s="2" t="n">
-        <v>99.37</v>
+        <v>91.89</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>97.47</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>95.06</v>
+        <v>69.91</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>97.11</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.016737</v>
       </c>
       <c r="L148" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.100404</v>
       </c>
       <c r="M148" s="2" t="n"/>
       <c r="N148" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
@@ -8280,42 +8280,42 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>89.73999999999999</v>
+        <v>92.78</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>93.42</v>
+        <v>95.23</v>
       </c>
       <c r="G149" s="2" t="n">
-        <v>99.16</v>
+        <v>99.53</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>91.54000000000001</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>84.40000000000001</v>
+        <v>88.66</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>93.75</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.016737</v>
       </c>
       <c r="L149" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.100404</v>
       </c>
       <c r="M149" s="2" t="n"/>
       <c r="N149" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
@@ -8337,26 +8337,26 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>77.78</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>84.04000000000001</v>
+        <v>97.45</v>
       </c>
       <c r="G150" s="2" t="n">
-        <v>91.28</v>
+        <v>99.37</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>80.79000000000001</v>
+        <v>97.47</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>67.77</v>
+        <v>95.06</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>75.16</v>
+        <v>97.11</v>
       </c>
       <c r="K150" s="2" t="n">
         <v>3.050665</v>
@@ -8389,26 +8389,26 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E151" s="2" t="n">
-        <v>93.05</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>96.14</v>
+        <v>93.42</v>
       </c>
       <c r="G151" s="2" t="n">
-        <v>99.58</v>
+        <v>99.16</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>94.56999999999999</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>89.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>94.34999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="K151" s="2" t="n">
         <v>3.050665</v>
@@ -8436,42 +8436,42 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E152" s="2" t="n">
-        <v>97.41</v>
+        <v>77.78</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>97.53</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="G152" s="2" t="n">
-        <v>99.38</v>
+        <v>91.28</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>97.47</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>95.06</v>
+        <v>67.77</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>97.11</v>
+        <v>75.16</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.050665</v>
       </c>
       <c r="L152" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.134332</v>
       </c>
       <c r="M152" s="2" t="n"/>
       <c r="N152" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
@@ -8488,42 +8488,42 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E153" s="2" t="n">
-        <v>90.68000000000001</v>
+        <v>93.05</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>91.98</v>
+        <v>96.14</v>
       </c>
       <c r="G153" s="2" t="n">
-        <v>99.12</v>
+        <v>99.58</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>91.33</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>84.04000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>90.87</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.050665</v>
       </c>
       <c r="L153" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.134332</v>
       </c>
       <c r="M153" s="2" t="n"/>
       <c r="N153" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
@@ -8545,26 +8545,26 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E154" s="2" t="n">
-        <v>77.18000000000001</v>
+        <v>97.41</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>85.53</v>
+        <v>97.53</v>
       </c>
       <c r="G154" s="2" t="n">
-        <v>91.54000000000001</v>
+        <v>99.38</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>81.14</v>
+        <v>97.47</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>68.27</v>
+        <v>95.06</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>75.70999999999999</v>
+        <v>97.11</v>
       </c>
       <c r="K154" s="2" t="n">
         <v>3.067561</v>
@@ -8597,26 +8597,26 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>92.63</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>96.55</v>
+        <v>91.98</v>
       </c>
       <c r="G155" s="2" t="n">
-        <v>99.58</v>
+        <v>99.12</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>94.55</v>
+        <v>91.33</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>89.67</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>94.33</v>
+        <v>90.87</v>
       </c>
       <c r="K155" s="2" t="n">
         <v>3.067561</v>
@@ -8634,108 +8634,104 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E156" s="2" t="n">
-        <v>93.13</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>95.16</v>
+        <v>85.53</v>
       </c>
       <c r="G156" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>94.13</v>
+        <v>81.14</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>88.91</v>
+        <v>68.27</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>2.596</v>
+        <v>3.067561</v>
       </c>
       <c r="L156" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M156" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M156" s="2" t="n"/>
       <c r="N156" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E157" s="2" t="n">
-        <v>86.37</v>
+        <v>92.63</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>89.25</v>
+        <v>96.55</v>
       </c>
       <c r="G157" s="2" t="n">
-        <v>98.78</v>
+        <v>99.58</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>94.55</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>89.67</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>87.14</v>
+        <v>94.33</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>2.596</v>
+        <v>3.067561</v>
       </c>
       <c r="L157" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M157" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M157" s="2" t="n"/>
       <c r="N157" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
@@ -8757,26 +8753,26 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E158" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>93.13</v>
       </c>
       <c r="F158" s="2" t="n">
-        <v>84.5</v>
+        <v>95.16</v>
       </c>
       <c r="G158" s="2" t="n">
-        <v>91.81</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>94.13</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>88.91</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>76.84</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K158" s="2" t="n">
         <v>2.596</v>
@@ -8811,26 +8807,26 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>90.16</v>
+        <v>86.37</v>
       </c>
       <c r="F159" s="2" t="n">
-        <v>93.97</v>
+        <v>89.25</v>
       </c>
       <c r="G159" s="2" t="n">
-        <v>99.38</v>
+        <v>98.78</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>92.02</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>85.23</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>91.7</v>
+        <v>87.14</v>
       </c>
       <c r="K159" s="2" t="n">
         <v>2.596</v>
@@ -8860,40 +8856,40 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>94.7</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F160" s="2" t="n">
-        <v>96.13</v>
+        <v>84.5</v>
       </c>
       <c r="G160" s="2" t="n">
-        <v>98.88</v>
+        <v>91.81</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>95.41</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>91.22</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>94.77</v>
+        <v>76.84</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L160" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N160" t="inlineStr">
         <is>
@@ -8914,40 +8910,40 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>88.42</v>
+        <v>90.16</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>91.97</v>
+        <v>93.97</v>
       </c>
       <c r="G161" s="2" t="n">
-        <v>99.02</v>
+        <v>99.38</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>90.16</v>
+        <v>92.02</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>82.08</v>
+        <v>85.23</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>89.64</v>
+        <v>91.7</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>3.455</v>
+        <v>2.596</v>
       </c>
       <c r="L161" s="2" t="n">
-        <v>1.478</v>
+        <v>0.62</v>
       </c>
       <c r="M161" s="2" t="n">
-        <v>3.5459</v>
+        <v>2.2136</v>
       </c>
       <c r="N161" t="inlineStr">
         <is>
@@ -8973,26 +8969,26 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E162" s="2" t="n">
-        <v>78.73</v>
+        <v>94.7</v>
       </c>
       <c r="F162" s="2" t="n">
-        <v>84.98</v>
+        <v>96.13</v>
       </c>
       <c r="G162" s="2" t="n">
-        <v>91.7</v>
+        <v>98.88</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>95.41</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>69.11</v>
+        <v>91.22</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>76.38</v>
+        <v>94.77</v>
       </c>
       <c r="K162" s="2" t="n">
         <v>3.455</v>
@@ -9027,26 +9023,26 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E163" s="2" t="n">
-        <v>91.64</v>
+        <v>88.42</v>
       </c>
       <c r="F163" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>91.97</v>
       </c>
       <c r="G163" s="2" t="n">
-        <v>99.47</v>
+        <v>99.02</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>93.2</v>
+        <v>90.16</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>87.27</v>
+        <v>82.08</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>89.64</v>
       </c>
       <c r="K163" s="2" t="n">
         <v>3.455</v>
@@ -9066,17 +9062,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -9085,89 +9081,89 @@
         </is>
       </c>
       <c r="E164" s="2" t="n">
-        <v>82.42</v>
+        <v>78.73</v>
       </c>
       <c r="F164" s="2" t="n">
-        <v>83.87</v>
+        <v>84.98</v>
       </c>
       <c r="G164" s="2" t="n">
-        <v>92.12</v>
+        <v>91.7</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>83.14</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>71.14</v>
+        <v>69.11</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>76.38</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>11.754</v>
+        <v>3.455</v>
       </c>
       <c r="L164" s="2" t="n">
-        <v>15.125</v>
+        <v>1.478</v>
       </c>
       <c r="M164" s="2" t="n">
-        <v>26.3246</v>
+        <v>3.5459</v>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>M1_TASS</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E165" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>91.64</v>
       </c>
       <c r="F165" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="G165" s="2" t="n">
-        <v>91.94</v>
+        <v>99.47</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>82.77</v>
+        <v>93.2</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>70.61</v>
+        <v>87.27</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>8.195</v>
+        <v>3.455</v>
       </c>
       <c r="L165" s="2" t="n">
-        <v>15.125</v>
+        <v>1.478</v>
       </c>
       <c r="M165" s="2" t="n">
-        <v>24.1021</v>
+        <v>3.5459</v>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9180,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>R4_0_A0_FULL12_FROZEN</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -9193,31 +9189,31 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>79.94</v>
+        <v>82.42</v>
       </c>
       <c r="F166" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>83.87</v>
       </c>
       <c r="G166" s="2" t="n">
-        <v>91.89</v>
+        <v>92.12</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>82.3</v>
+        <v>83.14</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>69.92</v>
+        <v>71.14</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>5.492</v>
+        <v>11.754</v>
       </c>
       <c r="L166" s="2" t="n">
-        <v>3.515</v>
+        <v>15.125</v>
       </c>
       <c r="M166" s="2" t="n">
-        <v>10.7311</v>
+        <v>26.3246</v>
       </c>
       <c r="N166" t="inlineStr">
         <is>
@@ -9238,7 +9234,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>R4_1_VIT4_OLDHEAD</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -9247,31 +9243,31 @@
         </is>
       </c>
       <c r="E167" s="2" t="n">
-        <v>80.87</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="F167" s="2" t="n">
-        <v>83.81</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G167" s="2" t="n">
-        <v>91.81</v>
+        <v>91.94</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>82.77</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>69.95</v>
+        <v>70.61</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>5.533</v>
+        <v>8.195</v>
       </c>
       <c r="L167" s="2" t="n">
-        <v>3.556</v>
+        <v>15.125</v>
       </c>
       <c r="M167" s="2" t="n">
-        <v>10.9824</v>
+        <v>24.1021</v>
       </c>
       <c r="N167" t="inlineStr">
         <is>
@@ -9292,7 +9288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -9301,31 +9297,31 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>79.78</v>
+        <v>79.94</v>
       </c>
       <c r="F168" s="2" t="n">
-        <v>84.39</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="G168" s="2" t="n">
-        <v>91.75</v>
+        <v>91.89</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>82.02</v>
+        <v>82.3</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>69.52</v>
+        <v>69.92</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>5.491</v>
+        <v>5.492</v>
       </c>
       <c r="L168" s="2" t="n">
-        <v>3.514</v>
+        <v>3.515</v>
       </c>
       <c r="M168" s="2" t="n">
-        <v>11.5239</v>
+        <v>10.7311</v>
       </c>
       <c r="N168" t="inlineStr">
         <is>
@@ -9336,46 +9332,50 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E169" s="2" t="n">
-        <v>97.72</v>
+        <v>80.87</v>
       </c>
       <c r="F169" s="2" t="n">
-        <v>97.78</v>
+        <v>83.81</v>
       </c>
       <c r="G169" s="2" t="n">
-        <v>99.44</v>
+        <v>91.81</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>97.75</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>69.95</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>11.754</v>
+        <v>5.533</v>
       </c>
       <c r="L169" s="2" t="n">
-        <v>20.661</v>
+        <v>3.556</v>
       </c>
       <c r="M169" s="2" t="n">
-        <v>26.3246</v>
+        <v>10.9824</v>
       </c>
       <c r="N169" t="inlineStr">
         <is>
@@ -9386,46 +9386,50 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>UltraLight</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr"/>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E170" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>79.78</v>
       </c>
       <c r="F170" s="2" t="n">
-        <v>92.33</v>
+        <v>84.39</v>
       </c>
       <c r="G170" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.75</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>91.95</v>
+        <v>82.02</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.52</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>91.52</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>11.754</v>
+        <v>5.491</v>
       </c>
       <c r="L170" s="2" t="n">
-        <v>20.661</v>
+        <v>3.514</v>
       </c>
       <c r="M170" s="2" t="n">
-        <v>26.3246</v>
+        <v>11.5239</v>
       </c>
       <c r="N170" t="inlineStr">
         <is>
@@ -9447,26 +9451,26 @@
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E171" s="2" t="n">
-        <v>80.77</v>
+        <v>97.72</v>
       </c>
       <c r="F171" s="2" t="n">
-        <v>84.27</v>
+        <v>97.78</v>
       </c>
       <c r="G171" s="2" t="n">
-        <v>91.91</v>
+        <v>99.44</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>82.48</v>
+        <v>97.75</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>70.19</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>77.23</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="K171" s="2" t="n">
         <v>11.754</v>
@@ -9497,26 +9501,26 @@
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E172" s="2" t="n">
-        <v>93.62</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="F172" s="2" t="n">
-        <v>96.09</v>
+        <v>92.33</v>
       </c>
       <c r="G172" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>94.84</v>
+        <v>91.95</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>90.18000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>94.63</v>
+        <v>91.52</v>
       </c>
       <c r="K172" s="2" t="n">
         <v>11.754</v>
@@ -9533,8 +9537,108 @@
         </is>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G173" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H173" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K173" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M173" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="G174" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N172"/>
+  <autoFilter ref="A1:N174"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N174"/>
+  <dimension ref="A1:N186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Run2_val</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1153,26 +1153,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>89.58</v>
+        <v>96.87</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>92.09999999999999</v>
+        <v>96.95</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>99.08</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>90.83</v>
+        <v>96.91</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>83.19</v>
+        <v>94</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>90.34</v>
+        <v>96.47</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>1.93581</v>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Run2_val</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1209,681 +1209,657 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>89.88</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>91.91</v>
+        <v>92.25</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>99.08</v>
+        <v>99.09</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>90.88</v>
+        <v>90.98</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>83.29000000000001</v>
+        <v>83.45</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>90.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1.952266</v>
+        <v>1.93581</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>2.063581</v>
+        <v>2.047125</v>
       </c>
       <c r="M15" s="2" t="n"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>casa_pyramid_qkv</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>94.08</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>95.26000000000001</v>
+        <v>85.22</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>98.69</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>94.67</v>
+        <v>83.37</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>89.87</v>
+        <v>71.48</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>93.92</v>
+        <v>78.38</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2.378</v>
+        <v>1.93581</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.047125</v>
+      </c>
+      <c r="M16" s="2" t="n"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>88.55</v>
+        <v>92.64</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>91.3</v>
+        <v>96.12</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>98.98999999999999</v>
+        <v>99.56</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>89.90000000000001</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>81.66</v>
+        <v>89.31</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>89.37</v>
+        <v>94.12</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>2.378</v>
+        <v>1.93581</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.047125</v>
+      </c>
+      <c r="M17" s="2" t="n"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>82.09</v>
+        <v>96.83</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>82.84</v>
+        <v>97.03</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>91.77</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>82.47</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>70.16</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>77.09</v>
+        <v>96.5</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>2.378</v>
+        <v>1.94817</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.059485</v>
+      </c>
+      <c r="M18" s="2" t="n"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>92.34</v>
+        <v>90.38</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>99.11</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>93.7</v>
+        <v>91.16</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>88.15000000000001</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>93.44</v>
+        <v>90.69</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2.378</v>
+        <v>1.94817</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.059485</v>
+      </c>
+      <c r="M19" s="2" t="n"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>93.90000000000001</v>
+        <v>79.53</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>95.19</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>98.66</v>
+        <v>92.23</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>94.54000000000001</v>
+        <v>82.84</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>89.64</v>
+        <v>70.7</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>93.78</v>
+        <v>77.83</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>2.416</v>
+        <v>1.94817</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.059485</v>
+      </c>
+      <c r="M20" s="2" t="n"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>88.81999999999999</v>
+        <v>92.69</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>90.93000000000001</v>
+        <v>96.52</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>98.98</v>
+        <v>99.58</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>89.87</v>
+        <v>94.56</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>81.59999999999999</v>
+        <v>89.69</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>89.33</v>
+        <v>94.34</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2.416</v>
+        <v>1.94817</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.059485</v>
+      </c>
+      <c r="M21" s="2" t="n"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>79.66</v>
+        <v>96.84</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>85.53</v>
+        <v>96.89</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>92.03</v>
+        <v>99.23</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>82.48999999999999</v>
+        <v>96.87</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>70.2</v>
+        <v>93.92</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>77.34</v>
+        <v>96.42</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>2.416</v>
+        <v>1.94817</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.059485</v>
+      </c>
+      <c r="M22" s="2" t="n"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>91.81999999999999</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>95.56</v>
+        <v>91.98</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>93.65000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>88.06999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>93.40000000000001</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>2.416</v>
+        <v>1.94817</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.059485</v>
+      </c>
+      <c r="M23" s="2" t="n"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>95.05</v>
+        <v>80.34</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>96.02</v>
+        <v>84.86</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>91.98</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>95.53</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>91.45</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>94.91</v>
+        <v>77.34</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>2.378</v>
+        <v>1.94817</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.059485</v>
+      </c>
+      <c r="M24" s="2" t="n"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>88.98999999999999</v>
+        <v>93.11</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>91.62</v>
+        <v>96.34</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>99.02</v>
+        <v>99.59</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>90.28</v>
+        <v>94.7</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>82.29000000000001</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>89.77</v>
+        <v>94.48</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>2.378</v>
+        <v>1.94817</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.059485</v>
+      </c>
+      <c r="M25" s="2" t="n"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2_val</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>79.3</v>
+        <v>89.58</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>85.94</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>92.06</v>
+        <v>99.08</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>82.48999999999999</v>
+        <v>90.83</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>70.19</v>
+        <v>83.19</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>77.36</v>
+        <v>90.34</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>2.378</v>
+        <v>1.93581</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.047125</v>
+      </c>
+      <c r="M26" s="2" t="n"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2_val</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>92.15000000000001</v>
+        <v>89.88</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>94.7</v>
+        <v>91.91</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>99.48</v>
+        <v>99.08</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>93.41</v>
+        <v>90.88</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>87.63</v>
+        <v>83.29000000000001</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>93.14</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>2.378</v>
+        <v>1.952266</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.063581</v>
+      </c>
+      <c r="M27" s="2" t="n"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1876,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1909,31 +1885,31 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>95.06</v>
+        <v>94.08</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>96.01000000000001</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>98.69</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>95.54000000000001</v>
+        <v>94.67</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>91.45</v>
+        <v>89.87</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>94.91</v>
+        <v>93.92</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -1954,7 +1930,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1963,31 +1939,31 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>89.47</v>
+        <v>88.55</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>91.28</v>
+        <v>91.3</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>99.03</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>90.37</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>82.43000000000001</v>
+        <v>81.66</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>89.86</v>
+        <v>89.37</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2008,7 +1984,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2017,31 +1993,31 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>81.39</v>
+        <v>82.09</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>84.72</v>
+        <v>82.84</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>92.15000000000001</v>
+        <v>91.77</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>83.02</v>
+        <v>82.47</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>70.97</v>
+        <v>70.16</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>77.92</v>
+        <v>77.09</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2062,7 +2038,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2071,31 +2047,31 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>92</v>
+        <v>92.34</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>99.51000000000001</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>93.72</v>
+        <v>93.7</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>88.19</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>93.47</v>
+        <v>93.44</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2106,275 +2082,331 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_INJ</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>90.38</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>91.91</v>
+        <v>95.19</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>98.66</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>91.14</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>83.72</v>
+        <v>89.64</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>90.66</v>
-      </c>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
+        <v>93.78</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_INJ</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>81.18000000000001</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>82.19</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>91.41</v>
+        <v>98.98</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>81.68000000000001</v>
+        <v>89.87</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>69.04000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>76.08</v>
-      </c>
-      <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="n"/>
+        <v>89.33</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_SUP</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>90.63</v>
+        <v>79.66</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>91.56</v>
+        <v>85.53</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>92.03</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>91.09</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>83.64</v>
+        <v>70.2</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>90.62</v>
+        <v>77.34</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>31.978582</v>
-      </c>
-      <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
+        <v>2.416</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_SUP</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>81.28</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>82.75</v>
+        <v>95.56</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>91.59</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>82.01000000000001</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>69.5</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>76.52</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>31.978582</v>
-      </c>
-      <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="n"/>
+        <v>2.416</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_V2</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>90.52</v>
+        <v>95.05</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>91.84999999999999</v>
+        <v>96.02</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>99.11</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>95.53</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>83.79000000000001</v>
+        <v>91.45</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>90.70999999999999</v>
-      </c>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
-      <c r="M36" s="2" t="n"/>
+        <v>94.91</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>1.2051</v>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_V2</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>79.34</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>84.23999999999999</v>
+        <v>91.62</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>91.63</v>
+        <v>99.02</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>81.72</v>
+        <v>90.28</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>69.09</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="n"/>
+        <v>89.77</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>1.2051</v>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2384,51 +2416,51 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>96.58</v>
+        <v>79.3</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>96.94</v>
+        <v>85.94</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>99.2</v>
+        <v>92.06</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>96.76000000000001</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>93.73</v>
+        <v>70.19</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>96.31</v>
+        <v>77.36</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>4.88</v>
+        <v>2.378</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>4.88</v>
+        <v>2.378</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2051</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2438,51 +2470,51 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>89.52</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>92.69</v>
+        <v>94.7</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>99.11</v>
+        <v>99.48</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>91.08</v>
+        <v>93.41</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>83.62</v>
+        <v>87.63</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>90.61</v>
+        <v>93.14</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>4.88</v>
+        <v>2.378</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>4.88</v>
+        <v>2.378</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2051</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2492,51 +2524,51 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>95.06</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>85.01000000000001</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>91.94</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>82.39</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>70.06</v>
+        <v>91.45</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>77.18000000000001</v>
+        <v>94.91</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2365</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2546,51 +2578,51 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>92.69</v>
+        <v>89.47</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>96.95999999999999</v>
+        <v>91.28</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>99.59</v>
+        <v>99.03</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>94.78</v>
+        <v>90.37</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>90.08</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>94.56999999999999</v>
+        <v>89.86</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2365</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2600,51 +2632,51 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>96.62</v>
+        <v>81.39</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>96.88</v>
+        <v>84.72</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>99.2</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>96.75</v>
+        <v>83.02</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>93.7</v>
+        <v>70.97</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>96.29000000000001</v>
+        <v>77.92</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2365</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2654,44 +2686,44 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>89.95</v>
+        <v>92</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>92.13</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>91.03</v>
+        <v>93.72</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>83.53</v>
+        <v>88.19</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>90.55</v>
+        <v>93.47</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2365</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
@@ -2701,51 +2733,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>Exploration/Exp1/STG_INJ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>80.14</v>
+        <v>90.38</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>84.18000000000001</v>
+        <v>91.91</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>91.76000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>82.11</v>
+        <v>91.14</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>69.65000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>76.76000000000001</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M44" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>90.66</v>
+      </c>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -2755,51 +2777,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>Exploration/Exp1/STG_INJ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>92.45</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>97.37</v>
+        <v>82.19</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>91.41</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>94.84</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>90.19</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>94.64</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M45" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>76.08</v>
+      </c>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -2809,51 +2821,43 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>Exploration/Exp1/STG_SUP</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>97.02</v>
+        <v>90.63</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>97.20999999999999</v>
+        <v>91.56</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>99.29000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>97.11</v>
+        <v>91.09</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>94.39</v>
+        <v>83.64</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>96.70999999999999</v>
+        <v>90.62</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>31.978582</v>
+      </c>
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="n"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -2863,51 +2867,43 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>Exploration/Exp1/STG_SUP</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>89.59</v>
+        <v>81.28</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>92.84</v>
+        <v>82.75</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>99.12</v>
+        <v>91.59</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>91.19</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>83.81</v>
+        <v>69.5</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>90.73</v>
+        <v>76.52</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M47" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>31.978582</v>
+      </c>
+      <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="n"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -2917,51 +2913,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>Exploration/Exp1/STG_V2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>81.23999999999999</v>
+        <v>90.52</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>85.29000000000001</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>92.27</v>
+        <v>99.11</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>83.20999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>71.25</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M48" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>90.70999999999999</v>
+      </c>
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="n"/>
+      <c r="M48" s="2" t="n"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -2971,51 +2957,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>Exploration/Exp1/STG_V2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>93.09999999999999</v>
+        <v>79.34</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>96.01000000000001</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>99.56999999999999</v>
+        <v>91.63</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>94.53</v>
+        <v>81.72</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>89.63</v>
+        <v>69.09</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>94.31</v>
-      </c>
-      <c r="K49" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M49" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>76.3</v>
+      </c>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="n"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3008,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3041,22 +3017,22 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>97.03</v>
+        <v>96.58</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>97.33</v>
+        <v>96.94</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>97.18000000000001</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>94.51000000000001</v>
+        <v>93.73</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>96.78</v>
+        <v>96.31</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>4.88</v>
@@ -3086,7 +3062,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3095,22 +3071,22 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>90.33</v>
+        <v>89.52</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>91.81999999999999</v>
+        <v>92.69</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.11</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>91.06999999999999</v>
+        <v>91.08</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>83.62</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>90.59</v>
+        <v>90.61</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>4.88</v>
@@ -3140,7 +3116,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3149,22 +3125,22 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>84.41</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>82.55</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>92.12</v>
+        <v>91.94</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>83.47</v>
+        <v>82.39</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>71.63</v>
+        <v>70.06</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>78.29000000000001</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>4.88</v>
@@ -3194,7 +3170,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3203,22 +3179,22 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>93.56</v>
+        <v>92.69</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>96.62</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>99.61</v>
+        <v>99.59</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>94.78</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>90.08</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>94.87</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>4.88</v>
@@ -3243,12 +3219,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3257,22 +3233,22 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>97.02</v>
+        <v>96.62</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>97.27</v>
+        <v>96.88</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>97.14</v>
+        <v>96.75</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>94.45</v>
+        <v>93.7</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>96.73999999999999</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>4.88</v>
@@ -3297,12 +3273,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3311,22 +3287,22 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>90.64</v>
+        <v>89.95</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>91.64</v>
+        <v>92.13</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>99.09999999999999</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>91.14</v>
+        <v>91.03</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>83.72</v>
+        <v>83.53</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>90.66</v>
+        <v>90.55</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>4.88</v>
@@ -3351,12 +3327,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3365,22 +3341,22 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>80.94</v>
+        <v>80.14</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>85.43000000000001</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>92.25</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>83.13</v>
+        <v>82.11</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>71.12</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>4.88</v>
@@ -3405,12 +3381,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3419,22 +3395,22 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>93.73999999999999</v>
+        <v>92.45</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>96.67</v>
+        <v>97.37</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>99.62</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>95.18000000000001</v>
+        <v>94.84</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>90.81</v>
+        <v>90.19</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>94.98999999999999</v>
+        <v>94.64</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>4.88</v>
@@ -3459,12 +3435,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3476,28 +3452,28 @@
         <v>97.02</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>97.33</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>99.3</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>97.17</v>
+        <v>97.11</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>94.5</v>
+        <v>94.39</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>96.78</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -3513,12 +3489,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3527,31 +3503,31 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>90.22</v>
+        <v>89.59</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>92.22</v>
+        <v>92.84</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>99.11</v>
+        <v>99.12</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>91.19</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>83.83</v>
+        <v>83.81</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>90.73999999999999</v>
+        <v>90.73</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -3567,12 +3543,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3581,31 +3557,31 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>80.09999999999999</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>86.05</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>92.23999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>82.97</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>70.89</v>
+        <v>71.25</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>77.95999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -3621,12 +3597,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3635,31 +3611,31 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>93.45999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>96</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>99.59</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>94.70999999999999</v>
+        <v>94.53</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>89.95</v>
+        <v>89.63</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>94.48999999999999</v>
+        <v>94.31</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -3675,12 +3651,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3689,10 +3665,10 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>97.02</v>
+        <v>97.03</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>97.34</v>
+        <v>97.33</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>99.3</v>
@@ -3707,13 +3683,13 @@
         <v>96.78</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -3729,12 +3705,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3743,31 +3719,31 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>90.20999999999999</v>
+        <v>90.33</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>92.41</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>99.12</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>91.29000000000001</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>83.98</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>90.83</v>
+        <v>90.59</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -3783,12 +3759,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3797,31 +3773,31 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>80.69</v>
+        <v>84.41</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>85.12</v>
+        <v>82.55</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>92.12</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>82.84999999999999</v>
+        <v>83.47</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>70.72</v>
+        <v>71.63</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>77.73999999999999</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -3837,12 +3813,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3851,31 +3827,31 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>93.8</v>
+        <v>93.56</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>96.18000000000001</v>
+        <v>96.62</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>99.61</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>94.98</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>90.44</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>94.77</v>
+        <v>94.87</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -3891,12 +3867,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3908,19 +3884,19 @@
         <v>97.02</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>97.25</v>
+        <v>97.27</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>99.29000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>97.13</v>
+        <v>97.14</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>94.42</v>
+        <v>94.45</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>96.73</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>4.88</v>
@@ -3945,12 +3921,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3959,22 +3935,22 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>90.05</v>
+        <v>90.64</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>92.12</v>
+        <v>91.64</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>99.09999999999999</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>91.06999999999999</v>
+        <v>91.14</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>83.72</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>90.66</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>4.88</v>
@@ -3999,12 +3975,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4013,19 +3989,19 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>81.44</v>
+        <v>80.94</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>84.94</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>92.22</v>
+        <v>92.25</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>83.16</v>
+        <v>83.13</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>71.17</v>
+        <v>71.12</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>78.09999999999999</v>
@@ -4053,12 +4029,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4067,22 +4043,22 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>93.42</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>96.66</v>
+        <v>96.67</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>99.61</v>
+        <v>99.62</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>95.02</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>90.5</v>
+        <v>90.81</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>94.81</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>4.88</v>
@@ -4107,12 +4083,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4121,31 +4097,31 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>97.03</v>
+        <v>97.02</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>97.23999999999999</v>
+        <v>97.33</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>99.29000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>97.13</v>
+        <v>97.17</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>94.43000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>96.73</v>
+        <v>96.78</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6947</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
@@ -4161,12 +4137,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4175,31 +4151,31 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>90.25</v>
+        <v>90.22</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>92.12</v>
+        <v>92.22</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>99.11</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>83.78</v>
+        <v>83.83</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>90.70999999999999</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6947</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -4215,12 +4191,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4229,31 +4205,31 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>81.26000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>85.31</v>
+        <v>86.05</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>92.28</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>83.23999999999999</v>
+        <v>82.97</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>71.29000000000001</v>
+        <v>70.89</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>78.23</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6947</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -4269,12 +4245,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4283,31 +4259,31 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>93.11</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>96.78</v>
+        <v>96</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.59</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>94.91</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>90.31</v>
+        <v>89.95</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>94.7</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6947</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
@@ -4323,12 +4299,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4337,31 +4313,31 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>96.97</v>
+        <v>97.02</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>97.08</v>
+        <v>97.34</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>99.27</v>
+        <v>99.3</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>97.02</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>94.22</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>96.59999999999999</v>
+        <v>96.78</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2.717</v>
+        <v>2.6947</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
@@ -4377,12 +4353,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4391,31 +4367,31 @@
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>90.15000000000001</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>92.33</v>
+        <v>92.41</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>99.12</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>91.23</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>83.87</v>
+        <v>83.98</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>90.76000000000001</v>
+        <v>90.83</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2.717</v>
+        <v>2.6947</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
@@ -4431,12 +4407,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4445,31 +4421,31 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>81.90000000000001</v>
+        <v>80.69</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>84.53</v>
+        <v>85.12</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>92.2</v>
+        <v>92.12</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>83.19</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>71.22</v>
+        <v>70.72</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>78.11</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2.717</v>
+        <v>2.6947</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -4485,12 +4461,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4499,31 +4475,31 @@
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>94.02</v>
+        <v>93.8</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>96.37</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>99.62</v>
+        <v>99.61</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>95.18000000000001</v>
+        <v>94.98</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>90.8</v>
+        <v>90.44</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>94.98</v>
+        <v>94.77</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2.717</v>
+        <v>2.6947</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
@@ -4539,12 +4515,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4553,22 +4529,22 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>96.94</v>
+        <v>97.02</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>97.17</v>
+        <v>97.25</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>99.27</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>97.05</v>
+        <v>97.13</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>94.27</v>
+        <v>94.42</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>96.64</v>
+        <v>96.73</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>4.88</v>
@@ -4593,12 +4569,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4607,22 +4583,22 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>90.09</v>
+        <v>90.05</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>92.62</v>
+        <v>92.12</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>99.13</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>91.34</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>84.06</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>90.88</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>4.88</v>
@@ -4647,12 +4623,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4661,22 +4637,22 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>81.09999999999999</v>
+        <v>81.44</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>85.65000000000001</v>
+        <v>84.94</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>92.34</v>
+        <v>92.22</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>83.31</v>
+        <v>83.16</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>71.17</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>78.34999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>4.88</v>
@@ -4701,12 +4677,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4715,22 +4691,22 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>93.8</v>
+        <v>93.42</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>96.38</v>
+        <v>96.66</v>
       </c>
       <c r="G81" s="2" t="n">
         <v>99.61</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>95.02</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>90.61</v>
+        <v>90.5</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>94.87</v>
+        <v>94.81</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>4.88</v>
@@ -4755,12 +4731,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4769,31 +4745,31 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>97</v>
+        <v>97.03</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>97.33</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>99.3</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>97.17</v>
+        <v>97.13</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>94.48999999999999</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>96.77</v>
+        <v>96.73</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.9767</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
@@ -4809,12 +4785,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4823,31 +4799,31 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>89.63</v>
+        <v>90.25</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>92.70999999999999</v>
+        <v>92.12</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>99.11</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>91.15000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>83.73</v>
+        <v>83.78</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>90.68000000000001</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.9767</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -4863,12 +4839,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4877,31 +4853,31 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>80.41</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>85.06999999999999</v>
+        <v>85.31</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>92.05</v>
+        <v>92.28</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>82.68000000000001</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>70.47</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>77.53</v>
+        <v>78.23</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.9767</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -4917,12 +4893,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4931,31 +4907,31 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>93.44</v>
+        <v>93.11</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>96.28</v>
+        <v>96.78</v>
       </c>
       <c r="G85" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>94.84</v>
+        <v>94.91</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>90.19</v>
+        <v>90.31</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>94.63</v>
+        <v>94.7</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.9767</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -4971,49 +4947,49 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Run8</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CTRL_R8</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>90.43000000000001</v>
+        <v>96.97</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>92.01000000000001</v>
+        <v>97.08</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>99.11</v>
+        <v>99.27</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>97.02</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>83.84</v>
+        <v>94.22</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>90.73999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>31.026</v>
+        <v>4.89</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>31.026</v>
+        <v>4.89</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>13.6715</v>
+        <v>2.717</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>casa_vmamba_str</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -5025,49 +5001,49 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Run8</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CTRL_R8</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>79.66</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>84.22</v>
+        <v>92.33</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>91.69</v>
+        <v>99.12</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>81.88</v>
+        <v>91.23</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>69.31999999999999</v>
+        <v>83.87</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>76.48999999999999</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>31.026</v>
+        <v>4.89</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>31.026</v>
+        <v>4.89</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>13.6715</v>
+        <v>2.717</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>casa_vmamba_str</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -5079,49 +5055,49 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Run9</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>S0_CTRL</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>97.77</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>97.77</v>
+        <v>84.53</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>99.45</v>
+        <v>92.2</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>97.77</v>
+        <v>83.19</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>95.65000000000001</v>
+        <v>71.22</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>97.45999999999999</v>
+        <v>78.11</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>31.977</v>
+        <v>4.89</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>31.977</v>
+        <v>4.89</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>14.6841</v>
+        <v>2.717</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -5133,49 +5109,49 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Run9</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>S0_CTRL</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>89.79000000000001</v>
+        <v>94.02</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>92.53</v>
+        <v>96.37</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>99.11</v>
+        <v>99.62</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>91.14</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>83.72</v>
+        <v>90.8</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>90.67</v>
+        <v>94.98</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>31.977</v>
+        <v>4.89</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>31.977</v>
+        <v>4.89</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>14.6841</v>
+        <v>2.717</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -5187,12 +5163,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Run9</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>S1_HSAM</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5201,260 +5177,268 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>97.66</v>
+        <v>96.94</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>97.65000000000001</v>
+        <v>97.17</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>99.42</v>
+        <v>99.27</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>97.65000000000001</v>
+        <v>97.05</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>95.42</v>
+        <v>94.27</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>97.31999999999999</v>
+        <v>96.64</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>31.977</v>
+        <v>4.88</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>31.977</v>
+        <v>4.88</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>14.769</v>
+        <v>2.6747</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>80.27</v>
+        <v>90.09</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>85.19</v>
+        <v>92.62</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>92.06</v>
+        <v>99.13</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>82.65000000000001</v>
+        <v>91.34</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>70.44</v>
+        <v>84.06</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>90.88</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>3.016737</v>
+        <v>4.88</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M91" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_none</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>91.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>91.72</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>99.13</v>
+        <v>92.34</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>91.45999999999999</v>
+        <v>83.31</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>84.26000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>91</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>3.016737</v>
+        <v>4.88</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M92" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_none</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>80.39</v>
+        <v>93.8</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>82.89</v>
+        <v>96.38</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>91.45999999999999</v>
+        <v>99.61</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>81.62</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>68.95</v>
+        <v>90.61</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>76.06999999999999</v>
+        <v>94.87</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>3.016737</v>
+        <v>4.88</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M93" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_none</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>92.61</v>
+        <v>97</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>95.26000000000001</v>
+        <v>97.33</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>99.52</v>
+        <v>99.3</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>93.92</v>
+        <v>97.17</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>88.53</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>93.67</v>
+        <v>96.77</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>3.016737</v>
+        <v>4.88</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M94" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_none</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5463,50 +5447,52 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>90.55</v>
+        <v>89.63</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>92.03</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>99.12</v>
+        <v>99.11</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>91.28</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>83.95999999999999</v>
+        <v>83.73</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>90.81999999999999</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>3.049509</v>
+        <v>4.88</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M95" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_hyperbolic</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5515,50 +5501,52 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>78.67</v>
+        <v>80.41</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>85.08</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>91.72</v>
+        <v>92.05</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>81.75</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>69.13</v>
+        <v>70.47</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>76.40000000000001</v>
+        <v>77.53</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>3.049509</v>
+        <v>4.88</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M96" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_hyperbolic</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5567,50 +5555,52 @@
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>92.84999999999999</v>
+        <v>93.44</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>95.31999999999999</v>
+        <v>96.28</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>99.54000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>94.06999999999999</v>
+        <v>94.84</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>88.8</v>
+        <v>90.19</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>93.83</v>
+        <v>94.63</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>3.049509</v>
+        <v>4.88</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M97" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_hyperbolic</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run8</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>CTRL_R8</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5619,50 +5609,52 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>89.72</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>93.12</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>99.14</v>
+        <v>99.11</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>91.39</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>84.14</v>
+        <v>83.84</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>90.93000000000001</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>3.049509</v>
+        <v>31.026</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M98" s="2" t="n"/>
+        <v>31.026</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>13.6715</v>
+      </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>casa_vmamba_str</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run8</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>CTRL_R8</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5671,102 +5663,106 @@
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>82.83</v>
+        <v>79.66</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>82.86</v>
+        <v>84.22</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>91.91</v>
+        <v>91.69</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>82.84999999999999</v>
+        <v>81.88</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>70.72</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>77.56</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>3.049509</v>
+        <v>31.026</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M99" s="2" t="n"/>
+        <v>31.026</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>13.6715</v>
+      </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>casa_vmamba_str</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run9</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>S0_CTRL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>93.04000000000001</v>
+        <v>97.77</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>96.08</v>
+        <v>97.77</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>99.56999999999999</v>
+        <v>99.45</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>94.53</v>
+        <v>97.77</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>89.63</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>94.31</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>3.049509</v>
+        <v>31.977</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M100" s="2" t="n"/>
+        <v>31.977</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>14.6841</v>
+      </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run9</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>S0_CTRL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5775,96 +5771,96 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>91.09</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>92.8</v>
+        <v>92.53</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>99.19</v>
+        <v>99.11</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>91.94</v>
+        <v>91.14</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>85.08</v>
+        <v>83.72</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>90.67</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>11.754</v>
+        <v>31.977</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>20.661</v>
+        <v>31.977</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>26.3183</v>
+        <v>14.6841</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run9</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>S1_HSAM</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>80.3</v>
+        <v>97.66</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>84.81</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>99.42</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>82.5</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>95.42</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>11.754</v>
+        <v>31.977</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>20.661</v>
+        <v>31.977</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>26.3183</v>
+        <v>14.769</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5874,105 +5870,101 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>80.27</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>92.75</v>
+        <v>85.19</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>92.06</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>91.86</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>84.94</v>
+        <v>70.44</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>11.754</v>
+        <v>3.016737</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M103" s="2" t="n">
-        <v>26.2593</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M103" s="2" t="n"/>
       <c r="N103" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>80.55</v>
+        <v>91.2</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>84.23</v>
+        <v>91.72</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>91.86</v>
+        <v>99.13</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>82.34999999999999</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>70</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>77.06</v>
+        <v>91</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>11.754</v>
+        <v>3.016737</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M104" s="2" t="n">
-        <v>26.2593</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M104" s="2" t="n"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5982,51 +5974,49 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>91.38</v>
+        <v>80.39</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>92.3</v>
+        <v>82.89</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>99.17</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>91.84</v>
+        <v>81.62</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>84.91</v>
+        <v>68.95</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>11.754</v>
+        <v>3.016737</v>
       </c>
       <c r="L105" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M105" s="2" t="n">
-        <v>26.1484</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M105" s="2" t="n"/>
       <c r="N105" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6036,51 +6026,49 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>92.61</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>86.03</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>99.52</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>93.92</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>69.55</v>
+        <v>88.53</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>76.83</v>
+        <v>93.67</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>11.754</v>
+        <v>3.016737</v>
       </c>
       <c r="L106" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M106" s="2" t="n">
-        <v>26.1484</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M106" s="2" t="n"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6090,7 +6078,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6099,42 +6087,40 @@
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>91.13</v>
+        <v>90.55</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>92.03</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.12</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>91.88</v>
+        <v>91.28</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>84.98</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>91.45</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L107" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M107" s="2" t="n">
-        <v>26.0894</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M107" s="2" t="n"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6144,7 +6130,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6153,366 +6139,366 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>78.67</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>85.05</v>
+        <v>85.08</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>92.36</v>
+        <v>91.72</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>83.52</v>
+        <v>81.75</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>71.7</v>
+        <v>69.13</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>78.55</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M108" s="2" t="n">
-        <v>26.0894</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M108" s="2" t="n"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>84.28</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>91.7</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>81.92</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>69.37</v>
+        <v>88.8</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>93.83</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M109" s="2" t="n">
-        <v>26.0894</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M109" s="2" t="n"/>
       <c r="N109" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>89.72</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>97.47</v>
+        <v>93.12</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>99.37</v>
+        <v>99.14</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>97.45</v>
+        <v>91.39</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>95.02</v>
+        <v>84.14</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>97.09</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>3.016737</v>
+        <v>3.049509</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>3.100404</v>
+        <v>3.133176</v>
       </c>
       <c r="M110" s="2" t="n"/>
       <c r="N110" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>90.41</v>
+        <v>82.83</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>91.83</v>
+        <v>82.86</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>91.11</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>83.67</v>
+        <v>70.72</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>90.64</v>
+        <v>77.56</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>3.016737</v>
+        <v>3.049509</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>3.100404</v>
+        <v>3.133176</v>
       </c>
       <c r="M111" s="2" t="n"/>
       <c r="N111" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>79.81</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>83.84999999999999</v>
+        <v>96.08</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>91.61</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>81.78</v>
+        <v>94.53</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>69.18000000000001</v>
+        <v>89.63</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>76.34</v>
+        <v>94.31</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>3.016737</v>
+        <v>3.049509</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>3.100404</v>
+        <v>3.133176</v>
       </c>
       <c r="M112" s="2" t="n"/>
       <c r="N112" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>93.2</v>
+        <v>91.09</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>94.70999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>99.52</v>
+        <v>99.19</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>93.95</v>
+        <v>91.94</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>88.59</v>
+        <v>85.08</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>93.7</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>3.016737</v>
+        <v>11.754</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M113" s="2" t="n"/>
+        <v>20.661</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>26.3183</v>
+      </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>97.48</v>
+        <v>80.3</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>97.45</v>
+        <v>84.81</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>99.37</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>97.47</v>
+        <v>82.5</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>95.06</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>97.11</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>3.050665</v>
+        <v>11.754</v>
       </c>
       <c r="L114" s="2" t="n">
-        <v>3.134332</v>
-      </c>
-      <c r="M114" s="2" t="n"/>
+        <v>20.661</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>26.3183</v>
+      </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6521,50 +6507,52 @@
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>90.61</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>92.37</v>
+        <v>92.75</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>99.14</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>91.48</v>
+        <v>91.86</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>84.3</v>
+        <v>84.94</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>91.03</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>3.050665</v>
+        <v>11.754</v>
       </c>
       <c r="L115" s="2" t="n">
-        <v>3.134332</v>
-      </c>
-      <c r="M115" s="2" t="n"/>
+        <v>20.661</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>26.2593</v>
+      </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6573,154 +6561,160 @@
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>77.55</v>
+        <v>80.55</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>85.81</v>
+        <v>84.23</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>91.68000000000001</v>
+        <v>91.86</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>81.47</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>68.73</v>
+        <v>70</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>76.12</v>
+        <v>77.06</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>3.050665</v>
+        <v>11.754</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>3.134332</v>
-      </c>
-      <c r="M116" s="2" t="n"/>
+        <v>20.661</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>26.2593</v>
+      </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>92.5</v>
+        <v>91.38</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>96.20999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>99.56</v>
+        <v>99.17</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>94.31999999999999</v>
+        <v>91.84</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>89.25</v>
+        <v>84.91</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>94.09</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>3.050665</v>
+        <v>11.754</v>
       </c>
       <c r="L117" s="2" t="n">
-        <v>3.134332</v>
-      </c>
-      <c r="M117" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>26.1484</v>
+      </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>97.51000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>97.45</v>
+        <v>86.03</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>99.38</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>97.48</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>95.09</v>
+        <v>69.55</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>97.13</v>
+        <v>76.83</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>3.059369</v>
+        <v>11.754</v>
       </c>
       <c r="L118" s="2" t="n">
-        <v>3.143036</v>
-      </c>
-      <c r="M118" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>26.1484</v>
+      </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6729,50 +6723,52 @@
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>90.58</v>
+        <v>91.13</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>91.77</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>99.11</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>91.17</v>
+        <v>91.88</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>83.77</v>
+        <v>84.98</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>90.7</v>
+        <v>91.45</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>3.059369</v>
+        <v>11.754</v>
       </c>
       <c r="L119" s="2" t="n">
-        <v>3.143036</v>
-      </c>
-      <c r="M119" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>26.0894</v>
+      </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6781,40 +6777,42 @@
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>76.7</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>85.81999999999999</v>
+        <v>85.05</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>91.52</v>
+        <v>92.36</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>81.01000000000001</v>
+        <v>83.52</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>68.06999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>75.56999999999999</v>
+        <v>78.55</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>3.059369</v>
+        <v>11.754</v>
       </c>
       <c r="L120" s="2" t="n">
-        <v>3.143036</v>
-      </c>
-      <c r="M120" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>26.0894</v>
+      </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6824,42 +6822,44 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>A4_DETAIL_FROZEN</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>92.61</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>95.31</v>
+        <v>84.28</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>99.53</v>
+        <v>91.7</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>93.94</v>
+        <v>81.92</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>88.58</v>
+        <v>69.37</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>93.69</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>3.059369</v>
+        <v>11.754</v>
       </c>
       <c r="L121" s="2" t="n">
-        <v>3.143036</v>
-      </c>
-      <c r="M121" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>26.0894</v>
+      </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6885,22 +6885,22 @@
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>97.41</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>97.47</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>99.36</v>
+        <v>99.37</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>97.42</v>
+        <v>97.45</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>94.98</v>
+        <v>95.02</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>97.06</v>
+        <v>97.09</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>3.016737</v>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6937,22 +6937,22 @@
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>90.29000000000001</v>
+        <v>90.41</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>92.58</v>
+        <v>91.83</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>99.14</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>91.42</v>
+        <v>91.11</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>84.19</v>
+        <v>83.67</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>90.95999999999999</v>
+        <v>90.64</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>3.016737</v>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6989,22 +6989,22 @@
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>80.38</v>
+        <v>79.81</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>85.22</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>92.09</v>
+        <v>91.61</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>82.73</v>
+        <v>81.78</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>70.55</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>77.59999999999999</v>
+        <v>76.34</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>3.016737</v>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7041,22 +7041,22 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>92.87</v>
+        <v>93.2</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>96.04000000000001</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>99.56999999999999</v>
+        <v>99.52</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>94.43000000000001</v>
+        <v>93.95</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>89.44</v>
+        <v>88.59</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>94.2</v>
+        <v>93.7</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>3.016737</v>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7093,28 +7093,28 @@
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>97.52</v>
+        <v>97.48</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>97.42</v>
+        <v>97.45</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>99.38</v>
+        <v>99.37</v>
       </c>
       <c r="H126" s="2" t="n">
         <v>97.47</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>95.06</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>97.11</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>3.060525</v>
+        <v>3.050665</v>
       </c>
       <c r="L126" s="2" t="n">
-        <v>3.144192</v>
+        <v>3.134332</v>
       </c>
       <c r="M126" s="2" t="n"/>
       <c r="N126" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7145,28 +7145,28 @@
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>90.48</v>
+        <v>90.61</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>92.91</v>
+        <v>92.37</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>99.16</v>
+        <v>99.14</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>91.68000000000001</v>
+        <v>91.48</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>84.64</v>
+        <v>84.3</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>91.23999999999999</v>
+        <v>91.03</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>3.060525</v>
+        <v>3.050665</v>
       </c>
       <c r="L127" s="2" t="n">
-        <v>3.144192</v>
+        <v>3.134332</v>
       </c>
       <c r="M127" s="2" t="n"/>
       <c r="N127" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7197,28 +7197,28 @@
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>83.2</v>
+        <v>77.55</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>80.95</v>
+        <v>85.81</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>91.42</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>82.06</v>
+        <v>81.47</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>69.58</v>
+        <v>68.73</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>76.42</v>
+        <v>76.12</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>3.060525</v>
+        <v>3.050665</v>
       </c>
       <c r="L128" s="2" t="n">
-        <v>3.144192</v>
+        <v>3.134332</v>
       </c>
       <c r="M128" s="2" t="n"/>
       <c r="N128" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7249,28 +7249,28 @@
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>92.36</v>
+        <v>92.5</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>95.44</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>99.52</v>
+        <v>99.56</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>93.88</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>88.45999999999999</v>
+        <v>89.25</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>93.63</v>
+        <v>94.09</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>3.060525</v>
+        <v>3.050665</v>
       </c>
       <c r="L129" s="2" t="n">
-        <v>3.144192</v>
+        <v>3.134332</v>
       </c>
       <c r="M129" s="2" t="n"/>
       <c r="N129" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7301,28 +7301,28 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>97.51000000000001</v>
+        <v>97.45</v>
       </c>
       <c r="G130" s="2" t="n">
         <v>99.38</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>97.47</v>
+        <v>97.48</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>95.06</v>
+        <v>95.09</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>97.11</v>
+        <v>97.13</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>3.077293</v>
+        <v>3.059369</v>
       </c>
       <c r="L130" s="2" t="n">
-        <v>3.16096</v>
+        <v>3.143036</v>
       </c>
       <c r="M130" s="2" t="n"/>
       <c r="N130" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7353,28 +7353,28 @@
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>90.45</v>
+        <v>90.58</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>92.68000000000001</v>
+        <v>91.77</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>99.15000000000001</v>
+        <v>99.11</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>91.55</v>
+        <v>91.17</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>84.42</v>
+        <v>83.77</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>91.11</v>
+        <v>90.7</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>3.077293</v>
+        <v>3.059369</v>
       </c>
       <c r="L131" s="2" t="n">
-        <v>3.16096</v>
+        <v>3.143036</v>
       </c>
       <c r="M131" s="2" t="n"/>
       <c r="N131" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7405,28 +7405,28 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>78.5</v>
+        <v>76.7</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>86.2</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>91.97</v>
+        <v>91.52</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>82.17</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>69.73999999999999</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>77</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>3.077293</v>
+        <v>3.059369</v>
       </c>
       <c r="L132" s="2" t="n">
-        <v>3.16096</v>
+        <v>3.143036</v>
       </c>
       <c r="M132" s="2" t="n"/>
       <c r="N132" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7457,28 +7457,28 @@
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>91.88</v>
+        <v>92.61</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>94.98999999999999</v>
+        <v>95.31</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>99.48999999999999</v>
+        <v>99.53</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>93.41</v>
+        <v>93.94</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>87.63</v>
+        <v>88.58</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>93.14</v>
+        <v>93.69</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>3.077293</v>
+        <v>3.059369</v>
       </c>
       <c r="L133" s="2" t="n">
-        <v>3.16096</v>
+        <v>3.143036</v>
       </c>
       <c r="M133" s="2" t="n"/>
       <c r="N133" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7509,22 +7509,22 @@
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>97.5</v>
+        <v>97.41</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>97.34999999999999</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="G134" s="2" t="n">
         <v>99.36</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>97.42</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>94.98999999999999</v>
+        <v>94.98</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>97.06999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="K134" s="2" t="n">
         <v>3.016737</v>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7561,22 +7561,22 @@
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>90.69</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>92.43000000000001</v>
+        <v>92.58</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>99.15000000000001</v>
+        <v>99.14</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>91.55</v>
+        <v>91.42</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>84.42</v>
+        <v>84.19</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>3.016737</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7613,22 +7613,22 @@
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>82.58</v>
+        <v>80.38</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>82.25</v>
+        <v>85.22</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>91.69</v>
+        <v>92.09</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>82.42</v>
+        <v>82.73</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>70.09</v>
+        <v>70.55</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>76.98</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>3.016737</v>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7665,22 +7665,22 @@
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>92.31</v>
+        <v>92.87</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>94.59999999999999</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>99.48999999999999</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>93.44</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>87.69</v>
+        <v>89.44</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>93.17</v>
+        <v>94.2</v>
       </c>
       <c r="K137" s="2" t="n">
         <v>3.016737</v>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7717,28 +7717,28 @@
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>97.53</v>
+        <v>97.52</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>97.38</v>
+        <v>97.42</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>99.37</v>
+        <v>99.38</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>97.45</v>
+        <v>97.47</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>95.03</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>97.09</v>
+        <v>97.11</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.060525</v>
       </c>
       <c r="L138" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.144192</v>
       </c>
       <c r="M138" s="2" t="n"/>
       <c r="N138" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7769,28 +7769,28 @@
         </is>
       </c>
       <c r="E139" s="2" t="n">
-        <v>90.34999999999999</v>
+        <v>90.48</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>91.77</v>
+        <v>92.91</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.16</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>91.05</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>83.56999999999999</v>
+        <v>84.64</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>90.58</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.060525</v>
       </c>
       <c r="L139" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.144192</v>
       </c>
       <c r="M139" s="2" t="n"/>
       <c r="N139" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7821,28 +7821,28 @@
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>76.31999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>85.91</v>
+        <v>80.95</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>91.45999999999999</v>
+        <v>91.42</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>80.83</v>
+        <v>82.06</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>67.83</v>
+        <v>69.58</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>75.37</v>
+        <v>76.42</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.060525</v>
       </c>
       <c r="L140" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.144192</v>
       </c>
       <c r="M140" s="2" t="n"/>
       <c r="N140" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7873,28 +7873,28 @@
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>93.55</v>
+        <v>92.36</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>95.95</v>
+        <v>95.44</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>99.59</v>
+        <v>99.52</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>94.73</v>
+        <v>93.88</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>89.98999999999999</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>94.52</v>
+        <v>93.63</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.060525</v>
       </c>
       <c r="L141" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.144192</v>
       </c>
       <c r="M141" s="2" t="n"/>
       <c r="N141" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>97.45</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>97.48999999999999</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="G142" s="2" t="n">
         <v>99.38</v>
@@ -7937,16 +7937,16 @@
         <v>97.47</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>95.06</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>97.12</v>
+        <v>97.11</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.077293</v>
       </c>
       <c r="L142" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.16096</v>
       </c>
       <c r="M142" s="2" t="n"/>
       <c r="N142" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -7977,28 +7977,28 @@
         </is>
       </c>
       <c r="E143" s="2" t="n">
-        <v>90.67</v>
+        <v>90.45</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>92.58</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="G143" s="2" t="n">
         <v>99.15000000000001</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>91.62</v>
+        <v>91.55</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>84.53</v>
+        <v>84.42</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>91.17</v>
+        <v>91.11</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.077293</v>
       </c>
       <c r="L143" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.16096</v>
       </c>
       <c r="M143" s="2" t="n"/>
       <c r="N143" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8029,28 +8029,28 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>77.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>87.42</v>
+        <v>86.2</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>92.15000000000001</v>
+        <v>91.97</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>82.39</v>
+        <v>82.17</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>70.05</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>77.36</v>
+        <v>77</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.077293</v>
       </c>
       <c r="L144" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.16096</v>
       </c>
       <c r="M144" s="2" t="n"/>
       <c r="N144" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8081,28 +8081,28 @@
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>92.61</v>
+        <v>91.88</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>95.77</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="G145" s="2" t="n">
-        <v>99.54000000000001</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>94.16</v>
+        <v>93.41</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>88.97</v>
+        <v>87.63</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>93.93000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.077293</v>
       </c>
       <c r="L145" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.16096</v>
       </c>
       <c r="M145" s="2" t="n"/>
       <c r="N145" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="E146" s="2" t="n">
-        <v>97.31999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>97.54000000000001</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="G146" s="2" t="n">
-        <v>99.37</v>
+        <v>99.36</v>
       </c>
       <c r="H146" s="2" t="n">
         <v>97.43000000000001</v>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8185,22 +8185,22 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>89.79000000000001</v>
+        <v>90.69</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>92.27</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>91.01000000000001</v>
+        <v>91.55</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>83.51000000000001</v>
+        <v>84.42</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>90.54000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="K147" s="2" t="n">
         <v>3.016737</v>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8237,22 +8237,22 @@
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>79.92</v>
+        <v>82.58</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>84.81</v>
+        <v>82.25</v>
       </c>
       <c r="G148" s="2" t="n">
-        <v>91.89</v>
+        <v>91.69</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>82.29000000000001</v>
+        <v>82.42</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>69.91</v>
+        <v>70.09</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>76.98</v>
       </c>
       <c r="K148" s="2" t="n">
         <v>3.016737</v>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8289,22 +8289,22 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>92.78</v>
+        <v>92.31</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>95.23</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G149" s="2" t="n">
-        <v>99.53</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>93.98999999999999</v>
+        <v>93.44</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>88.66</v>
+        <v>87.69</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>93.75</v>
+        <v>93.17</v>
       </c>
       <c r="K149" s="2" t="n">
         <v>3.016737</v>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8341,22 +8341,22 @@
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>97.48999999999999</v>
+        <v>97.53</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>97.45</v>
+        <v>97.38</v>
       </c>
       <c r="G150" s="2" t="n">
         <v>99.37</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>97.47</v>
+        <v>97.45</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>95.06</v>
+        <v>95.03</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>97.11</v>
+        <v>97.09</v>
       </c>
       <c r="K150" s="2" t="n">
         <v>3.050665</v>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8393,22 +8393,22 @@
         </is>
       </c>
       <c r="E151" s="2" t="n">
-        <v>89.73999999999999</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>93.42</v>
+        <v>91.77</v>
       </c>
       <c r="G151" s="2" t="n">
-        <v>99.16</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>91.54000000000001</v>
+        <v>91.05</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>84.40000000000001</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>90.58</v>
       </c>
       <c r="K151" s="2" t="n">
         <v>3.050665</v>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8445,22 +8445,22 @@
         </is>
       </c>
       <c r="E152" s="2" t="n">
-        <v>77.78</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>84.04000000000001</v>
+        <v>85.91</v>
       </c>
       <c r="G152" s="2" t="n">
-        <v>91.28</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>80.79000000000001</v>
+        <v>80.83</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>67.77</v>
+        <v>67.83</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>75.16</v>
+        <v>75.37</v>
       </c>
       <c r="K152" s="2" t="n">
         <v>3.050665</v>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8497,22 +8497,22 @@
         </is>
       </c>
       <c r="E153" s="2" t="n">
-        <v>93.05</v>
+        <v>93.55</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>96.14</v>
+        <v>95.95</v>
       </c>
       <c r="G153" s="2" t="n">
-        <v>99.58</v>
+        <v>99.59</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>94.56999999999999</v>
+        <v>94.73</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>89.7</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>94.34999999999999</v>
+        <v>94.52</v>
       </c>
       <c r="K153" s="2" t="n">
         <v>3.050665</v>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8549,10 +8549,10 @@
         </is>
       </c>
       <c r="E154" s="2" t="n">
-        <v>97.41</v>
+        <v>97.45</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>97.53</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="G154" s="2" t="n">
         <v>99.38</v>
@@ -8561,10 +8561,10 @@
         <v>97.47</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>95.06</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>97.11</v>
+        <v>97.12</v>
       </c>
       <c r="K154" s="2" t="n">
         <v>3.067561</v>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -8601,22 +8601,22 @@
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>90.68000000000001</v>
+        <v>90.67</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>91.98</v>
+        <v>92.58</v>
       </c>
       <c r="G155" s="2" t="n">
-        <v>99.12</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>91.33</v>
+        <v>91.62</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>84.04000000000001</v>
+        <v>84.53</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>90.87</v>
+        <v>91.17</v>
       </c>
       <c r="K155" s="2" t="n">
         <v>3.067561</v>
@@ -8639,7 +8639,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -8653,22 +8653,22 @@
         </is>
       </c>
       <c r="E156" s="2" t="n">
-        <v>77.18000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>85.53</v>
+        <v>87.42</v>
       </c>
       <c r="G156" s="2" t="n">
-        <v>91.54000000000001</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>81.14</v>
+        <v>82.39</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>68.27</v>
+        <v>70.05</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>75.70999999999999</v>
+        <v>77.36</v>
       </c>
       <c r="K156" s="2" t="n">
         <v>3.067561</v>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -8705,22 +8705,22 @@
         </is>
       </c>
       <c r="E157" s="2" t="n">
-        <v>92.63</v>
+        <v>92.61</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>96.55</v>
+        <v>95.77</v>
       </c>
       <c r="G157" s="2" t="n">
-        <v>99.58</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>94.55</v>
+        <v>94.16</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>89.67</v>
+        <v>88.97</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>94.33</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="K157" s="2" t="n">
         <v>3.067561</v>
@@ -8738,17 +8738,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -8757,52 +8757,50 @@
         </is>
       </c>
       <c r="E158" s="2" t="n">
-        <v>93.13</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="F158" s="2" t="n">
-        <v>95.16</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="G158" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>99.37</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>94.13</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>88.91</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L158" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M158" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M158" s="2" t="n"/>
       <c r="N158" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -8811,52 +8809,50 @@
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>86.37</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F159" s="2" t="n">
-        <v>89.25</v>
+        <v>92.27</v>
       </c>
       <c r="G159" s="2" t="n">
-        <v>98.78</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>87.14</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L159" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M159" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M159" s="2" t="n"/>
       <c r="N159" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8865,52 +8861,50 @@
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>79.92</v>
       </c>
       <c r="F160" s="2" t="n">
-        <v>84.5</v>
+        <v>84.81</v>
       </c>
       <c r="G160" s="2" t="n">
-        <v>91.81</v>
+        <v>91.89</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>69.91</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>76.84</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L160" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M160" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M160" s="2" t="n"/>
       <c r="N160" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8919,52 +8913,50 @@
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>90.16</v>
+        <v>92.78</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>93.97</v>
+        <v>95.23</v>
       </c>
       <c r="G161" s="2" t="n">
-        <v>99.38</v>
+        <v>99.53</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>92.02</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>85.23</v>
+        <v>88.66</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>91.7</v>
+        <v>93.75</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L161" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M161" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M161" s="2" t="n"/>
       <c r="N161" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8973,52 +8965,50 @@
         </is>
       </c>
       <c r="E162" s="2" t="n">
-        <v>94.7</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="F162" s="2" t="n">
-        <v>96.13</v>
+        <v>97.45</v>
       </c>
       <c r="G162" s="2" t="n">
-        <v>98.88</v>
+        <v>99.37</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>95.41</v>
+        <v>97.47</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>91.22</v>
+        <v>95.06</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>94.77</v>
+        <v>97.11</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L162" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M162" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M162" s="2" t="n"/>
       <c r="N162" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -9027,52 +9017,50 @@
         </is>
       </c>
       <c r="E163" s="2" t="n">
-        <v>88.42</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="F163" s="2" t="n">
-        <v>91.97</v>
+        <v>93.42</v>
       </c>
       <c r="G163" s="2" t="n">
-        <v>99.02</v>
+        <v>99.16</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>90.16</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>82.08</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>89.64</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L163" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M163" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M163" s="2" t="n"/>
       <c r="N163" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -9081,52 +9069,50 @@
         </is>
       </c>
       <c r="E164" s="2" t="n">
-        <v>78.73</v>
+        <v>77.78</v>
       </c>
       <c r="F164" s="2" t="n">
-        <v>84.98</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="G164" s="2" t="n">
-        <v>91.7</v>
+        <v>91.28</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>69.11</v>
+        <v>67.77</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>76.38</v>
+        <v>75.16</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L164" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M164" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M164" s="2" t="n"/>
       <c r="N164" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -9135,160 +9121,154 @@
         </is>
       </c>
       <c r="E165" s="2" t="n">
-        <v>91.64</v>
+        <v>93.05</v>
       </c>
       <c r="F165" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>96.14</v>
       </c>
       <c r="G165" s="2" t="n">
-        <v>99.47</v>
+        <v>99.58</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>93.2</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>87.27</v>
+        <v>89.7</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L165" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M165" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M165" s="2" t="n"/>
       <c r="N165" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>82.42</v>
+        <v>97.41</v>
       </c>
       <c r="F166" s="2" t="n">
-        <v>83.87</v>
+        <v>97.53</v>
       </c>
       <c r="G166" s="2" t="n">
-        <v>92.12</v>
+        <v>99.38</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>83.14</v>
+        <v>97.47</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>71.14</v>
+        <v>95.06</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>97.11</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>11.754</v>
+        <v>3.067561</v>
       </c>
       <c r="L166" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M166" s="2" t="n">
-        <v>26.3246</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M166" s="2" t="n"/>
       <c r="N166" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E167" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="F167" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>91.98</v>
       </c>
       <c r="G167" s="2" t="n">
-        <v>91.94</v>
+        <v>99.12</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>82.77</v>
+        <v>91.33</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>70.61</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>90.87</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>8.195</v>
+        <v>3.067561</v>
       </c>
       <c r="L167" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M167" s="2" t="n">
-        <v>24.1021</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M167" s="2" t="n"/>
       <c r="N167" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -9297,348 +9277,992 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>79.94</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="F168" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>85.53</v>
       </c>
       <c r="G168" s="2" t="n">
-        <v>91.89</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>82.3</v>
+        <v>81.14</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>69.92</v>
+        <v>68.27</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>5.492</v>
+        <v>3.067561</v>
       </c>
       <c r="L168" s="2" t="n">
-        <v>3.515</v>
-      </c>
-      <c r="M168" s="2" t="n">
-        <v>10.7311</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M168" s="2" t="n"/>
       <c r="N168" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E169" s="2" t="n">
-        <v>80.87</v>
+        <v>92.63</v>
       </c>
       <c r="F169" s="2" t="n">
-        <v>83.81</v>
+        <v>96.55</v>
       </c>
       <c r="G169" s="2" t="n">
-        <v>91.81</v>
+        <v>99.58</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>94.55</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>69.95</v>
+        <v>89.67</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>94.33</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>5.533</v>
+        <v>3.067561</v>
       </c>
       <c r="L169" s="2" t="n">
-        <v>3.556</v>
-      </c>
-      <c r="M169" s="2" t="n">
-        <v>10.9824</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M169" s="2" t="n"/>
       <c r="N169" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E170" s="2" t="n">
-        <v>79.78</v>
+        <v>93.13</v>
       </c>
       <c r="F170" s="2" t="n">
-        <v>84.39</v>
+        <v>95.16</v>
       </c>
       <c r="G170" s="2" t="n">
-        <v>91.75</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>82.02</v>
+        <v>94.13</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>69.52</v>
+        <v>88.91</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>5.491</v>
+        <v>2.596</v>
       </c>
       <c r="L170" s="2" t="n">
-        <v>3.514</v>
+        <v>0.62</v>
       </c>
       <c r="M170" s="2" t="n">
-        <v>11.5239</v>
+        <v>2.2136</v>
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E171" s="2" t="n">
-        <v>97.72</v>
+        <v>86.37</v>
       </c>
       <c r="F171" s="2" t="n">
-        <v>97.78</v>
+        <v>89.25</v>
       </c>
       <c r="G171" s="2" t="n">
-        <v>99.44</v>
+        <v>98.78</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>97.75</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>87.14</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L171" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M171" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E172" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F172" s="2" t="n">
-        <v>92.33</v>
+        <v>84.5</v>
       </c>
       <c r="G172" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.81</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>91.95</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>91.52</v>
+        <v>76.84</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L172" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M172" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E173" s="2" t="n">
-        <v>80.77</v>
+        <v>90.16</v>
       </c>
       <c r="F173" s="2" t="n">
-        <v>84.27</v>
+        <v>93.97</v>
       </c>
       <c r="G173" s="2" t="n">
-        <v>91.91</v>
+        <v>99.38</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>82.48</v>
+        <v>92.02</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>70.19</v>
+        <v>85.23</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>77.23</v>
+        <v>91.7</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L173" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M173" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>96.13</v>
+      </c>
+      <c r="G174" s="2" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>95.41</v>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>94.77</v>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>91.97</v>
+      </c>
+      <c r="G175" s="2" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>78.73</v>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>84.98</v>
+      </c>
+      <c r="G176" s="2" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="H176" s="2" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>69.11</v>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>76.38</v>
+      </c>
+      <c r="K176" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M176" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="F177" s="2" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="G177" s="2" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="H177" s="2" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>87.27</v>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="K177" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M177" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>R4_0_A0_FULL12_FROZEN</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>82.42</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>83.87</v>
+      </c>
+      <c r="G178" s="2" t="n">
+        <v>92.12</v>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="K178" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M178" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>R4_1_VIT4_OLDHEAD</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G179" s="2" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="H179" s="2" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="K179" s="2" t="n">
+        <v>8.195</v>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M179" s="2" t="n">
+        <v>24.1021</v>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="G180" s="2" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="H180" s="2" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="K180" s="2" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="M180" s="2" t="n">
+        <v>10.7311</v>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>83.81</v>
+      </c>
+      <c r="G181" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H181" s="2" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="K181" s="2" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="M181" s="2" t="n">
+        <v>10.9824</v>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="F182" s="2" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="G182" s="2" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="H182" s="2" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="K182" s="2" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>3.514</v>
+      </c>
+      <c r="M182" s="2" t="n">
+        <v>11.5239</v>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
         <is>
           <t>Run1</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr">
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G183" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H183" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I183" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K183" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L183" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M183" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G184" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H184" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I184" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K184" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L184" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M184" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G185" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H185" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I185" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J185" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K185" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L185" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M185" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
-      <c r="E174" s="2" t="n">
+      <c r="E186" s="2" t="n">
         <v>93.62</v>
       </c>
-      <c r="F174" s="2" t="n">
+      <c r="F186" s="2" t="n">
         <v>96.09</v>
       </c>
-      <c r="G174" s="2" t="n">
+      <c r="G186" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="H174" s="2" t="n">
+      <c r="H186" s="2" t="n">
         <v>94.84</v>
       </c>
-      <c r="I174" s="2" t="n">
+      <c r="I186" s="2" t="n">
         <v>90.18000000000001</v>
       </c>
-      <c r="J174" s="2" t="n">
+      <c r="J186" s="2" t="n">
         <v>94.63</v>
       </c>
-      <c r="K174" s="2" t="n">
+      <c r="K186" s="2" t="n">
         <v>11.754</v>
       </c>
-      <c r="L174" s="2" t="n">
+      <c r="L186" s="2" t="n">
         <v>20.661</v>
       </c>
-      <c r="M174" s="2" t="n">
+      <c r="M186" s="2" t="n">
         <v>26.3246</v>
       </c>
-      <c r="N174" t="inlineStr">
+      <c r="N186" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N174"/>
+  <autoFilter ref="A1:N186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$198</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N186"/>
+  <dimension ref="A1:N198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1866,17 +1866,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1885,52 +1885,50 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>94.08</v>
+        <v>94.97</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>95.26000000000001</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>98.69</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>94.67</v>
+        <v>95.31</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>89.87</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>93.92</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>2.378</v>
+        <v>1.935875</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.04719</v>
+      </c>
+      <c r="M28" s="2" t="n"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1939,52 +1937,50 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>88.55</v>
+        <v>88.97</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>91.3</v>
+        <v>92.09</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>98.98999999999999</v>
+        <v>99.05</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>89.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>81.66</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>89.37</v>
+        <v>90</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2.378</v>
+        <v>1.935875</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.04719</v>
+      </c>
+      <c r="M29" s="2" t="n"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1993,52 +1989,50 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>82.09</v>
+        <v>78.09</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>82.84</v>
+        <v>86.17</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>91.77</v>
+        <v>91.88</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>82.47</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>70.16</v>
+        <v>69.39</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>77.09</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2.378</v>
+        <v>1.935875</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.04719</v>
+      </c>
+      <c r="M30" s="2" t="n"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2047,52 +2041,50 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>92.34</v>
+        <v>92.62</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>96.73</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>99.58</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>93.7</v>
+        <v>94.63</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>88.15000000000001</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>93.44</v>
+        <v>94.42</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2.378</v>
+        <v>1.935875</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.04719</v>
+      </c>
+      <c r="M31" s="2" t="n"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2101,52 +2093,50 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>93.90000000000001</v>
+        <v>95.12</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>95.19</v>
+        <v>95.81</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>98.66</v>
+        <v>98.88</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>94.54000000000001</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>89.64</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>93.78</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>2.416</v>
+        <v>1.962305</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.07362</v>
+      </c>
+      <c r="M32" s="2" t="n"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2155,52 +2145,50 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>88.81999999999999</v>
+        <v>89.97</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>90.93000000000001</v>
+        <v>91.03</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>98.98</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>89.87</v>
+        <v>90.5</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>81.59999999999999</v>
+        <v>82.64</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>89.33</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>2.416</v>
+        <v>1.962305</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M33" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.07362</v>
+      </c>
+      <c r="M33" s="2" t="n"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2209,52 +2197,50 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>79.66</v>
+        <v>76.88</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>85.53</v>
+        <v>88.53</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>92.03</v>
+        <v>92.2</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>82.48999999999999</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>70.2</v>
+        <v>69.91</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>77.34</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>2.416</v>
+        <v>1.962305</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M34" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.07362</v>
+      </c>
+      <c r="M34" s="2" t="n"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2263,52 +2249,50 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>91.81999999999999</v>
+        <v>92.72</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>95.56</v>
+        <v>96.03</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>99.56</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>93.65000000000001</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>88.06999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>93.40000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2.416</v>
+        <v>1.962305</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M35" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.07362</v>
+      </c>
+      <c r="M35" s="2" t="n"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2317,52 +2301,50 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>95.05</v>
+        <v>95.23</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>96.02</v>
+        <v>95.81</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>95.53</v>
+        <v>95.52</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>91.45</v>
+        <v>91.42</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>94.91</v>
+        <v>94.89</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>2.378</v>
+        <v>1.974649</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M36" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.085964</v>
+      </c>
+      <c r="M36" s="2" t="n"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2371,52 +2353,50 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>88.98999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>91.62</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>99.02</v>
+        <v>99.05</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>90.28</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>82.29000000000001</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>89.77</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2.378</v>
+        <v>1.974649</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M37" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.085964</v>
+      </c>
+      <c r="M37" s="2" t="n"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2425,52 +2405,50 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>79.3</v>
+        <v>79.06</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>85.94</v>
+        <v>85.58</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>92.06</v>
+        <v>91.92</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>82.48999999999999</v>
+        <v>82.19</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>70.19</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>77.36</v>
+        <v>76.97</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2.378</v>
+        <v>1.974649</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M38" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.085964</v>
+      </c>
+      <c r="M38" s="2" t="n"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2479,35 +2457,33 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>92.15000000000001</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>94.7</v>
+        <v>96.55</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>99.48</v>
+        <v>99.56</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>93.41</v>
+        <v>94.36</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>87.63</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>93.14</v>
+        <v>94.13</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2.378</v>
+        <v>1.974649</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M39" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.085964</v>
+      </c>
+      <c r="M39" s="2" t="n"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2500,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2533,31 +2509,31 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>95.06</v>
+        <v>94.08</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>96.01000000000001</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>98.69</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>95.54000000000001</v>
+        <v>94.67</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>91.45</v>
+        <v>89.87</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>94.91</v>
+        <v>93.92</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -2578,7 +2554,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2587,31 +2563,31 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>89.47</v>
+        <v>88.55</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>91.28</v>
+        <v>91.3</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>99.03</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>90.37</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>82.43000000000001</v>
+        <v>81.66</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>89.86</v>
+        <v>89.37</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -2632,7 +2608,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2641,31 +2617,31 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>81.39</v>
+        <v>82.09</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>84.72</v>
+        <v>82.84</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>92.15000000000001</v>
+        <v>91.77</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>83.02</v>
+        <v>82.47</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>70.97</v>
+        <v>70.16</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>77.92</v>
+        <v>77.09</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -2686,7 +2662,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2695,31 +2671,31 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>92</v>
+        <v>92.34</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>99.51000000000001</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>93.72</v>
+        <v>93.7</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>88.19</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>93.47</v>
+        <v>93.44</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -2730,275 +2706,331 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_INJ</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>90.38</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>91.91</v>
+        <v>95.19</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>98.66</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>91.14</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>83.72</v>
+        <v>89.64</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>90.66</v>
-      </c>
-      <c r="K44" s="2" t="n"/>
-      <c r="L44" s="2" t="n"/>
-      <c r="M44" s="2" t="n"/>
+        <v>93.78</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_INJ</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>81.18000000000001</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>82.19</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>91.41</v>
+        <v>98.98</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>81.68000000000001</v>
+        <v>89.87</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>69.04000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>76.08</v>
-      </c>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="n"/>
-      <c r="M45" s="2" t="n"/>
+        <v>89.33</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_SUP</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>90.63</v>
+        <v>79.66</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>91.56</v>
+        <v>85.53</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>92.03</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>91.09</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>83.64</v>
+        <v>70.2</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>90.62</v>
+        <v>77.34</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>31.978582</v>
-      </c>
-      <c r="L46" s="2" t="n"/>
-      <c r="M46" s="2" t="n"/>
+        <v>2.416</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_SUP</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>81.28</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>82.75</v>
+        <v>95.56</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>91.59</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>82.01000000000001</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>69.5</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>76.52</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>31.978582</v>
-      </c>
-      <c r="L47" s="2" t="n"/>
-      <c r="M47" s="2" t="n"/>
+        <v>2.416</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_V2</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>90.52</v>
+        <v>95.05</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>91.84999999999999</v>
+        <v>96.02</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>99.11</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>95.53</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>83.79000000000001</v>
+        <v>91.45</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>90.70999999999999</v>
-      </c>
-      <c r="K48" s="2" t="n"/>
-      <c r="L48" s="2" t="n"/>
-      <c r="M48" s="2" t="n"/>
+        <v>94.91</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>1.2051</v>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_V2</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>79.34</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>84.23999999999999</v>
+        <v>91.62</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>91.63</v>
+        <v>99.02</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>81.72</v>
+        <v>90.28</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>69.09</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="K49" s="2" t="n"/>
-      <c r="L49" s="2" t="n"/>
-      <c r="M49" s="2" t="n"/>
+        <v>89.77</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>1.2051</v>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3008,51 +3040,51 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>96.58</v>
+        <v>79.3</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>96.94</v>
+        <v>85.94</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>99.2</v>
+        <v>92.06</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>96.76000000000001</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>93.73</v>
+        <v>70.19</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>96.31</v>
+        <v>77.36</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>4.88</v>
+        <v>2.378</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>4.88</v>
+        <v>2.378</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2051</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3062,51 +3094,51 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>89.52</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>92.69</v>
+        <v>94.7</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>99.11</v>
+        <v>99.48</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>91.08</v>
+        <v>93.41</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>83.62</v>
+        <v>87.63</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>90.61</v>
+        <v>93.14</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>4.88</v>
+        <v>2.378</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>4.88</v>
+        <v>2.378</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2051</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3116,51 +3148,51 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>95.06</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>85.01000000000001</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>91.94</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>82.39</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>70.06</v>
+        <v>91.45</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>77.18000000000001</v>
+        <v>94.91</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2365</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3170,51 +3202,51 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>92.69</v>
+        <v>89.47</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>96.95999999999999</v>
+        <v>91.28</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>99.59</v>
+        <v>99.03</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>94.78</v>
+        <v>90.37</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>90.08</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>94.56999999999999</v>
+        <v>89.86</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2365</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3224,51 +3256,51 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>96.62</v>
+        <v>81.39</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>96.88</v>
+        <v>84.72</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>99.2</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>96.75</v>
+        <v>83.02</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>93.7</v>
+        <v>70.97</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>96.29000000000001</v>
+        <v>77.92</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2365</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3278,44 +3310,44 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>89.95</v>
+        <v>92</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>92.13</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>91.03</v>
+        <v>93.72</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>83.53</v>
+        <v>88.19</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>90.55</v>
+        <v>93.47</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2365</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
@@ -3325,51 +3357,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>Exploration/Exp1/STG_INJ</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>80.14</v>
+        <v>90.38</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>84.18000000000001</v>
+        <v>91.91</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>91.76000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>82.11</v>
+        <v>91.14</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>69.65000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>76.76000000000001</v>
-      </c>
-      <c r="K56" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M56" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>90.66</v>
+      </c>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
+      <c r="M56" s="2" t="n"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -3379,51 +3401,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>Exploration/Exp1/STG_INJ</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>92.45</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>97.37</v>
+        <v>82.19</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>91.41</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>94.84</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>90.19</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>94.64</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M57" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>76.08</v>
+      </c>
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" s="2" t="n"/>
+      <c r="M57" s="2" t="n"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -3433,51 +3445,43 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>Exploration/Exp1/STG_SUP</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>97.02</v>
+        <v>90.63</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>97.20999999999999</v>
+        <v>91.56</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>99.29000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>97.11</v>
+        <v>91.09</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>94.39</v>
+        <v>83.64</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>96.70999999999999</v>
+        <v>90.62</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M58" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>31.978582</v>
+      </c>
+      <c r="L58" s="2" t="n"/>
+      <c r="M58" s="2" t="n"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -3487,51 +3491,43 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>Exploration/Exp1/STG_SUP</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>89.59</v>
+        <v>81.28</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>92.84</v>
+        <v>82.75</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>99.12</v>
+        <v>91.59</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>91.19</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>83.81</v>
+        <v>69.5</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>90.73</v>
+        <v>76.52</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M59" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>31.978582</v>
+      </c>
+      <c r="L59" s="2" t="n"/>
+      <c r="M59" s="2" t="n"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -3541,51 +3537,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>Exploration/Exp1/STG_V2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>81.23999999999999</v>
+        <v>90.52</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>85.29000000000001</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>92.27</v>
+        <v>99.11</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>83.20999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>71.25</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="K60" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M60" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>90.70999999999999</v>
+      </c>
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="2" t="n"/>
+      <c r="M60" s="2" t="n"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -3595,51 +3581,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>Exploration/Exp1/STG_V2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>93.09999999999999</v>
+        <v>79.34</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>96.01000000000001</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>99.56999999999999</v>
+        <v>91.63</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>94.53</v>
+        <v>81.72</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>89.63</v>
+        <v>69.09</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>94.31</v>
-      </c>
-      <c r="K61" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M61" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>76.3</v>
+      </c>
+      <c r="K61" s="2" t="n"/>
+      <c r="L61" s="2" t="n"/>
+      <c r="M61" s="2" t="n"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3632,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3665,22 +3641,22 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>97.03</v>
+        <v>96.58</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>97.33</v>
+        <v>96.94</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>97.18000000000001</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>94.51000000000001</v>
+        <v>93.73</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>96.78</v>
+        <v>96.31</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>4.88</v>
@@ -3710,7 +3686,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3719,22 +3695,22 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>90.33</v>
+        <v>89.52</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>91.81999999999999</v>
+        <v>92.69</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.11</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>91.06999999999999</v>
+        <v>91.08</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>83.62</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>90.59</v>
+        <v>90.61</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>4.88</v>
@@ -3764,7 +3740,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3773,22 +3749,22 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>84.41</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>82.55</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>92.12</v>
+        <v>91.94</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>83.47</v>
+        <v>82.39</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>71.63</v>
+        <v>70.06</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>78.29000000000001</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>4.88</v>
@@ -3818,7 +3794,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3827,22 +3803,22 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>93.56</v>
+        <v>92.69</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>96.62</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>99.61</v>
+        <v>99.59</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>94.78</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>90.08</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>94.87</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>4.88</v>
@@ -3867,12 +3843,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3881,22 +3857,22 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>97.02</v>
+        <v>96.62</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>97.27</v>
+        <v>96.88</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>97.14</v>
+        <v>96.75</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>94.45</v>
+        <v>93.7</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>96.73999999999999</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>4.88</v>
@@ -3921,12 +3897,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3935,22 +3911,22 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>90.64</v>
+        <v>89.95</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>91.64</v>
+        <v>92.13</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>99.09999999999999</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>91.14</v>
+        <v>91.03</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>83.72</v>
+        <v>83.53</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>90.66</v>
+        <v>90.55</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>4.88</v>
@@ -3975,12 +3951,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3989,22 +3965,22 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>80.94</v>
+        <v>80.14</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>85.43000000000001</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>92.25</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>83.13</v>
+        <v>82.11</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>71.12</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>4.88</v>
@@ -4029,12 +4005,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4043,22 +4019,22 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>93.73999999999999</v>
+        <v>92.45</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>96.67</v>
+        <v>97.37</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>99.62</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>95.18000000000001</v>
+        <v>94.84</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>90.81</v>
+        <v>90.19</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>94.98999999999999</v>
+        <v>94.64</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>4.88</v>
@@ -4083,12 +4059,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4100,28 +4076,28 @@
         <v>97.02</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>97.33</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>99.3</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>97.17</v>
+        <v>97.11</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>94.5</v>
+        <v>94.39</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>96.78</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
@@ -4137,12 +4113,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4151,31 +4127,31 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>90.22</v>
+        <v>89.59</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>92.22</v>
+        <v>92.84</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>99.11</v>
+        <v>99.12</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>91.19</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>83.83</v>
+        <v>83.81</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>90.73999999999999</v>
+        <v>90.73</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -4191,12 +4167,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4205,31 +4181,31 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>80.09999999999999</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>86.05</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>92.23999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>82.97</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>70.89</v>
+        <v>71.25</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>77.95999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -4245,12 +4221,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4259,31 +4235,31 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>93.45999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>96</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>99.59</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>94.70999999999999</v>
+        <v>94.53</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>89.95</v>
+        <v>89.63</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>94.48999999999999</v>
+        <v>94.31</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
@@ -4299,12 +4275,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4313,10 +4289,10 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>97.02</v>
+        <v>97.03</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>97.34</v>
+        <v>97.33</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>99.3</v>
@@ -4331,13 +4307,13 @@
         <v>96.78</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
@@ -4353,12 +4329,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4367,31 +4343,31 @@
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>90.20999999999999</v>
+        <v>90.33</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>92.41</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>99.12</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>91.29000000000001</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>83.98</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>90.83</v>
+        <v>90.59</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
@@ -4407,12 +4383,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4421,31 +4397,31 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>80.69</v>
+        <v>84.41</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>85.12</v>
+        <v>82.55</v>
       </c>
       <c r="G76" s="2" t="n">
         <v>92.12</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>82.84999999999999</v>
+        <v>83.47</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>70.72</v>
+        <v>71.63</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>77.73999999999999</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -4461,12 +4437,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4475,31 +4451,31 @@
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>93.8</v>
+        <v>93.56</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>96.18000000000001</v>
+        <v>96.62</v>
       </c>
       <c r="G77" s="2" t="n">
         <v>99.61</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>94.98</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>90.44</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>94.77</v>
+        <v>94.87</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
@@ -4515,12 +4491,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4532,19 +4508,19 @@
         <v>97.02</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>97.25</v>
+        <v>97.27</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>99.29000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>97.13</v>
+        <v>97.14</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>94.42</v>
+        <v>94.45</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>96.73</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>4.88</v>
@@ -4569,12 +4545,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4583,22 +4559,22 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>90.05</v>
+        <v>90.64</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>92.12</v>
+        <v>91.64</v>
       </c>
       <c r="G79" s="2" t="n">
         <v>99.09999999999999</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>91.06999999999999</v>
+        <v>91.14</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>83.72</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>90.66</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>4.88</v>
@@ -4623,12 +4599,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4637,19 +4613,19 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>81.44</v>
+        <v>80.94</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>84.94</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>92.22</v>
+        <v>92.25</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>83.16</v>
+        <v>83.13</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>71.17</v>
+        <v>71.12</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>78.09999999999999</v>
@@ -4677,12 +4653,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4691,22 +4667,22 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>93.42</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>96.66</v>
+        <v>96.67</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>99.61</v>
+        <v>99.62</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>95.02</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>90.5</v>
+        <v>90.81</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>94.81</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>4.88</v>
@@ -4731,12 +4707,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4745,31 +4721,31 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>97.03</v>
+        <v>97.02</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>97.23999999999999</v>
+        <v>97.33</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>99.29000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>97.13</v>
+        <v>97.17</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>94.43000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>96.73</v>
+        <v>96.78</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6947</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
@@ -4785,12 +4761,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4799,31 +4775,31 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>90.25</v>
+        <v>90.22</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>92.12</v>
+        <v>92.22</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>99.11</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>83.78</v>
+        <v>83.83</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>90.70999999999999</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6947</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -4839,12 +4815,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4853,31 +4829,31 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>81.26000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>85.31</v>
+        <v>86.05</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>92.28</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>83.23999999999999</v>
+        <v>82.97</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>71.29000000000001</v>
+        <v>70.89</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>78.23</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6947</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -4893,12 +4869,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4907,31 +4883,31 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>93.11</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>96.78</v>
+        <v>96</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.59</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>94.91</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>90.31</v>
+        <v>89.95</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>94.7</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6947</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -4947,12 +4923,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4961,31 +4937,31 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>96.97</v>
+        <v>97.02</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>97.08</v>
+        <v>97.34</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>99.27</v>
+        <v>99.3</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>97.02</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>94.22</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>96.59999999999999</v>
+        <v>96.78</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2.717</v>
+        <v>2.6947</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -5001,12 +4977,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5015,31 +4991,31 @@
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>90.15000000000001</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>92.33</v>
+        <v>92.41</v>
       </c>
       <c r="G87" s="2" t="n">
         <v>99.12</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>91.23</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>83.87</v>
+        <v>83.98</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>90.76000000000001</v>
+        <v>90.83</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2.717</v>
+        <v>2.6947</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -5055,12 +5031,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5069,31 +5045,31 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>81.90000000000001</v>
+        <v>80.69</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>84.53</v>
+        <v>85.12</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>92.2</v>
+        <v>92.12</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>83.19</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>71.22</v>
+        <v>70.72</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>78.11</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2.717</v>
+        <v>2.6947</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -5109,12 +5085,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5123,31 +5099,31 @@
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>94.02</v>
+        <v>93.8</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>96.37</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>99.62</v>
+        <v>99.61</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>95.18000000000001</v>
+        <v>94.98</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>90.8</v>
+        <v>90.44</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>94.98</v>
+        <v>94.77</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2.717</v>
+        <v>2.6947</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -5163,12 +5139,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5177,22 +5153,22 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>96.94</v>
+        <v>97.02</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>97.17</v>
+        <v>97.25</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>99.27</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>97.05</v>
+        <v>97.13</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>94.27</v>
+        <v>94.42</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>96.64</v>
+        <v>96.73</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>4.88</v>
@@ -5217,12 +5193,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5231,22 +5207,22 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>90.09</v>
+        <v>90.05</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>92.62</v>
+        <v>92.12</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>99.13</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>91.34</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>84.06</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>90.88</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>4.88</v>
@@ -5271,12 +5247,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5285,22 +5261,22 @@
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>81.09999999999999</v>
+        <v>81.44</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>85.65000000000001</v>
+        <v>84.94</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>92.34</v>
+        <v>92.22</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>83.31</v>
+        <v>83.16</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>71.17</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>78.34999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>4.88</v>
@@ -5325,12 +5301,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5339,22 +5315,22 @@
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>93.8</v>
+        <v>93.42</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>96.38</v>
+        <v>96.66</v>
       </c>
       <c r="G93" s="2" t="n">
         <v>99.61</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>95.02</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>90.61</v>
+        <v>90.5</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>94.87</v>
+        <v>94.81</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>4.88</v>
@@ -5379,12 +5355,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5393,31 +5369,31 @@
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>97</v>
+        <v>97.03</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>97.33</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>99.3</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>97.17</v>
+        <v>97.13</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>94.48999999999999</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>96.77</v>
+        <v>96.73</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.9767</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
@@ -5433,12 +5409,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5447,31 +5423,31 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>89.63</v>
+        <v>90.25</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>92.70999999999999</v>
+        <v>92.12</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>99.11</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>91.15000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>83.73</v>
+        <v>83.78</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>90.68000000000001</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.9767</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -5487,12 +5463,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5501,31 +5477,31 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>80.41</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>85.06999999999999</v>
+        <v>85.31</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>92.05</v>
+        <v>92.28</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>82.68000000000001</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>70.47</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>77.53</v>
+        <v>78.23</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.9767</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -5541,12 +5517,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5555,31 +5531,31 @@
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>93.44</v>
+        <v>93.11</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>96.28</v>
+        <v>96.78</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>94.84</v>
+        <v>94.91</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>90.19</v>
+        <v>90.31</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>94.63</v>
+        <v>94.7</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.9767</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -5595,49 +5571,49 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Run8</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CTRL_R8</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>90.43000000000001</v>
+        <v>96.97</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>92.01000000000001</v>
+        <v>97.08</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>99.11</v>
+        <v>99.27</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>97.02</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>83.84</v>
+        <v>94.22</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>90.73999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>31.026</v>
+        <v>4.89</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>31.026</v>
+        <v>4.89</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>13.6715</v>
+        <v>2.717</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>casa_vmamba_str</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -5649,49 +5625,49 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Run8</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CTRL_R8</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>79.66</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>84.22</v>
+        <v>92.33</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>91.69</v>
+        <v>99.12</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>81.88</v>
+        <v>91.23</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>69.31999999999999</v>
+        <v>83.87</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>76.48999999999999</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>31.026</v>
+        <v>4.89</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>31.026</v>
+        <v>4.89</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>13.6715</v>
+        <v>2.717</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>casa_vmamba_str</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -5703,49 +5679,49 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Run9</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>S0_CTRL</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>97.77</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>97.77</v>
+        <v>84.53</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>99.45</v>
+        <v>92.2</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>97.77</v>
+        <v>83.19</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>95.65000000000001</v>
+        <v>71.22</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>97.45999999999999</v>
+        <v>78.11</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>31.977</v>
+        <v>4.89</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>31.977</v>
+        <v>4.89</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>14.6841</v>
+        <v>2.717</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -5757,49 +5733,49 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Run9</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>S0_CTRL</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>89.79000000000001</v>
+        <v>94.02</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>92.53</v>
+        <v>96.37</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>99.11</v>
+        <v>99.62</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>91.14</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>83.72</v>
+        <v>90.8</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>90.67</v>
+        <v>94.98</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>31.977</v>
+        <v>4.89</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>31.977</v>
+        <v>4.89</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>14.6841</v>
+        <v>2.717</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -5811,12 +5787,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Run9</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>S1_HSAM</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5825,260 +5801,268 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>97.66</v>
+        <v>96.94</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>97.65000000000001</v>
+        <v>97.17</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>99.42</v>
+        <v>99.27</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>97.65000000000001</v>
+        <v>97.05</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>95.42</v>
+        <v>94.27</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>97.31999999999999</v>
+        <v>96.64</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>31.977</v>
+        <v>4.88</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>31.977</v>
+        <v>4.88</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>14.769</v>
+        <v>2.6747</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>80.27</v>
+        <v>90.09</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>85.19</v>
+        <v>92.62</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>92.06</v>
+        <v>99.13</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>82.65000000000001</v>
+        <v>91.34</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>70.44</v>
+        <v>84.06</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>90.88</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>3.016737</v>
+        <v>4.88</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M103" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_none</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>91.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>91.72</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>99.13</v>
+        <v>92.34</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>91.45999999999999</v>
+        <v>83.31</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>84.26000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>91</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>3.016737</v>
+        <v>4.88</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M104" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_none</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>80.39</v>
+        <v>93.8</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>82.89</v>
+        <v>96.38</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>91.45999999999999</v>
+        <v>99.61</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>81.62</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>68.95</v>
+        <v>90.61</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>76.06999999999999</v>
+        <v>94.87</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>3.016737</v>
+        <v>4.88</v>
       </c>
       <c r="L105" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M105" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_none</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>92.61</v>
+        <v>97</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>95.26000000000001</v>
+        <v>97.33</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>99.52</v>
+        <v>99.3</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>93.92</v>
+        <v>97.17</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>88.53</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>93.67</v>
+        <v>96.77</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>3.016737</v>
+        <v>4.88</v>
       </c>
       <c r="L106" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M106" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_none</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6087,50 +6071,52 @@
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>90.55</v>
+        <v>89.63</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>92.03</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>99.12</v>
+        <v>99.11</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>91.28</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>83.95999999999999</v>
+        <v>83.73</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>90.81999999999999</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>3.049509</v>
+        <v>4.88</v>
       </c>
       <c r="L107" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M107" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_hyperbolic</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6139,50 +6125,52 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>78.67</v>
+        <v>80.41</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>85.08</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>91.72</v>
+        <v>92.05</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>81.75</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>69.13</v>
+        <v>70.47</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>76.40000000000001</v>
+        <v>77.53</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>3.049509</v>
+        <v>4.88</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M108" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_hyperbolic</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6191,50 +6179,52 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>92.84999999999999</v>
+        <v>93.44</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>95.31999999999999</v>
+        <v>96.28</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>99.54000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>94.06999999999999</v>
+        <v>94.84</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>88.8</v>
+        <v>90.19</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>93.83</v>
+        <v>94.63</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>3.049509</v>
+        <v>4.88</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M109" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_hyperbolic</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run8</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>CTRL_R8</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6243,50 +6233,52 @@
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>89.72</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>93.12</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>99.14</v>
+        <v>99.11</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>91.39</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>84.14</v>
+        <v>83.84</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>90.93000000000001</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>3.049509</v>
+        <v>31.026</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M110" s="2" t="n"/>
+        <v>31.026</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>13.6715</v>
+      </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>casa_vmamba_str</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run8</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>CTRL_R8</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6295,102 +6287,106 @@
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>82.83</v>
+        <v>79.66</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>82.86</v>
+        <v>84.22</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>91.91</v>
+        <v>91.69</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>82.84999999999999</v>
+        <v>81.88</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>70.72</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>77.56</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>3.049509</v>
+        <v>31.026</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M111" s="2" t="n"/>
+        <v>31.026</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>13.6715</v>
+      </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>casa_vmamba_str</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run9</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>S0_CTRL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>93.04000000000001</v>
+        <v>97.77</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>96.08</v>
+        <v>97.77</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>99.56999999999999</v>
+        <v>99.45</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>94.53</v>
+        <v>97.77</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>89.63</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>94.31</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>3.049509</v>
+        <v>31.977</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M112" s="2" t="n"/>
+        <v>31.977</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>14.6841</v>
+      </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run9</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>S0_CTRL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6399,96 +6395,96 @@
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>91.09</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>92.8</v>
+        <v>92.53</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>99.19</v>
+        <v>99.11</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>91.94</v>
+        <v>91.14</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>85.08</v>
+        <v>83.72</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>90.67</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>11.754</v>
+        <v>31.977</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>20.661</v>
+        <v>31.977</v>
       </c>
       <c r="M113" s="2" t="n">
-        <v>26.3183</v>
+        <v>14.6841</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run9</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>S1_HSAM</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>80.3</v>
+        <v>97.66</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>84.81</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>99.42</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>82.5</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>95.42</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>11.754</v>
+        <v>31.977</v>
       </c>
       <c r="L114" s="2" t="n">
-        <v>20.661</v>
+        <v>31.977</v>
       </c>
       <c r="M114" s="2" t="n">
-        <v>26.3183</v>
+        <v>14.769</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6498,105 +6494,101 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>80.27</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>92.75</v>
+        <v>85.19</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>92.06</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>91.86</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>84.94</v>
+        <v>70.44</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>11.754</v>
+        <v>3.016737</v>
       </c>
       <c r="L115" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>26.2593</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M115" s="2" t="n"/>
       <c r="N115" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>80.55</v>
+        <v>91.2</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>84.23</v>
+        <v>91.72</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>91.86</v>
+        <v>99.13</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>82.34999999999999</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>70</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>77.06</v>
+        <v>91</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>11.754</v>
+        <v>3.016737</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>26.2593</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M116" s="2" t="n"/>
       <c r="N116" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6606,51 +6598,49 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>91.38</v>
+        <v>80.39</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>92.3</v>
+        <v>82.89</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>99.17</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>91.84</v>
+        <v>81.62</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>84.91</v>
+        <v>68.95</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>11.754</v>
+        <v>3.016737</v>
       </c>
       <c r="L117" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M117" s="2" t="n">
-        <v>26.1484</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M117" s="2" t="n"/>
       <c r="N117" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6660,51 +6650,49 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>92.61</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>86.03</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>99.52</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>93.92</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>69.55</v>
+        <v>88.53</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>76.83</v>
+        <v>93.67</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>11.754</v>
+        <v>3.016737</v>
       </c>
       <c r="L118" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M118" s="2" t="n">
-        <v>26.1484</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M118" s="2" t="n"/>
       <c r="N118" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6714,7 +6702,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6723,42 +6711,40 @@
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>91.13</v>
+        <v>90.55</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>92.03</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.12</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>91.88</v>
+        <v>91.28</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>84.98</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>91.45</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L119" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M119" s="2" t="n">
-        <v>26.0894</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M119" s="2" t="n"/>
       <c r="N119" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6768,7 +6754,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6777,366 +6763,366 @@
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>78.67</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>85.05</v>
+        <v>85.08</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>92.36</v>
+        <v>91.72</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>83.52</v>
+        <v>81.75</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>71.7</v>
+        <v>69.13</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>78.55</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L120" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M120" s="2" t="n">
-        <v>26.0894</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M120" s="2" t="n"/>
       <c r="N120" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>84.28</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>91.7</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>81.92</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>69.37</v>
+        <v>88.8</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>93.83</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L121" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M121" s="2" t="n">
-        <v>26.0894</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M121" s="2" t="n"/>
       <c r="N121" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>89.72</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>97.47</v>
+        <v>93.12</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>99.37</v>
+        <v>99.14</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>97.45</v>
+        <v>91.39</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>95.02</v>
+        <v>84.14</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>97.09</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>3.016737</v>
+        <v>3.049509</v>
       </c>
       <c r="L122" s="2" t="n">
-        <v>3.100404</v>
+        <v>3.133176</v>
       </c>
       <c r="M122" s="2" t="n"/>
       <c r="N122" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>90.41</v>
+        <v>82.83</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>91.83</v>
+        <v>82.86</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>91.11</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>83.67</v>
+        <v>70.72</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>90.64</v>
+        <v>77.56</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>3.016737</v>
+        <v>3.049509</v>
       </c>
       <c r="L123" s="2" t="n">
-        <v>3.100404</v>
+        <v>3.133176</v>
       </c>
       <c r="M123" s="2" t="n"/>
       <c r="N123" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>79.81</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>83.84999999999999</v>
+        <v>96.08</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>91.61</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>81.78</v>
+        <v>94.53</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>69.18000000000001</v>
+        <v>89.63</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>76.34</v>
+        <v>94.31</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>3.016737</v>
+        <v>3.049509</v>
       </c>
       <c r="L124" s="2" t="n">
-        <v>3.100404</v>
+        <v>3.133176</v>
       </c>
       <c r="M124" s="2" t="n"/>
       <c r="N124" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>93.2</v>
+        <v>91.09</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>94.70999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>99.52</v>
+        <v>99.19</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>93.95</v>
+        <v>91.94</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>88.59</v>
+        <v>85.08</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>93.7</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>3.016737</v>
+        <v>11.754</v>
       </c>
       <c r="L125" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M125" s="2" t="n"/>
+        <v>20.661</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>26.3183</v>
+      </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>97.48</v>
+        <v>80.3</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>97.45</v>
+        <v>84.81</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>99.37</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>97.47</v>
+        <v>82.5</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>95.06</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>97.11</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>3.050665</v>
+        <v>11.754</v>
       </c>
       <c r="L126" s="2" t="n">
-        <v>3.134332</v>
-      </c>
-      <c r="M126" s="2" t="n"/>
+        <v>20.661</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>26.3183</v>
+      </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -7145,50 +7131,52 @@
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>90.61</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>92.37</v>
+        <v>92.75</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>99.14</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>91.48</v>
+        <v>91.86</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>84.3</v>
+        <v>84.94</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>91.03</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>3.050665</v>
+        <v>11.754</v>
       </c>
       <c r="L127" s="2" t="n">
-        <v>3.134332</v>
-      </c>
-      <c r="M127" s="2" t="n"/>
+        <v>20.661</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>26.2593</v>
+      </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7197,154 +7185,160 @@
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>77.55</v>
+        <v>80.55</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>85.81</v>
+        <v>84.23</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>91.68000000000001</v>
+        <v>91.86</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>81.47</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>68.73</v>
+        <v>70</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>76.12</v>
+        <v>77.06</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>3.050665</v>
+        <v>11.754</v>
       </c>
       <c r="L128" s="2" t="n">
-        <v>3.134332</v>
-      </c>
-      <c r="M128" s="2" t="n"/>
+        <v>20.661</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>26.2593</v>
+      </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>92.5</v>
+        <v>91.38</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>96.20999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>99.56</v>
+        <v>99.17</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>94.31999999999999</v>
+        <v>91.84</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>89.25</v>
+        <v>84.91</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>94.09</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>3.050665</v>
+        <v>11.754</v>
       </c>
       <c r="L129" s="2" t="n">
-        <v>3.134332</v>
-      </c>
-      <c r="M129" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>26.1484</v>
+      </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>97.51000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>97.45</v>
+        <v>86.03</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>99.38</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>97.48</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>95.09</v>
+        <v>69.55</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>97.13</v>
+        <v>76.83</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>3.059369</v>
+        <v>11.754</v>
       </c>
       <c r="L130" s="2" t="n">
-        <v>3.143036</v>
-      </c>
-      <c r="M130" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>26.1484</v>
+      </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7353,50 +7347,52 @@
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>90.58</v>
+        <v>91.13</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>91.77</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>99.11</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>91.17</v>
+        <v>91.88</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>83.77</v>
+        <v>84.98</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>90.7</v>
+        <v>91.45</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>3.059369</v>
+        <v>11.754</v>
       </c>
       <c r="L131" s="2" t="n">
-        <v>3.143036</v>
-      </c>
-      <c r="M131" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>26.0894</v>
+      </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7405,40 +7401,42 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>76.7</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>85.81999999999999</v>
+        <v>85.05</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>91.52</v>
+        <v>92.36</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>81.01000000000001</v>
+        <v>83.52</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>68.06999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>75.56999999999999</v>
+        <v>78.55</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>3.059369</v>
+        <v>11.754</v>
       </c>
       <c r="L132" s="2" t="n">
-        <v>3.143036</v>
-      </c>
-      <c r="M132" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>26.0894</v>
+      </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7448,42 +7446,44 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>A4_DETAIL_FROZEN</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>92.61</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>95.31</v>
+        <v>84.28</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>99.53</v>
+        <v>91.7</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>93.94</v>
+        <v>81.92</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>88.58</v>
+        <v>69.37</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>93.69</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>3.059369</v>
+        <v>11.754</v>
       </c>
       <c r="L133" s="2" t="n">
-        <v>3.143036</v>
-      </c>
-      <c r="M133" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>26.0894</v>
+      </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7509,22 +7509,22 @@
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>97.41</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>97.47</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>99.36</v>
+        <v>99.37</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>97.42</v>
+        <v>97.45</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>94.98</v>
+        <v>95.02</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>97.06</v>
+        <v>97.09</v>
       </c>
       <c r="K134" s="2" t="n">
         <v>3.016737</v>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7561,22 +7561,22 @@
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>90.29000000000001</v>
+        <v>90.41</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>92.58</v>
+        <v>91.83</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>99.14</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>91.42</v>
+        <v>91.11</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>84.19</v>
+        <v>83.67</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>90.95999999999999</v>
+        <v>90.64</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>3.016737</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7613,22 +7613,22 @@
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>80.38</v>
+        <v>79.81</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>85.22</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>92.09</v>
+        <v>91.61</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>82.73</v>
+        <v>81.78</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>70.55</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>77.59999999999999</v>
+        <v>76.34</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>3.016737</v>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7665,22 +7665,22 @@
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>92.87</v>
+        <v>93.2</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>96.04000000000001</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>99.56999999999999</v>
+        <v>99.52</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>94.43000000000001</v>
+        <v>93.95</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>89.44</v>
+        <v>88.59</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>94.2</v>
+        <v>93.7</v>
       </c>
       <c r="K137" s="2" t="n">
         <v>3.016737</v>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7717,28 +7717,28 @@
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>97.52</v>
+        <v>97.48</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>97.42</v>
+        <v>97.45</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>99.38</v>
+        <v>99.37</v>
       </c>
       <c r="H138" s="2" t="n">
         <v>97.47</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>95.06</v>
       </c>
       <c r="J138" s="2" t="n">
         <v>97.11</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>3.060525</v>
+        <v>3.050665</v>
       </c>
       <c r="L138" s="2" t="n">
-        <v>3.144192</v>
+        <v>3.134332</v>
       </c>
       <c r="M138" s="2" t="n"/>
       <c r="N138" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7769,28 +7769,28 @@
         </is>
       </c>
       <c r="E139" s="2" t="n">
-        <v>90.48</v>
+        <v>90.61</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>92.91</v>
+        <v>92.37</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>99.16</v>
+        <v>99.14</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>91.68000000000001</v>
+        <v>91.48</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>84.64</v>
+        <v>84.3</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>91.23999999999999</v>
+        <v>91.03</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>3.060525</v>
+        <v>3.050665</v>
       </c>
       <c r="L139" s="2" t="n">
-        <v>3.144192</v>
+        <v>3.134332</v>
       </c>
       <c r="M139" s="2" t="n"/>
       <c r="N139" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7821,28 +7821,28 @@
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>83.2</v>
+        <v>77.55</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>80.95</v>
+        <v>85.81</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>91.42</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>82.06</v>
+        <v>81.47</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>69.58</v>
+        <v>68.73</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>76.42</v>
+        <v>76.12</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>3.060525</v>
+        <v>3.050665</v>
       </c>
       <c r="L140" s="2" t="n">
-        <v>3.144192</v>
+        <v>3.134332</v>
       </c>
       <c r="M140" s="2" t="n"/>
       <c r="N140" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7873,28 +7873,28 @@
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>92.36</v>
+        <v>92.5</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>95.44</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>99.52</v>
+        <v>99.56</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>93.88</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>88.45999999999999</v>
+        <v>89.25</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>93.63</v>
+        <v>94.09</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>3.060525</v>
+        <v>3.050665</v>
       </c>
       <c r="L141" s="2" t="n">
-        <v>3.144192</v>
+        <v>3.134332</v>
       </c>
       <c r="M141" s="2" t="n"/>
       <c r="N141" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7925,28 +7925,28 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>97.51000000000001</v>
+        <v>97.45</v>
       </c>
       <c r="G142" s="2" t="n">
         <v>99.38</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>97.47</v>
+        <v>97.48</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>95.06</v>
+        <v>95.09</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>97.11</v>
+        <v>97.13</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>3.077293</v>
+        <v>3.059369</v>
       </c>
       <c r="L142" s="2" t="n">
-        <v>3.16096</v>
+        <v>3.143036</v>
       </c>
       <c r="M142" s="2" t="n"/>
       <c r="N142" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -7977,28 +7977,28 @@
         </is>
       </c>
       <c r="E143" s="2" t="n">
-        <v>90.45</v>
+        <v>90.58</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>92.68000000000001</v>
+        <v>91.77</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>99.15000000000001</v>
+        <v>99.11</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>91.55</v>
+        <v>91.17</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>84.42</v>
+        <v>83.77</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>91.11</v>
+        <v>90.7</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>3.077293</v>
+        <v>3.059369</v>
       </c>
       <c r="L143" s="2" t="n">
-        <v>3.16096</v>
+        <v>3.143036</v>
       </c>
       <c r="M143" s="2" t="n"/>
       <c r="N143" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8029,28 +8029,28 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>78.5</v>
+        <v>76.7</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>86.2</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>91.97</v>
+        <v>91.52</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>82.17</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>69.73999999999999</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>77</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>3.077293</v>
+        <v>3.059369</v>
       </c>
       <c r="L144" s="2" t="n">
-        <v>3.16096</v>
+        <v>3.143036</v>
       </c>
       <c r="M144" s="2" t="n"/>
       <c r="N144" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8081,28 +8081,28 @@
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>91.88</v>
+        <v>92.61</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>94.98999999999999</v>
+        <v>95.31</v>
       </c>
       <c r="G145" s="2" t="n">
-        <v>99.48999999999999</v>
+        <v>99.53</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>93.41</v>
+        <v>93.94</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>87.63</v>
+        <v>88.58</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>93.14</v>
+        <v>93.69</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>3.077293</v>
+        <v>3.059369</v>
       </c>
       <c r="L145" s="2" t="n">
-        <v>3.16096</v>
+        <v>3.143036</v>
       </c>
       <c r="M145" s="2" t="n"/>
       <c r="N145" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8133,22 +8133,22 @@
         </is>
       </c>
       <c r="E146" s="2" t="n">
-        <v>97.5</v>
+        <v>97.41</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>97.34999999999999</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="G146" s="2" t="n">
         <v>99.36</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>97.42</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>94.98999999999999</v>
+        <v>94.98</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>97.06999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="K146" s="2" t="n">
         <v>3.016737</v>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8185,22 +8185,22 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>90.69</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>92.43000000000001</v>
+        <v>92.58</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>99.15000000000001</v>
+        <v>99.14</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>91.55</v>
+        <v>91.42</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>84.42</v>
+        <v>84.19</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="K147" s="2" t="n">
         <v>3.016737</v>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8237,22 +8237,22 @@
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>82.58</v>
+        <v>80.38</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>82.25</v>
+        <v>85.22</v>
       </c>
       <c r="G148" s="2" t="n">
-        <v>91.69</v>
+        <v>92.09</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>82.42</v>
+        <v>82.73</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>70.09</v>
+        <v>70.55</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>76.98</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K148" s="2" t="n">
         <v>3.016737</v>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8289,22 +8289,22 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>92.31</v>
+        <v>92.87</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>94.59999999999999</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="G149" s="2" t="n">
-        <v>99.48999999999999</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>93.44</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>87.69</v>
+        <v>89.44</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>93.17</v>
+        <v>94.2</v>
       </c>
       <c r="K149" s="2" t="n">
         <v>3.016737</v>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8341,28 +8341,28 @@
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>97.53</v>
+        <v>97.52</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>97.38</v>
+        <v>97.42</v>
       </c>
       <c r="G150" s="2" t="n">
-        <v>99.37</v>
+        <v>99.38</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>97.45</v>
+        <v>97.47</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>95.03</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>97.09</v>
+        <v>97.11</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.060525</v>
       </c>
       <c r="L150" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.144192</v>
       </c>
       <c r="M150" s="2" t="n"/>
       <c r="N150" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8393,28 +8393,28 @@
         </is>
       </c>
       <c r="E151" s="2" t="n">
-        <v>90.34999999999999</v>
+        <v>90.48</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>91.77</v>
+        <v>92.91</v>
       </c>
       <c r="G151" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.16</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>91.05</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>83.56999999999999</v>
+        <v>84.64</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>90.58</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.060525</v>
       </c>
       <c r="L151" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.144192</v>
       </c>
       <c r="M151" s="2" t="n"/>
       <c r="N151" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8445,28 +8445,28 @@
         </is>
       </c>
       <c r="E152" s="2" t="n">
-        <v>76.31999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>85.91</v>
+        <v>80.95</v>
       </c>
       <c r="G152" s="2" t="n">
-        <v>91.45999999999999</v>
+        <v>91.42</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>80.83</v>
+        <v>82.06</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>67.83</v>
+        <v>69.58</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>75.37</v>
+        <v>76.42</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.060525</v>
       </c>
       <c r="L152" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.144192</v>
       </c>
       <c r="M152" s="2" t="n"/>
       <c r="N152" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8497,28 +8497,28 @@
         </is>
       </c>
       <c r="E153" s="2" t="n">
-        <v>93.55</v>
+        <v>92.36</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>95.95</v>
+        <v>95.44</v>
       </c>
       <c r="G153" s="2" t="n">
-        <v>99.59</v>
+        <v>99.52</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>94.73</v>
+        <v>93.88</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>89.98999999999999</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>94.52</v>
+        <v>93.63</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.060525</v>
       </c>
       <c r="L153" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.144192</v>
       </c>
       <c r="M153" s="2" t="n"/>
       <c r="N153" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8549,10 +8549,10 @@
         </is>
       </c>
       <c r="E154" s="2" t="n">
-        <v>97.45</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>97.48999999999999</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="G154" s="2" t="n">
         <v>99.38</v>
@@ -8561,16 +8561,16 @@
         <v>97.47</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>95.06</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>97.12</v>
+        <v>97.11</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.077293</v>
       </c>
       <c r="L154" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.16096</v>
       </c>
       <c r="M154" s="2" t="n"/>
       <c r="N154" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -8601,28 +8601,28 @@
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>90.67</v>
+        <v>90.45</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>92.58</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="G155" s="2" t="n">
         <v>99.15000000000001</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>91.62</v>
+        <v>91.55</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>84.53</v>
+        <v>84.42</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>91.17</v>
+        <v>91.11</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.077293</v>
       </c>
       <c r="L155" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.16096</v>
       </c>
       <c r="M155" s="2" t="n"/>
       <c r="N155" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -8653,28 +8653,28 @@
         </is>
       </c>
       <c r="E156" s="2" t="n">
-        <v>77.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>87.42</v>
+        <v>86.2</v>
       </c>
       <c r="G156" s="2" t="n">
-        <v>92.15000000000001</v>
+        <v>91.97</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>82.39</v>
+        <v>82.17</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>70.05</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>77.36</v>
+        <v>77</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.077293</v>
       </c>
       <c r="L156" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.16096</v>
       </c>
       <c r="M156" s="2" t="n"/>
       <c r="N156" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -8705,28 +8705,28 @@
         </is>
       </c>
       <c r="E157" s="2" t="n">
-        <v>92.61</v>
+        <v>91.88</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>95.77</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="G157" s="2" t="n">
-        <v>99.54000000000001</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>94.16</v>
+        <v>93.41</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>88.97</v>
+        <v>87.63</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>93.93000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.077293</v>
       </c>
       <c r="L157" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.16096</v>
       </c>
       <c r="M157" s="2" t="n"/>
       <c r="N157" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -8757,13 +8757,13 @@
         </is>
       </c>
       <c r="E158" s="2" t="n">
-        <v>97.31999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="F158" s="2" t="n">
-        <v>97.54000000000001</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="G158" s="2" t="n">
-        <v>99.37</v>
+        <v>99.36</v>
       </c>
       <c r="H158" s="2" t="n">
         <v>97.43000000000001</v>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -8809,22 +8809,22 @@
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>89.79000000000001</v>
+        <v>90.69</v>
       </c>
       <c r="F159" s="2" t="n">
-        <v>92.27</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="G159" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>91.01000000000001</v>
+        <v>91.55</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>83.51000000000001</v>
+        <v>84.42</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>90.54000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="K159" s="2" t="n">
         <v>3.016737</v>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -8861,22 +8861,22 @@
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>79.92</v>
+        <v>82.58</v>
       </c>
       <c r="F160" s="2" t="n">
-        <v>84.81</v>
+        <v>82.25</v>
       </c>
       <c r="G160" s="2" t="n">
-        <v>91.89</v>
+        <v>91.69</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>82.29000000000001</v>
+        <v>82.42</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>69.91</v>
+        <v>70.09</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>76.98</v>
       </c>
       <c r="K160" s="2" t="n">
         <v>3.016737</v>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -8913,22 +8913,22 @@
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>92.78</v>
+        <v>92.31</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>95.23</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G161" s="2" t="n">
-        <v>99.53</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>93.98999999999999</v>
+        <v>93.44</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>88.66</v>
+        <v>87.69</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>93.75</v>
+        <v>93.17</v>
       </c>
       <c r="K161" s="2" t="n">
         <v>3.016737</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -8965,22 +8965,22 @@
         </is>
       </c>
       <c r="E162" s="2" t="n">
-        <v>97.48999999999999</v>
+        <v>97.53</v>
       </c>
       <c r="F162" s="2" t="n">
-        <v>97.45</v>
+        <v>97.38</v>
       </c>
       <c r="G162" s="2" t="n">
         <v>99.37</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>97.47</v>
+        <v>97.45</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>95.06</v>
+        <v>95.03</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>97.11</v>
+        <v>97.09</v>
       </c>
       <c r="K162" s="2" t="n">
         <v>3.050665</v>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9017,22 +9017,22 @@
         </is>
       </c>
       <c r="E163" s="2" t="n">
-        <v>89.73999999999999</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="F163" s="2" t="n">
-        <v>93.42</v>
+        <v>91.77</v>
       </c>
       <c r="G163" s="2" t="n">
-        <v>99.16</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>91.54000000000001</v>
+        <v>91.05</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>84.40000000000001</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>90.58</v>
       </c>
       <c r="K163" s="2" t="n">
         <v>3.050665</v>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9069,22 +9069,22 @@
         </is>
       </c>
       <c r="E164" s="2" t="n">
-        <v>77.78</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F164" s="2" t="n">
-        <v>84.04000000000001</v>
+        <v>85.91</v>
       </c>
       <c r="G164" s="2" t="n">
-        <v>91.28</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>80.79000000000001</v>
+        <v>80.83</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>67.77</v>
+        <v>67.83</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>75.16</v>
+        <v>75.37</v>
       </c>
       <c r="K164" s="2" t="n">
         <v>3.050665</v>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9121,22 +9121,22 @@
         </is>
       </c>
       <c r="E165" s="2" t="n">
-        <v>93.05</v>
+        <v>93.55</v>
       </c>
       <c r="F165" s="2" t="n">
-        <v>96.14</v>
+        <v>95.95</v>
       </c>
       <c r="G165" s="2" t="n">
-        <v>99.58</v>
+        <v>99.59</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>94.56999999999999</v>
+        <v>94.73</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>89.7</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>94.34999999999999</v>
+        <v>94.52</v>
       </c>
       <c r="K165" s="2" t="n">
         <v>3.050665</v>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9173,10 +9173,10 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>97.41</v>
+        <v>97.45</v>
       </c>
       <c r="F166" s="2" t="n">
-        <v>97.53</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="G166" s="2" t="n">
         <v>99.38</v>
@@ -9185,10 +9185,10 @@
         <v>97.47</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>95.06</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>97.11</v>
+        <v>97.12</v>
       </c>
       <c r="K166" s="2" t="n">
         <v>3.067561</v>
@@ -9211,7 +9211,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9225,22 +9225,22 @@
         </is>
       </c>
       <c r="E167" s="2" t="n">
-        <v>90.68000000000001</v>
+        <v>90.67</v>
       </c>
       <c r="F167" s="2" t="n">
-        <v>91.98</v>
+        <v>92.58</v>
       </c>
       <c r="G167" s="2" t="n">
-        <v>99.12</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>91.33</v>
+        <v>91.62</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>84.04000000000001</v>
+        <v>84.53</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>90.87</v>
+        <v>91.17</v>
       </c>
       <c r="K167" s="2" t="n">
         <v>3.067561</v>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9277,22 +9277,22 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>77.18000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F168" s="2" t="n">
-        <v>85.53</v>
+        <v>87.42</v>
       </c>
       <c r="G168" s="2" t="n">
-        <v>91.54000000000001</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>81.14</v>
+        <v>82.39</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>68.27</v>
+        <v>70.05</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>75.70999999999999</v>
+        <v>77.36</v>
       </c>
       <c r="K168" s="2" t="n">
         <v>3.067561</v>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9329,22 +9329,22 @@
         </is>
       </c>
       <c r="E169" s="2" t="n">
-        <v>92.63</v>
+        <v>92.61</v>
       </c>
       <c r="F169" s="2" t="n">
-        <v>96.55</v>
+        <v>95.77</v>
       </c>
       <c r="G169" s="2" t="n">
-        <v>99.58</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>94.55</v>
+        <v>94.16</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>89.67</v>
+        <v>88.97</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>94.33</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="K169" s="2" t="n">
         <v>3.067561</v>
@@ -9362,17 +9362,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -9381,52 +9381,50 @@
         </is>
       </c>
       <c r="E170" s="2" t="n">
-        <v>93.13</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="F170" s="2" t="n">
-        <v>95.16</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="G170" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>99.37</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>94.13</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>88.91</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L170" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M170" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M170" s="2" t="n"/>
       <c r="N170" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -9435,52 +9433,50 @@
         </is>
       </c>
       <c r="E171" s="2" t="n">
-        <v>86.37</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F171" s="2" t="n">
-        <v>89.25</v>
+        <v>92.27</v>
       </c>
       <c r="G171" s="2" t="n">
-        <v>98.78</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>87.14</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L171" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M171" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M171" s="2" t="n"/>
       <c r="N171" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -9489,52 +9485,50 @@
         </is>
       </c>
       <c r="E172" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>79.92</v>
       </c>
       <c r="F172" s="2" t="n">
-        <v>84.5</v>
+        <v>84.81</v>
       </c>
       <c r="G172" s="2" t="n">
-        <v>91.81</v>
+        <v>91.89</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>69.91</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>76.84</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L172" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M172" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M172" s="2" t="n"/>
       <c r="N172" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -9543,52 +9537,50 @@
         </is>
       </c>
       <c r="E173" s="2" t="n">
-        <v>90.16</v>
+        <v>92.78</v>
       </c>
       <c r="F173" s="2" t="n">
-        <v>93.97</v>
+        <v>95.23</v>
       </c>
       <c r="G173" s="2" t="n">
-        <v>99.38</v>
+        <v>99.53</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>92.02</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>85.23</v>
+        <v>88.66</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>91.7</v>
+        <v>93.75</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L173" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M173" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M173" s="2" t="n"/>
       <c r="N173" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -9597,52 +9589,50 @@
         </is>
       </c>
       <c r="E174" s="2" t="n">
-        <v>94.7</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="F174" s="2" t="n">
-        <v>96.13</v>
+        <v>97.45</v>
       </c>
       <c r="G174" s="2" t="n">
-        <v>98.88</v>
+        <v>99.37</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>95.41</v>
+        <v>97.47</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>91.22</v>
+        <v>95.06</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>94.77</v>
+        <v>97.11</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L174" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M174" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M174" s="2" t="n"/>
       <c r="N174" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -9651,52 +9641,50 @@
         </is>
       </c>
       <c r="E175" s="2" t="n">
-        <v>88.42</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="F175" s="2" t="n">
-        <v>91.97</v>
+        <v>93.42</v>
       </c>
       <c r="G175" s="2" t="n">
-        <v>99.02</v>
+        <v>99.16</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>90.16</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>82.08</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>89.64</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L175" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M175" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M175" s="2" t="n"/>
       <c r="N175" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -9705,52 +9693,50 @@
         </is>
       </c>
       <c r="E176" s="2" t="n">
-        <v>78.73</v>
+        <v>77.78</v>
       </c>
       <c r="F176" s="2" t="n">
-        <v>84.98</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="G176" s="2" t="n">
-        <v>91.7</v>
+        <v>91.28</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>69.11</v>
+        <v>67.77</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>76.38</v>
+        <v>75.16</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L176" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M176" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M176" s="2" t="n"/>
       <c r="N176" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -9759,160 +9745,154 @@
         </is>
       </c>
       <c r="E177" s="2" t="n">
-        <v>91.64</v>
+        <v>93.05</v>
       </c>
       <c r="F177" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>96.14</v>
       </c>
       <c r="G177" s="2" t="n">
-        <v>99.47</v>
+        <v>99.58</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>93.2</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>87.27</v>
+        <v>89.7</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L177" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M177" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M177" s="2" t="n"/>
       <c r="N177" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>82.42</v>
+        <v>97.41</v>
       </c>
       <c r="F178" s="2" t="n">
-        <v>83.87</v>
+        <v>97.53</v>
       </c>
       <c r="G178" s="2" t="n">
-        <v>92.12</v>
+        <v>99.38</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>83.14</v>
+        <v>97.47</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>71.14</v>
+        <v>95.06</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>97.11</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>11.754</v>
+        <v>3.067561</v>
       </c>
       <c r="L178" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M178" s="2" t="n">
-        <v>26.3246</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M178" s="2" t="n"/>
       <c r="N178" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E179" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="F179" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>91.98</v>
       </c>
       <c r="G179" s="2" t="n">
-        <v>91.94</v>
+        <v>99.12</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>82.77</v>
+        <v>91.33</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>70.61</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>90.87</v>
       </c>
       <c r="K179" s="2" t="n">
-        <v>8.195</v>
+        <v>3.067561</v>
       </c>
       <c r="L179" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M179" s="2" t="n">
-        <v>24.1021</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M179" s="2" t="n"/>
       <c r="N179" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -9921,348 +9901,992 @@
         </is>
       </c>
       <c r="E180" s="2" t="n">
-        <v>79.94</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="F180" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>85.53</v>
       </c>
       <c r="G180" s="2" t="n">
-        <v>91.89</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>82.3</v>
+        <v>81.14</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>69.92</v>
+        <v>68.27</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>5.492</v>
+        <v>3.067561</v>
       </c>
       <c r="L180" s="2" t="n">
-        <v>3.515</v>
-      </c>
-      <c r="M180" s="2" t="n">
-        <v>10.7311</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M180" s="2" t="n"/>
       <c r="N180" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E181" s="2" t="n">
-        <v>80.87</v>
+        <v>92.63</v>
       </c>
       <c r="F181" s="2" t="n">
-        <v>83.81</v>
+        <v>96.55</v>
       </c>
       <c r="G181" s="2" t="n">
-        <v>91.81</v>
+        <v>99.58</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>94.55</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>69.95</v>
+        <v>89.67</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>94.33</v>
       </c>
       <c r="K181" s="2" t="n">
-        <v>5.533</v>
+        <v>3.067561</v>
       </c>
       <c r="L181" s="2" t="n">
-        <v>3.556</v>
-      </c>
-      <c r="M181" s="2" t="n">
-        <v>10.9824</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M181" s="2" t="n"/>
       <c r="N181" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E182" s="2" t="n">
-        <v>79.78</v>
+        <v>93.13</v>
       </c>
       <c r="F182" s="2" t="n">
-        <v>84.39</v>
+        <v>95.16</v>
       </c>
       <c r="G182" s="2" t="n">
-        <v>91.75</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>82.02</v>
+        <v>94.13</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>69.52</v>
+        <v>88.91</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>5.491</v>
+        <v>2.596</v>
       </c>
       <c r="L182" s="2" t="n">
-        <v>3.514</v>
+        <v>0.62</v>
       </c>
       <c r="M182" s="2" t="n">
-        <v>11.5239</v>
+        <v>2.2136</v>
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>97.72</v>
+        <v>86.37</v>
       </c>
       <c r="F183" s="2" t="n">
-        <v>97.78</v>
+        <v>89.25</v>
       </c>
       <c r="G183" s="2" t="n">
-        <v>99.44</v>
+        <v>98.78</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>97.75</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>87.14</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L183" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M183" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E184" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F184" s="2" t="n">
-        <v>92.33</v>
+        <v>84.5</v>
       </c>
       <c r="G184" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.81</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>91.95</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>91.52</v>
+        <v>76.84</v>
       </c>
       <c r="K184" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L184" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M184" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>80.77</v>
+        <v>90.16</v>
       </c>
       <c r="F185" s="2" t="n">
-        <v>84.27</v>
+        <v>93.97</v>
       </c>
       <c r="G185" s="2" t="n">
-        <v>91.91</v>
+        <v>99.38</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>82.48</v>
+        <v>92.02</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>70.19</v>
+        <v>85.23</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>77.23</v>
+        <v>91.7</v>
       </c>
       <c r="K185" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L185" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M185" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>96.13</v>
+      </c>
+      <c r="G186" s="2" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="H186" s="2" t="n">
+        <v>95.41</v>
+      </c>
+      <c r="I186" s="2" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="J186" s="2" t="n">
+        <v>94.77</v>
+      </c>
+      <c r="K186" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L186" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M186" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="F187" s="2" t="n">
+        <v>91.97</v>
+      </c>
+      <c r="G187" s="2" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="H187" s="2" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="I187" s="2" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="J187" s="2" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="K187" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L187" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M187" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>78.73</v>
+      </c>
+      <c r="F188" s="2" t="n">
+        <v>84.98</v>
+      </c>
+      <c r="G188" s="2" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="H188" s="2" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="I188" s="2" t="n">
+        <v>69.11</v>
+      </c>
+      <c r="J188" s="2" t="n">
+        <v>76.38</v>
+      </c>
+      <c r="K188" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L188" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M188" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="G189" s="2" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="H189" s="2" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I189" s="2" t="n">
+        <v>87.27</v>
+      </c>
+      <c r="J189" s="2" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="K189" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L189" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M189" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>R4_0_A0_FULL12_FROZEN</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>82.42</v>
+      </c>
+      <c r="F190" s="2" t="n">
+        <v>83.87</v>
+      </c>
+      <c r="G190" s="2" t="n">
+        <v>92.12</v>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="I190" s="2" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="J190" s="2" t="n">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="K190" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L190" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M190" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>R4_1_VIT4_OLDHEAD</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="F191" s="2" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G191" s="2" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="H191" s="2" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="I191" s="2" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="J191" s="2" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="K191" s="2" t="n">
+        <v>8.195</v>
+      </c>
+      <c r="L191" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M191" s="2" t="n">
+        <v>24.1021</v>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="F192" s="2" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="G192" s="2" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="H192" s="2" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I192" s="2" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="J192" s="2" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="K192" s="2" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="L192" s="2" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="M192" s="2" t="n">
+        <v>10.7311</v>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="F193" s="2" t="n">
+        <v>83.81</v>
+      </c>
+      <c r="G193" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H193" s="2" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="I193" s="2" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="J193" s="2" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="K193" s="2" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="L193" s="2" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="M193" s="2" t="n">
+        <v>10.9824</v>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="F194" s="2" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="G194" s="2" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="H194" s="2" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="I194" s="2" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="J194" s="2" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="K194" s="2" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="L194" s="2" t="n">
+        <v>3.514</v>
+      </c>
+      <c r="M194" s="2" t="n">
+        <v>11.5239</v>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
         <is>
           <t>Run1</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr">
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F195" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G195" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H195" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I195" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J195" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K195" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L195" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F196" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G196" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H196" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I196" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J196" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K196" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L196" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F197" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G197" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H197" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I197" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J197" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K197" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L197" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M197" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
-      <c r="E186" s="2" t="n">
+      <c r="E198" s="2" t="n">
         <v>93.62</v>
       </c>
-      <c r="F186" s="2" t="n">
+      <c r="F198" s="2" t="n">
         <v>96.09</v>
       </c>
-      <c r="G186" s="2" t="n">
+      <c r="G198" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="H186" s="2" t="n">
+      <c r="H198" s="2" t="n">
         <v>94.84</v>
       </c>
-      <c r="I186" s="2" t="n">
+      <c r="I198" s="2" t="n">
         <v>90.18000000000001</v>
       </c>
-      <c r="J186" s="2" t="n">
+      <c r="J198" s="2" t="n">
         <v>94.63</v>
       </c>
-      <c r="K186" s="2" t="n">
+      <c r="K198" s="2" t="n">
         <v>11.754</v>
       </c>
-      <c r="L186" s="2" t="n">
+      <c r="L198" s="2" t="n">
         <v>20.661</v>
       </c>
-      <c r="M186" s="2" t="n">
+      <c r="M198" s="2" t="n">
         <v>26.3246</v>
       </c>
-      <c r="N186" t="inlineStr">
+      <c r="N198" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N186"/>
+  <autoFilter ref="A1:N198"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$210</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N198"/>
+  <dimension ref="A1:N210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2490,17 +2490,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2509,52 +2509,50 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>94.08</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>95.26000000000001</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>98.69</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>94.67</v>
+        <v>96.91</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>89.87</v>
+        <v>94.01000000000001</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>93.92</v>
+        <v>96.48</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>2.378</v>
+        <v>1.93581</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M40" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.047125</v>
+      </c>
+      <c r="M40" s="2" t="n"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2563,52 +2561,50 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>88.55</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>91.3</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>98.98999999999999</v>
+        <v>99.09</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>89.90000000000001</v>
+        <v>90.95</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>81.66</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>89.37</v>
+        <v>90.47</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>2.378</v>
+        <v>1.93581</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M41" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.047125</v>
+      </c>
+      <c r="M41" s="2" t="n"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2617,52 +2613,50 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>82.09</v>
+        <v>78.44</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>82.84</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>91.77</v>
+        <v>92.05</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>82.47</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>70.16</v>
+        <v>69.95</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>77.09</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2.378</v>
+        <v>1.93581</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M42" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.047125</v>
+      </c>
+      <c r="M42" s="2" t="n"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2671,52 +2665,50 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>92.34</v>
+        <v>93.06</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>95.34</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>93.7</v>
+        <v>94.19</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>88.15000000000001</v>
+        <v>89.02</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>93.44</v>
+        <v>93.95</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2.378</v>
+        <v>1.93581</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M43" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.047125</v>
+      </c>
+      <c r="M43" s="2" t="n"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2725,52 +2717,50 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>93.90000000000001</v>
+        <v>96.89</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>95.19</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>98.66</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>94.54000000000001</v>
+        <v>96.94</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>89.64</v>
+        <v>94.06</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>93.78</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>2.416</v>
+        <v>1.953222</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M44" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.064537</v>
+      </c>
+      <c r="M44" s="2" t="n"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2779,52 +2769,50 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>88.81999999999999</v>
+        <v>90.16</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>90.93000000000001</v>
+        <v>92.09</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>98.98</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>89.87</v>
+        <v>91.12</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>81.59999999999999</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>89.33</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2.416</v>
+        <v>1.953222</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M45" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.064537</v>
+      </c>
+      <c r="M45" s="2" t="n"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2833,52 +2821,50 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>79.66</v>
+        <v>79.95</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>85.53</v>
+        <v>85.81</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>92.03</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>82.48999999999999</v>
+        <v>82.78</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>70.2</v>
+        <v>70.61</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>77.34</v>
+        <v>77.7</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2.416</v>
+        <v>1.953222</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.064537</v>
+      </c>
+      <c r="M46" s="2" t="n"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2887,52 +2873,50 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>91.81999999999999</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>95.56</v>
+        <v>96.11</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>99.58</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>93.65000000000001</v>
+        <v>94.61</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>88.06999999999999</v>
+        <v>89.77</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>93.40000000000001</v>
+        <v>94.39</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2.416</v>
+        <v>1.953222</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M47" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.064537</v>
+      </c>
+      <c r="M47" s="2" t="n"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2941,52 +2925,50 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>95.05</v>
+        <v>96.79000000000001</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>96.02</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>95.53</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>91.45</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>94.91</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2.378</v>
+        <v>1.953222</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M48" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.064537</v>
+      </c>
+      <c r="M48" s="2" t="n"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2995,52 +2977,50 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>88.98999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>91.62</v>
+        <v>91.59</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>99.02</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>90.28</v>
+        <v>91.14</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>82.29000000000001</v>
+        <v>83.73</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>89.77</v>
+        <v>90.67</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>2.378</v>
+        <v>1.953222</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M49" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.064537</v>
+      </c>
+      <c r="M49" s="2" t="n"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3049,52 +3029,50 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>79.3</v>
+        <v>81.97</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>85.94</v>
+        <v>83.84</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>92.06</v>
+        <v>92.02</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>82.48999999999999</v>
+        <v>82.89</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>70.19</v>
+        <v>70.78</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>77.36</v>
+        <v>77.69</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>2.378</v>
+        <v>1.953222</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M50" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.064537</v>
+      </c>
+      <c r="M50" s="2" t="n"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3103,35 +3081,33 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>92.15000000000001</v>
+        <v>93.06</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>94.7</v>
+        <v>96.45</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>99.48</v>
+        <v>99.59</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>93.41</v>
+        <v>94.72</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>87.63</v>
+        <v>89.98</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>93.14</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2.378</v>
+        <v>1.953222</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M51" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.064537</v>
+      </c>
+      <c r="M51" s="2" t="n"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3124,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3157,31 +3133,31 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>95.06</v>
+        <v>94.08</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>96.01000000000001</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>98.69</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>95.54000000000001</v>
+        <v>94.67</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>91.45</v>
+        <v>89.87</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>94.91</v>
+        <v>93.92</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -3202,7 +3178,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3211,31 +3187,31 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>89.47</v>
+        <v>88.55</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>91.28</v>
+        <v>91.3</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>99.03</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>90.37</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>82.43000000000001</v>
+        <v>81.66</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>89.86</v>
+        <v>89.37</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -3256,7 +3232,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3265,31 +3241,31 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>81.39</v>
+        <v>82.09</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>84.72</v>
+        <v>82.84</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>92.15000000000001</v>
+        <v>91.77</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>83.02</v>
+        <v>82.47</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>70.97</v>
+        <v>70.16</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>77.92</v>
+        <v>77.09</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -3310,7 +3286,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3319,31 +3295,31 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>92</v>
+        <v>92.34</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>99.51000000000001</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>93.72</v>
+        <v>93.7</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>88.19</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>93.47</v>
+        <v>93.44</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -3354,275 +3330,331 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_INJ</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>90.38</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>91.91</v>
+        <v>95.19</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>98.66</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>91.14</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>83.72</v>
+        <v>89.64</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>90.66</v>
-      </c>
-      <c r="K56" s="2" t="n"/>
-      <c r="L56" s="2" t="n"/>
-      <c r="M56" s="2" t="n"/>
+        <v>93.78</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_INJ</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>81.18000000000001</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>82.19</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>91.41</v>
+        <v>98.98</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>81.68000000000001</v>
+        <v>89.87</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>69.04000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>76.08</v>
-      </c>
-      <c r="K57" s="2" t="n"/>
-      <c r="L57" s="2" t="n"/>
-      <c r="M57" s="2" t="n"/>
+        <v>89.33</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_SUP</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>90.63</v>
+        <v>79.66</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>91.56</v>
+        <v>85.53</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>92.03</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>91.09</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>83.64</v>
+        <v>70.2</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>90.62</v>
+        <v>77.34</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>31.978582</v>
-      </c>
-      <c r="L58" s="2" t="n"/>
-      <c r="M58" s="2" t="n"/>
+        <v>2.416</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_SUP</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>81.28</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>82.75</v>
+        <v>95.56</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>91.59</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>82.01000000000001</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>69.5</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>76.52</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>31.978582</v>
-      </c>
-      <c r="L59" s="2" t="n"/>
-      <c r="M59" s="2" t="n"/>
+        <v>2.416</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_V2</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>90.52</v>
+        <v>95.05</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>91.84999999999999</v>
+        <v>96.02</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>99.11</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>95.53</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>83.79000000000001</v>
+        <v>91.45</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>90.70999999999999</v>
-      </c>
-      <c r="K60" s="2" t="n"/>
-      <c r="L60" s="2" t="n"/>
-      <c r="M60" s="2" t="n"/>
+        <v>94.91</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>1.2051</v>
+      </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_V2</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>79.34</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>84.23999999999999</v>
+        <v>91.62</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>91.63</v>
+        <v>99.02</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>81.72</v>
+        <v>90.28</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>69.09</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="K61" s="2" t="n"/>
-      <c r="L61" s="2" t="n"/>
-      <c r="M61" s="2" t="n"/>
+        <v>89.77</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>1.2051</v>
+      </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3632,51 +3664,51 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>96.58</v>
+        <v>79.3</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>96.94</v>
+        <v>85.94</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>99.2</v>
+        <v>92.06</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>96.76000000000001</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>93.73</v>
+        <v>70.19</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>96.31</v>
+        <v>77.36</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>4.88</v>
+        <v>2.378</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>4.88</v>
+        <v>2.378</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2051</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3686,51 +3718,51 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>A2_STR_ONLY</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>89.52</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>92.69</v>
+        <v>94.7</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>99.11</v>
+        <v>99.48</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>91.08</v>
+        <v>93.41</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>83.62</v>
+        <v>87.63</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>90.61</v>
+        <v>93.14</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>4.88</v>
+        <v>2.378</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>4.88</v>
+        <v>2.378</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2051</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3740,51 +3772,51 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>95.06</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>85.01000000000001</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>91.94</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>82.39</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>70.06</v>
+        <v>91.45</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>77.18000000000001</v>
+        <v>94.91</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2365</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3794,51 +3826,51 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>A0_TVIM_PLAIN</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>92.69</v>
+        <v>89.47</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>96.95999999999999</v>
+        <v>91.28</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>99.59</v>
+        <v>99.03</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>94.78</v>
+        <v>90.37</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>90.08</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>94.56999999999999</v>
+        <v>89.86</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2365</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3848,51 +3880,51 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>96.62</v>
+        <v>81.39</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>96.88</v>
+        <v>84.72</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>99.2</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>96.75</v>
+        <v>83.02</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>93.7</v>
+        <v>70.97</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>96.29000000000001</v>
+        <v>77.92</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2365</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
+          <t>CASA-STR</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3902,44 +3934,44 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>M1_CASAA_STR</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>89.95</v>
+        <v>92</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>92.13</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>91.03</v>
+        <v>93.72</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>83.53</v>
+        <v>88.19</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>90.55</v>
+        <v>93.47</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>4.88</v>
+        <v>2.416</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2.6747</v>
+        <v>1.2365</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
@@ -3949,51 +3981,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>Exploration/Exp1/STG_INJ</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>80.14</v>
+        <v>90.38</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>84.18000000000001</v>
+        <v>91.91</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>91.76000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>82.11</v>
+        <v>91.14</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>69.65000000000001</v>
+        <v>83.72</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>76.76000000000001</v>
-      </c>
-      <c r="K68" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M68" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>90.66</v>
+      </c>
+      <c r="K68" s="2" t="n"/>
+      <c r="L68" s="2" t="n"/>
+      <c r="M68" s="2" t="n"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -4003,51 +4025,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>A1_CAACP</t>
+          <t>Exploration/Exp1/STG_INJ</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>92.45</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>97.37</v>
+        <v>82.19</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>91.41</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>94.84</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>90.19</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>94.64</v>
-      </c>
-      <c r="K69" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M69" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>76.08</v>
+      </c>
+      <c r="K69" s="2" t="n"/>
+      <c r="L69" s="2" t="n"/>
+      <c r="M69" s="2" t="n"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -4057,51 +4069,43 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>Exploration/Exp1/STG_SUP</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>97.02</v>
+        <v>90.63</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>97.20999999999999</v>
+        <v>91.56</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>99.29000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>97.11</v>
+        <v>91.09</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>94.39</v>
+        <v>83.64</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>96.70999999999999</v>
+        <v>90.62</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M70" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>31.978582</v>
+      </c>
+      <c r="L70" s="2" t="n"/>
+      <c r="M70" s="2" t="n"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -4111,51 +4115,43 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>Exploration/Exp1/STG_SUP</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>89.59</v>
+        <v>81.28</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>92.84</v>
+        <v>82.75</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>99.12</v>
+        <v>91.59</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>91.19</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>83.81</v>
+        <v>69.5</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>90.73</v>
+        <v>76.52</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M71" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>31.978582</v>
+      </c>
+      <c r="L71" s="2" t="n"/>
+      <c r="M71" s="2" t="n"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -4165,51 +4161,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>Exploration/Exp1/STG_V2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>81.23999999999999</v>
+        <v>90.52</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>85.29000000000001</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>92.27</v>
+        <v>99.11</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>83.20999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>71.25</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="K72" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M72" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>90.70999999999999</v>
+      </c>
+      <c r="K72" s="2" t="n"/>
+      <c r="L72" s="2" t="n"/>
+      <c r="M72" s="2" t="n"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -4219,51 +4205,41 @@
           <t>CASA-TViM</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Run1</t>
-        </is>
-      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>A2_STR</t>
+          <t>Exploration/Exp1/STG_V2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>93.09999999999999</v>
+        <v>79.34</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>96.01000000000001</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>99.56999999999999</v>
+        <v>91.63</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>94.53</v>
+        <v>81.72</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>89.63</v>
+        <v>69.09</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>94.31</v>
-      </c>
-      <c r="K73" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M73" s="2" t="n">
-        <v>2.6747</v>
-      </c>
+        <v>76.3</v>
+      </c>
+      <c r="K73" s="2" t="n"/>
+      <c r="L73" s="2" t="n"/>
+      <c r="M73" s="2" t="n"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>casa_tvim_str</t>
+          <t>casa_vmamba_stgeo</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4256,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4289,22 +4265,22 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>97.03</v>
+        <v>96.58</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>97.33</v>
+        <v>96.94</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>97.18000000000001</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>94.51000000000001</v>
+        <v>93.73</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>96.78</v>
+        <v>96.31</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>4.88</v>
@@ -4334,7 +4310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4343,22 +4319,22 @@
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>90.33</v>
+        <v>89.52</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>91.81999999999999</v>
+        <v>92.69</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.11</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>91.06999999999999</v>
+        <v>91.08</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>83.62</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>90.59</v>
+        <v>90.61</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>4.88</v>
@@ -4388,7 +4364,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4397,22 +4373,22 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>84.41</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>82.55</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>92.12</v>
+        <v>91.94</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>83.47</v>
+        <v>82.39</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>71.63</v>
+        <v>70.06</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>78.29000000000001</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>4.88</v>
@@ -4442,7 +4418,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>M1_FULL</t>
+          <t>A0_TVIM_PLAIN</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4451,22 +4427,22 @@
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>93.56</v>
+        <v>92.69</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>96.62</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>99.61</v>
+        <v>99.59</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>94.78</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>90.08</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>94.87</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>4.88</v>
@@ -4491,12 +4467,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4505,22 +4481,22 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>97.02</v>
+        <v>96.62</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>97.27</v>
+        <v>96.88</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>97.14</v>
+        <v>96.75</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>94.45</v>
+        <v>93.7</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>96.73999999999999</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>4.88</v>
@@ -4545,12 +4521,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4559,22 +4535,22 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>90.64</v>
+        <v>89.95</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>91.64</v>
+        <v>92.13</v>
       </c>
       <c r="G79" s="2" t="n">
         <v>99.09999999999999</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>91.14</v>
+        <v>91.03</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>83.72</v>
+        <v>83.53</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>90.66</v>
+        <v>90.55</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>4.88</v>
@@ -4599,12 +4575,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4613,22 +4589,22 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>80.94</v>
+        <v>80.14</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>85.43000000000001</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>92.25</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>83.13</v>
+        <v>82.11</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>71.12</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>4.88</v>
@@ -4653,12 +4629,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>E1_CP_CAACP</t>
+          <t>A1_CAACP</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4667,22 +4643,22 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>93.73999999999999</v>
+        <v>92.45</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>96.67</v>
+        <v>97.37</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>99.62</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>95.18000000000001</v>
+        <v>94.84</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>90.81</v>
+        <v>90.19</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>94.98999999999999</v>
+        <v>94.64</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>4.88</v>
@@ -4707,12 +4683,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4724,28 +4700,28 @@
         <v>97.02</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>97.33</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>99.3</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>97.17</v>
+        <v>97.11</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>94.5</v>
+        <v>94.39</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>96.78</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
@@ -4761,12 +4737,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4775,31 +4751,31 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>90.22</v>
+        <v>89.59</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>92.22</v>
+        <v>92.84</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>99.11</v>
+        <v>99.12</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>91.19</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>83.83</v>
+        <v>83.81</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>90.73999999999999</v>
+        <v>90.73</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -4815,12 +4791,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4829,31 +4805,31 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>80.09999999999999</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>86.05</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>92.23999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>82.97</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>70.89</v>
+        <v>71.25</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>77.95999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -4869,12 +4845,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>E2_FRH</t>
+          <t>A2_STR</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4883,31 +4859,31 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>93.45999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>96</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>99.59</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>94.70999999999999</v>
+        <v>94.53</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>89.95</v>
+        <v>89.63</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>94.48999999999999</v>
+        <v>94.31</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -4923,12 +4899,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4937,10 +4913,10 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>97.02</v>
+        <v>97.03</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>97.34</v>
+        <v>97.33</v>
       </c>
       <c r="G86" s="2" t="n">
         <v>99.3</v>
@@ -4955,13 +4931,13 @@
         <v>96.78</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -4977,12 +4953,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4991,31 +4967,31 @@
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>90.20999999999999</v>
+        <v>90.33</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>92.41</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>99.12</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>91.29000000000001</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>83.98</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>90.83</v>
+        <v>90.59</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -5031,12 +5007,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5045,31 +5021,31 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>80.69</v>
+        <v>84.41</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>85.12</v>
+        <v>82.55</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>92.12</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>82.84999999999999</v>
+        <v>83.47</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>70.72</v>
+        <v>71.63</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>77.73999999999999</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -5085,12 +5061,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>E3_CP_FRH</t>
+          <t>M1_FULL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5099,31 +5075,31 @@
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>93.8</v>
+        <v>93.56</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>96.18000000000001</v>
+        <v>96.62</v>
       </c>
       <c r="G89" s="2" t="n">
         <v>99.61</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>94.98</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>90.44</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>94.77</v>
+        <v>94.87</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>4.881</v>
+        <v>4.88</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2.6947</v>
+        <v>2.6747</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -5139,12 +5115,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5156,19 +5132,19 @@
         <v>97.02</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>97.25</v>
+        <v>97.27</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>99.29000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>97.13</v>
+        <v>97.14</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>94.42</v>
+        <v>94.45</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>96.73</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>4.88</v>
@@ -5193,12 +5169,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5207,22 +5183,22 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>90.05</v>
+        <v>90.64</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>92.12</v>
+        <v>91.64</v>
       </c>
       <c r="G91" s="2" t="n">
         <v>99.09999999999999</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>91.06999999999999</v>
+        <v>91.14</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>83.72</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>90.66</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>4.88</v>
@@ -5247,12 +5223,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5261,19 +5237,19 @@
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>81.44</v>
+        <v>80.94</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>84.94</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>92.22</v>
+        <v>92.25</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>83.16</v>
+        <v>83.13</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>71.17</v>
+        <v>71.12</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>78.09999999999999</v>
@@ -5301,12 +5277,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>E4_RA_CAACP</t>
+          <t>E1_CP_CAACP</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5315,22 +5291,22 @@
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>93.42</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>96.66</v>
+        <v>96.67</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>99.61</v>
+        <v>99.62</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>95.02</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>90.5</v>
+        <v>90.81</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>94.81</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>4.88</v>
@@ -5355,12 +5331,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5369,31 +5345,31 @@
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>97.03</v>
+        <v>97.02</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>97.23999999999999</v>
+        <v>97.33</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>99.29000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>97.13</v>
+        <v>97.17</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>94.43000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>96.73</v>
+        <v>96.78</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6947</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
@@ -5409,12 +5385,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5423,31 +5399,31 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>90.25</v>
+        <v>90.22</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>92.12</v>
+        <v>92.22</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>99.11</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>83.78</v>
+        <v>83.83</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>90.70999999999999</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6947</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -5463,12 +5439,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5477,31 +5453,31 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>81.26000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>85.31</v>
+        <v>86.05</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>92.28</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>83.23999999999999</v>
+        <v>82.97</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>71.29000000000001</v>
+        <v>70.89</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>78.23</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6947</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -5517,12 +5493,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>E5_FS_TAR</t>
+          <t>E2_FRH</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5531,31 +5507,31 @@
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>93.11</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>96.78</v>
+        <v>96</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.59</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>94.91</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>90.31</v>
+        <v>89.95</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>94.7</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>4.954</v>
+        <v>4.881</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2.9767</v>
+        <v>2.6947</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -5571,12 +5547,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5585,31 +5561,31 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>96.97</v>
+        <v>97.02</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>97.08</v>
+        <v>97.34</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>99.27</v>
+        <v>99.3</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>97.02</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>94.22</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>96.59999999999999</v>
+        <v>96.78</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2.717</v>
+        <v>2.6947</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -5625,12 +5601,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5639,31 +5615,31 @@
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>90.15000000000001</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>92.33</v>
+        <v>92.41</v>
       </c>
       <c r="G99" s="2" t="n">
         <v>99.12</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>91.23</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>83.87</v>
+        <v>83.98</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>90.76000000000001</v>
+        <v>90.83</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2.717</v>
+        <v>2.6947</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -5679,12 +5655,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5693,31 +5669,31 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>81.90000000000001</v>
+        <v>80.69</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>84.53</v>
+        <v>85.12</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>92.2</v>
+        <v>92.12</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>83.19</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>71.22</v>
+        <v>70.72</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>78.11</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2.717</v>
+        <v>2.6947</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -5733,12 +5709,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>E10_HFAE_B</t>
+          <t>E3_CP_FRH</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5747,31 +5723,31 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>94.02</v>
+        <v>93.8</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>96.37</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>99.62</v>
+        <v>99.61</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>95.18000000000001</v>
+        <v>94.98</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>90.8</v>
+        <v>90.44</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>94.98</v>
+        <v>94.77</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>4.89</v>
+        <v>4.881</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2.717</v>
+        <v>2.6947</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -5787,12 +5763,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5801,22 +5777,22 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>96.94</v>
+        <v>97.02</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>97.17</v>
+        <v>97.25</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>99.27</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>97.05</v>
+        <v>97.13</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>94.27</v>
+        <v>94.42</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>96.64</v>
+        <v>96.73</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>4.88</v>
@@ -5841,12 +5817,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5855,22 +5831,22 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>90.09</v>
+        <v>90.05</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>92.62</v>
+        <v>92.12</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>99.13</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>91.34</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>84.06</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>90.88</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>4.88</v>
@@ -5895,12 +5871,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5909,22 +5885,22 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>81.09999999999999</v>
+        <v>81.44</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>85.65000000000001</v>
+        <v>84.94</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>92.34</v>
+        <v>92.22</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>83.31</v>
+        <v>83.16</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>71.17</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>78.34999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>4.88</v>
@@ -5949,12 +5925,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>E9_HFAE_A</t>
+          <t>E4_RA_CAACP</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5963,22 +5939,22 @@
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>93.8</v>
+        <v>93.42</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>96.38</v>
+        <v>96.66</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>99.61</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>95.02</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>90.61</v>
+        <v>90.5</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>94.87</v>
+        <v>94.81</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>4.88</v>
@@ -6003,12 +5979,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6017,31 +5993,31 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>97</v>
+        <v>97.03</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>97.33</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>99.3</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>97.17</v>
+        <v>97.13</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>94.48999999999999</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>96.77</v>
+        <v>96.73</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="L106" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.9767</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
@@ -6057,12 +6033,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6071,31 +6047,31 @@
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>89.63</v>
+        <v>90.25</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>92.70999999999999</v>
+        <v>92.12</v>
       </c>
       <c r="G107" s="2" t="n">
         <v>99.11</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>91.15000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>83.73</v>
+        <v>83.78</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>90.68000000000001</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="L107" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.9767</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
@@ -6111,12 +6087,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6125,31 +6101,31 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>80.41</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>85.06999999999999</v>
+        <v>85.31</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>92.05</v>
+        <v>92.28</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>82.68000000000001</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>70.47</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>77.53</v>
+        <v>78.23</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.9767</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -6165,12 +6141,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>M1_R7CTRL</t>
+          <t>E5_FS_TAR</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6179,31 +6155,31 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>93.44</v>
+        <v>93.11</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>96.28</v>
+        <v>96.78</v>
       </c>
       <c r="G109" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>94.84</v>
+        <v>94.91</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>90.19</v>
+        <v>90.31</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>94.63</v>
+        <v>94.7</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>4.88</v>
+        <v>4.954</v>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2.6747</v>
+        <v>2.9767</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
@@ -6219,49 +6195,49 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Run8</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CTRL_R8</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>90.43000000000001</v>
+        <v>96.97</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>92.01000000000001</v>
+        <v>97.08</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>99.11</v>
+        <v>99.27</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>97.02</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>83.84</v>
+        <v>94.22</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>90.73999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>31.026</v>
+        <v>4.89</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>31.026</v>
+        <v>4.89</v>
       </c>
       <c r="M110" s="2" t="n">
-        <v>13.6715</v>
+        <v>2.717</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>casa_vmamba_str</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -6273,49 +6249,49 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Run8</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CTRL_R8</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>79.66</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>84.22</v>
+        <v>92.33</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>91.69</v>
+        <v>99.12</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>81.88</v>
+        <v>91.23</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>69.31999999999999</v>
+        <v>83.87</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>76.48999999999999</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>31.026</v>
+        <v>4.89</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>31.026</v>
+        <v>4.89</v>
       </c>
       <c r="M111" s="2" t="n">
-        <v>13.6715</v>
+        <v>2.717</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>casa_vmamba_str</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -6327,49 +6303,49 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Run9</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>S0_CTRL</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>97.77</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>97.77</v>
+        <v>84.53</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>99.45</v>
+        <v>92.2</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>97.77</v>
+        <v>83.19</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>95.65000000000001</v>
+        <v>71.22</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>97.45999999999999</v>
+        <v>78.11</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>31.977</v>
+        <v>4.89</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>31.977</v>
+        <v>4.89</v>
       </c>
       <c r="M112" s="2" t="n">
-        <v>14.6841</v>
+        <v>2.717</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -6381,49 +6357,49 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Run9</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>S0_CTRL</t>
+          <t>E10_HFAE_B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>89.79000000000001</v>
+        <v>94.02</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>92.53</v>
+        <v>96.37</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>99.11</v>
+        <v>99.62</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>91.14</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>83.72</v>
+        <v>90.8</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>90.67</v>
+        <v>94.98</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>31.977</v>
+        <v>4.89</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>31.977</v>
+        <v>4.89</v>
       </c>
       <c r="M113" s="2" t="n">
-        <v>14.6841</v>
+        <v>2.717</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
@@ -6435,12 +6411,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Run9</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>S1_HSAM</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6449,260 +6425,268 @@
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>97.66</v>
+        <v>96.94</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>97.65000000000001</v>
+        <v>97.17</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>99.42</v>
+        <v>99.27</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>97.65000000000001</v>
+        <v>97.05</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>95.42</v>
+        <v>94.27</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>97.31999999999999</v>
+        <v>96.64</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>31.977</v>
+        <v>4.88</v>
       </c>
       <c r="L114" s="2" t="n">
-        <v>31.977</v>
+        <v>4.88</v>
       </c>
       <c r="M114" s="2" t="n">
-        <v>14.769</v>
+        <v>2.6747</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>80.27</v>
+        <v>90.09</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>85.19</v>
+        <v>92.62</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>92.06</v>
+        <v>99.13</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>82.65000000000001</v>
+        <v>91.34</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>70.44</v>
+        <v>84.06</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>90.88</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>3.016737</v>
+        <v>4.88</v>
       </c>
       <c r="L115" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M115" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_none</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>91.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>91.72</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>99.13</v>
+        <v>92.34</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>91.45999999999999</v>
+        <v>83.31</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>84.26000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>91</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>3.016737</v>
+        <v>4.88</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M116" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_none</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>E9_HFAE_A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>80.39</v>
+        <v>93.8</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>82.89</v>
+        <v>96.38</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>91.45999999999999</v>
+        <v>99.61</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>81.62</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>68.95</v>
+        <v>90.61</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>76.06999999999999</v>
+        <v>94.87</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>3.016737</v>
+        <v>4.88</v>
       </c>
       <c r="L117" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M117" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_none</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>92.61</v>
+        <v>97</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>95.26000000000001</v>
+        <v>97.33</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>99.52</v>
+        <v>99.3</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>93.92</v>
+        <v>97.17</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>88.53</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>93.67</v>
+        <v>96.77</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>3.016737</v>
+        <v>4.88</v>
       </c>
       <c r="L118" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M118" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_none</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6711,50 +6695,52 @@
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>90.55</v>
+        <v>89.63</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>92.03</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>99.12</v>
+        <v>99.11</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>91.28</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>83.95999999999999</v>
+        <v>83.73</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>90.81999999999999</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>3.049509</v>
+        <v>4.88</v>
       </c>
       <c r="L119" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M119" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_hyperbolic</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6763,50 +6749,52 @@
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>78.67</v>
+        <v>80.41</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>85.08</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>91.72</v>
+        <v>92.05</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>81.75</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>69.13</v>
+        <v>70.47</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>76.40000000000001</v>
+        <v>77.53</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>3.049509</v>
+        <v>4.88</v>
       </c>
       <c r="L120" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M120" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_hyperbolic</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>M1_R7CTRL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6815,50 +6803,52 @@
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>92.84999999999999</v>
+        <v>93.44</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>95.31999999999999</v>
+        <v>96.28</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>99.54000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>94.06999999999999</v>
+        <v>94.84</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>88.8</v>
+        <v>90.19</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>93.83</v>
+        <v>94.63</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>3.049509</v>
+        <v>4.88</v>
       </c>
       <c r="L121" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M121" s="2" t="n"/>
+        <v>4.88</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>2.6747</v>
+      </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_hyperbolic</t>
+          <t>casa_tvim_str</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run8</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>CTRL_R8</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6867,50 +6857,52 @@
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>89.72</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>93.12</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>99.14</v>
+        <v>99.11</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>91.39</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>84.14</v>
+        <v>83.84</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>90.93000000000001</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>3.049509</v>
+        <v>31.026</v>
       </c>
       <c r="L122" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M122" s="2" t="n"/>
+        <v>31.026</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>13.6715</v>
+      </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>casa_vmamba_str</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run8</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>CTRL_R8</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6919,102 +6911,106 @@
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>82.83</v>
+        <v>79.66</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>82.86</v>
+        <v>84.22</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>91.91</v>
+        <v>91.69</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>82.84999999999999</v>
+        <v>81.88</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>70.72</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>77.56</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>3.049509</v>
+        <v>31.026</v>
       </c>
       <c r="L123" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M123" s="2" t="n"/>
+        <v>31.026</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>13.6715</v>
+      </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>casa_vmamba_str</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CASA-WDMF</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run9</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>S0_CTRL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>93.04000000000001</v>
+        <v>97.77</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>96.08</v>
+        <v>97.77</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>99.56999999999999</v>
+        <v>99.45</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>94.53</v>
+        <v>97.77</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>89.63</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>94.31</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>3.049509</v>
+        <v>31.977</v>
       </c>
       <c r="L124" s="2" t="n">
-        <v>3.133176</v>
-      </c>
-      <c r="M124" s="2" t="n"/>
+        <v>31.977</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>14.6841</v>
+      </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>casa_wdmf_str_qkv</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run9</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>S0_CTRL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7023,96 +7019,96 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>91.09</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>92.8</v>
+        <v>92.53</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>99.19</v>
+        <v>99.11</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>91.94</v>
+        <v>91.14</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>85.08</v>
+        <v>83.72</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>91.51000000000001</v>
+        <v>90.67</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>11.754</v>
+        <v>31.977</v>
       </c>
       <c r="L125" s="2" t="n">
-        <v>20.661</v>
+        <v>31.977</v>
       </c>
       <c r="M125" s="2" t="n">
-        <v>26.3183</v>
+        <v>14.6841</v>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-TViM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run9</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>A1_SAA</t>
+          <t>S1_HSAM</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>80.3</v>
+        <v>97.66</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>84.81</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>99.42</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>82.5</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>70.20999999999999</v>
+        <v>95.42</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>77.29000000000001</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>11.754</v>
+        <v>31.977</v>
       </c>
       <c r="L126" s="2" t="n">
-        <v>20.661</v>
+        <v>31.977</v>
       </c>
       <c r="M126" s="2" t="n">
-        <v>26.3183</v>
+        <v>14.769</v>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>baseline</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7122,105 +7118,101 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>80.27</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>92.75</v>
+        <v>85.19</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>92.06</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>91.86</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>84.94</v>
+        <v>70.44</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>11.754</v>
+        <v>3.016737</v>
       </c>
       <c r="L127" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>26.2593</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M127" s="2" t="n"/>
       <c r="N127" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>A2_CASAA</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>80.55</v>
+        <v>91.2</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>84.23</v>
+        <v>91.72</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>91.86</v>
+        <v>99.13</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>82.34999999999999</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>70</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>77.06</v>
+        <v>91</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>11.754</v>
+        <v>3.016737</v>
       </c>
       <c r="L128" s="2" t="n">
-        <v>20.661</v>
-      </c>
-      <c r="M128" s="2" t="n">
-        <v>26.2593</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M128" s="2" t="n"/>
       <c r="N128" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7230,51 +7222,49 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>91.38</v>
+        <v>80.39</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>92.3</v>
+        <v>82.89</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>99.17</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>91.84</v>
+        <v>81.62</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>84.91</v>
+        <v>68.95</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>11.754</v>
+        <v>3.016737</v>
       </c>
       <c r="L129" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M129" s="2" t="n">
-        <v>26.1484</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M129" s="2" t="n"/>
       <c r="N129" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7284,51 +7274,49 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>A1_SAA_FROZEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>92.61</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>86.03</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>99.52</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>93.92</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>69.55</v>
+        <v>88.53</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>76.83</v>
+        <v>93.67</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>11.754</v>
+        <v>3.016737</v>
       </c>
       <c r="L130" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M130" s="2" t="n">
-        <v>26.1484</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M130" s="2" t="n"/>
       <c r="N130" t="inlineStr">
         <is>
-          <t>saa</t>
+          <t>casa_wdmf_str_none</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7338,7 +7326,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7347,42 +7335,40 @@
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>91.13</v>
+        <v>90.55</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>92.65000000000001</v>
+        <v>92.03</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>99.12</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>91.88</v>
+        <v>91.28</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>84.98</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>91.45</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L131" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M131" s="2" t="n">
-        <v>26.0894</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M131" s="2" t="n"/>
       <c r="N131" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7392,7 +7378,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>A3_ORACLE_FROZEN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7401,366 +7387,366 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>78.67</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>85.05</v>
+        <v>85.08</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>92.36</v>
+        <v>91.72</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>83.52</v>
+        <v>81.75</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>71.7</v>
+        <v>69.13</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>78.55</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L132" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M132" s="2" t="n">
-        <v>26.0894</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M132" s="2" t="n"/>
       <c r="N132" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CASAA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>A4_DETAIL_FROZEN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>79.68000000000001</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>84.28</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>91.7</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>81.92</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>69.37</v>
+        <v>88.8</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>76.54000000000001</v>
+        <v>93.83</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>11.754</v>
+        <v>3.049509</v>
       </c>
       <c r="L133" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M133" s="2" t="n">
-        <v>26.0894</v>
-      </c>
+        <v>3.133176</v>
+      </c>
+      <c r="M133" s="2" t="n"/>
       <c r="N133" t="inlineStr">
         <is>
-          <t>casaa</t>
+          <t>casa_wdmf_str_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>89.72</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>97.47</v>
+        <v>93.12</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>99.37</v>
+        <v>99.14</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>97.45</v>
+        <v>91.39</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>95.02</v>
+        <v>84.14</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>97.09</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>3.016737</v>
+        <v>3.049509</v>
       </c>
       <c r="L134" s="2" t="n">
-        <v>3.100404</v>
+        <v>3.133176</v>
       </c>
       <c r="M134" s="2" t="n"/>
       <c r="N134" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>90.41</v>
+        <v>82.83</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>91.83</v>
+        <v>82.86</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>91.11</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>83.67</v>
+        <v>70.72</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>90.64</v>
+        <v>77.56</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>3.016737</v>
+        <v>3.049509</v>
       </c>
       <c r="L135" s="2" t="n">
-        <v>3.100404</v>
+        <v>3.133176</v>
       </c>
       <c r="M135" s="2" t="n"/>
       <c r="N135" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASA-WDMF</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>79.81</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>83.84999999999999</v>
+        <v>96.08</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>91.61</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>81.78</v>
+        <v>94.53</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>69.18000000000001</v>
+        <v>89.63</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>76.34</v>
+        <v>94.31</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>3.016737</v>
+        <v>3.049509</v>
       </c>
       <c r="L136" s="2" t="n">
-        <v>3.100404</v>
+        <v>3.133176</v>
       </c>
       <c r="M136" s="2" t="n"/>
       <c r="N136" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>casa_wdmf_str_qkv</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>M0_CTRL</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>93.2</v>
+        <v>91.09</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>94.70999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>99.52</v>
+        <v>99.19</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>93.95</v>
+        <v>91.94</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>88.59</v>
+        <v>85.08</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>93.7</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>3.016737</v>
+        <v>11.754</v>
       </c>
       <c r="L137" s="2" t="n">
-        <v>3.100404</v>
-      </c>
-      <c r="M137" s="2" t="n"/>
+        <v>20.661</v>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>26.3183</v>
+      </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>casa_none</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>A1_SAA</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>97.48</v>
+        <v>80.3</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>97.45</v>
+        <v>84.81</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>99.37</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>97.47</v>
+        <v>82.5</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>95.06</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>97.11</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>3.050665</v>
+        <v>11.754</v>
       </c>
       <c r="L138" s="2" t="n">
-        <v>3.134332</v>
-      </c>
-      <c r="M138" s="2" t="n"/>
+        <v>20.661</v>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>26.3183</v>
+      </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7769,50 +7755,52 @@
         </is>
       </c>
       <c r="E139" s="2" t="n">
-        <v>90.61</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>92.37</v>
+        <v>92.75</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>99.14</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>91.48</v>
+        <v>91.86</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>84.3</v>
+        <v>84.94</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>91.03</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>3.050665</v>
+        <v>11.754</v>
       </c>
       <c r="L139" s="2" t="n">
-        <v>3.134332</v>
-      </c>
-      <c r="M139" s="2" t="n"/>
+        <v>20.661</v>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>26.2593</v>
+      </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>A2_CASAA</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7821,154 +7809,160 @@
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>77.55</v>
+        <v>80.55</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>85.81</v>
+        <v>84.23</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>91.68000000000001</v>
+        <v>91.86</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>81.47</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>68.73</v>
+        <v>70</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>76.12</v>
+        <v>77.06</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>3.050665</v>
+        <v>11.754</v>
       </c>
       <c r="L140" s="2" t="n">
-        <v>3.134332</v>
-      </c>
-      <c r="M140" s="2" t="n"/>
+        <v>20.661</v>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>26.2593</v>
+      </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>M1_HYPER_QKV</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>92.5</v>
+        <v>91.38</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>96.20999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>99.56</v>
+        <v>99.17</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>94.31999999999999</v>
+        <v>91.84</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>89.25</v>
+        <v>84.91</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>94.09</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>3.050665</v>
+        <v>11.754</v>
       </c>
       <c r="L141" s="2" t="n">
-        <v>3.134332</v>
-      </c>
-      <c r="M141" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>26.1484</v>
+      </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>casa_hyperbolic</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>A1_SAA_FROZEN</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>97.51000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>97.45</v>
+        <v>86.03</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>99.38</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>97.48</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>95.09</v>
+        <v>69.55</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>97.13</v>
+        <v>76.83</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>3.059369</v>
+        <v>11.754</v>
       </c>
       <c r="L142" s="2" t="n">
-        <v>3.143036</v>
-      </c>
-      <c r="M142" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>26.1484</v>
+      </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>saa</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7977,50 +7971,52 @@
         </is>
       </c>
       <c r="E143" s="2" t="n">
-        <v>90.58</v>
+        <v>91.13</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>91.77</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>99.11</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>91.17</v>
+        <v>91.88</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>83.77</v>
+        <v>84.98</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>90.7</v>
+        <v>91.45</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>3.059369</v>
+        <v>11.754</v>
       </c>
       <c r="L143" s="2" t="n">
-        <v>3.143036</v>
-      </c>
-      <c r="M143" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>26.0894</v>
+      </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Run3</t>
+          <t>Run2</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>A3_ORACLE_FROZEN</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8029,40 +8025,42 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>76.7</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>85.81999999999999</v>
+        <v>85.05</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>91.52</v>
+        <v>92.36</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>81.01000000000001</v>
+        <v>83.52</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>68.06999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>75.56999999999999</v>
+        <v>78.55</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>3.059369</v>
+        <v>11.754</v>
       </c>
       <c r="L144" s="2" t="n">
-        <v>3.143036</v>
-      </c>
-      <c r="M144" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>26.0894</v>
+      </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>CASAA</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8072,42 +8070,44 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>M2_CA_QKV</t>
+          <t>A4_DETAIL_FROZEN</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>92.61</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>95.31</v>
+        <v>84.28</v>
       </c>
       <c r="G145" s="2" t="n">
-        <v>99.53</v>
+        <v>91.7</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>93.94</v>
+        <v>81.92</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>88.58</v>
+        <v>69.37</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>93.69</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>3.059369</v>
+        <v>11.754</v>
       </c>
       <c r="L145" s="2" t="n">
-        <v>3.143036</v>
-      </c>
-      <c r="M145" s="2" t="n"/>
+        <v>15.125</v>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>26.0894</v>
+      </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>casa_qkv</t>
+          <t>casaa</t>
         </is>
       </c>
     </row>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8133,22 +8133,22 @@
         </is>
       </c>
       <c r="E146" s="2" t="n">
-        <v>97.41</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>97.47</v>
       </c>
       <c r="G146" s="2" t="n">
-        <v>99.36</v>
+        <v>99.37</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>97.42</v>
+        <v>97.45</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>94.98</v>
+        <v>95.02</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>97.06</v>
+        <v>97.09</v>
       </c>
       <c r="K146" s="2" t="n">
         <v>3.016737</v>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8185,22 +8185,22 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>90.29000000000001</v>
+        <v>90.41</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>92.58</v>
+        <v>91.83</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>99.14</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>91.42</v>
+        <v>91.11</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>84.19</v>
+        <v>83.67</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>90.95999999999999</v>
+        <v>90.64</v>
       </c>
       <c r="K147" s="2" t="n">
         <v>3.016737</v>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8237,22 +8237,22 @@
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>80.38</v>
+        <v>79.81</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>85.22</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="G148" s="2" t="n">
-        <v>92.09</v>
+        <v>91.61</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>82.73</v>
+        <v>81.78</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>70.55</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>77.59999999999999</v>
+        <v>76.34</v>
       </c>
       <c r="K148" s="2" t="n">
         <v>3.016737</v>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8289,22 +8289,22 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>92.87</v>
+        <v>93.2</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>96.04000000000001</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="G149" s="2" t="n">
-        <v>99.56999999999999</v>
+        <v>99.52</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>94.43000000000001</v>
+        <v>93.95</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>89.44</v>
+        <v>88.59</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>94.2</v>
+        <v>93.7</v>
       </c>
       <c r="K149" s="2" t="n">
         <v>3.016737</v>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8341,28 +8341,28 @@
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>97.52</v>
+        <v>97.48</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>97.42</v>
+        <v>97.45</v>
       </c>
       <c r="G150" s="2" t="n">
-        <v>99.38</v>
+        <v>99.37</v>
       </c>
       <c r="H150" s="2" t="n">
         <v>97.47</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>95.06</v>
       </c>
       <c r="J150" s="2" t="n">
         <v>97.11</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>3.060525</v>
+        <v>3.050665</v>
       </c>
       <c r="L150" s="2" t="n">
-        <v>3.144192</v>
+        <v>3.134332</v>
       </c>
       <c r="M150" s="2" t="n"/>
       <c r="N150" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8393,28 +8393,28 @@
         </is>
       </c>
       <c r="E151" s="2" t="n">
-        <v>90.48</v>
+        <v>90.61</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>92.91</v>
+        <v>92.37</v>
       </c>
       <c r="G151" s="2" t="n">
-        <v>99.16</v>
+        <v>99.14</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>91.68000000000001</v>
+        <v>91.48</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>84.64</v>
+        <v>84.3</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>91.23999999999999</v>
+        <v>91.03</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>3.060525</v>
+        <v>3.050665</v>
       </c>
       <c r="L151" s="2" t="n">
-        <v>3.144192</v>
+        <v>3.134332</v>
       </c>
       <c r="M151" s="2" t="n"/>
       <c r="N151" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8445,28 +8445,28 @@
         </is>
       </c>
       <c r="E152" s="2" t="n">
-        <v>83.2</v>
+        <v>77.55</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>80.95</v>
+        <v>85.81</v>
       </c>
       <c r="G152" s="2" t="n">
-        <v>91.42</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>82.06</v>
+        <v>81.47</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>69.58</v>
+        <v>68.73</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>76.42</v>
+        <v>76.12</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>3.060525</v>
+        <v>3.050665</v>
       </c>
       <c r="L152" s="2" t="n">
-        <v>3.144192</v>
+        <v>3.134332</v>
       </c>
       <c r="M152" s="2" t="n"/>
       <c r="N152" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8497,28 +8497,28 @@
         </is>
       </c>
       <c r="E153" s="2" t="n">
-        <v>92.36</v>
+        <v>92.5</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>95.44</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="G153" s="2" t="n">
-        <v>99.52</v>
+        <v>99.56</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>93.88</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>88.45999999999999</v>
+        <v>89.25</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>93.63</v>
+        <v>94.09</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>3.060525</v>
+        <v>3.050665</v>
       </c>
       <c r="L153" s="2" t="n">
-        <v>3.144192</v>
+        <v>3.134332</v>
       </c>
       <c r="M153" s="2" t="n"/>
       <c r="N153" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8549,28 +8549,28 @@
         </is>
       </c>
       <c r="E154" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>97.51000000000001</v>
+        <v>97.45</v>
       </c>
       <c r="G154" s="2" t="n">
         <v>99.38</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>97.47</v>
+        <v>97.48</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>95.06</v>
+        <v>95.09</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>97.11</v>
+        <v>97.13</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>3.077293</v>
+        <v>3.059369</v>
       </c>
       <c r="L154" s="2" t="n">
-        <v>3.16096</v>
+        <v>3.143036</v>
       </c>
       <c r="M154" s="2" t="n"/>
       <c r="N154" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -8601,28 +8601,28 @@
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>90.45</v>
+        <v>90.58</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>92.68000000000001</v>
+        <v>91.77</v>
       </c>
       <c r="G155" s="2" t="n">
-        <v>99.15000000000001</v>
+        <v>99.11</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>91.55</v>
+        <v>91.17</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>84.42</v>
+        <v>83.77</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>91.11</v>
+        <v>90.7</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>3.077293</v>
+        <v>3.059369</v>
       </c>
       <c r="L155" s="2" t="n">
-        <v>3.16096</v>
+        <v>3.143036</v>
       </c>
       <c r="M155" s="2" t="n"/>
       <c r="N155" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -8653,28 +8653,28 @@
         </is>
       </c>
       <c r="E156" s="2" t="n">
-        <v>78.5</v>
+        <v>76.7</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>86.2</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="G156" s="2" t="n">
-        <v>91.97</v>
+        <v>91.52</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>82.17</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>69.73999999999999</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>77</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>3.077293</v>
+        <v>3.059369</v>
       </c>
       <c r="L156" s="2" t="n">
-        <v>3.16096</v>
+        <v>3.143036</v>
       </c>
       <c r="M156" s="2" t="n"/>
       <c r="N156" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Run5</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -8705,28 +8705,28 @@
         </is>
       </c>
       <c r="E157" s="2" t="n">
-        <v>91.88</v>
+        <v>92.61</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>94.98999999999999</v>
+        <v>95.31</v>
       </c>
       <c r="G157" s="2" t="n">
-        <v>99.48999999999999</v>
+        <v>99.53</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>93.41</v>
+        <v>93.94</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>87.63</v>
+        <v>88.58</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>93.14</v>
+        <v>93.69</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>3.077293</v>
+        <v>3.059369</v>
       </c>
       <c r="L157" s="2" t="n">
-        <v>3.16096</v>
+        <v>3.143036</v>
       </c>
       <c r="M157" s="2" t="n"/>
       <c r="N157" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -8757,22 +8757,22 @@
         </is>
       </c>
       <c r="E158" s="2" t="n">
-        <v>97.5</v>
+        <v>97.41</v>
       </c>
       <c r="F158" s="2" t="n">
-        <v>97.34999999999999</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="G158" s="2" t="n">
         <v>99.36</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>97.42</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>94.98999999999999</v>
+        <v>94.98</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>97.06999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="K158" s="2" t="n">
         <v>3.016737</v>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -8809,22 +8809,22 @@
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>90.69</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="F159" s="2" t="n">
-        <v>92.43000000000001</v>
+        <v>92.58</v>
       </c>
       <c r="G159" s="2" t="n">
-        <v>99.15000000000001</v>
+        <v>99.14</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>91.55</v>
+        <v>91.42</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>84.42</v>
+        <v>84.19</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="K159" s="2" t="n">
         <v>3.016737</v>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -8861,22 +8861,22 @@
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>82.58</v>
+        <v>80.38</v>
       </c>
       <c r="F160" s="2" t="n">
-        <v>82.25</v>
+        <v>85.22</v>
       </c>
       <c r="G160" s="2" t="n">
-        <v>91.69</v>
+        <v>92.09</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>82.42</v>
+        <v>82.73</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>70.09</v>
+        <v>70.55</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>76.98</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K160" s="2" t="n">
         <v>3.016737</v>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -8913,22 +8913,22 @@
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>92.31</v>
+        <v>92.87</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>94.59999999999999</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="G161" s="2" t="n">
-        <v>99.48999999999999</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>93.44</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>87.69</v>
+        <v>89.44</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>93.17</v>
+        <v>94.2</v>
       </c>
       <c r="K161" s="2" t="n">
         <v>3.016737</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -8965,28 +8965,28 @@
         </is>
       </c>
       <c r="E162" s="2" t="n">
-        <v>97.53</v>
+        <v>97.52</v>
       </c>
       <c r="F162" s="2" t="n">
-        <v>97.38</v>
+        <v>97.42</v>
       </c>
       <c r="G162" s="2" t="n">
-        <v>99.37</v>
+        <v>99.38</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>97.45</v>
+        <v>97.47</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>95.03</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>97.09</v>
+        <v>97.11</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.060525</v>
       </c>
       <c r="L162" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.144192</v>
       </c>
       <c r="M162" s="2" t="n"/>
       <c r="N162" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9017,28 +9017,28 @@
         </is>
       </c>
       <c r="E163" s="2" t="n">
-        <v>90.34999999999999</v>
+        <v>90.48</v>
       </c>
       <c r="F163" s="2" t="n">
-        <v>91.77</v>
+        <v>92.91</v>
       </c>
       <c r="G163" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.16</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>91.05</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>83.56999999999999</v>
+        <v>84.64</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>90.58</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.060525</v>
       </c>
       <c r="L163" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.144192</v>
       </c>
       <c r="M163" s="2" t="n"/>
       <c r="N163" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9069,28 +9069,28 @@
         </is>
       </c>
       <c r="E164" s="2" t="n">
-        <v>76.31999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="F164" s="2" t="n">
-        <v>85.91</v>
+        <v>80.95</v>
       </c>
       <c r="G164" s="2" t="n">
-        <v>91.45999999999999</v>
+        <v>91.42</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>80.83</v>
+        <v>82.06</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>67.83</v>
+        <v>69.58</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>75.37</v>
+        <v>76.42</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.060525</v>
       </c>
       <c r="L164" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.144192</v>
       </c>
       <c r="M164" s="2" t="n"/>
       <c r="N164" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9121,28 +9121,28 @@
         </is>
       </c>
       <c r="E165" s="2" t="n">
-        <v>93.55</v>
+        <v>92.36</v>
       </c>
       <c r="F165" s="2" t="n">
-        <v>95.95</v>
+        <v>95.44</v>
       </c>
       <c r="G165" s="2" t="n">
-        <v>99.59</v>
+        <v>99.52</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>94.73</v>
+        <v>93.88</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>89.98999999999999</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>94.52</v>
+        <v>93.63</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>3.050665</v>
+        <v>3.060525</v>
       </c>
       <c r="L165" s="2" t="n">
-        <v>3.134332</v>
+        <v>3.144192</v>
       </c>
       <c r="M165" s="2" t="n"/>
       <c r="N165" t="inlineStr">
@@ -9159,7 +9159,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9173,10 +9173,10 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>97.45</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="F166" s="2" t="n">
-        <v>97.48999999999999</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="G166" s="2" t="n">
         <v>99.38</v>
@@ -9185,16 +9185,16 @@
         <v>97.47</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>95.06999999999999</v>
+        <v>95.06</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>97.12</v>
+        <v>97.11</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.077293</v>
       </c>
       <c r="L166" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.16096</v>
       </c>
       <c r="M166" s="2" t="n"/>
       <c r="N166" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9225,28 +9225,28 @@
         </is>
       </c>
       <c r="E167" s="2" t="n">
-        <v>90.67</v>
+        <v>90.45</v>
       </c>
       <c r="F167" s="2" t="n">
-        <v>92.58</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="G167" s="2" t="n">
         <v>99.15000000000001</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>91.62</v>
+        <v>91.55</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>84.53</v>
+        <v>84.42</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>91.17</v>
+        <v>91.11</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.077293</v>
       </c>
       <c r="L167" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.16096</v>
       </c>
       <c r="M167" s="2" t="n"/>
       <c r="N167" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9277,28 +9277,28 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>77.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="F168" s="2" t="n">
-        <v>87.42</v>
+        <v>86.2</v>
       </c>
       <c r="G168" s="2" t="n">
-        <v>92.15000000000001</v>
+        <v>91.97</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>82.39</v>
+        <v>82.17</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>70.05</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>77.36</v>
+        <v>77</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.077293</v>
       </c>
       <c r="L168" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.16096</v>
       </c>
       <c r="M168" s="2" t="n"/>
       <c r="N168" t="inlineStr">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9329,28 +9329,28 @@
         </is>
       </c>
       <c r="E169" s="2" t="n">
-        <v>92.61</v>
+        <v>91.88</v>
       </c>
       <c r="F169" s="2" t="n">
-        <v>95.77</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="G169" s="2" t="n">
-        <v>99.54000000000001</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>94.16</v>
+        <v>93.41</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>88.97</v>
+        <v>87.63</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>93.93000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>3.067561</v>
+        <v>3.077293</v>
       </c>
       <c r="L169" s="2" t="n">
-        <v>3.151228</v>
+        <v>3.16096</v>
       </c>
       <c r="M169" s="2" t="n"/>
       <c r="N169" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9381,13 +9381,13 @@
         </is>
       </c>
       <c r="E170" s="2" t="n">
-        <v>97.31999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="F170" s="2" t="n">
-        <v>97.54000000000001</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="G170" s="2" t="n">
-        <v>99.37</v>
+        <v>99.36</v>
       </c>
       <c r="H170" s="2" t="n">
         <v>97.43000000000001</v>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -9433,22 +9433,22 @@
         </is>
       </c>
       <c r="E171" s="2" t="n">
-        <v>89.79000000000001</v>
+        <v>90.69</v>
       </c>
       <c r="F171" s="2" t="n">
-        <v>92.27</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="G171" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>91.01000000000001</v>
+        <v>91.55</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>83.51000000000001</v>
+        <v>84.42</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>90.54000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="K171" s="2" t="n">
         <v>3.016737</v>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -9485,22 +9485,22 @@
         </is>
       </c>
       <c r="E172" s="2" t="n">
-        <v>79.92</v>
+        <v>82.58</v>
       </c>
       <c r="F172" s="2" t="n">
-        <v>84.81</v>
+        <v>82.25</v>
       </c>
       <c r="G172" s="2" t="n">
-        <v>91.89</v>
+        <v>91.69</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>82.29000000000001</v>
+        <v>82.42</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>69.91</v>
+        <v>70.09</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>76.98</v>
       </c>
       <c r="K172" s="2" t="n">
         <v>3.016737</v>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -9537,22 +9537,22 @@
         </is>
       </c>
       <c r="E173" s="2" t="n">
-        <v>92.78</v>
+        <v>92.31</v>
       </c>
       <c r="F173" s="2" t="n">
-        <v>95.23</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G173" s="2" t="n">
-        <v>99.53</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>93.98999999999999</v>
+        <v>93.44</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>88.66</v>
+        <v>87.69</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>93.75</v>
+        <v>93.17</v>
       </c>
       <c r="K173" s="2" t="n">
         <v>3.016737</v>
@@ -9575,7 +9575,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9589,22 +9589,22 @@
         </is>
       </c>
       <c r="E174" s="2" t="n">
-        <v>97.48999999999999</v>
+        <v>97.53</v>
       </c>
       <c r="F174" s="2" t="n">
-        <v>97.45</v>
+        <v>97.38</v>
       </c>
       <c r="G174" s="2" t="n">
         <v>99.37</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>97.47</v>
+        <v>97.45</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>95.06</v>
+        <v>95.03</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>97.11</v>
+        <v>97.09</v>
       </c>
       <c r="K174" s="2" t="n">
         <v>3.050665</v>
@@ -9627,7 +9627,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -9641,22 +9641,22 @@
         </is>
       </c>
       <c r="E175" s="2" t="n">
-        <v>89.73999999999999</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="F175" s="2" t="n">
-        <v>93.42</v>
+        <v>91.77</v>
       </c>
       <c r="G175" s="2" t="n">
-        <v>99.16</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>91.54000000000001</v>
+        <v>91.05</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>84.40000000000001</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>90.58</v>
       </c>
       <c r="K175" s="2" t="n">
         <v>3.050665</v>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -9693,22 +9693,22 @@
         </is>
       </c>
       <c r="E176" s="2" t="n">
-        <v>77.78</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F176" s="2" t="n">
-        <v>84.04000000000001</v>
+        <v>85.91</v>
       </c>
       <c r="G176" s="2" t="n">
-        <v>91.28</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>80.79000000000001</v>
+        <v>80.83</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>67.77</v>
+        <v>67.83</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>75.16</v>
+        <v>75.37</v>
       </c>
       <c r="K176" s="2" t="n">
         <v>3.050665</v>
@@ -9731,7 +9731,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -9745,22 +9745,22 @@
         </is>
       </c>
       <c r="E177" s="2" t="n">
-        <v>93.05</v>
+        <v>93.55</v>
       </c>
       <c r="F177" s="2" t="n">
-        <v>96.14</v>
+        <v>95.95</v>
       </c>
       <c r="G177" s="2" t="n">
-        <v>99.58</v>
+        <v>99.59</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>94.56999999999999</v>
+        <v>94.73</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>89.7</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>94.34999999999999</v>
+        <v>94.52</v>
       </c>
       <c r="K177" s="2" t="n">
         <v>3.050665</v>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -9797,10 +9797,10 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>97.41</v>
+        <v>97.45</v>
       </c>
       <c r="F178" s="2" t="n">
-        <v>97.53</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="G178" s="2" t="n">
         <v>99.38</v>
@@ -9809,10 +9809,10 @@
         <v>97.47</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>95.06</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>97.11</v>
+        <v>97.12</v>
       </c>
       <c r="K178" s="2" t="n">
         <v>3.067561</v>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -9849,22 +9849,22 @@
         </is>
       </c>
       <c r="E179" s="2" t="n">
-        <v>90.68000000000001</v>
+        <v>90.67</v>
       </c>
       <c r="F179" s="2" t="n">
-        <v>91.98</v>
+        <v>92.58</v>
       </c>
       <c r="G179" s="2" t="n">
-        <v>99.12</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>91.33</v>
+        <v>91.62</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>84.04000000000001</v>
+        <v>84.53</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>90.87</v>
+        <v>91.17</v>
       </c>
       <c r="K179" s="2" t="n">
         <v>3.067561</v>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -9901,22 +9901,22 @@
         </is>
       </c>
       <c r="E180" s="2" t="n">
-        <v>77.18000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F180" s="2" t="n">
-        <v>85.53</v>
+        <v>87.42</v>
       </c>
       <c r="G180" s="2" t="n">
-        <v>91.54000000000001</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>81.14</v>
+        <v>82.39</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>68.27</v>
+        <v>70.05</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>75.70999999999999</v>
+        <v>77.36</v>
       </c>
       <c r="K180" s="2" t="n">
         <v>3.067561</v>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -9953,22 +9953,22 @@
         </is>
       </c>
       <c r="E181" s="2" t="n">
-        <v>92.63</v>
+        <v>92.61</v>
       </c>
       <c r="F181" s="2" t="n">
-        <v>96.55</v>
+        <v>95.77</v>
       </c>
       <c r="G181" s="2" t="n">
-        <v>99.58</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>94.55</v>
+        <v>94.16</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>89.67</v>
+        <v>88.97</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>94.33</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="K181" s="2" t="n">
         <v>3.067561</v>
@@ -9986,17 +9986,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -10005,52 +10005,50 @@
         </is>
       </c>
       <c r="E182" s="2" t="n">
-        <v>93.13</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="F182" s="2" t="n">
-        <v>95.16</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="G182" s="2" t="n">
-        <v>98.56999999999999</v>
+        <v>99.37</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>94.13</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>88.91</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L182" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M182" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M182" s="2" t="n"/>
       <c r="N182" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -10059,52 +10057,50 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>86.37</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="F183" s="2" t="n">
-        <v>89.25</v>
+        <v>92.27</v>
       </c>
       <c r="G183" s="2" t="n">
-        <v>98.78</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>87.79000000000001</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>78.23999999999999</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>87.14</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L183" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M183" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M183" s="2" t="n"/>
       <c r="N183" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -10113,52 +10109,50 @@
         </is>
       </c>
       <c r="E184" s="2" t="n">
-        <v>79.93000000000001</v>
+        <v>79.92</v>
       </c>
       <c r="F184" s="2" t="n">
-        <v>84.5</v>
+        <v>84.81</v>
       </c>
       <c r="G184" s="2" t="n">
-        <v>91.81</v>
+        <v>91.89</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>69.70999999999999</v>
+        <v>69.91</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>76.84</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="K184" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L184" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M184" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M184" s="2" t="n"/>
       <c r="N184" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>C0_TOKEN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -10167,52 +10161,50 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>90.16</v>
+        <v>92.78</v>
       </c>
       <c r="F185" s="2" t="n">
-        <v>93.97</v>
+        <v>95.23</v>
       </c>
       <c r="G185" s="2" t="n">
-        <v>99.38</v>
+        <v>99.53</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>92.02</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>85.23</v>
+        <v>88.66</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>91.7</v>
+        <v>93.75</v>
       </c>
       <c r="K185" s="2" t="n">
-        <v>2.596</v>
+        <v>3.016737</v>
       </c>
       <c r="L185" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="M185" s="2" t="n">
-        <v>2.2136</v>
-      </c>
+        <v>3.100404</v>
+      </c>
+      <c r="M185" s="2" t="n"/>
       <c r="N185" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_none</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -10221,52 +10213,50 @@
         </is>
       </c>
       <c r="E186" s="2" t="n">
-        <v>94.7</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="F186" s="2" t="n">
-        <v>96.13</v>
+        <v>97.45</v>
       </c>
       <c r="G186" s="2" t="n">
-        <v>98.88</v>
+        <v>99.37</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>95.41</v>
+        <v>97.47</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>91.22</v>
+        <v>95.06</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>94.77</v>
+        <v>97.11</v>
       </c>
       <c r="K186" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L186" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M186" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M186" s="2" t="n"/>
       <c r="N186" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -10275,52 +10265,50 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>88.42</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="F187" s="2" t="n">
-        <v>91.97</v>
+        <v>93.42</v>
       </c>
       <c r="G187" s="2" t="n">
-        <v>99.02</v>
+        <v>99.16</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>90.16</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>82.08</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>89.64</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="K187" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L187" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M187" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M187" s="2" t="n"/>
       <c r="N187" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -10329,52 +10317,50 @@
         </is>
       </c>
       <c r="E188" s="2" t="n">
-        <v>78.73</v>
+        <v>77.78</v>
       </c>
       <c r="F188" s="2" t="n">
-        <v>84.98</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="G188" s="2" t="n">
-        <v>91.7</v>
+        <v>91.28</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>81.73999999999999</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>69.11</v>
+        <v>67.77</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>76.38</v>
+        <v>75.16</v>
       </c>
       <c r="K188" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L188" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M188" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M188" s="2" t="n"/>
       <c r="N188" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>STR-Fusion</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Run2_TASS</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>M1_TASS</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -10383,160 +10369,154 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>91.64</v>
+        <v>93.05</v>
       </c>
       <c r="F189" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>96.14</v>
       </c>
       <c r="G189" s="2" t="n">
-        <v>99.47</v>
+        <v>99.58</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>93.2</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>87.27</v>
+        <v>89.7</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>92.93000000000001</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="K189" s="2" t="n">
-        <v>3.455</v>
+        <v>3.050665</v>
       </c>
       <c r="L189" s="2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="M189" s="2" t="n">
-        <v>3.5459</v>
-      </c>
+        <v>3.134332</v>
+      </c>
+      <c r="M189" s="2" t="n"/>
       <c r="N189" t="inlineStr">
         <is>
-          <t>str_tass</t>
+          <t>casa_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>R4_0_A0_FULL12_FROZEN</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E190" s="2" t="n">
-        <v>82.42</v>
+        <v>97.41</v>
       </c>
       <c r="F190" s="2" t="n">
-        <v>83.87</v>
+        <v>97.53</v>
       </c>
       <c r="G190" s="2" t="n">
-        <v>92.12</v>
+        <v>99.38</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>83.14</v>
+        <v>97.47</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>71.14</v>
+        <v>95.06</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>77.98999999999999</v>
+        <v>97.11</v>
       </c>
       <c r="K190" s="2" t="n">
-        <v>11.754</v>
+        <v>3.067561</v>
       </c>
       <c r="L190" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M190" s="2" t="n">
-        <v>26.3246</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M190" s="2" t="n"/>
       <c r="N190" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>R4_1_VIT4_OLDHEAD</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E191" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="F191" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>91.98</v>
       </c>
       <c r="G191" s="2" t="n">
-        <v>91.94</v>
+        <v>99.12</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>82.77</v>
+        <v>91.33</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>70.61</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>77.51000000000001</v>
+        <v>90.87</v>
       </c>
       <c r="K191" s="2" t="n">
-        <v>8.195</v>
+        <v>3.067561</v>
       </c>
       <c r="L191" s="2" t="n">
-        <v>15.125</v>
-      </c>
-      <c r="M191" s="2" t="n">
-        <v>24.1021</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M191" s="2" t="n"/>
       <c r="N191" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>R4_2_VIT4_LIGHTDETAIL</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -10545,348 +10525,992 @@
         </is>
       </c>
       <c r="E192" s="2" t="n">
-        <v>79.94</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="F192" s="2" t="n">
-        <v>84.79000000000001</v>
+        <v>85.53</v>
       </c>
       <c r="G192" s="2" t="n">
-        <v>91.89</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>82.3</v>
+        <v>81.14</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>69.92</v>
+        <v>68.27</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>77.04000000000001</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="K192" s="2" t="n">
-        <v>5.492</v>
+        <v>3.067561</v>
       </c>
       <c r="L192" s="2" t="n">
-        <v>3.515</v>
-      </c>
-      <c r="M192" s="2" t="n">
-        <v>10.7311</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M192" s="2" t="n"/>
       <c r="N192" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>80.87</v>
+        <v>92.63</v>
       </c>
       <c r="F193" s="2" t="n">
-        <v>83.81</v>
+        <v>96.55</v>
       </c>
       <c r="G193" s="2" t="n">
-        <v>91.81</v>
+        <v>99.58</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>94.55</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>69.95</v>
+        <v>89.67</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>76.98999999999999</v>
+        <v>94.33</v>
       </c>
       <c r="K193" s="2" t="n">
-        <v>5.533</v>
+        <v>3.067561</v>
       </c>
       <c r="L193" s="2" t="n">
-        <v>3.556</v>
-      </c>
-      <c r="M193" s="2" t="n">
-        <v>10.9824</v>
-      </c>
+        <v>3.151228</v>
+      </c>
+      <c r="M193" s="2" t="n"/>
       <c r="N193" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>casa_qkv</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>UltraLight</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run2_TASS</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>R4_2d_PSD_DETAIL</t>
+          <t>C0_TOKEN</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E194" s="2" t="n">
-        <v>79.78</v>
+        <v>93.13</v>
       </c>
       <c r="F194" s="2" t="n">
-        <v>84.39</v>
+        <v>95.16</v>
       </c>
       <c r="G194" s="2" t="n">
-        <v>91.75</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>82.02</v>
+        <v>94.13</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>69.52</v>
+        <v>88.91</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>76.68000000000001</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K194" s="2" t="n">
-        <v>5.491</v>
+        <v>2.596</v>
       </c>
       <c r="L194" s="2" t="n">
-        <v>3.514</v>
+        <v>0.62</v>
       </c>
       <c r="M194" s="2" t="n">
-        <v>11.5239</v>
+        <v>2.2136</v>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E195" s="2" t="n">
-        <v>97.72</v>
+        <v>86.37</v>
       </c>
       <c r="F195" s="2" t="n">
-        <v>97.78</v>
+        <v>89.25</v>
       </c>
       <c r="G195" s="2" t="n">
-        <v>99.44</v>
+        <v>98.78</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>97.75</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="J195" s="2" t="n">
-        <v>97.43000000000001</v>
+        <v>87.14</v>
       </c>
       <c r="K195" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L195" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M195" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E196" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F196" s="2" t="n">
-        <v>92.33</v>
+        <v>84.5</v>
       </c>
       <c r="G196" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>91.81</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>91.95</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>91.52</v>
+        <v>76.84</v>
       </c>
       <c r="K196" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L196" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M196" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>STR-Fusion</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr"/>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>C0_TOKEN</t>
+        </is>
+      </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E197" s="2" t="n">
-        <v>80.77</v>
+        <v>90.16</v>
       </c>
       <c r="F197" s="2" t="n">
-        <v>84.27</v>
+        <v>93.97</v>
       </c>
       <c r="G197" s="2" t="n">
-        <v>91.91</v>
+        <v>99.38</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>82.48</v>
+        <v>92.02</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>70.19</v>
+        <v>85.23</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>77.23</v>
+        <v>91.7</v>
       </c>
       <c r="K197" s="2" t="n">
-        <v>11.754</v>
+        <v>2.596</v>
       </c>
       <c r="L197" s="2" t="n">
-        <v>20.661</v>
+        <v>0.62</v>
       </c>
       <c r="M197" s="2" t="n">
-        <v>26.3246</v>
+        <v>2.2136</v>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>str_tass</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="F198" s="2" t="n">
+        <v>96.13</v>
+      </c>
+      <c r="G198" s="2" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="H198" s="2" t="n">
+        <v>95.41</v>
+      </c>
+      <c r="I198" s="2" t="n">
+        <v>91.22</v>
+      </c>
+      <c r="J198" s="2" t="n">
+        <v>94.77</v>
+      </c>
+      <c r="K198" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L198" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M198" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="F199" s="2" t="n">
+        <v>91.97</v>
+      </c>
+      <c r="G199" s="2" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="H199" s="2" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="I199" s="2" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="J199" s="2" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="K199" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L199" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M199" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>78.73</v>
+      </c>
+      <c r="F200" s="2" t="n">
+        <v>84.98</v>
+      </c>
+      <c r="G200" s="2" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="H200" s="2" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="I200" s="2" t="n">
+        <v>69.11</v>
+      </c>
+      <c r="J200" s="2" t="n">
+        <v>76.38</v>
+      </c>
+      <c r="K200" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L200" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M200" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>STR-Fusion</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Run2_TASS</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>M1_TASS</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="F201" s="2" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="G201" s="2" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="H201" s="2" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I201" s="2" t="n">
+        <v>87.27</v>
+      </c>
+      <c r="J201" s="2" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="K201" s="2" t="n">
+        <v>3.455</v>
+      </c>
+      <c r="L201" s="2" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>3.5459</v>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>str_tass</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>R4_0_A0_FULL12_FROZEN</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>82.42</v>
+      </c>
+      <c r="F202" s="2" t="n">
+        <v>83.87</v>
+      </c>
+      <c r="G202" s="2" t="n">
+        <v>92.12</v>
+      </c>
+      <c r="H202" s="2" t="n">
+        <v>83.14</v>
+      </c>
+      <c r="I202" s="2" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="J202" s="2" t="n">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="K202" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L202" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M202" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>R4_1_VIT4_OLDHEAD</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="F203" s="2" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="G203" s="2" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="H203" s="2" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="I203" s="2" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="J203" s="2" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="K203" s="2" t="n">
+        <v>8.195</v>
+      </c>
+      <c r="L203" s="2" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="M203" s="2" t="n">
+        <v>24.1021</v>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>R4_2_VIT4_LIGHTDETAIL</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="F204" s="2" t="n">
+        <v>84.79000000000001</v>
+      </c>
+      <c r="G204" s="2" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="H204" s="2" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I204" s="2" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="J204" s="2" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="K204" s="2" t="n">
+        <v>5.492</v>
+      </c>
+      <c r="L204" s="2" t="n">
+        <v>3.515</v>
+      </c>
+      <c r="M204" s="2" t="n">
+        <v>10.7311</v>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>R4_2b_VIT4_LIGHTDETAIL48</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="F205" s="2" t="n">
+        <v>83.81</v>
+      </c>
+      <c r="G205" s="2" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="H205" s="2" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="I205" s="2" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="J205" s="2" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="K205" s="2" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="L205" s="2" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>10.9824</v>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>UltraLight</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>R4_2d_PSD_DETAIL</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="F206" s="2" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="G206" s="2" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="H206" s="2" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="I206" s="2" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="J206" s="2" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="K206" s="2" t="n">
+        <v>5.491</v>
+      </c>
+      <c r="L206" s="2" t="n">
+        <v>3.514</v>
+      </c>
+      <c r="M206" s="2" t="n">
+        <v>11.5239</v>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
         <is>
           <t>Run1</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr">
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="F207" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="G207" s="2" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="H207" s="2" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I207" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J207" s="2" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="K207" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L207" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M207" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="F208" s="2" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="G208" s="2" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="H208" s="2" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="I208" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="J208" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="K208" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L208" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M208" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="F209" s="2" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G209" s="2" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="H209" s="2" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="I209" s="2" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="J209" s="2" t="n">
+        <v>77.23</v>
+      </c>
+      <c r="K209" s="2" t="n">
+        <v>11.754</v>
+      </c>
+      <c r="L209" s="2" t="n">
+        <v>20.661</v>
+      </c>
+      <c r="M209" s="2" t="n">
+        <v>26.3246</v>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
-      <c r="E198" s="2" t="n">
+      <c r="E210" s="2" t="n">
         <v>93.62</v>
       </c>
-      <c r="F198" s="2" t="n">
+      <c r="F210" s="2" t="n">
         <v>96.09</v>
       </c>
-      <c r="G198" s="2" t="n">
+      <c r="G210" s="2" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="H198" s="2" t="n">
+      <c r="H210" s="2" t="n">
         <v>94.84</v>
       </c>
-      <c r="I198" s="2" t="n">
+      <c r="I210" s="2" t="n">
         <v>90.18000000000001</v>
       </c>
-      <c r="J198" s="2" t="n">
+      <c r="J210" s="2" t="n">
         <v>94.63</v>
       </c>
-      <c r="K198" s="2" t="n">
+      <c r="K210" s="2" t="n">
         <v>11.754</v>
       </c>
-      <c r="L198" s="2" t="n">
+      <c r="L210" s="2" t="n">
         <v>20.661</v>
       </c>
-      <c r="M198" s="2" t="n">
+      <c r="M210" s="2" t="n">
         <v>26.3246</v>
       </c>
-      <c r="N198" t="inlineStr">
+      <c r="N210" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N198"/>
+  <autoFilter ref="A1:N210"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$210</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$N$222</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N210"/>
+  <dimension ref="A1:N222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3114,17 +3114,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3133,52 +3133,50 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>97.05</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>96.95</v>
+      </c>
+      <c r="I52" s="2" t="n">
         <v>94.08</v>
       </c>
-      <c r="F52" s="2" t="n">
-        <v>95.26000000000001</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>98.69</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>94.67</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>89.87</v>
-      </c>
       <c r="J52" s="2" t="n">
-        <v>93.92</v>
+        <v>96.52</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>2.378</v>
+        <v>1.93581</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M52" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.047125</v>
+      </c>
+      <c r="M52" s="2" t="n"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3187,52 +3185,50 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>88.55</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>91.3</v>
+        <v>91.81</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>98.98999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>89.90000000000001</v>
+        <v>91.06</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>81.66</v>
+        <v>83.58</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>89.37</v>
+        <v>90.58</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>2.378</v>
+        <v>1.93581</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M53" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.047125</v>
+      </c>
+      <c r="M53" s="2" t="n"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3241,52 +3237,50 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>82.09</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>82.84</v>
+        <v>86.05</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>91.77</v>
+        <v>92.12</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>82.47</v>
+        <v>82.64</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>70.16</v>
+        <v>70.42</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>77.09</v>
+        <v>77.56</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>2.378</v>
+        <v>1.93581</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M54" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.047125</v>
+      </c>
+      <c r="M54" s="2" t="n"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>A0_BASE_PLAIN</t>
+          <t>M0_CTRL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3295,52 +3289,50 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>92.34</v>
+        <v>93.13</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>95.61</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>99.56</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>93.7</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>88.15000000000001</v>
+        <v>89.31</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>93.44</v>
+        <v>94.12</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2.378</v>
+        <v>1.93581</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M55" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.047125</v>
+      </c>
+      <c r="M55" s="2" t="n"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_none</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3349,52 +3341,50 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>93.90000000000001</v>
+        <v>96.73</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>95.19</v>
+        <v>97.08</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>98.66</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>94.54000000000001</v>
+        <v>96.91</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>89.64</v>
+        <v>94</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>93.78</v>
+        <v>96.47</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2.416</v>
+        <v>1.953222</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M56" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.064537</v>
+      </c>
+      <c r="M56" s="2" t="n"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3403,52 +3393,50 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>88.81999999999999</v>
+        <v>90.17</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>90.93000000000001</v>
+        <v>92.03</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>98.98</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>89.87</v>
+        <v>91.09</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>81.59999999999999</v>
+        <v>83.64</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>89.33</v>
+        <v>90.62</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2.416</v>
+        <v>1.953222</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M57" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.064537</v>
+      </c>
+      <c r="M57" s="2" t="n"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3457,52 +3445,50 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>79.66</v>
+        <v>79.37</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>85.53</v>
+        <v>85.52</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>92.03</v>
+        <v>91.97</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>82.48999999999999</v>
+        <v>82.33</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>70.2</v>
+        <v>69.97</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>77.34</v>
+        <v>77.14</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>2.416</v>
+        <v>1.953222</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M58" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.064537</v>
+      </c>
+      <c r="M58" s="2" t="n"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>A1_CASAA_PLAIN</t>
+          <t>M1_HYPER_QKV</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3511,52 +3497,50 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>91.81999999999999</v>
+        <v>93.34</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>95.56</v>
+        <v>95.55</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>99.56</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>93.65000000000001</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>88.06999999999999</v>
+        <v>89.45</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>93.40000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>2.416</v>
+        <v>1.953222</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>2.416</v>
-      </c>
-      <c r="M59" s="2" t="n">
-        <v>1.2365</v>
-      </c>
+        <v>2.064537</v>
+      </c>
+      <c r="M59" s="2" t="n"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_hyperbolic</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3565,52 +3549,50 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>95.05</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>96.02</v>
+        <v>96.92</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>99.23</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>95.53</v>
+        <v>96.87</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>91.45</v>
+        <v>93.94</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>94.91</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2.378</v>
+        <v>1.953222</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M60" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.064537</v>
+      </c>
+      <c r="M60" s="2" t="n"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3619,52 +3601,50 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>88.98999999999999</v>
+        <v>90.64</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>91.62</v>
+        <v>91.83</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>99.02</v>
+        <v>99.11</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>90.28</v>
+        <v>91.23</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>82.29000000000001</v>
+        <v>83.88</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>89.77</v>
+        <v>90.77</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>2.378</v>
+        <v>1.953222</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M61" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.064537</v>
+      </c>
+      <c r="M61" s="2" t="n"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3673,52 +3653,50 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>79.3</v>
+        <v>80.25</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>85.94</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>92.06</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>82.48999999999999</v>
+        <v>82.94</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>70.19</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>77.36</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>2.378</v>
+        <v>1.953222</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M62" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.064537</v>
+      </c>
+      <c r="M62" s="2" t="n"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CASA-STR</t>
+          <t>CASA-Pyramid</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>A2_STR_ONLY</t>
+          <t>M2_CA_QKV</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3727,35 +3705,33 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>92.15000000000001</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>94.7</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>99.48</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>93.41</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>87.63</v>
+        <v>89.56</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>93.14</v>
+        <v>94.27</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>2.378</v>
+        <v>1.953222</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="M63" s="2" t="n">
-        <v>1.2051</v>
-      </c>
+        <v>2.064537</v>
+      </c>
+      <c r="M63" s="2" t="n"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>casa_str</t>
+          <t>casa_pyramid_qkv</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3748,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3781,31 +3757,31 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>95.06</v>
+        <v>94.08</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>96.01000000000001</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>98.69</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>95.54000000000001</v>
+        <v>94.67</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>91.45</v>
+        <v>89.87</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>94.91</v>
+        <v>93.92</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -3826,7 +3802,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3835,31 +3811,31 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>89.47</v>
+        <v>88.55</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>91.28</v>
+        <v>91.3</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>99.03</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>90.37</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>82.43000000000001</v>
+        <v>81.66</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>89.86</v>
+        <v>89.37</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -3880,7 +3856,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3889,31 +3865,31 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>81.39</v>
+        <v>82.09</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>84.72</v>
+        <v>82.84</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>92.15000000000001</v>
+        <v>91.77</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>83.02</v>
+        <v>82.47</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>70.97</v>
+        <v>70.16</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>77.92</v>
+        <v>77.09</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -3934,7 +3910,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>M1_CASAA_STR</t>
+          <t>A0_BASE_PLAIN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3943,31 +3919,31 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>92</v>
+        <v>92.34</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>99.51000000000001</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>93.72</v>
+        <v>93.7</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>88.19</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>93.47</v>
+        <v>93.44</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>2.416</v>
+        <v>2.378</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1.2365</v>
+        <v>1.2051</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
@@ -3978,275 +3954,331 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_INJ</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>90.38</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>91.91</v>
+        <v>95.19</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>98.66</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>91.14</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>83.72</v>
+        <v>89.64</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>90.66</v>
-      </c>
-      <c r="K68" s="2" t="n"/>
-      <c r="L68" s="2" t="n"/>
-      <c r="M68" s="2" t="n"/>
+        <v>93.78</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_INJ</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>81.18000000000001</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>82.19</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>91.41</v>
+        <v>98.98</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>81.68000000000001</v>
+        <v>89.87</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>69.04000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>76.08</v>
-      </c>
-      <c r="K69" s="2" t="n"/>
-      <c r="L69" s="2" t="n"/>
-      <c r="M69" s="2" t="n"/>
+        <v>89.33</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Exploration/Exp1/STG_SUP</t>
+          <t>A1_CASAA_PLAIN</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>90.63</v>
+        <v>79.66</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>91.56</v>
+        <v>85.53</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>92.03</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>91.09</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>83.64</v>
+        <v>70.2</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>90.62</v>
+        <v>77.34</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>31.978582</v>
-      </c>
-      <c r="L70" s="2" t="n"/>
-      <c r="M70" s="2" t="n"/>
+        <v>2.416</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>2.416</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>1.2365</v>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>casa_vmamba_stgeo</t>
+          <t>casa_str</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CASA-TViM</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
+          <t>CASA-STR</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">